--- a/bbs_log.xlsx
+++ b/bbs_log.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H514"/>
+  <dimension ref="A1:H524"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15729,7 +15729,6 @@
           <t>おとは</t>
         </is>
       </c>
-      <c r="E486" t="inlineStr"/>
       <c r="F486" t="inlineStr">
         <is>
           <t>お祝いー！</t>
@@ -15740,7 +15739,6 @@
           <t>きちゃ！</t>
         </is>
       </c>
-      <c r="H486" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" t="n">
@@ -15761,7 +15759,6 @@
           <t>変態マッスル</t>
         </is>
       </c>
-      <c r="E487" t="inlineStr"/>
       <c r="F487" t="inlineStr">
         <is>
           <t>お祝いに</t>
@@ -15772,7 +15769,6 @@
           <t>きました！</t>
         </is>
       </c>
-      <c r="H487" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" t="n">
@@ -15793,7 +15789,6 @@
           <t>さと</t>
         </is>
       </c>
-      <c r="E488" t="inlineStr"/>
       <c r="F488" t="inlineStr">
         <is>
           <t>お祝いだよー</t>
@@ -15804,7 +15799,6 @@
           <t>きました！</t>
         </is>
       </c>
-      <c r="H488" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" t="n">
@@ -15825,7 +15819,6 @@
           <t>あき、こう</t>
         </is>
       </c>
-      <c r="E489" t="inlineStr"/>
       <c r="F489" t="inlineStr">
         <is>
           <t>おめでとうございます</t>
@@ -15836,7 +15829,6 @@
           <t>イベ行けないけど、気持ちだけお届け!!!</t>
         </is>
       </c>
-      <c r="H489" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" t="n">
@@ -15857,7 +15849,6 @@
           <t>まいなす</t>
         </is>
       </c>
-      <c r="E490" t="inlineStr"/>
       <c r="F490" t="inlineStr">
         <is>
           <t>はぴば</t>
@@ -15868,7 +15859,6 @@
           <t>きました！</t>
         </is>
       </c>
-      <c r="H490" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" t="n">
@@ -15889,7 +15879,6 @@
           <t>あいちゃん</t>
         </is>
       </c>
-      <c r="E491" t="inlineStr"/>
       <c r="F491" t="inlineStr">
         <is>
           <t>ハピバ</t>
@@ -15900,7 +15889,6 @@
           <t>きました！</t>
         </is>
       </c>
-      <c r="H491" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" t="n">
@@ -15921,7 +15909,6 @@
           <t>てる、いぶお</t>
         </is>
       </c>
-      <c r="E492" t="inlineStr"/>
       <c r="F492" t="inlineStr">
         <is>
           <t>おめでとう</t>
@@ -15932,7 +15919,6 @@
           <t>きました！</t>
         </is>
       </c>
-      <c r="H492" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" t="n">
@@ -15953,7 +15939,6 @@
           <t>キムとドMみい</t>
         </is>
       </c>
-      <c r="E493" t="inlineStr"/>
       <c r="F493" t="inlineStr">
         <is>
           <t>お誕生日おめでとうございます</t>
@@ -15964,7 +15949,6 @@
           <t>来店します</t>
         </is>
       </c>
-      <c r="H493" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" t="n">
@@ -15985,7 +15969,6 @@
           <t>番</t>
         </is>
       </c>
-      <c r="E494" t="inlineStr"/>
       <c r="F494" t="inlineStr">
         <is>
           <t>バースデーイベント参加のご連絡</t>
@@ -15998,7 +15981,6 @@
 皆様とお祝いのひとときを共有できますことを大変楽しみにしております。</t>
         </is>
       </c>
-      <c r="H494" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" t="n">
@@ -16019,7 +16001,6 @@
           <t>おでで</t>
         </is>
       </c>
-      <c r="E495" t="inlineStr"/>
       <c r="F495" t="inlineStr">
         <is>
           <t>おいわいに</t>
@@ -16030,7 +16011,6 @@
           <t>きたよ！！！</t>
         </is>
       </c>
-      <c r="H495" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" t="n">
@@ -16051,7 +16031,6 @@
           <t>しん</t>
         </is>
       </c>
-      <c r="E496" t="inlineStr"/>
       <c r="F496" t="inlineStr">
         <is>
           <t>グッズ</t>
@@ -16062,7 +16041,6 @@
           <t>作ってきました</t>
         </is>
       </c>
-      <c r="H496" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" t="n">
@@ -16083,7 +16061,6 @@
           <t>ローズ</t>
         </is>
       </c>
-      <c r="E497" t="inlineStr"/>
       <c r="F497" t="inlineStr">
         <is>
           <t>こんばんわ</t>
@@ -16094,7 +16071,6 @@
           <t>先日ぶり</t>
         </is>
       </c>
-      <c r="H497" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" t="n">
@@ -16115,7 +16091,6 @@
           <t>キムさん</t>
         </is>
       </c>
-      <c r="E498" t="inlineStr"/>
       <c r="F498" t="inlineStr">
         <is>
           <t>お祝いに</t>
@@ -16126,7 +16101,6 @@
           <t>きました♪</t>
         </is>
       </c>
-      <c r="H498" t="inlineStr"/>
     </row>
     <row r="499">
       <c r="A499" t="n">
@@ -16147,7 +16121,6 @@
           <t>やえ</t>
         </is>
       </c>
-      <c r="E499" t="inlineStr"/>
       <c r="F499" t="inlineStr">
         <is>
           <t>お祝いに</t>
@@ -16158,7 +16131,6 @@
           <t>きました！</t>
         </is>
       </c>
-      <c r="H499" t="inlineStr"/>
     </row>
     <row r="500">
       <c r="A500" t="n">
@@ -16179,7 +16151,6 @@
           <t>ゆずきち、ましゅ社長</t>
         </is>
       </c>
-      <c r="E500" t="inlineStr"/>
       <c r="F500" t="inlineStr">
         <is>
           <t>今</t>
@@ -16190,7 +16161,6 @@
           <t>おいわいしに！</t>
         </is>
       </c>
-      <c r="H500" t="inlineStr"/>
     </row>
     <row r="501">
       <c r="A501" t="n">
@@ -16211,7 +16181,6 @@
           <t>みん</t>
         </is>
       </c>
-      <c r="E501" t="inlineStr"/>
       <c r="F501" t="inlineStr">
         <is>
           <t>初めて</t>
@@ -16222,7 +16191,6 @@
           <t>きました！！！</t>
         </is>
       </c>
-      <c r="H501" t="inlineStr"/>
     </row>
     <row r="502">
       <c r="A502" t="n">
@@ -16243,7 +16211,6 @@
           <t>ゆうた、だいざく、しん、たくや</t>
         </is>
       </c>
-      <c r="E502" t="inlineStr"/>
       <c r="F502" t="inlineStr">
         <is>
           <t>お祝いに</t>
@@ -16254,7 +16221,6 @@
           <t>きました！！</t>
         </is>
       </c>
-      <c r="H502" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" t="n">
@@ -16275,7 +16241,6 @@
           <t>すーたく</t>
         </is>
       </c>
-      <c r="E503" t="inlineStr"/>
       <c r="F503" t="inlineStr">
         <is>
           <t>今</t>
@@ -16286,7 +16251,6 @@
           <t>祝に！</t>
         </is>
       </c>
-      <c r="H503" t="inlineStr"/>
     </row>
     <row r="504">
       <c r="A504" t="n">
@@ -16307,7 +16271,6 @@
           <t>かず、だいご</t>
         </is>
       </c>
-      <c r="E504" t="inlineStr"/>
       <c r="F504" t="inlineStr">
         <is>
           <t>おめでとう</t>
@@ -16318,7 +16281,6 @@
           <t>きました！</t>
         </is>
       </c>
-      <c r="H504" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" t="n">
@@ -16339,7 +16301,6 @@
           <t>のんのん</t>
         </is>
       </c>
-      <c r="E505" t="inlineStr"/>
       <c r="F505" t="inlineStr">
         <is>
           <t>おいわい</t>
@@ -16350,7 +16311,6 @@
           <t>きました！</t>
         </is>
       </c>
-      <c r="H505" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" t="n">
@@ -16371,7 +16331,6 @@
           <t>ニャンまげ</t>
         </is>
       </c>
-      <c r="E506" t="inlineStr"/>
       <c r="F506" t="inlineStr">
         <is>
           <t>これから</t>
@@ -16382,7 +16341,6 @@
           <t>お祝いしに向かいます！</t>
         </is>
       </c>
-      <c r="H506" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" t="n">
@@ -16403,7 +16361,6 @@
           <t>とも、テクノ</t>
         </is>
       </c>
-      <c r="E507" t="inlineStr"/>
       <c r="F507" t="inlineStr">
         <is>
           <t>お祝い</t>
@@ -16414,7 +16371,6 @@
           <t>きました！</t>
         </is>
       </c>
-      <c r="H507" t="inlineStr"/>
     </row>
     <row r="508">
       <c r="A508" t="n">
@@ -16435,7 +16391,6 @@
           <t>あや</t>
         </is>
       </c>
-      <c r="E508" t="inlineStr"/>
       <c r="F508" t="inlineStr">
         <is>
           <t>アネホ</t>
@@ -16446,7 +16401,6 @@
           <t>もってきたよお</t>
         </is>
       </c>
-      <c r="H508" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" t="n">
@@ -16467,7 +16421,6 @@
           <t>こてつ</t>
         </is>
       </c>
-      <c r="E509" t="inlineStr"/>
       <c r="F509" t="inlineStr">
         <is>
           <t>今</t>
@@ -16478,7 +16431,6 @@
           <t>おいわいしに！</t>
         </is>
       </c>
-      <c r="H509" t="inlineStr"/>
     </row>
     <row r="510">
       <c r="A510" t="n">
@@ -16499,7 +16451,6 @@
           <t>まゆ</t>
         </is>
       </c>
-      <c r="E510" t="inlineStr"/>
       <c r="F510" t="inlineStr">
         <is>
           <t>はじめて</t>
@@ -16510,7 +16461,6 @@
           <t>きました！</t>
         </is>
       </c>
-      <c r="H510" t="inlineStr"/>
     </row>
     <row r="511">
       <c r="A511" t="n">
@@ -16531,7 +16481,6 @@
           <t>まり、あす、たかし</t>
         </is>
       </c>
-      <c r="E511" t="inlineStr"/>
       <c r="F511" t="inlineStr">
         <is>
           <t>お祝いに</t>
@@ -16542,7 +16491,6 @@
           <t>きました！</t>
         </is>
       </c>
-      <c r="H511" t="inlineStr"/>
     </row>
     <row r="512">
       <c r="A512" t="n">
@@ -16563,7 +16511,6 @@
           <t>じん、あまねちゃん</t>
         </is>
       </c>
-      <c r="E512" t="inlineStr"/>
       <c r="F512" t="inlineStr">
         <is>
           <t>しごおわ</t>
@@ -16574,7 +16521,6 @@
           <t>おめでとうございます</t>
         </is>
       </c>
-      <c r="H512" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" t="n">
@@ -16595,7 +16541,6 @@
           <t>りょうが、たか</t>
         </is>
       </c>
-      <c r="E513" t="inlineStr"/>
       <c r="F513" t="inlineStr">
         <is>
           <t>おくれました</t>
@@ -16606,7 +16551,6 @@
           <t>きました！</t>
         </is>
       </c>
-      <c r="H513" t="inlineStr"/>
     </row>
     <row r="514">
       <c r="A514" t="n">
@@ -16660,6 +16604,346 @@
         </is>
       </c>
     </row>
+    <row r="515">
+      <c r="A515" t="n">
+        <v>27755</v>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>18:00:10</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>キムとドMみい</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr"/>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>みんなで</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>いじめて下さい</t>
+        </is>
+      </c>
+      <c r="H515" t="inlineStr"/>
+    </row>
+    <row r="516">
+      <c r="A516" t="n">
+        <v>27757</v>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>19:24:51</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>タケ</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr"/>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>初めて</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>来ました</t>
+        </is>
+      </c>
+      <c r="H516" t="inlineStr"/>
+    </row>
+    <row r="517">
+      <c r="A517" t="n">
+        <v>27759</v>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>19:46:18</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>くれは</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr"/>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+      <c r="H517" t="inlineStr"/>
+    </row>
+    <row r="518">
+      <c r="A518" t="n">
+        <v>27761</v>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>20:15:05</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>キム、みー</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr"/>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>きたたった</t>
+        </is>
+      </c>
+      <c r="H518" t="inlineStr"/>
+    </row>
+    <row r="519">
+      <c r="A519" t="n">
+        <v>27763</v>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>21:05:58</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>ゆずきち</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr"/>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>きたんご</t>
+        </is>
+      </c>
+      <c r="H519" t="inlineStr"/>
+    </row>
+    <row r="520">
+      <c r="A520" t="n">
+        <v>27765</v>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>21:53:47</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>ゆう</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr"/>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>はじめて</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+      <c r="H520" t="inlineStr"/>
+    </row>
+    <row r="521">
+      <c r="A521" t="n">
+        <v>27767</v>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>22:30:22</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>ましゅ</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr"/>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>パチンコ</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>まけちゃった</t>
+        </is>
+      </c>
+      <c r="H521" t="inlineStr"/>
+    </row>
+    <row r="522">
+      <c r="A522" t="n">
+        <v>27768</v>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>23:27:55</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>りゅーちゃん、まな</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr"/>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>新規</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>連れてきました</t>
+        </is>
+      </c>
+      <c r="H522" t="inlineStr"/>
+    </row>
+    <row r="523">
+      <c r="A523" t="n">
+        <v>27771</v>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>00:02:47</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>ひがん</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr"/>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>ねむすぎ</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>来たっちゃ</t>
+        </is>
+      </c>
+      <c r="H523" t="inlineStr"/>
+    </row>
+    <row r="524">
+      <c r="A524" t="n">
+        <v>27773</v>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>04:55:21</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t>新妻マゾヒストのミコト</t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>★☆★朝までアゲアゲの月曜日営業が始まるわよ♪★☆★</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>本日9月14日の営業時間は♪
+オープン19:00！ラスト5:00なのよ☆
+担当は
+新妻マゾヒストのミコト
+なのよ♪
+どんな季節でも★BAMBITCH★は色気ムンムンで暑すぎる♪
+バンビッチでおもいっきりはじけちゃって（笑）
+精力は無くても性欲がある！？
+大人の憩いと禁断サークル盛りだくさん！
+憩いと交流の魔性の遊び場バンビッチは素敵な出会いを 提供いたします（笑)☆☆
+おつまみ等の持ち込みは自由なのでみんなで持ち寄ってお近づきのきっかけにどうぞ♪
+強制や無理強いは一切ございませんので楽しく遊びましょう♪
+宇都宮市宿郷1−12−9　カサブランカビル5F</t>
+        </is>
+      </c>
+      <c r="H524" t="inlineStr">
+        <is>
+          <t>img20260914045521.jpg</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16671,7 +16955,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I612"/>
+  <dimension ref="A1:I623"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43001,6 +43285,479 @@
       <c r="I612" t="inlineStr">
         <is>
           <t>きました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>18:00:10</t>
+        </is>
+      </c>
+      <c r="D613" t="n">
+        <v>27755</v>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>キムとドMみい</t>
+        </is>
+      </c>
+      <c r="F613" t="n">
+        <v>3</v>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>キムとドMみい</t>
+        </is>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>みんなで</t>
+        </is>
+      </c>
+      <c r="I613" t="inlineStr">
+        <is>
+          <t>いじめて下さい</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>19:24:51</t>
+        </is>
+      </c>
+      <c r="D614" t="n">
+        <v>27757</v>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>タケ</t>
+        </is>
+      </c>
+      <c r="F614" t="n">
+        <v>2</v>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>タケ</t>
+        </is>
+      </c>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>初めて</t>
+        </is>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>来ました</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>19:46:18</t>
+        </is>
+      </c>
+      <c r="D615" t="n">
+        <v>27759</v>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>くれは</t>
+        </is>
+      </c>
+      <c r="F615" t="n">
+        <v>4</v>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>くれは</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>20:15:05</t>
+        </is>
+      </c>
+      <c r="D616" t="n">
+        <v>27761</v>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>キム</t>
+        </is>
+      </c>
+      <c r="F616" t="n">
+        <v>3</v>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>キム、みー</t>
+        </is>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>きたたった</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>20:15:05</t>
+        </is>
+      </c>
+      <c r="D617" t="n">
+        <v>27761</v>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>みー</t>
+        </is>
+      </c>
+      <c r="F617" t="n">
+        <v>1</v>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>キム、みー</t>
+        </is>
+      </c>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="I617" t="inlineStr">
+        <is>
+          <t>きたたった</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>21:05:58</t>
+        </is>
+      </c>
+      <c r="D618" t="n">
+        <v>27763</v>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>ゆずきち</t>
+        </is>
+      </c>
+      <c r="F618" t="n">
+        <v>7</v>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>ゆずきち</t>
+        </is>
+      </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="I618" t="inlineStr">
+        <is>
+          <t>きたんご</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>21:53:47</t>
+        </is>
+      </c>
+      <c r="D619" t="n">
+        <v>27765</v>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>ゆう</t>
+        </is>
+      </c>
+      <c r="F619" t="n">
+        <v>4</v>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>ゆう</t>
+        </is>
+      </c>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>はじめて</t>
+        </is>
+      </c>
+      <c r="I619" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>22:30:22</t>
+        </is>
+      </c>
+      <c r="D620" t="n">
+        <v>27767</v>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>ましゅ</t>
+        </is>
+      </c>
+      <c r="F620" t="n">
+        <v>12</v>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>ましゅ</t>
+        </is>
+      </c>
+      <c r="H620" t="inlineStr">
+        <is>
+          <t>パチンコ</t>
+        </is>
+      </c>
+      <c r="I620" t="inlineStr">
+        <is>
+          <t>まけちゃった</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>23:27:55</t>
+        </is>
+      </c>
+      <c r="D621" t="n">
+        <v>27768</v>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>りゅーちゃん</t>
+        </is>
+      </c>
+      <c r="F621" t="n">
+        <v>1</v>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>りゅーちゃん、まな</t>
+        </is>
+      </c>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>新規</t>
+        </is>
+      </c>
+      <c r="I621" t="inlineStr">
+        <is>
+          <t>連れてきました</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>23:27:55</t>
+        </is>
+      </c>
+      <c r="D622" t="n">
+        <v>27768</v>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>まな</t>
+        </is>
+      </c>
+      <c r="F622" t="n">
+        <v>1</v>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>りゅーちゃん、まな</t>
+        </is>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>新規</t>
+        </is>
+      </c>
+      <c r="I622" t="inlineStr">
+        <is>
+          <t>連れてきました</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>00:02:47</t>
+        </is>
+      </c>
+      <c r="D623" t="n">
+        <v>27771</v>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>ひがん</t>
+        </is>
+      </c>
+      <c r="F623" t="n">
+        <v>16</v>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>ひがん</t>
+        </is>
+      </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>ねむすぎ</t>
+        </is>
+      </c>
+      <c r="I623" t="inlineStr">
+        <is>
+          <t>来たっちゃ</t>
         </is>
       </c>
     </row>
@@ -43015,7 +43772,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D367"/>
+  <dimension ref="A1:D370"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43047,7 +43804,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -43056,7 +43813,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
@@ -43067,7 +43824,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -43076,7 +43833,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -43203,27 +43960,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>zin</t>
+          <t>ゆずきち</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>おとは</t>
+          <t>zin</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -43236,14 +43993,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ゆずきち</t>
+          <t>おとは</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -43251,7 +44008,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -43483,7 +44240,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>すず</t>
+          <t>くれは</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -43491,19 +44248,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>たかやま</t>
+          <t>すず</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -43511,19 +44268,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>まいなちゅ</t>
+          <t>たかやま</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -43531,19 +44288,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>まーくん</t>
+          <t>まいなちゅ</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -43551,19 +44308,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ゆうき</t>
+          <t>まーくん</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -43571,19 +44328,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>るい</t>
+          <t>ゆう</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -43591,23 +44348,23 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>ゆうき</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -43616,34 +44373,34 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>るい</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -43651,19 +44408,19 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>T山</t>
+          <t>K</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -43671,19 +44428,19 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bee</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -43691,19 +44448,19 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>あや</t>
+          <t>T山</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -43711,19 +44468,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>かな</t>
+          <t>bee</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -43731,19 +44488,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>くれは</t>
+          <t>あや</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -43751,19 +44508,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>こてっちゃん</t>
+          <t>かな</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -43771,19 +44528,19 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>さと</t>
+          <t>こてっちゃん</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -43791,19 +44548,19 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>すー</t>
+          <t>さと</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -43811,19 +44568,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>すーさん</t>
+          <t>すー</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -43831,19 +44588,19 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>だいご</t>
+          <t>すーさん</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -43851,19 +44608,19 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>てくのちゃん</t>
+          <t>だいご</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -43871,19 +44628,19 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>でで</t>
+          <t>てくのちゃん</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -43891,19 +44648,19 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ひがんたん</t>
+          <t>でで</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -43911,19 +44668,19 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ゆう</t>
+          <t>ひがんたん</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -43936,7 +44693,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
@@ -44043,7 +44800,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>コテッチャン</t>
+          <t>キム</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -44051,19 +44808,19 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>タツヤ</t>
+          <t>キムとドMみい</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -44071,19 +44828,19 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>マロ</t>
+          <t>コテッチャン</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -44091,59 +44848,59 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>タツヤ</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Bee</t>
+          <t>マロ</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -44151,19 +44908,19 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
           <t>2026-08-23</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>あゆ</t>
+          <t>Bee</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -44171,19 +44928,19 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>あんこ</t>
+          <t>R</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -44196,14 +44953,14 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>いっちゃん</t>
+          <t>あゆ</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -44211,19 +44968,19 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>いぬ</t>
+          <t>あんこ</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -44231,19 +44988,19 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>おでで</t>
+          <t>いっちゃん</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -44251,19 +45008,19 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
           <t>2026-08-22</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>かい</t>
+          <t>いぬ</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -44271,19 +45028,19 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>きむ</t>
+          <t>おでで</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -44291,19 +45048,19 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>けん</t>
+          <t>かい</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -44311,19 +45068,19 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>さとるん</t>
+          <t>きむ</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -44331,19 +45088,19 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>しゅん</t>
+          <t>けん</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -44351,19 +45108,19 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>しょうた</t>
+          <t>さとるん</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -44371,19 +45128,19 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>しーたん</t>
+          <t>しゅん</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -44391,19 +45148,19 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>すーたく</t>
+          <t>しょうた</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -44411,19 +45168,19 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>たかやまん</t>
+          <t>しーたん</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -44431,19 +45188,19 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>たくや</t>
+          <t>すーたく</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -44451,7 +45208,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -44463,7 +45220,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>たつや</t>
+          <t>たかやまん</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -44471,19 +45228,19 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ちゃそたけ</t>
+          <t>たくや</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -44491,19 +45248,19 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>とし</t>
+          <t>たつや</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -44511,19 +45268,19 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>なな</t>
+          <t>ちゃそたけ</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -44531,19 +45288,19 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>なまがき</t>
+          <t>とし</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -44551,19 +45308,19 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ぶりちゃん</t>
+          <t>なな</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -44571,19 +45328,19 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ぽちゃりす組</t>
+          <t>なまがき</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -44591,19 +45348,19 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>まい</t>
+          <t>ぶりちゃん</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -44616,14 +45373,14 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>まなみ</t>
+          <t>ぽちゃりす組</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -44631,19 +45388,19 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>まゆ</t>
+          <t>まい</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -44651,19 +45408,19 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>まろ</t>
+          <t>まなみ</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -44671,19 +45428,19 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>みれい</t>
+          <t>まゆ</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -44691,19 +45448,19 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>めい</t>
+          <t>まろ</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -44716,14 +45473,14 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>もっぷ</t>
+          <t>みれい</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -44731,19 +45488,19 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>やえ</t>
+          <t>めい</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -44751,19 +45508,19 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>よしやん</t>
+          <t>もっぷ</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -44771,19 +45528,19 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>よっしー</t>
+          <t>やえ</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -44791,19 +45548,19 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>よっち</t>
+          <t>よしやん</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -44811,19 +45568,19 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>りお</t>
+          <t>よっしー</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -44836,14 +45593,14 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>りゅう</t>
+          <t>よっち</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -44851,19 +45608,19 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>りょう</t>
+          <t>りお</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -44871,19 +45628,19 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>オカニー</t>
+          <t>りゅう</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -44891,19 +45648,19 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>キム</t>
+          <t>りょう</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -44911,19 +45668,19 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>キムとドMまゆ</t>
+          <t>オカニー</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -44931,19 +45688,19 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>キムとドMみい</t>
+          <t>キムとドMまゆ</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -44951,12 +45708,12 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
@@ -45003,7 +45760,7 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>マッスル</t>
+          <t>タケ</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -45011,19 +45768,19 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ミコト</t>
+          <t>マッスル</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -45031,19 +45788,19 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>愛とスケベの戦士</t>
+          <t>ミコト</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -45051,39 +45808,39 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>愛とスケベの戦士</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>HGN</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -45091,19 +45848,19 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>JPTR</t>
+          <t>HGN</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -45111,19 +45868,19 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>JPTR</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -45131,19 +45888,19 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>KUMA</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -45151,19 +45908,19 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>KUMA</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -45171,19 +45928,19 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>NMGK</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -45191,19 +45948,19 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>N氏御一行</t>
+          <t>NMGK</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -45211,19 +45968,19 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>STR</t>
+          <t>N氏御一行</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -45231,19 +45988,19 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>STR</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -45251,19 +46008,19 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>TARU</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -45271,19 +46028,19 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>TARU</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -45291,19 +46048,19 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Tやま</t>
+          <t>TT</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -45311,19 +46068,19 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>Tやま</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -45331,19 +46088,19 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>YZK</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -45351,19 +46108,19 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>hikari</t>
+          <t>YZK</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -45371,19 +46128,19 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>nuri</t>
+          <t>hikari</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -45391,19 +46148,19 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>nuri</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -45411,19 +46168,19 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>★Zakk★</t>
+          <t>−</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -45431,19 +46188,19 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>あいちゃん</t>
+          <t>★Zakk★</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -45451,19 +46208,19 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>あき</t>
+          <t>あいちゃん</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -45483,7 +46240,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>あさみ</t>
+          <t>あき</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -45491,19 +46248,19 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>あさみん</t>
+          <t>あさみ</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -45511,19 +46268,19 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>あす</t>
+          <t>あさみん</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -45531,19 +46288,19 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>あっくん</t>
+          <t>あす</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -45551,19 +46308,19 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>あにー</t>
+          <t>あっくん</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -45571,19 +46328,19 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>あまねちゃん</t>
+          <t>あにー</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -45591,19 +46348,19 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>いおり</t>
+          <t>あまねちゃん</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -45611,19 +46368,19 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>いけちゃん</t>
+          <t>いおり</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -45631,19 +46388,19 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>いぶお</t>
+          <t>いけちゃん</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -45651,19 +46408,19 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>うらら</t>
+          <t>いぶお</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -45671,19 +46428,19 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>えぬ</t>
+          <t>うらら</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -45691,19 +46448,19 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>える</t>
+          <t>えぬ</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -45711,19 +46468,19 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>おじき</t>
+          <t>える</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -45731,19 +46488,19 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>おじきち</t>
+          <t>おじき</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -45751,19 +46508,19 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>おすー</t>
+          <t>おじきち</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -45771,19 +46528,19 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>おちんぽベルセルク</t>
+          <t>おすー</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -45791,19 +46548,19 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>おにゃん</t>
+          <t>おちんぽベルセルク</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -45811,19 +46568,19 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>おにゃんにゃん</t>
+          <t>おにゃん</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -45831,19 +46588,19 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>かける</t>
+          <t>おにゃんにゃん</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -45851,19 +46608,19 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>かずき</t>
+          <t>かける</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -45871,19 +46628,19 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>かず＆TKC＆のんのん</t>
+          <t>かずき</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -45891,19 +46648,19 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>かな(絶ちゃん</t>
+          <t>かず＆TKC＆のんのん</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -45923,7 +46680,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>かな(絶ちゃん)/おっつん</t>
+          <t>かな(絶ちゃん</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -45931,19 +46688,19 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>がん</t>
+          <t>かな(絶ちゃん)/おっつん</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -45951,19 +46708,19 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>きむさん</t>
+          <t>がん</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -45971,19 +46728,19 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>きむむ</t>
+          <t>きむさん</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -45991,19 +46748,19 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>きむら</t>
+          <t>きむむ</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -46011,19 +46768,19 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>きょうちゃん</t>
+          <t>きむら</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -46031,19 +46788,19 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>きんたまよ</t>
+          <t>きょうちゃん</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -46051,19 +46808,19 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>くま</t>
+          <t>きんたまよ</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -46071,19 +46828,19 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ぐっちゃん</t>
+          <t>くま</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -46091,19 +46848,19 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>けい</t>
+          <t>ぐっちゃん</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -46111,19 +46868,19 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>けいちゃん</t>
+          <t>けい</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -46131,19 +46888,19 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>けんけん</t>
+          <t>けいちゃん</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -46151,19 +46908,19 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>げん</t>
+          <t>けんけん</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -46171,19 +46928,19 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>こう</t>
+          <t>げん</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -46191,19 +46948,19 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>こうた</t>
+          <t>こう</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -46211,19 +46968,19 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>こてつ</t>
+          <t>こうた</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -46231,19 +46988,19 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ことねえ</t>
+          <t>こてつ</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -46251,19 +47008,19 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ことり</t>
+          <t>ことねえ</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -46271,19 +47028,19 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ごん</t>
+          <t>ことり</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -46291,19 +47048,19 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>さかもと</t>
+          <t>ごん</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -46311,19 +47068,19 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>さくら</t>
+          <t>さかもと</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -46331,19 +47088,19 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>さとりゅ</t>
+          <t>さくら</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -46351,19 +47108,19 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>さとる</t>
+          <t>さとりゅ</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -46371,19 +47128,19 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>さな</t>
+          <t>さとる</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -46391,19 +47148,19 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>さない</t>
+          <t>さな</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -46411,19 +47168,19 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>さや</t>
+          <t>さない</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -46431,19 +47188,19 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>しずか</t>
+          <t>さや</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -46451,19 +47208,19 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>しりゅう</t>
+          <t>しずか</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -46471,19 +47228,19 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>じん</t>
+          <t>しりゅう</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -46491,19 +47248,19 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>せいら</t>
+          <t>じん</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -46511,19 +47268,19 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>たいせー</t>
+          <t>せいら</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -46531,19 +47288,19 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>たか</t>
+          <t>たいせー</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -46551,19 +47308,19 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>たかし</t>
+          <t>たか</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -46583,7 +47340,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>たかち</t>
+          <t>たかし</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -46591,19 +47348,19 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>たく</t>
+          <t>たかち</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -46611,19 +47368,19 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>たけ</t>
+          <t>たく</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -46631,19 +47388,19 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>たけし</t>
+          <t>たけ</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -46651,19 +47408,19 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>たつ</t>
+          <t>たけし</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -46671,19 +47428,19 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>たます</t>
+          <t>たつ</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -46691,19 +47448,19 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>たろー</t>
+          <t>たます</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -46711,19 +47468,19 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>だいさく</t>
+          <t>たろー</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -46731,19 +47488,19 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>だいざく</t>
+          <t>だいさく</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -46751,19 +47508,19 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>だいち</t>
+          <t>だいざく</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -46771,19 +47528,19 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>ちぇちぇ</t>
+          <t>だいち</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -46791,19 +47548,19 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ちっち</t>
+          <t>ちぇちぇ</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -46811,19 +47568,19 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>てくのっち</t>
+          <t>ちっち</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -46831,19 +47588,19 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>てっちゃん</t>
+          <t>てくのっち</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -46851,19 +47608,19 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>てつ</t>
+          <t>てっちゃん</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -46871,19 +47628,19 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>てつじ</t>
+          <t>てつ</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -46891,19 +47648,19 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>てる</t>
+          <t>てつじ</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -46911,19 +47668,19 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>でかかわ</t>
+          <t>てる</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -46931,19 +47688,19 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>ででたゃ</t>
+          <t>でかかわ</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -46951,19 +47708,19 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>とうや</t>
+          <t>ででたゃ</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -46971,19 +47728,19 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>とおちゃん</t>
+          <t>とうや</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -46991,19 +47748,19 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>とっしー</t>
+          <t>とおちゃん</t>
         </is>
       </c>
       <c r="B200" t="n">
@@ -47011,19 +47768,19 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>とも</t>
+          <t>とっしー</t>
         </is>
       </c>
       <c r="B201" t="n">
@@ -47031,19 +47788,19 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>ともち</t>
+          <t>とも</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -47051,19 +47808,19 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>ともひろ</t>
+          <t>ともち</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -47071,19 +47828,19 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>ともや</t>
+          <t>ともひろ</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -47091,19 +47848,19 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>ともゆき</t>
+          <t>ともや</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -47111,19 +47868,19 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>とーり</t>
+          <t>ともゆき</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -47131,19 +47888,19 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>どえむちゃん</t>
+          <t>とーり</t>
         </is>
       </c>
       <c r="B207" t="n">
@@ -47151,19 +47908,19 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>ながとも</t>
+          <t>どえむちゃん</t>
         </is>
       </c>
       <c r="B208" t="n">
@@ -47171,19 +47928,19 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>なべ</t>
+          <t>ながとも</t>
         </is>
       </c>
       <c r="B209" t="n">
@@ -47191,19 +47948,19 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>にこちん</t>
+          <t>なべ</t>
         </is>
       </c>
       <c r="B210" t="n">
@@ -47211,19 +47968,19 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>にゃんまげ</t>
+          <t>にこちん</t>
         </is>
       </c>
       <c r="B211" t="n">
@@ -47231,19 +47988,19 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>にょ</t>
+          <t>にゃんまげ</t>
         </is>
       </c>
       <c r="B212" t="n">
@@ -47251,19 +48008,19 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>ねここ</t>
+          <t>にょ</t>
         </is>
       </c>
       <c r="B213" t="n">
@@ -47271,19 +48028,19 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>のぼ</t>
+          <t>ねここ</t>
         </is>
       </c>
       <c r="B214" t="n">
@@ -47291,19 +48048,19 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>のり</t>
+          <t>のぼ</t>
         </is>
       </c>
       <c r="B215" t="n">
@@ -47311,19 +48068,19 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>はち</t>
+          <t>のり</t>
         </is>
       </c>
       <c r="B216" t="n">
@@ -47331,19 +48088,19 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>はな</t>
+          <t>はち</t>
         </is>
       </c>
       <c r="B217" t="n">
@@ -47351,19 +48108,19 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>はなちゃん</t>
+          <t>はな</t>
         </is>
       </c>
       <c r="B218" t="n">
@@ -47371,19 +48128,19 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>はなまる</t>
+          <t>はなちゃん</t>
         </is>
       </c>
       <c r="B219" t="n">
@@ -47391,19 +48148,19 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>はんまー</t>
+          <t>はなまる</t>
         </is>
       </c>
       <c r="B220" t="n">
@@ -47411,19 +48168,19 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>ひがんちゃん</t>
+          <t>はんまー</t>
         </is>
       </c>
       <c r="B221" t="n">
@@ -47431,19 +48188,19 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>ひったん</t>
+          <t>ひがんちゃん</t>
         </is>
       </c>
       <c r="B222" t="n">
@@ -47451,19 +48208,19 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>ひろとも</t>
+          <t>ひったん</t>
         </is>
       </c>
       <c r="B223" t="n">
@@ -47471,19 +48228,19 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>ふく</t>
+          <t>ひろとも</t>
         </is>
       </c>
       <c r="B224" t="n">
@@ -47491,19 +48248,19 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>ふくちゃん</t>
+          <t>ふく</t>
         </is>
       </c>
       <c r="B225" t="n">
@@ -47511,19 +48268,19 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>ふみ</t>
+          <t>ふくちゃん</t>
         </is>
       </c>
       <c r="B226" t="n">
@@ -47531,19 +48288,19 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>ぷらぐいん</t>
+          <t>ふみ</t>
         </is>
       </c>
       <c r="B227" t="n">
@@ -47551,19 +48308,19 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>べー</t>
+          <t>ぷらぐいん</t>
         </is>
       </c>
       <c r="B228" t="n">
@@ -47571,19 +48328,19 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>ぺぺ</t>
+          <t>べー</t>
         </is>
       </c>
       <c r="B229" t="n">
@@ -47591,19 +48348,19 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>まいまいまいまい</t>
+          <t>ぺぺ</t>
         </is>
       </c>
       <c r="B230" t="n">
@@ -47611,19 +48368,19 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>まいまいん</t>
+          <t>まいまいまいまい</t>
         </is>
       </c>
       <c r="B231" t="n">
@@ -47631,19 +48388,19 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>まおし</t>
+          <t>まいまいん</t>
         </is>
       </c>
       <c r="B232" t="n">
@@ -47663,7 +48420,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>ましゅ社長</t>
+          <t>まおし</t>
         </is>
       </c>
       <c r="B233" t="n">
@@ -47671,19 +48428,19 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>ますみ</t>
+          <t>ましゅ社長</t>
         </is>
       </c>
       <c r="B234" t="n">
@@ -47691,19 +48448,19 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>まっする</t>
+          <t>ますみ</t>
         </is>
       </c>
       <c r="B235" t="n">
@@ -47711,19 +48468,19 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>まっぴー</t>
+          <t>まっする</t>
         </is>
       </c>
       <c r="B236" t="n">
@@ -47731,19 +48488,19 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>まや</t>
+          <t>まっぴー</t>
         </is>
       </c>
       <c r="B237" t="n">
@@ -47751,19 +48508,19 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>まり</t>
+          <t>まな</t>
         </is>
       </c>
       <c r="B238" t="n">
@@ -47783,7 +48540,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>まりん</t>
+          <t>まや</t>
         </is>
       </c>
       <c r="B239" t="n">
@@ -47791,19 +48548,19 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>まー</t>
+          <t>まり</t>
         </is>
       </c>
       <c r="B240" t="n">
@@ -47811,19 +48568,19 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>まーさん</t>
+          <t>まりん</t>
         </is>
       </c>
       <c r="B241" t="n">
@@ -47831,19 +48588,19 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>まーちゃん</t>
+          <t>まー</t>
         </is>
       </c>
       <c r="B242" t="n">
@@ -47851,19 +48608,19 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>みかん</t>
+          <t>まーさん</t>
         </is>
       </c>
       <c r="B243" t="n">
@@ -47871,19 +48628,19 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>みずき</t>
+          <t>まーちゃん</t>
         </is>
       </c>
       <c r="B244" t="n">
@@ -47891,19 +48648,19 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>みちゃ</t>
+          <t>みかん</t>
         </is>
       </c>
       <c r="B245" t="n">
@@ -47911,19 +48668,19 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>みっちー</t>
+          <t>みずき</t>
         </is>
       </c>
       <c r="B246" t="n">
@@ -47931,19 +48688,19 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>みなつちん</t>
+          <t>みちゃ</t>
         </is>
       </c>
       <c r="B247" t="n">
@@ -47951,19 +48708,19 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>みみ</t>
+          <t>みっちー</t>
         </is>
       </c>
       <c r="B248" t="n">
@@ -47971,19 +48728,19 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>みゆき</t>
+          <t>みなつちん</t>
         </is>
       </c>
       <c r="B249" t="n">
@@ -47991,19 +48748,19 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>みらい</t>
+          <t>みみ</t>
         </is>
       </c>
       <c r="B250" t="n">
@@ -48011,19 +48768,19 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>みるこ</t>
+          <t>みゆき</t>
         </is>
       </c>
       <c r="B251" t="n">
@@ -48031,19 +48788,19 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>みん</t>
+          <t>みらい</t>
         </is>
       </c>
       <c r="B252" t="n">
@@ -48051,19 +48808,19 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>みーみ</t>
+          <t>みるこ</t>
         </is>
       </c>
       <c r="B253" t="n">
@@ -48071,19 +48828,19 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>もかちんぽぽ</t>
+          <t>みん</t>
         </is>
       </c>
       <c r="B254" t="n">
@@ -48091,19 +48848,19 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>もっち</t>
+          <t>みー</t>
         </is>
       </c>
       <c r="B255" t="n">
@@ -48111,19 +48868,19 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>もと</t>
+          <t>みーみ</t>
         </is>
       </c>
       <c r="B256" t="n">
@@ -48131,19 +48888,19 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>ももたろ</t>
+          <t>もかちんぽぽ</t>
         </is>
       </c>
       <c r="B257" t="n">
@@ -48151,19 +48908,19 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>ゆい</t>
+          <t>もっち</t>
         </is>
       </c>
       <c r="B258" t="n">
@@ -48183,7 +48940,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>ゆうくん</t>
+          <t>もと</t>
         </is>
       </c>
       <c r="B259" t="n">
@@ -48191,19 +48948,19 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>ゆうた</t>
+          <t>ももたろ</t>
         </is>
       </c>
       <c r="B260" t="n">
@@ -48211,19 +48968,19 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>ゆうたん</t>
+          <t>ゆい</t>
         </is>
       </c>
       <c r="B261" t="n">
@@ -48231,19 +48988,19 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>ゆうと</t>
+          <t>ゆうくん</t>
         </is>
       </c>
       <c r="B262" t="n">
@@ -48251,19 +49008,19 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>ゆうや</t>
+          <t>ゆうた</t>
         </is>
       </c>
       <c r="B263" t="n">
@@ -48271,19 +49028,19 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>ゆきんこ</t>
+          <t>ゆうたん</t>
         </is>
       </c>
       <c r="B264" t="n">
@@ -48291,19 +49048,19 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>ゆず</t>
+          <t>ゆうと</t>
         </is>
       </c>
       <c r="B265" t="n">
@@ -48311,19 +49068,19 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>ゆずき＆ましゅ</t>
+          <t>ゆうや</t>
         </is>
       </c>
       <c r="B266" t="n">
@@ -48331,19 +49088,19 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>ゆぴ</t>
+          <t>ゆきんこ</t>
         </is>
       </c>
       <c r="B267" t="n">
@@ -48351,19 +49108,19 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>ゆり</t>
+          <t>ゆず</t>
         </is>
       </c>
       <c r="B268" t="n">
@@ -48383,7 +49140,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>ゆりな</t>
+          <t>ゆずき＆ましゅ</t>
         </is>
       </c>
       <c r="B269" t="n">
@@ -48391,19 +49148,19 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>ゆん</t>
+          <t>ゆぴ</t>
         </is>
       </c>
       <c r="B270" t="n">
@@ -48411,19 +49168,19 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>よこい</t>
+          <t>ゆり</t>
         </is>
       </c>
       <c r="B271" t="n">
@@ -48431,19 +49188,19 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>よちお</t>
+          <t>ゆりな</t>
         </is>
       </c>
       <c r="B272" t="n">
@@ -48451,19 +49208,19 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>らうら</t>
+          <t>ゆん</t>
         </is>
       </c>
       <c r="B273" t="n">
@@ -48483,7 +49240,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>らお</t>
+          <t>よこい</t>
         </is>
       </c>
       <c r="B274" t="n">
@@ -48491,19 +49248,19 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>りえ</t>
+          <t>よちお</t>
         </is>
       </c>
       <c r="B275" t="n">
@@ -48511,19 +49268,19 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>りく</t>
+          <t>らうら</t>
         </is>
       </c>
       <c r="B276" t="n">
@@ -48531,19 +49288,19 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>りさ</t>
+          <t>らお</t>
         </is>
       </c>
       <c r="B277" t="n">
@@ -48551,19 +49308,19 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>りゅうくん</t>
+          <t>りえ</t>
         </is>
       </c>
       <c r="B278" t="n">
@@ -48571,19 +49328,19 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>りょうが</t>
+          <t>りく</t>
         </is>
       </c>
       <c r="B279" t="n">
@@ -48591,19 +49348,19 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>りょうちゃん</t>
+          <t>りさ</t>
         </is>
       </c>
       <c r="B280" t="n">
@@ -48611,19 +49368,19 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>りょーが</t>
+          <t>りゅうくん</t>
         </is>
       </c>
       <c r="B281" t="n">
@@ -48631,19 +49388,19 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>りりこ</t>
+          <t>りゅーちゃん</t>
         </is>
       </c>
       <c r="B282" t="n">
@@ -48651,19 +49408,19 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>りん＆ゆち</t>
+          <t>りょうが</t>
         </is>
       </c>
       <c r="B283" t="n">
@@ -48671,19 +49428,19 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>れー</t>
+          <t>りょうちゃん</t>
         </is>
       </c>
       <c r="B284" t="n">
@@ -48691,19 +49448,19 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>アイ</t>
+          <t>りょーが</t>
         </is>
       </c>
       <c r="B285" t="n">
@@ -48711,19 +49468,19 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>アイちゃん</t>
+          <t>りりこ</t>
         </is>
       </c>
       <c r="B286" t="n">
@@ -48731,19 +49488,19 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>アキ</t>
+          <t>りん＆ゆち</t>
         </is>
       </c>
       <c r="B287" t="n">
@@ -48751,19 +49508,19 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>アナルプリンス</t>
+          <t>れー</t>
         </is>
       </c>
       <c r="B288" t="n">
@@ -48771,19 +49528,19 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>イエモン</t>
+          <t>アイ</t>
         </is>
       </c>
       <c r="B289" t="n">
@@ -48803,7 +49560,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>オ・スー</t>
+          <t>アイちゃん</t>
         </is>
       </c>
       <c r="B290" t="n">
@@ -48811,19 +49568,19 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>カイト</t>
+          <t>アキ</t>
         </is>
       </c>
       <c r="B291" t="n">
@@ -48831,19 +49588,19 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>カズヤ</t>
+          <t>アナルプリンス</t>
         </is>
       </c>
       <c r="B292" t="n">
@@ -48851,19 +49608,19 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>カミさん</t>
+          <t>イエモン</t>
         </is>
       </c>
       <c r="B293" t="n">
@@ -48871,19 +49628,19 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>カモリ</t>
+          <t>オ・スー</t>
         </is>
       </c>
       <c r="B294" t="n">
@@ -48891,19 +49648,19 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>カー</t>
+          <t>カイト</t>
         </is>
       </c>
       <c r="B295" t="n">
@@ -48911,19 +49668,19 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>キムさん</t>
+          <t>カズヤ</t>
         </is>
       </c>
       <c r="B296" t="n">
@@ -48931,19 +49688,19 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>キムとどえむちゃん</t>
+          <t>カミさん</t>
         </is>
       </c>
       <c r="B297" t="n">
@@ -48951,19 +49708,19 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>キムとまゆ</t>
+          <t>カモリ</t>
         </is>
       </c>
       <c r="B298" t="n">
@@ -48971,19 +49728,19 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>キムとドM女R</t>
+          <t>カー</t>
         </is>
       </c>
       <c r="B299" t="n">
@@ -48991,19 +49748,19 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>キムと奴隷</t>
+          <t>キムさん</t>
         </is>
       </c>
       <c r="B300" t="n">
@@ -49011,19 +49768,19 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>キムと新しい奴隷ちゃん</t>
+          <t>キムとどえむちゃん</t>
         </is>
       </c>
       <c r="B301" t="n">
@@ -49031,19 +49788,19 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>クロちゃん</t>
+          <t>キムとまゆ</t>
         </is>
       </c>
       <c r="B302" t="n">
@@ -49051,19 +49808,19 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>ケケ</t>
+          <t>キムとドM女R</t>
         </is>
       </c>
       <c r="B303" t="n">
@@ -49071,19 +49828,19 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>ゲン</t>
+          <t>キムと奴隷</t>
         </is>
       </c>
       <c r="B304" t="n">
@@ -49091,19 +49848,19 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>コオリ</t>
+          <t>キムと新しい奴隷ちゃん</t>
         </is>
       </c>
       <c r="B305" t="n">
@@ -49111,19 +49868,19 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>サトル</t>
+          <t>クロちゃん</t>
         </is>
       </c>
       <c r="B306" t="n">
@@ -49131,19 +49888,19 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>ザッキー</t>
+          <t>ケケ</t>
         </is>
       </c>
       <c r="B307" t="n">
@@ -49151,19 +49908,19 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>シゲ</t>
+          <t>ゲン</t>
         </is>
       </c>
       <c r="B308" t="n">
@@ -49183,7 +49940,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>シュン</t>
+          <t>コオリ</t>
         </is>
       </c>
       <c r="B309" t="n">
@@ -49191,19 +49948,19 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>シュンヤ</t>
+          <t>サトル</t>
         </is>
       </c>
       <c r="B310" t="n">
@@ -49211,19 +49968,19 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>ジャッキー</t>
+          <t>ザッキー</t>
         </is>
       </c>
       <c r="B311" t="n">
@@ -49231,19 +49988,19 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>ジョーカー</t>
+          <t>シゲ</t>
         </is>
       </c>
       <c r="B312" t="n">
@@ -49251,19 +50008,19 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>タカ</t>
+          <t>シュン</t>
         </is>
       </c>
       <c r="B313" t="n">
@@ -49271,19 +50028,19 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>タカス</t>
+          <t>シュンヤ</t>
         </is>
       </c>
       <c r="B314" t="n">
@@ -49291,19 +50048,19 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>タカ御一行</t>
+          <t>ジャッキー</t>
         </is>
       </c>
       <c r="B315" t="n">
@@ -49311,19 +50068,19 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>タケ</t>
+          <t>ジョーカー</t>
         </is>
       </c>
       <c r="B316" t="n">
@@ -49331,19 +50088,19 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>ダイキ</t>
+          <t>タカ</t>
         </is>
       </c>
       <c r="B317" t="n">
@@ -49351,19 +50108,19 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>ダイゴ</t>
+          <t>タカス</t>
         </is>
       </c>
       <c r="B318" t="n">
@@ -49371,19 +50128,19 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>ダイチ</t>
+          <t>タカ御一行</t>
         </is>
       </c>
       <c r="B319" t="n">
@@ -49391,19 +50148,19 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>ツシマ</t>
+          <t>ダイキ</t>
         </is>
       </c>
       <c r="B320" t="n">
@@ -49411,19 +50168,19 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>ツボ</t>
+          <t>ダイゴ</t>
         </is>
       </c>
       <c r="B321" t="n">
@@ -49431,19 +50188,19 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>テクノっち</t>
+          <t>ダイチ</t>
         </is>
       </c>
       <c r="B322" t="n">
@@ -49451,19 +50208,19 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>テクノとポチ</t>
+          <t>ツシマ</t>
         </is>
       </c>
       <c r="B323" t="n">
@@ -49471,19 +50228,19 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>テクノ＆てるくん＆イブオ</t>
+          <t>ツボ</t>
         </is>
       </c>
       <c r="B324" t="n">
@@ -49491,19 +50248,19 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>トニー・トニー・チョッパー</t>
+          <t>テクノっち</t>
         </is>
       </c>
       <c r="B325" t="n">
@@ -49511,19 +50268,19 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>ナカヤマヤ</t>
+          <t>テクノとポチ</t>
         </is>
       </c>
       <c r="B326" t="n">
@@ -49531,19 +50288,19 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>ニト</t>
+          <t>テクノ＆てるくん＆イブオ</t>
         </is>
       </c>
       <c r="B327" t="n">
@@ -49551,19 +50308,19 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>ニャンまげ</t>
+          <t>トニー・トニー・チョッパー</t>
         </is>
       </c>
       <c r="B328" t="n">
@@ -49571,19 +50328,19 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>ビコー</t>
+          <t>ナカヤマヤ</t>
         </is>
       </c>
       <c r="B329" t="n">
@@ -49591,19 +50348,19 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>フジ</t>
+          <t>ニト</t>
         </is>
       </c>
       <c r="B330" t="n">
@@ -49611,19 +50368,19 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>ボンタ</t>
+          <t>ニャンまげ</t>
         </is>
       </c>
       <c r="B331" t="n">
@@ -49631,19 +50388,19 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>ポチ</t>
+          <t>ビコー</t>
         </is>
       </c>
       <c r="B332" t="n">
@@ -49651,19 +50408,19 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>マイナス</t>
+          <t>フジ</t>
         </is>
       </c>
       <c r="B333" t="n">
@@ -49671,19 +50428,19 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>マサ</t>
+          <t>ボンタ</t>
         </is>
       </c>
       <c r="B334" t="n">
@@ -49691,19 +50448,19 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>マッチョ</t>
+          <t>ポチ</t>
         </is>
       </c>
       <c r="B335" t="n">
@@ -49711,19 +50468,19 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>マナティ</t>
+          <t>マイナス</t>
         </is>
       </c>
       <c r="B336" t="n">
@@ -49731,19 +50488,19 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>ミスター工事マン</t>
+          <t>マサ</t>
         </is>
       </c>
       <c r="B337" t="n">
@@ -49751,19 +50508,19 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>ミッシ</t>
+          <t>マッチョ</t>
         </is>
       </c>
       <c r="B338" t="n">
@@ -49771,19 +50528,19 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>ミッチー</t>
+          <t>マナティ</t>
         </is>
       </c>
       <c r="B339" t="n">
@@ -49791,19 +50548,19 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>ミルコ</t>
+          <t>ミスター工事マン</t>
         </is>
       </c>
       <c r="B340" t="n">
@@ -49811,19 +50568,19 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>モジャ</t>
+          <t>ミッシ</t>
         </is>
       </c>
       <c r="B341" t="n">
@@ -49831,19 +50588,19 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>ヤノちゃん</t>
+          <t>ミッチー</t>
         </is>
       </c>
       <c r="B342" t="n">
@@ -49851,19 +50608,19 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>ヤマ</t>
+          <t>ミルコ</t>
         </is>
       </c>
       <c r="B343" t="n">
@@ -49871,19 +50628,19 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>ユウ</t>
+          <t>モジャ</t>
         </is>
       </c>
       <c r="B344" t="n">
@@ -49891,19 +50648,19 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>ユキ</t>
+          <t>ヤノちゃん</t>
         </is>
       </c>
       <c r="B345" t="n">
@@ -49911,19 +50668,19 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>ユッキー</t>
+          <t>ヤマ</t>
         </is>
       </c>
       <c r="B346" t="n">
@@ -49931,19 +50688,19 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>ヨシヤ</t>
+          <t>ユウ</t>
         </is>
       </c>
       <c r="B347" t="n">
@@ -49951,19 +50708,19 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>リク</t>
+          <t>ユキ</t>
         </is>
       </c>
       <c r="B348" t="n">
@@ -49971,19 +50728,19 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>リョウ</t>
+          <t>ユッキー</t>
         </is>
       </c>
       <c r="B349" t="n">
@@ -49991,19 +50748,19 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>リン</t>
+          <t>ヨシヤ</t>
         </is>
       </c>
       <c r="B350" t="n">
@@ -50011,19 +50768,19 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>ロタポジ</t>
+          <t>リク</t>
         </is>
       </c>
       <c r="B351" t="n">
@@ -50031,19 +50788,19 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>ローズ</t>
+          <t>リョウ</t>
         </is>
       </c>
       <c r="B352" t="n">
@@ -50051,19 +50808,19 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>僕と私</t>
+          <t>リン</t>
         </is>
       </c>
       <c r="B353" t="n">
@@ -50071,19 +50828,19 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>名無し</t>
+          <t>ロタポジ</t>
         </is>
       </c>
       <c r="B354" t="n">
@@ -50091,19 +50848,19 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>変態マッスル</t>
+          <t>ローズ</t>
         </is>
       </c>
       <c r="B355" t="n">
@@ -50123,7 +50880,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>大塚</t>
+          <t>僕と私</t>
         </is>
       </c>
       <c r="B356" t="n">
@@ -50131,19 +50888,19 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>天我迅</t>
+          <t>名無し</t>
         </is>
       </c>
       <c r="B357" t="n">
@@ -50151,19 +50908,19 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>女子三人衆</t>
+          <t>変態マッスル</t>
         </is>
       </c>
       <c r="B358" t="n">
@@ -50171,19 +50928,19 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>正装しん</t>
+          <t>大塚</t>
         </is>
       </c>
       <c r="B359" t="n">
@@ -50191,19 +50948,19 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>海砂利水魚</t>
+          <t>天我迅</t>
         </is>
       </c>
       <c r="B360" t="n">
@@ -50211,19 +50968,19 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>田中</t>
+          <t>女子三人衆</t>
         </is>
       </c>
       <c r="B361" t="n">
@@ -50231,19 +50988,19 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>番</t>
+          <t>正装しん</t>
         </is>
       </c>
       <c r="B362" t="n">
@@ -50251,19 +51008,19 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>絶</t>
+          <t>海砂利水魚</t>
         </is>
       </c>
       <c r="B363" t="n">
@@ -50271,19 +51028,19 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>絶ちゃん</t>
+          <t>田中</t>
         </is>
       </c>
       <c r="B364" t="n">
@@ -50291,19 +51048,19 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>美優</t>
+          <t>番</t>
         </is>
       </c>
       <c r="B365" t="n">
@@ -50311,19 +51068,19 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>赤ちゃん</t>
+          <t>絶</t>
         </is>
       </c>
       <c r="B366" t="n">
@@ -50331,30 +51088,90 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
+          <t>絶ちゃん</t>
+        </is>
+      </c>
+      <c r="B367" t="n">
+        <v>1</v>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>美優</t>
+        </is>
+      </c>
+      <c r="B368" t="n">
+        <v>1</v>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>赤ちゃん</t>
+        </is>
+      </c>
+      <c r="B369" t="n">
+        <v>1</v>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
           <t>高田</t>
         </is>
       </c>
-      <c r="B367" t="n">
-        <v>1</v>
-      </c>
-      <c r="C367" t="inlineStr">
+      <c r="B370" t="n">
+        <v>1</v>
+      </c>
+      <c r="C370" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="D367" t="inlineStr">
+      <c r="D370" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
@@ -50398,10 +51215,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C2" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3">
@@ -50476,10 +51293,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="C8" t="n">
-        <v>106</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -50520,10 +51337,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C2" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3">
@@ -50754,10 +51571,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -50767,10 +51584,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C21" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="22">
@@ -50780,10 +51597,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C22" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23">
@@ -50793,10 +51610,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C23" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24">
@@ -50806,10 +51623,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C24" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25">
@@ -50819,10 +51636,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C25" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -50884,13 +51701,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="C3" t="n">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="D3" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -50904,7 +51721,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C154"/>
+  <dimension ref="A1:C156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52757,12 +53574,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>まーくん</t>
+          <t>まな</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>まーちゃん</t>
+          <t>りゅーちゃん</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -52777,7 +53594,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>りゅうくん</t>
+          <t>まーちゃん</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -52787,12 +53604,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>みずき</t>
+          <t>まーくん</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>りく</t>
+          <t>りゅうくん</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -52807,7 +53624,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>りん</t>
+          <t>りく</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -52817,12 +53634,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>みちゃ</t>
+          <t>みずき</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>ゆう</t>
+          <t>りん</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -52837,7 +53654,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>りょう</t>
+          <t>ゆう</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -52847,12 +53664,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>みゆき</t>
+          <t>みちゃ</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>ゆりな</t>
+          <t>りょう</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -52862,12 +53679,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>みらい</t>
+          <t>みゆき</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>ジャッキー</t>
+          <t>ゆりな</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -52877,12 +53694,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>みれい</t>
+          <t>みらい</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>キム</t>
+          <t>ジャッキー</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -52892,12 +53709,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ももたろ</t>
+          <t>みれい</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>マッチョ</t>
+          <t>キム</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -52907,12 +53724,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ゆう</t>
+          <t>みー</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>りょう</t>
+          <t>キム</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -52922,12 +53739,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ゆうき</t>
+          <t>ももたろ</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>カイト</t>
+          <t>マッチョ</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -52937,12 +53754,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ゆうたん</t>
+          <t>ゆう</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>カモリ</t>
+          <t>りょう</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -52952,12 +53769,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ゆずき</t>
+          <t>ゆうき</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>田中</t>
+          <t>カイト</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -52967,12 +53784,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ゆり</t>
+          <t>ゆうたん</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>りえ</t>
+          <t>カモリ</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -52982,12 +53799,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>よこい</t>
+          <t>ゆずき</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>ビコー</t>
+          <t>田中</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -52997,12 +53814,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>よっしー</t>
+          <t>ゆり</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>ザッキー</t>
+          <t>りえ</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -53012,12 +53829,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>りく</t>
+          <t>よこい</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>りん</t>
+          <t>ビコー</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -53027,12 +53844,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>アキ</t>
+          <t>よっしー</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>コオリ</t>
+          <t>ザッキー</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -53042,12 +53859,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>オカニー</t>
+          <t>りく</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>ダイキ</t>
+          <t>りん</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -53057,12 +53874,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>オカニー</t>
+          <t>アキ</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>ミッシ</t>
+          <t>コオリ</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -53072,12 +53889,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>カズ</t>
+          <t>オカニー</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>ダイゴ</t>
+          <t>ダイキ</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -53087,12 +53904,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>クロちゃん</t>
+          <t>オカニー</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>ポチ</t>
+          <t>ミッシ</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -53102,12 +53919,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ケン</t>
+          <t>カズ</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>ツボ</t>
+          <t>ダイゴ</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -53117,12 +53934,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ゲン</t>
+          <t>クロちゃん</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>シゲ</t>
+          <t>ポチ</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -53132,12 +53949,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>タカ</t>
+          <t>ケン</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>タク</t>
+          <t>ツボ</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -53147,12 +53964,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>タカス</t>
+          <t>ゲン</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>マサ</t>
+          <t>シゲ</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -53162,12 +53979,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
+          <t>タカ</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
           <t>タク</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>リョウ</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -53177,12 +53994,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ダイキ</t>
+          <t>タカス</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>ミッシ</t>
+          <t>マサ</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -53192,12 +54009,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>テクノ</t>
+          <t>タク</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>ミコト</t>
+          <t>リョウ</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -53207,15 +54024,45 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
+          <t>ダイキ</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>ミッシ</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>テクノ</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>ミコト</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
           <t>天我迅</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
+      <c r="B156" t="inlineStr">
         <is>
           <t>美優</t>
         </is>
       </c>
-      <c r="C154" t="n">
+      <c r="C156" t="n">
         <v>1</v>
       </c>
     </row>

--- a/bbs_log.xlsx
+++ b/bbs_log.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H524"/>
+  <dimension ref="A1:H530"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16623,7 +16623,6 @@
           <t>キムとドMみい</t>
         </is>
       </c>
-      <c r="E515" t="inlineStr"/>
       <c r="F515" t="inlineStr">
         <is>
           <t>みんなで</t>
@@ -16634,7 +16633,6 @@
           <t>いじめて下さい</t>
         </is>
       </c>
-      <c r="H515" t="inlineStr"/>
     </row>
     <row r="516">
       <c r="A516" t="n">
@@ -16655,7 +16653,6 @@
           <t>タケ</t>
         </is>
       </c>
-      <c r="E516" t="inlineStr"/>
       <c r="F516" t="inlineStr">
         <is>
           <t>初めて</t>
@@ -16666,7 +16663,6 @@
           <t>来ました</t>
         </is>
       </c>
-      <c r="H516" t="inlineStr"/>
     </row>
     <row r="517">
       <c r="A517" t="n">
@@ -16687,7 +16683,6 @@
           <t>くれは</t>
         </is>
       </c>
-      <c r="E517" t="inlineStr"/>
       <c r="F517" t="inlineStr">
         <is>
           <t>今</t>
@@ -16698,7 +16693,6 @@
           <t>きました！</t>
         </is>
       </c>
-      <c r="H517" t="inlineStr"/>
     </row>
     <row r="518">
       <c r="A518" t="n">
@@ -16719,7 +16713,6 @@
           <t>キム、みー</t>
         </is>
       </c>
-      <c r="E518" t="inlineStr"/>
       <c r="F518" t="inlineStr">
         <is>
           <t>今</t>
@@ -16730,7 +16723,6 @@
           <t>きたたった</t>
         </is>
       </c>
-      <c r="H518" t="inlineStr"/>
     </row>
     <row r="519">
       <c r="A519" t="n">
@@ -16751,7 +16743,6 @@
           <t>ゆずきち</t>
         </is>
       </c>
-      <c r="E519" t="inlineStr"/>
       <c r="F519" t="inlineStr">
         <is>
           <t>今</t>
@@ -16762,7 +16753,6 @@
           <t>きたんご</t>
         </is>
       </c>
-      <c r="H519" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" t="n">
@@ -16783,7 +16773,6 @@
           <t>ゆう</t>
         </is>
       </c>
-      <c r="E520" t="inlineStr"/>
       <c r="F520" t="inlineStr">
         <is>
           <t>はじめて</t>
@@ -16794,7 +16783,6 @@
           <t>きました！</t>
         </is>
       </c>
-      <c r="H520" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" t="n">
@@ -16815,7 +16803,6 @@
           <t>ましゅ</t>
         </is>
       </c>
-      <c r="E521" t="inlineStr"/>
       <c r="F521" t="inlineStr">
         <is>
           <t>パチンコ</t>
@@ -16826,7 +16813,6 @@
           <t>まけちゃった</t>
         </is>
       </c>
-      <c r="H521" t="inlineStr"/>
     </row>
     <row r="522">
       <c r="A522" t="n">
@@ -16847,7 +16833,6 @@
           <t>りゅーちゃん、まな</t>
         </is>
       </c>
-      <c r="E522" t="inlineStr"/>
       <c r="F522" t="inlineStr">
         <is>
           <t>新規</t>
@@ -16858,7 +16843,6 @@
           <t>連れてきました</t>
         </is>
       </c>
-      <c r="H522" t="inlineStr"/>
     </row>
     <row r="523">
       <c r="A523" t="n">
@@ -16879,7 +16863,6 @@
           <t>ひがん</t>
         </is>
       </c>
-      <c r="E523" t="inlineStr"/>
       <c r="F523" t="inlineStr">
         <is>
           <t>ねむすぎ</t>
@@ -16890,7 +16873,6 @@
           <t>来たっちゃ</t>
         </is>
       </c>
-      <c r="H523" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" t="n">
@@ -16944,6 +16926,218 @@
         </is>
       </c>
     </row>
+    <row r="525">
+      <c r="A525" t="n">
+        <v>27775</v>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>19:21:38</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>ひがん</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr"/>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>ちいかわ観て</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>来ました♪</t>
+        </is>
+      </c>
+      <c r="H525" t="inlineStr"/>
+    </row>
+    <row r="526">
+      <c r="A526" t="n">
+        <v>27776</v>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>19:22:11</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>bee</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr"/>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>遊びに</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>来ましたブン♪</t>
+        </is>
+      </c>
+      <c r="H526" t="inlineStr"/>
+    </row>
+    <row r="527">
+      <c r="A527" t="n">
+        <v>27779</v>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>19:57:51</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>ろくじ</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr"/>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>飲みに</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>来ました！</t>
+        </is>
+      </c>
+      <c r="H527" t="inlineStr"/>
+    </row>
+    <row r="528">
+      <c r="A528" t="n">
+        <v>27780</v>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>20:43:04</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>まみ</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr"/>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>初めて</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>新宿からきました！</t>
+        </is>
+      </c>
+      <c r="H528" t="inlineStr"/>
+    </row>
+    <row r="529">
+      <c r="A529" t="n">
+        <v>27783</v>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>02:46:10</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>ミカミと仲間たち</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr"/>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>新規さん連れて</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>きたよー</t>
+        </is>
+      </c>
+      <c r="H529" t="inlineStr"/>
+    </row>
+    <row r="530">
+      <c r="A530" t="n">
+        <v>27785</v>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>04:30:21</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr">
+        <is>
+          <t>天然の100人ネキ　ねむ</t>
+        </is>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>★☆★朝までアゲアゲの火曜日営業が始まるわよ♪★☆★</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>本日9月15日の営業時間は♪
+オープン19:00！ラスト5:00なのよ☆
+担当は
+天然の100人ネキ　ねむ
+なのよ♪
+どんな季節でも★BAMBITCH★は色気ムンムンで暑すぎる♪
+バンビッチでおもいっきりはじけちゃって（笑）
+精力は無くても性欲がある！？
+大人の憩いと禁断サークル盛りだくさん！
+憩いと交流の魔性の遊び場バンビッチは素敵な出会いを 提供いたします（笑)☆☆
+おつまみ等の持ち込みは自由なのでみんなで持ち寄ってお近づきのきっかけにどうぞ♪
+強制や無理強いは一切ございませんので楽しく遊びましょう♪
+宇都宮市宿郷1−12−9　カサブランカビル5F</t>
+        </is>
+      </c>
+      <c r="H530" t="inlineStr">
+        <is>
+          <t>img20260915043021.jpg</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16955,7 +17149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I623"/>
+  <dimension ref="A1:I628"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43758,6 +43952,221 @@
       <c r="I623" t="inlineStr">
         <is>
           <t>来たっちゃ</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>19:21:38</t>
+        </is>
+      </c>
+      <c r="D624" t="n">
+        <v>27775</v>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>ひがん</t>
+        </is>
+      </c>
+      <c r="F624" t="n">
+        <v>17</v>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>ひがん</t>
+        </is>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>ちいかわ観て</t>
+        </is>
+      </c>
+      <c r="I624" t="inlineStr">
+        <is>
+          <t>来ました♪</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>19:22:11</t>
+        </is>
+      </c>
+      <c r="D625" t="n">
+        <v>27776</v>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>bee</t>
+        </is>
+      </c>
+      <c r="F625" t="n">
+        <v>4</v>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>bee</t>
+        </is>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>遊びに</t>
+        </is>
+      </c>
+      <c r="I625" t="inlineStr">
+        <is>
+          <t>来ましたブン♪</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>19:57:51</t>
+        </is>
+      </c>
+      <c r="D626" t="n">
+        <v>27779</v>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>ろくじ</t>
+        </is>
+      </c>
+      <c r="F626" t="n">
+        <v>4</v>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>ろくじ</t>
+        </is>
+      </c>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>飲みに</t>
+        </is>
+      </c>
+      <c r="I626" t="inlineStr">
+        <is>
+          <t>来ました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>20:43:04</t>
+        </is>
+      </c>
+      <c r="D627" t="n">
+        <v>27780</v>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>まみ</t>
+        </is>
+      </c>
+      <c r="F627" t="n">
+        <v>1</v>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>まみ</t>
+        </is>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>初めて</t>
+        </is>
+      </c>
+      <c r="I627" t="inlineStr">
+        <is>
+          <t>新宿からきました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>02:46:10</t>
+        </is>
+      </c>
+      <c r="D628" t="n">
+        <v>27783</v>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>ミカミと仲間たち</t>
+        </is>
+      </c>
+      <c r="F628" t="n">
+        <v>1</v>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>ミカミと仲間たち</t>
+        </is>
+      </c>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>新規さん連れて</t>
+        </is>
+      </c>
+      <c r="I628" t="inlineStr">
+        <is>
+          <t>きたよー</t>
         </is>
       </c>
     </row>
@@ -43772,7 +44181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D370"/>
+  <dimension ref="A1:D372"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43804,7 +44213,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -44220,7 +44629,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>かず</t>
+          <t>bee</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -44228,19 +44637,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>くれは</t>
+          <t>かず</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -44248,19 +44657,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>すず</t>
+          <t>くれは</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -44268,19 +44677,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>たかやま</t>
+          <t>すず</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -44288,19 +44697,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>まいなちゅ</t>
+          <t>たかやま</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -44308,19 +44717,19 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>まーくん</t>
+          <t>まいなちゅ</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -44328,19 +44737,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ゆう</t>
+          <t>まーくん</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -44348,19 +44757,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ゆうき</t>
+          <t>ゆう</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -44368,19 +44777,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>るい</t>
+          <t>ゆうき</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -44388,59 +44797,59 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>るい</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>ろくじ</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -44448,19 +44857,19 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>T山</t>
+          <t>K</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -44468,19 +44877,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bee</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -44488,19 +44897,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>あや</t>
+          <t>T山</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -44508,19 +44917,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>かな</t>
+          <t>あや</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -44528,19 +44937,19 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>こてっちゃん</t>
+          <t>かな</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -44548,19 +44957,19 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>さと</t>
+          <t>こてっちゃん</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -44568,19 +44977,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>すー</t>
+          <t>さと</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -44588,19 +44997,19 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>すーさん</t>
+          <t>すー</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -44608,19 +45017,19 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>だいご</t>
+          <t>すーさん</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -44628,19 +45037,19 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>てくのちゃん</t>
+          <t>だいご</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -44648,19 +45057,19 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>でで</t>
+          <t>てくのちゃん</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -44668,19 +45077,19 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ひがんたん</t>
+          <t>でで</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -44688,19 +45097,19 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ゆずきん</t>
+          <t>ひがんたん</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -44713,14 +45122,14 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>よしお</t>
+          <t>ゆずきん</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -44728,19 +45137,19 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>よしおたん</t>
+          <t>よしお</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -44748,19 +45157,19 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>れいら</t>
+          <t>よしおたん</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -44768,19 +45177,19 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ろくじ</t>
+          <t>れいら</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -44788,12 +45197,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
@@ -48540,7 +48949,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>まや</t>
+          <t>まみ</t>
         </is>
       </c>
       <c r="B239" t="n">
@@ -48548,19 +48957,19 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>まり</t>
+          <t>まや</t>
         </is>
       </c>
       <c r="B240" t="n">
@@ -48568,19 +48977,19 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>まりん</t>
+          <t>まり</t>
         </is>
       </c>
       <c r="B241" t="n">
@@ -48588,19 +48997,19 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>まー</t>
+          <t>まりん</t>
         </is>
       </c>
       <c r="B242" t="n">
@@ -48608,19 +49017,19 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>まーさん</t>
+          <t>まー</t>
         </is>
       </c>
       <c r="B243" t="n">
@@ -48628,19 +49037,19 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>まーちゃん</t>
+          <t>まーさん</t>
         </is>
       </c>
       <c r="B244" t="n">
@@ -48648,19 +49057,19 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>みかん</t>
+          <t>まーちゃん</t>
         </is>
       </c>
       <c r="B245" t="n">
@@ -48668,19 +49077,19 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>みずき</t>
+          <t>みかん</t>
         </is>
       </c>
       <c r="B246" t="n">
@@ -48700,7 +49109,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>みちゃ</t>
+          <t>みずき</t>
         </is>
       </c>
       <c r="B247" t="n">
@@ -48708,19 +49117,19 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>みっちー</t>
+          <t>みちゃ</t>
         </is>
       </c>
       <c r="B248" t="n">
@@ -48728,19 +49137,19 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>みなつちん</t>
+          <t>みっちー</t>
         </is>
       </c>
       <c r="B249" t="n">
@@ -48748,19 +49157,19 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>みみ</t>
+          <t>みなつちん</t>
         </is>
       </c>
       <c r="B250" t="n">
@@ -48768,19 +49177,19 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>みゆき</t>
+          <t>みみ</t>
         </is>
       </c>
       <c r="B251" t="n">
@@ -48788,19 +49197,19 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>みらい</t>
+          <t>みゆき</t>
         </is>
       </c>
       <c r="B252" t="n">
@@ -48808,19 +49217,19 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>みるこ</t>
+          <t>みらい</t>
         </is>
       </c>
       <c r="B253" t="n">
@@ -48828,19 +49237,19 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>みん</t>
+          <t>みるこ</t>
         </is>
       </c>
       <c r="B254" t="n">
@@ -48848,19 +49257,19 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>みー</t>
+          <t>みん</t>
         </is>
       </c>
       <c r="B255" t="n">
@@ -48868,19 +49277,19 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>みーみ</t>
+          <t>みー</t>
         </is>
       </c>
       <c r="B256" t="n">
@@ -48888,19 +49297,19 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>もかちんぽぽ</t>
+          <t>みーみ</t>
         </is>
       </c>
       <c r="B257" t="n">
@@ -48908,19 +49317,19 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>もっち</t>
+          <t>もかちんぽぽ</t>
         </is>
       </c>
       <c r="B258" t="n">
@@ -48928,19 +49337,19 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>もと</t>
+          <t>もっち</t>
         </is>
       </c>
       <c r="B259" t="n">
@@ -48948,19 +49357,19 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>ももたろ</t>
+          <t>もと</t>
         </is>
       </c>
       <c r="B260" t="n">
@@ -48968,19 +49377,19 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>ゆい</t>
+          <t>ももたろ</t>
         </is>
       </c>
       <c r="B261" t="n">
@@ -48988,19 +49397,19 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>ゆうくん</t>
+          <t>ゆい</t>
         </is>
       </c>
       <c r="B262" t="n">
@@ -49008,19 +49417,19 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>ゆうた</t>
+          <t>ゆうくん</t>
         </is>
       </c>
       <c r="B263" t="n">
@@ -49028,19 +49437,19 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>ゆうたん</t>
+          <t>ゆうた</t>
         </is>
       </c>
       <c r="B264" t="n">
@@ -49048,19 +49457,19 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>ゆうと</t>
+          <t>ゆうたん</t>
         </is>
       </c>
       <c r="B265" t="n">
@@ -49068,19 +49477,19 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>ゆうや</t>
+          <t>ゆうと</t>
         </is>
       </c>
       <c r="B266" t="n">
@@ -49088,19 +49497,19 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>ゆきんこ</t>
+          <t>ゆうや</t>
         </is>
       </c>
       <c r="B267" t="n">
@@ -49108,19 +49517,19 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>ゆず</t>
+          <t>ゆきんこ</t>
         </is>
       </c>
       <c r="B268" t="n">
@@ -49128,19 +49537,19 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>ゆずき＆ましゅ</t>
+          <t>ゆず</t>
         </is>
       </c>
       <c r="B269" t="n">
@@ -49148,19 +49557,19 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>ゆぴ</t>
+          <t>ゆずき＆ましゅ</t>
         </is>
       </c>
       <c r="B270" t="n">
@@ -49168,19 +49577,19 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>ゆり</t>
+          <t>ゆぴ</t>
         </is>
       </c>
       <c r="B271" t="n">
@@ -49188,19 +49597,19 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>ゆりな</t>
+          <t>ゆり</t>
         </is>
       </c>
       <c r="B272" t="n">
@@ -49208,19 +49617,19 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>ゆん</t>
+          <t>ゆりな</t>
         </is>
       </c>
       <c r="B273" t="n">
@@ -49228,19 +49637,19 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>よこい</t>
+          <t>ゆん</t>
         </is>
       </c>
       <c r="B274" t="n">
@@ -49248,19 +49657,19 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>よちお</t>
+          <t>よこい</t>
         </is>
       </c>
       <c r="B275" t="n">
@@ -49268,19 +49677,19 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>らうら</t>
+          <t>よちお</t>
         </is>
       </c>
       <c r="B276" t="n">
@@ -49288,19 +49697,19 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>らお</t>
+          <t>らうら</t>
         </is>
       </c>
       <c r="B277" t="n">
@@ -49308,19 +49717,19 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>りえ</t>
+          <t>らお</t>
         </is>
       </c>
       <c r="B278" t="n">
@@ -49328,19 +49737,19 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>りく</t>
+          <t>りえ</t>
         </is>
       </c>
       <c r="B279" t="n">
@@ -49348,19 +49757,19 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>りさ</t>
+          <t>りく</t>
         </is>
       </c>
       <c r="B280" t="n">
@@ -49368,19 +49777,19 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>りゅうくん</t>
+          <t>りさ</t>
         </is>
       </c>
       <c r="B281" t="n">
@@ -49388,19 +49797,19 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>りゅーちゃん</t>
+          <t>りゅうくん</t>
         </is>
       </c>
       <c r="B282" t="n">
@@ -49408,19 +49817,19 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>りょうが</t>
+          <t>りゅーちゃん</t>
         </is>
       </c>
       <c r="B283" t="n">
@@ -49440,7 +49849,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>りょうちゃん</t>
+          <t>りょうが</t>
         </is>
       </c>
       <c r="B284" t="n">
@@ -49448,19 +49857,19 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>りょーが</t>
+          <t>りょうちゃん</t>
         </is>
       </c>
       <c r="B285" t="n">
@@ -49468,19 +49877,19 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>りりこ</t>
+          <t>りょーが</t>
         </is>
       </c>
       <c r="B286" t="n">
@@ -49488,19 +49897,19 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>りん＆ゆち</t>
+          <t>りりこ</t>
         </is>
       </c>
       <c r="B287" t="n">
@@ -49508,19 +49917,19 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>れー</t>
+          <t>りん＆ゆち</t>
         </is>
       </c>
       <c r="B288" t="n">
@@ -49528,19 +49937,19 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>アイ</t>
+          <t>れー</t>
         </is>
       </c>
       <c r="B289" t="n">
@@ -49548,19 +49957,19 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>アイちゃん</t>
+          <t>アイ</t>
         </is>
       </c>
       <c r="B290" t="n">
@@ -49568,19 +49977,19 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>アキ</t>
+          <t>アイちゃん</t>
         </is>
       </c>
       <c r="B291" t="n">
@@ -49588,19 +49997,19 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>アナルプリンス</t>
+          <t>アキ</t>
         </is>
       </c>
       <c r="B292" t="n">
@@ -49608,19 +50017,19 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>イエモン</t>
+          <t>アナルプリンス</t>
         </is>
       </c>
       <c r="B293" t="n">
@@ -49628,19 +50037,19 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>オ・スー</t>
+          <t>イエモン</t>
         </is>
       </c>
       <c r="B294" t="n">
@@ -49648,19 +50057,19 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>カイト</t>
+          <t>オ・スー</t>
         </is>
       </c>
       <c r="B295" t="n">
@@ -49668,19 +50077,19 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>カズヤ</t>
+          <t>カイト</t>
         </is>
       </c>
       <c r="B296" t="n">
@@ -49700,7 +50109,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>カミさん</t>
+          <t>カズヤ</t>
         </is>
       </c>
       <c r="B297" t="n">
@@ -49708,19 +50117,19 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>カモリ</t>
+          <t>カミさん</t>
         </is>
       </c>
       <c r="B298" t="n">
@@ -49728,19 +50137,19 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>カー</t>
+          <t>カモリ</t>
         </is>
       </c>
       <c r="B299" t="n">
@@ -49748,19 +50157,19 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>キムさん</t>
+          <t>カー</t>
         </is>
       </c>
       <c r="B300" t="n">
@@ -49768,19 +50177,19 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>キムとどえむちゃん</t>
+          <t>キムさん</t>
         </is>
       </c>
       <c r="B301" t="n">
@@ -49788,19 +50197,19 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>キムとまゆ</t>
+          <t>キムとどえむちゃん</t>
         </is>
       </c>
       <c r="B302" t="n">
@@ -49808,19 +50217,19 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>キムとドM女R</t>
+          <t>キムとまゆ</t>
         </is>
       </c>
       <c r="B303" t="n">
@@ -49828,19 +50237,19 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>キムと奴隷</t>
+          <t>キムとドM女R</t>
         </is>
       </c>
       <c r="B304" t="n">
@@ -49848,19 +50257,19 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>キムと新しい奴隷ちゃん</t>
+          <t>キムと奴隷</t>
         </is>
       </c>
       <c r="B305" t="n">
@@ -49868,19 +50277,19 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>クロちゃん</t>
+          <t>キムと新しい奴隷ちゃん</t>
         </is>
       </c>
       <c r="B306" t="n">
@@ -49888,19 +50297,19 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>ケケ</t>
+          <t>クロちゃん</t>
         </is>
       </c>
       <c r="B307" t="n">
@@ -49920,7 +50329,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>ゲン</t>
+          <t>ケケ</t>
         </is>
       </c>
       <c r="B308" t="n">
@@ -49940,7 +50349,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>コオリ</t>
+          <t>ゲン</t>
         </is>
       </c>
       <c r="B309" t="n">
@@ -49948,19 +50357,19 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>サトル</t>
+          <t>コオリ</t>
         </is>
       </c>
       <c r="B310" t="n">
@@ -49968,19 +50377,19 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>ザッキー</t>
+          <t>サトル</t>
         </is>
       </c>
       <c r="B311" t="n">
@@ -49988,19 +50397,19 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>シゲ</t>
+          <t>ザッキー</t>
         </is>
       </c>
       <c r="B312" t="n">
@@ -50008,19 +50417,19 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>シュン</t>
+          <t>シゲ</t>
         </is>
       </c>
       <c r="B313" t="n">
@@ -50028,19 +50437,19 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>シュンヤ</t>
+          <t>シュン</t>
         </is>
       </c>
       <c r="B314" t="n">
@@ -50048,19 +50457,19 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>ジャッキー</t>
+          <t>シュンヤ</t>
         </is>
       </c>
       <c r="B315" t="n">
@@ -50068,19 +50477,19 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>ジョーカー</t>
+          <t>ジャッキー</t>
         </is>
       </c>
       <c r="B316" t="n">
@@ -50088,19 +50497,19 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>タカ</t>
+          <t>ジョーカー</t>
         </is>
       </c>
       <c r="B317" t="n">
@@ -50108,19 +50517,19 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>タカス</t>
+          <t>タカ</t>
         </is>
       </c>
       <c r="B318" t="n">
@@ -50128,19 +50537,19 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>タカ御一行</t>
+          <t>タカス</t>
         </is>
       </c>
       <c r="B319" t="n">
@@ -50148,19 +50557,19 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>ダイキ</t>
+          <t>タカ御一行</t>
         </is>
       </c>
       <c r="B320" t="n">
@@ -50168,19 +50577,19 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>ダイゴ</t>
+          <t>ダイキ</t>
         </is>
       </c>
       <c r="B321" t="n">
@@ -50188,19 +50597,19 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>ダイチ</t>
+          <t>ダイゴ</t>
         </is>
       </c>
       <c r="B322" t="n">
@@ -50208,19 +50617,19 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>ツシマ</t>
+          <t>ダイチ</t>
         </is>
       </c>
       <c r="B323" t="n">
@@ -50228,19 +50637,19 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>ツボ</t>
+          <t>ツシマ</t>
         </is>
       </c>
       <c r="B324" t="n">
@@ -50248,19 +50657,19 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>テクノっち</t>
+          <t>ツボ</t>
         </is>
       </c>
       <c r="B325" t="n">
@@ -50280,7 +50689,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>テクノとポチ</t>
+          <t>テクノっち</t>
         </is>
       </c>
       <c r="B326" t="n">
@@ -50288,19 +50697,19 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>テクノ＆てるくん＆イブオ</t>
+          <t>テクノとポチ</t>
         </is>
       </c>
       <c r="B327" t="n">
@@ -50308,19 +50717,19 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>トニー・トニー・チョッパー</t>
+          <t>テクノ＆てるくん＆イブオ</t>
         </is>
       </c>
       <c r="B328" t="n">
@@ -50328,19 +50737,19 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>ナカヤマヤ</t>
+          <t>トニー・トニー・チョッパー</t>
         </is>
       </c>
       <c r="B329" t="n">
@@ -50348,19 +50757,19 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>ニト</t>
+          <t>ナカヤマヤ</t>
         </is>
       </c>
       <c r="B330" t="n">
@@ -50368,19 +50777,19 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>ニャンまげ</t>
+          <t>ニト</t>
         </is>
       </c>
       <c r="B331" t="n">
@@ -50388,19 +50797,19 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>ビコー</t>
+          <t>ニャンまげ</t>
         </is>
       </c>
       <c r="B332" t="n">
@@ -50408,19 +50817,19 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>フジ</t>
+          <t>ビコー</t>
         </is>
       </c>
       <c r="B333" t="n">
@@ -50428,19 +50837,19 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>ボンタ</t>
+          <t>フジ</t>
         </is>
       </c>
       <c r="B334" t="n">
@@ -50448,19 +50857,19 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>ポチ</t>
+          <t>ボンタ</t>
         </is>
       </c>
       <c r="B335" t="n">
@@ -50468,19 +50877,19 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>マイナス</t>
+          <t>ポチ</t>
         </is>
       </c>
       <c r="B336" t="n">
@@ -50488,19 +50897,19 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>マサ</t>
+          <t>マイナス</t>
         </is>
       </c>
       <c r="B337" t="n">
@@ -50508,19 +50917,19 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>マッチョ</t>
+          <t>マサ</t>
         </is>
       </c>
       <c r="B338" t="n">
@@ -50528,19 +50937,19 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>マナティ</t>
+          <t>マッチョ</t>
         </is>
       </c>
       <c r="B339" t="n">
@@ -50548,19 +50957,19 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>ミスター工事マン</t>
+          <t>マナティ</t>
         </is>
       </c>
       <c r="B340" t="n">
@@ -50568,19 +50977,19 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>ミッシ</t>
+          <t>ミカミと仲間たち</t>
         </is>
       </c>
       <c r="B341" t="n">
@@ -50588,19 +50997,19 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>ミッチー</t>
+          <t>ミスター工事マン</t>
         </is>
       </c>
       <c r="B342" t="n">
@@ -50608,19 +51017,19 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>ミルコ</t>
+          <t>ミッシ</t>
         </is>
       </c>
       <c r="B343" t="n">
@@ -50628,19 +51037,19 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>モジャ</t>
+          <t>ミッチー</t>
         </is>
       </c>
       <c r="B344" t="n">
@@ -50648,19 +51057,19 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>ヤノちゃん</t>
+          <t>ミルコ</t>
         </is>
       </c>
       <c r="B345" t="n">
@@ -50668,19 +51077,19 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>ヤマ</t>
+          <t>モジャ</t>
         </is>
       </c>
       <c r="B346" t="n">
@@ -50688,19 +51097,19 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>ユウ</t>
+          <t>ヤノちゃん</t>
         </is>
       </c>
       <c r="B347" t="n">
@@ -50708,19 +51117,19 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>ユキ</t>
+          <t>ヤマ</t>
         </is>
       </c>
       <c r="B348" t="n">
@@ -50728,19 +51137,19 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>ユッキー</t>
+          <t>ユウ</t>
         </is>
       </c>
       <c r="B349" t="n">
@@ -50748,19 +51157,19 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>ヨシヤ</t>
+          <t>ユキ</t>
         </is>
       </c>
       <c r="B350" t="n">
@@ -50768,19 +51177,19 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>リク</t>
+          <t>ユッキー</t>
         </is>
       </c>
       <c r="B351" t="n">
@@ -50788,19 +51197,19 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>リョウ</t>
+          <t>ヨシヤ</t>
         </is>
       </c>
       <c r="B352" t="n">
@@ -50820,7 +51229,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>リン</t>
+          <t>リク</t>
         </is>
       </c>
       <c r="B353" t="n">
@@ -50828,19 +51237,19 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>ロタポジ</t>
+          <t>リョウ</t>
         </is>
       </c>
       <c r="B354" t="n">
@@ -50848,19 +51257,19 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>ローズ</t>
+          <t>リン</t>
         </is>
       </c>
       <c r="B355" t="n">
@@ -50868,19 +51277,19 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>僕と私</t>
+          <t>ロタポジ</t>
         </is>
       </c>
       <c r="B356" t="n">
@@ -50888,19 +51297,19 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>名無し</t>
+          <t>ローズ</t>
         </is>
       </c>
       <c r="B357" t="n">
@@ -50908,19 +51317,19 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>変態マッスル</t>
+          <t>僕と私</t>
         </is>
       </c>
       <c r="B358" t="n">
@@ -50928,19 +51337,19 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>大塚</t>
+          <t>名無し</t>
         </is>
       </c>
       <c r="B359" t="n">
@@ -50948,19 +51357,19 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>天我迅</t>
+          <t>変態マッスル</t>
         </is>
       </c>
       <c r="B360" t="n">
@@ -50968,19 +51377,19 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>女子三人衆</t>
+          <t>大塚</t>
         </is>
       </c>
       <c r="B361" t="n">
@@ -50988,19 +51397,19 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>正装しん</t>
+          <t>天我迅</t>
         </is>
       </c>
       <c r="B362" t="n">
@@ -51008,19 +51417,19 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>海砂利水魚</t>
+          <t>女子三人衆</t>
         </is>
       </c>
       <c r="B363" t="n">
@@ -51028,19 +51437,19 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>田中</t>
+          <t>正装しん</t>
         </is>
       </c>
       <c r="B364" t="n">
@@ -51048,19 +51457,19 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>番</t>
+          <t>海砂利水魚</t>
         </is>
       </c>
       <c r="B365" t="n">
@@ -51068,19 +51477,19 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>絶</t>
+          <t>田中</t>
         </is>
       </c>
       <c r="B366" t="n">
@@ -51088,19 +51497,19 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>絶ちゃん</t>
+          <t>番</t>
         </is>
       </c>
       <c r="B367" t="n">
@@ -51108,19 +51517,19 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>美優</t>
+          <t>絶</t>
         </is>
       </c>
       <c r="B368" t="n">
@@ -51128,19 +51537,19 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>赤ちゃん</t>
+          <t>絶ちゃん</t>
         </is>
       </c>
       <c r="B369" t="n">
@@ -51148,30 +51557,70 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
+          <t>美優</t>
+        </is>
+      </c>
+      <c r="B370" t="n">
+        <v>1</v>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>赤ちゃん</t>
+        </is>
+      </c>
+      <c r="B371" t="n">
+        <v>1</v>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
           <t>高田</t>
         </is>
       </c>
-      <c r="B370" t="n">
-        <v>1</v>
-      </c>
-      <c r="C370" t="inlineStr">
+      <c r="B372" t="n">
+        <v>1</v>
+      </c>
+      <c r="C372" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="D370" t="inlineStr">
+      <c r="D372" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
@@ -51215,10 +51664,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C2" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3">
@@ -51228,10 +51677,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C3" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4">
@@ -51363,10 +51812,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
@@ -51584,10 +52033,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22">
@@ -51597,10 +52046,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C22" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23">
@@ -51701,13 +52150,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="C3" t="n">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="D3" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>

--- a/bbs_log.xlsx
+++ b/bbs_log.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H530"/>
+  <dimension ref="A1:H540"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16945,7 +16945,6 @@
           <t>ひがん</t>
         </is>
       </c>
-      <c r="E525" t="inlineStr"/>
       <c r="F525" t="inlineStr">
         <is>
           <t>ちいかわ観て</t>
@@ -16956,7 +16955,6 @@
           <t>来ました♪</t>
         </is>
       </c>
-      <c r="H525" t="inlineStr"/>
     </row>
     <row r="526">
       <c r="A526" t="n">
@@ -16977,7 +16975,6 @@
           <t>bee</t>
         </is>
       </c>
-      <c r="E526" t="inlineStr"/>
       <c r="F526" t="inlineStr">
         <is>
           <t>遊びに</t>
@@ -16988,7 +16985,6 @@
           <t>来ましたブン♪</t>
         </is>
       </c>
-      <c r="H526" t="inlineStr"/>
     </row>
     <row r="527">
       <c r="A527" t="n">
@@ -17009,7 +17005,6 @@
           <t>ろくじ</t>
         </is>
       </c>
-      <c r="E527" t="inlineStr"/>
       <c r="F527" t="inlineStr">
         <is>
           <t>飲みに</t>
@@ -17020,7 +17015,6 @@
           <t>来ました！</t>
         </is>
       </c>
-      <c r="H527" t="inlineStr"/>
     </row>
     <row r="528">
       <c r="A528" t="n">
@@ -17041,7 +17035,6 @@
           <t>まみ</t>
         </is>
       </c>
-      <c r="E528" t="inlineStr"/>
       <c r="F528" t="inlineStr">
         <is>
           <t>初めて</t>
@@ -17052,7 +17045,6 @@
           <t>新宿からきました！</t>
         </is>
       </c>
-      <c r="H528" t="inlineStr"/>
     </row>
     <row r="529">
       <c r="A529" t="n">
@@ -17073,7 +17065,6 @@
           <t>ミカミと仲間たち</t>
         </is>
       </c>
-      <c r="E529" t="inlineStr"/>
       <c r="F529" t="inlineStr">
         <is>
           <t>新規さん連れて</t>
@@ -17084,7 +17075,6 @@
           <t>きたよー</t>
         </is>
       </c>
-      <c r="H529" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" t="n">
@@ -17138,6 +17128,347 @@
         </is>
       </c>
     </row>
+    <row r="531">
+      <c r="A531" t="n">
+        <v>27787</v>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>18:43:10</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>ひがん</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr"/>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>おーぷんまえ</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>来ました！</t>
+        </is>
+      </c>
+      <c r="H531" t="inlineStr"/>
+    </row>
+    <row r="532">
+      <c r="A532" t="n">
+        <v>27789</v>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>18:45:27</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>さとる</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr"/>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>オープン前に</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>きちゃいました</t>
+        </is>
+      </c>
+      <c r="H532" t="inlineStr"/>
+    </row>
+    <row r="533">
+      <c r="A533" t="n">
+        <v>27791</v>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>20:19:24</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>ゆずきち</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr"/>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>しごおわ</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>きたよー♪</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr"/>
+    </row>
+    <row r="534">
+      <c r="A534" t="n">
+        <v>27793</v>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>21:23:36</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>コマ、ひろし、ゆうじ</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr"/>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>3人で</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>きたよー♪</t>
+        </is>
+      </c>
+      <c r="H534" t="inlineStr"/>
+    </row>
+    <row r="535">
+      <c r="A535" t="n">
+        <v>27795</v>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>00:12:25</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>テクノっち</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr"/>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>ガパオ持って</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>きたよーん</t>
+        </is>
+      </c>
+      <c r="H535" t="inlineStr"/>
+    </row>
+    <row r="536">
+      <c r="A536" t="n">
+        <v>27797</v>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>01:38:44</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>まいまい</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr"/>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>きたよー♪</t>
+        </is>
+      </c>
+      <c r="H536" t="inlineStr"/>
+    </row>
+    <row r="537">
+      <c r="A537" t="n">
+        <v>27798</v>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>01:39:38</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>ゆうくん</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr"/>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>ひさしぶりに遊びに</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>きたお</t>
+        </is>
+      </c>
+      <c r="H537" t="inlineStr"/>
+    </row>
+    <row r="538">
+      <c r="A538" t="n">
+        <v>27801</v>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>02:55:44</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>ありす、みやび</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr"/>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>女子二人で</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>来ちゃった＾＾</t>
+        </is>
+      </c>
+      <c r="H538" t="inlineStr"/>
+    </row>
+    <row r="539">
+      <c r="A539" t="n">
+        <v>27803</v>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>03:16:25</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>sho</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr"/>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>初めて</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>来ました</t>
+        </is>
+      </c>
+      <c r="H539" t="inlineStr"/>
+    </row>
+    <row r="540">
+      <c r="A540" t="n">
+        <v>27805</v>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>04:11:38</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>ツッコミはお任せのShizu / えちえち裏垢女子のモカチ</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>★☆★朝までアゲアゲの水曜日営業が始まるわよ♪★☆★</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>本日9月16日の営業時間は♪
+オープン14:00！ラスト5:00なのよ☆
+担当は
+ツッコミはお任せのShizu
+えちえち裏垢女子のモカチ
+なのよ♪
+どんな季節でも★BAMBITCH★は色気ムンムンで暑すぎる♪
+バンビッチでおもいっきりはじけちゃって（笑）
+精力は無くても性欲がある！？
+大人の憩いと禁断サークル盛りだくさん！
+憩いと交流の魔性の遊び場バンビッチは素敵な出会いを 提供いたします（笑)☆☆
+おつまみ等の持ち込みは自由なのでみんなで持ち寄ってお近づきのきっかけにどうぞ♪
+強制や無理強いは一切ございませんので楽しく遊びましょう♪
+宇都宮市宿郷1−12−9　カサブランカビル5F</t>
+        </is>
+      </c>
+      <c r="H540" t="inlineStr">
+        <is>
+          <t>img20260916041138.jpg</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17149,7 +17480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I628"/>
+  <dimension ref="A1:I640"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44167,6 +44498,522 @@
       <c r="I628" t="inlineStr">
         <is>
           <t>きたよー</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>18:43:10</t>
+        </is>
+      </c>
+      <c r="D629" t="n">
+        <v>27787</v>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>ひがん</t>
+        </is>
+      </c>
+      <c r="F629" t="n">
+        <v>18</v>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>ひがん</t>
+        </is>
+      </c>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>おーぷんまえ</t>
+        </is>
+      </c>
+      <c r="I629" t="inlineStr">
+        <is>
+          <t>来ました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>18:45:27</t>
+        </is>
+      </c>
+      <c r="D630" t="n">
+        <v>27789</v>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>さとる</t>
+        </is>
+      </c>
+      <c r="F630" t="n">
+        <v>2</v>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>さとる</t>
+        </is>
+      </c>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>オープン前に</t>
+        </is>
+      </c>
+      <c r="I630" t="inlineStr">
+        <is>
+          <t>きちゃいました</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>20:19:24</t>
+        </is>
+      </c>
+      <c r="D631" t="n">
+        <v>27791</v>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>ゆずきち</t>
+        </is>
+      </c>
+      <c r="F631" t="n">
+        <v>8</v>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>ゆずきち</t>
+        </is>
+      </c>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>しごおわ</t>
+        </is>
+      </c>
+      <c r="I631" t="inlineStr">
+        <is>
+          <t>きたよー♪</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>21:23:36</t>
+        </is>
+      </c>
+      <c r="D632" t="n">
+        <v>27793</v>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>コマ</t>
+        </is>
+      </c>
+      <c r="F632" t="n">
+        <v>1</v>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>コマ、ひろし、ゆうじ</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>3人で</t>
+        </is>
+      </c>
+      <c r="I632" t="inlineStr">
+        <is>
+          <t>きたよー♪</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>21:23:36</t>
+        </is>
+      </c>
+      <c r="D633" t="n">
+        <v>27793</v>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>ひろし</t>
+        </is>
+      </c>
+      <c r="F633" t="n">
+        <v>1</v>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>コマ、ひろし、ゆうじ</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>3人で</t>
+        </is>
+      </c>
+      <c r="I633" t="inlineStr">
+        <is>
+          <t>きたよー♪</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>21:23:36</t>
+        </is>
+      </c>
+      <c r="D634" t="n">
+        <v>27793</v>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>ゆうじ</t>
+        </is>
+      </c>
+      <c r="F634" t="n">
+        <v>1</v>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>コマ、ひろし、ゆうじ</t>
+        </is>
+      </c>
+      <c r="H634" t="inlineStr">
+        <is>
+          <t>3人で</t>
+        </is>
+      </c>
+      <c r="I634" t="inlineStr">
+        <is>
+          <t>きたよー♪</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>00:12:25</t>
+        </is>
+      </c>
+      <c r="D635" t="n">
+        <v>27795</v>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>テクノっち</t>
+        </is>
+      </c>
+      <c r="F635" t="n">
+        <v>2</v>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>テクノっち</t>
+        </is>
+      </c>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>ガパオ持って</t>
+        </is>
+      </c>
+      <c r="I635" t="inlineStr">
+        <is>
+          <t>きたよーん</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>01:38:44</t>
+        </is>
+      </c>
+      <c r="D636" t="n">
+        <v>27797</v>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>まいまい</t>
+        </is>
+      </c>
+      <c r="F636" t="n">
+        <v>9</v>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>まいまい</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="I636" t="inlineStr">
+        <is>
+          <t>きたよー♪</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>01:39:38</t>
+        </is>
+      </c>
+      <c r="D637" t="n">
+        <v>27798</v>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>ゆうくん</t>
+        </is>
+      </c>
+      <c r="F637" t="n">
+        <v>2</v>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>ゆうくん</t>
+        </is>
+      </c>
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>ひさしぶりに遊びに</t>
+        </is>
+      </c>
+      <c r="I637" t="inlineStr">
+        <is>
+          <t>きたお</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>02:55:44</t>
+        </is>
+      </c>
+      <c r="D638" t="n">
+        <v>27801</v>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>ありす</t>
+        </is>
+      </c>
+      <c r="F638" t="n">
+        <v>1</v>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>ありす、みやび</t>
+        </is>
+      </c>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>女子二人で</t>
+        </is>
+      </c>
+      <c r="I638" t="inlineStr">
+        <is>
+          <t>来ちゃった＾＾</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>02:55:44</t>
+        </is>
+      </c>
+      <c r="D639" t="n">
+        <v>27801</v>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>みやび</t>
+        </is>
+      </c>
+      <c r="F639" t="n">
+        <v>1</v>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>ありす、みやび</t>
+        </is>
+      </c>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>女子二人で</t>
+        </is>
+      </c>
+      <c r="I639" t="inlineStr">
+        <is>
+          <t>来ちゃった＾＾</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>03:16:25</t>
+        </is>
+      </c>
+      <c r="D640" t="n">
+        <v>27803</v>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>sho</t>
+        </is>
+      </c>
+      <c r="F640" t="n">
+        <v>1</v>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>sho</t>
+        </is>
+      </c>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>初めて</t>
+        </is>
+      </c>
+      <c r="I640" t="inlineStr">
+        <is>
+          <t>来ました</t>
         </is>
       </c>
     </row>
@@ -44181,7 +45028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D372"/>
+  <dimension ref="A1:D378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44213,7 +45060,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -44222,7 +45069,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
@@ -44309,27 +45156,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>のんのん</t>
+          <t>まいまい</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>まいまい</t>
+          <t>のんのん</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -44337,39 +45184,39 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>なお</t>
+          <t>ゆずきち</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ゆずきち</t>
+          <t>なお</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -44377,12 +45224,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -45529,7 +46376,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>さとるん</t>
+          <t>さとる</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -45537,19 +46384,19 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>しゅん</t>
+          <t>さとるん</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -45557,19 +46404,19 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>しょうた</t>
+          <t>しゅん</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -45577,19 +46424,19 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>しーたん</t>
+          <t>しょうた</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -45597,19 +46444,19 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>すーたく</t>
+          <t>しーたん</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -45622,14 +46469,14 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>たかやまん</t>
+          <t>すーたく</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -45637,19 +46484,19 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>たくや</t>
+          <t>たかやまん</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -45657,19 +46504,19 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>たつや</t>
+          <t>たくや</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -45682,14 +46529,14 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ちゃそたけ</t>
+          <t>たつや</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -45697,19 +46544,19 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>とし</t>
+          <t>ちゃそたけ</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -45717,19 +46564,19 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>なな</t>
+          <t>とし</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -45737,19 +46584,19 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>なまがき</t>
+          <t>なな</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -45757,19 +46604,19 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ぶりちゃん</t>
+          <t>なまがき</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -45777,19 +46624,19 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ぽちゃりす組</t>
+          <t>ぶりちゃん</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -45797,19 +46644,19 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>まい</t>
+          <t>ぽちゃりす組</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -45817,19 +46664,19 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>まなみ</t>
+          <t>まい</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -45837,19 +46684,19 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>まゆ</t>
+          <t>まなみ</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -45857,19 +46704,19 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>まろ</t>
+          <t>まゆ</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -45877,19 +46724,19 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>みれい</t>
+          <t>まろ</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -45897,19 +46744,19 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>めい</t>
+          <t>みれい</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -45917,19 +46764,19 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>もっぷ</t>
+          <t>めい</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -45937,19 +46784,19 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>やえ</t>
+          <t>もっぷ</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -45957,19 +46804,19 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>よしやん</t>
+          <t>やえ</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -45982,14 +46829,14 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>よっしー</t>
+          <t>ゆうくん</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -45997,19 +46844,19 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>よっち</t>
+          <t>よしやん</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -46017,19 +46864,19 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>りお</t>
+          <t>よっしー</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -46042,14 +46889,14 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>りゅう</t>
+          <t>よっち</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -46057,19 +46904,19 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>りょう</t>
+          <t>りお</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -46077,19 +46924,19 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>オカニー</t>
+          <t>りゅう</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -46097,19 +46944,19 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>キムとドMまゆ</t>
+          <t>りょう</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -46117,19 +46964,19 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ケン</t>
+          <t>オカニー</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -46137,19 +46984,19 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>タク</t>
+          <t>キムとドMまゆ</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -46157,19 +47004,19 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>タケ</t>
+          <t>ケン</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -46177,19 +47024,19 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>マッスル</t>
+          <t>タク</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -46197,19 +47044,19 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ミコト</t>
+          <t>タケ</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -46217,19 +47064,19 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>愛とスケベの戦士</t>
+          <t>テクノっち</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -46237,47 +47084,47 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>マッスル</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>HGN</t>
+          <t>ミコト</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -46289,27 +47136,27 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>JPTR</t>
+          <t>愛とスケベの戦士</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -46317,19 +47164,19 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>KUMA</t>
+          <t>HGN</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -46337,19 +47184,19 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>JPTR</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -46357,19 +47204,19 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>NMGK</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -46377,19 +47224,19 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>N氏御一行</t>
+          <t>KUMA</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -46397,19 +47244,19 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>STR</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -46417,19 +47264,19 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>NMGK</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -46437,19 +47284,19 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>TARU</t>
+          <t>N氏御一行</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -46457,19 +47304,19 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>STR</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -46477,19 +47324,19 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Tやま</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -46497,19 +47344,19 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>TARU</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -46517,19 +47364,19 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>YZK</t>
+          <t>TT</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -46537,19 +47384,19 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>hikari</t>
+          <t>Tやま</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -46557,19 +47404,19 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>nuri</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -46577,19 +47424,19 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>YZK</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -46597,19 +47444,19 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>★Zakk★</t>
+          <t>hikari</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -46617,19 +47464,19 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>あいちゃん</t>
+          <t>nuri</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -46637,19 +47484,19 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>あき</t>
+          <t>sho</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -46657,19 +47504,19 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>あさみ</t>
+          <t>−</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -46677,19 +47524,19 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>あさみん</t>
+          <t>★Zakk★</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -46697,19 +47544,19 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>あす</t>
+          <t>あいちゃん</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -46717,19 +47564,19 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>あっくん</t>
+          <t>あき</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -46737,19 +47584,19 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>あにー</t>
+          <t>あさみ</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -46757,19 +47604,19 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>あまねちゃん</t>
+          <t>あさみん</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -46777,19 +47624,19 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>いおり</t>
+          <t>あす</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -46797,19 +47644,19 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>いけちゃん</t>
+          <t>あっくん</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -46817,19 +47664,19 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>いぶお</t>
+          <t>あにー</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -46837,19 +47684,19 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>うらら</t>
+          <t>あまねちゃん</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -46857,19 +47704,19 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>えぬ</t>
+          <t>ありす</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -46877,19 +47724,19 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>える</t>
+          <t>いおり</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -46897,19 +47744,19 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>おじき</t>
+          <t>いけちゃん</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -46917,19 +47764,19 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>おじきち</t>
+          <t>いぶお</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -46937,19 +47784,19 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>おすー</t>
+          <t>うらら</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -46957,19 +47804,19 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>おちんぽベルセルク</t>
+          <t>えぬ</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -46977,19 +47824,19 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>おにゃん</t>
+          <t>える</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -46997,19 +47844,19 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>おにゃんにゃん</t>
+          <t>おじき</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -47017,19 +47864,19 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>かける</t>
+          <t>おじきち</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -47037,19 +47884,19 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>かずき</t>
+          <t>おすー</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -47057,19 +47904,19 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>かず＆TKC＆のんのん</t>
+          <t>おちんぽベルセルク</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -47077,19 +47924,19 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>かな(絶ちゃん</t>
+          <t>おにゃん</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -47097,19 +47944,19 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>かな(絶ちゃん)/おっつん</t>
+          <t>おにゃんにゃん</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -47117,19 +47964,19 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>がん</t>
+          <t>かける</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -47137,19 +47984,19 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>きむさん</t>
+          <t>かずき</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -47157,19 +48004,19 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>きむむ</t>
+          <t>かず＆TKC＆のんのん</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -47177,19 +48024,19 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>きむら</t>
+          <t>かな(絶ちゃん</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -47197,19 +48044,19 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>きょうちゃん</t>
+          <t>かな(絶ちゃん)/おっつん</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -47217,19 +48064,19 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>きんたまよ</t>
+          <t>がん</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -47237,19 +48084,19 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>くま</t>
+          <t>きむさん</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -47257,19 +48104,19 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ぐっちゃん</t>
+          <t>きむむ</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -47277,19 +48124,19 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>けい</t>
+          <t>きむら</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -47297,19 +48144,19 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>けいちゃん</t>
+          <t>きょうちゃん</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -47317,19 +48164,19 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>けんけん</t>
+          <t>きんたまよ</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -47337,19 +48184,19 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>げん</t>
+          <t>くま</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -47357,19 +48204,19 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>こう</t>
+          <t>ぐっちゃん</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -47377,19 +48224,19 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>こうた</t>
+          <t>けい</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -47397,19 +48244,19 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>こてつ</t>
+          <t>けいちゃん</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -47417,19 +48264,19 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ことねえ</t>
+          <t>けんけん</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -47437,19 +48284,19 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ことり</t>
+          <t>げん</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -47457,19 +48304,19 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ごん</t>
+          <t>こう</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -47477,19 +48324,19 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>さかもと</t>
+          <t>こうた</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -47497,19 +48344,19 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>さくら</t>
+          <t>こてつ</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -47517,19 +48364,19 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>さとりゅ</t>
+          <t>ことねえ</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -47537,19 +48384,19 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>さとる</t>
+          <t>ことり</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -47557,19 +48404,19 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>さな</t>
+          <t>ごん</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -47577,19 +48424,19 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>さない</t>
+          <t>さかもと</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -47597,19 +48444,19 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>さや</t>
+          <t>さくら</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -47617,19 +48464,19 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>しずか</t>
+          <t>さとりゅ</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -47637,19 +48484,19 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>しりゅう</t>
+          <t>さな</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -47657,19 +48504,19 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>じん</t>
+          <t>さない</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -47677,19 +48524,19 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>せいら</t>
+          <t>さや</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -47697,19 +48544,19 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>たいせー</t>
+          <t>しずか</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -47717,19 +48564,19 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>たか</t>
+          <t>しりゅう</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -47737,19 +48584,19 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>たかし</t>
+          <t>じん</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -47769,7 +48616,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>たかち</t>
+          <t>せいら</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -47777,19 +48624,19 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>たく</t>
+          <t>たいせー</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -47797,19 +48644,19 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>たけ</t>
+          <t>たか</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -47817,19 +48664,19 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>たけし</t>
+          <t>たかし</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -47837,19 +48684,19 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>たつ</t>
+          <t>たかち</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -47857,19 +48704,19 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>たます</t>
+          <t>たく</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -47877,19 +48724,19 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>たろー</t>
+          <t>たけ</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -47897,19 +48744,19 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>だいさく</t>
+          <t>たけし</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -47917,19 +48764,19 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>だいざく</t>
+          <t>たつ</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -47937,19 +48784,19 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>だいち</t>
+          <t>たます</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -47957,19 +48804,19 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ちぇちぇ</t>
+          <t>たろー</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -47977,19 +48824,19 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ちっち</t>
+          <t>だいさく</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -47997,19 +48844,19 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>てくのっち</t>
+          <t>だいざく</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -48017,19 +48864,19 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>てっちゃん</t>
+          <t>だいち</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -48037,19 +48884,19 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>てつ</t>
+          <t>ちぇちぇ</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -48057,19 +48904,19 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>てつじ</t>
+          <t>ちっち</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -48077,19 +48924,19 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>てる</t>
+          <t>てくのっち</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -48097,19 +48944,19 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>でかかわ</t>
+          <t>てっちゃん</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -48117,19 +48964,19 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>ででたゃ</t>
+          <t>てつ</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -48137,19 +48984,19 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>とうや</t>
+          <t>てつじ</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -48157,19 +49004,19 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>とおちゃん</t>
+          <t>てる</t>
         </is>
       </c>
       <c r="B200" t="n">
@@ -48177,19 +49024,19 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>とっしー</t>
+          <t>でかかわ</t>
         </is>
       </c>
       <c r="B201" t="n">
@@ -48197,19 +49044,19 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>とも</t>
+          <t>ででたゃ</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -48217,19 +49064,19 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>ともち</t>
+          <t>とうや</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -48237,19 +49084,19 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>ともひろ</t>
+          <t>とおちゃん</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -48257,19 +49104,19 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>ともや</t>
+          <t>とっしー</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -48277,19 +49124,19 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>ともゆき</t>
+          <t>とも</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -48297,19 +49144,19 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>とーり</t>
+          <t>ともち</t>
         </is>
       </c>
       <c r="B207" t="n">
@@ -48317,19 +49164,19 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>どえむちゃん</t>
+          <t>ともひろ</t>
         </is>
       </c>
       <c r="B208" t="n">
@@ -48337,19 +49184,19 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>ながとも</t>
+          <t>ともや</t>
         </is>
       </c>
       <c r="B209" t="n">
@@ -48357,19 +49204,19 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>なべ</t>
+          <t>ともゆき</t>
         </is>
       </c>
       <c r="B210" t="n">
@@ -48377,19 +49224,19 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>にこちん</t>
+          <t>とーり</t>
         </is>
       </c>
       <c r="B211" t="n">
@@ -48397,19 +49244,19 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>にゃんまげ</t>
+          <t>どえむちゃん</t>
         </is>
       </c>
       <c r="B212" t="n">
@@ -48417,19 +49264,19 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>にょ</t>
+          <t>ながとも</t>
         </is>
       </c>
       <c r="B213" t="n">
@@ -48437,19 +49284,19 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>ねここ</t>
+          <t>なべ</t>
         </is>
       </c>
       <c r="B214" t="n">
@@ -48457,19 +49304,19 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>のぼ</t>
+          <t>にこちん</t>
         </is>
       </c>
       <c r="B215" t="n">
@@ -48477,19 +49324,19 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>のり</t>
+          <t>にゃんまげ</t>
         </is>
       </c>
       <c r="B216" t="n">
@@ -48497,19 +49344,19 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>はち</t>
+          <t>にょ</t>
         </is>
       </c>
       <c r="B217" t="n">
@@ -48517,19 +49364,19 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>はな</t>
+          <t>ねここ</t>
         </is>
       </c>
       <c r="B218" t="n">
@@ -48537,19 +49384,19 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>はなちゃん</t>
+          <t>のぼ</t>
         </is>
       </c>
       <c r="B219" t="n">
@@ -48557,19 +49404,19 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>はなまる</t>
+          <t>のり</t>
         </is>
       </c>
       <c r="B220" t="n">
@@ -48577,19 +49424,19 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>はんまー</t>
+          <t>はち</t>
         </is>
       </c>
       <c r="B221" t="n">
@@ -48597,19 +49444,19 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>ひがんちゃん</t>
+          <t>はな</t>
         </is>
       </c>
       <c r="B222" t="n">
@@ -48617,19 +49464,19 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>ひったん</t>
+          <t>はなちゃん</t>
         </is>
       </c>
       <c r="B223" t="n">
@@ -48637,19 +49484,19 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>ひろとも</t>
+          <t>はなまる</t>
         </is>
       </c>
       <c r="B224" t="n">
@@ -48657,19 +49504,19 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>ふく</t>
+          <t>はんまー</t>
         </is>
       </c>
       <c r="B225" t="n">
@@ -48677,19 +49524,19 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>ふくちゃん</t>
+          <t>ひがんちゃん</t>
         </is>
       </c>
       <c r="B226" t="n">
@@ -48697,19 +49544,19 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>ふみ</t>
+          <t>ひったん</t>
         </is>
       </c>
       <c r="B227" t="n">
@@ -48717,19 +49564,19 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>ぷらぐいん</t>
+          <t>ひろし</t>
         </is>
       </c>
       <c r="B228" t="n">
@@ -48737,19 +49584,19 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>べー</t>
+          <t>ひろとも</t>
         </is>
       </c>
       <c r="B229" t="n">
@@ -48757,19 +49604,19 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>ぺぺ</t>
+          <t>ふく</t>
         </is>
       </c>
       <c r="B230" t="n">
@@ -48777,19 +49624,19 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>まいまいまいまい</t>
+          <t>ふくちゃん</t>
         </is>
       </c>
       <c r="B231" t="n">
@@ -48809,7 +49656,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>まいまいん</t>
+          <t>ふみ</t>
         </is>
       </c>
       <c r="B232" t="n">
@@ -48829,7 +49676,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>まおし</t>
+          <t>ぷらぐいん</t>
         </is>
       </c>
       <c r="B233" t="n">
@@ -48837,19 +49684,19 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>ましゅ社長</t>
+          <t>べー</t>
         </is>
       </c>
       <c r="B234" t="n">
@@ -48857,19 +49704,19 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>ますみ</t>
+          <t>ぺぺ</t>
         </is>
       </c>
       <c r="B235" t="n">
@@ -48877,19 +49724,19 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>まっする</t>
+          <t>まいまいまいまい</t>
         </is>
       </c>
       <c r="B236" t="n">
@@ -48897,19 +49744,19 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>まっぴー</t>
+          <t>まいまいん</t>
         </is>
       </c>
       <c r="B237" t="n">
@@ -48917,19 +49764,19 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>まな</t>
+          <t>まおし</t>
         </is>
       </c>
       <c r="B238" t="n">
@@ -48937,19 +49784,19 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>まみ</t>
+          <t>ましゅ社長</t>
         </is>
       </c>
       <c r="B239" t="n">
@@ -48957,19 +49804,19 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>まや</t>
+          <t>ますみ</t>
         </is>
       </c>
       <c r="B240" t="n">
@@ -48977,19 +49824,19 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>まり</t>
+          <t>まっする</t>
         </is>
       </c>
       <c r="B241" t="n">
@@ -48997,19 +49844,19 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>まりん</t>
+          <t>まっぴー</t>
         </is>
       </c>
       <c r="B242" t="n">
@@ -49017,19 +49864,19 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>まー</t>
+          <t>まな</t>
         </is>
       </c>
       <c r="B243" t="n">
@@ -49037,19 +49884,19 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>まーさん</t>
+          <t>まみ</t>
         </is>
       </c>
       <c r="B244" t="n">
@@ -49057,19 +49904,19 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>まーちゃん</t>
+          <t>まや</t>
         </is>
       </c>
       <c r="B245" t="n">
@@ -49077,19 +49924,19 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>みかん</t>
+          <t>まり</t>
         </is>
       </c>
       <c r="B246" t="n">
@@ -49097,19 +49944,19 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>みずき</t>
+          <t>まりん</t>
         </is>
       </c>
       <c r="B247" t="n">
@@ -49117,19 +49964,19 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>みちゃ</t>
+          <t>まー</t>
         </is>
       </c>
       <c r="B248" t="n">
@@ -49137,19 +49984,19 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>みっちー</t>
+          <t>まーさん</t>
         </is>
       </c>
       <c r="B249" t="n">
@@ -49157,19 +50004,19 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>みなつちん</t>
+          <t>まーちゃん</t>
         </is>
       </c>
       <c r="B250" t="n">
@@ -49177,19 +50024,19 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>みみ</t>
+          <t>みかん</t>
         </is>
       </c>
       <c r="B251" t="n">
@@ -49197,19 +50044,19 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>みゆき</t>
+          <t>みずき</t>
         </is>
       </c>
       <c r="B252" t="n">
@@ -49217,19 +50064,19 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>みらい</t>
+          <t>みちゃ</t>
         </is>
       </c>
       <c r="B253" t="n">
@@ -49237,19 +50084,19 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>みるこ</t>
+          <t>みっちー</t>
         </is>
       </c>
       <c r="B254" t="n">
@@ -49257,19 +50104,19 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>みん</t>
+          <t>みなつちん</t>
         </is>
       </c>
       <c r="B255" t="n">
@@ -49277,19 +50124,19 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>みー</t>
+          <t>みみ</t>
         </is>
       </c>
       <c r="B256" t="n">
@@ -49297,19 +50144,19 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>みーみ</t>
+          <t>みやび</t>
         </is>
       </c>
       <c r="B257" t="n">
@@ -49317,19 +50164,19 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>もかちんぽぽ</t>
+          <t>みゆき</t>
         </is>
       </c>
       <c r="B258" t="n">
@@ -49337,19 +50184,19 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>もっち</t>
+          <t>みらい</t>
         </is>
       </c>
       <c r="B259" t="n">
@@ -49357,19 +50204,19 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>もと</t>
+          <t>みるこ</t>
         </is>
       </c>
       <c r="B260" t="n">
@@ -49377,19 +50224,19 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>ももたろ</t>
+          <t>みん</t>
         </is>
       </c>
       <c r="B261" t="n">
@@ -49397,19 +50244,19 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>ゆい</t>
+          <t>みー</t>
         </is>
       </c>
       <c r="B262" t="n">
@@ -49417,19 +50264,19 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>ゆうくん</t>
+          <t>みーみ</t>
         </is>
       </c>
       <c r="B263" t="n">
@@ -49437,19 +50284,19 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>ゆうた</t>
+          <t>もかちんぽぽ</t>
         </is>
       </c>
       <c r="B264" t="n">
@@ -49457,19 +50304,19 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>ゆうたん</t>
+          <t>もっち</t>
         </is>
       </c>
       <c r="B265" t="n">
@@ -49477,19 +50324,19 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>ゆうと</t>
+          <t>もと</t>
         </is>
       </c>
       <c r="B266" t="n">
@@ -49497,19 +50344,19 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>ゆうや</t>
+          <t>ももたろ</t>
         </is>
       </c>
       <c r="B267" t="n">
@@ -49517,19 +50364,19 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>ゆきんこ</t>
+          <t>ゆい</t>
         </is>
       </c>
       <c r="B268" t="n">
@@ -49537,19 +50384,19 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>ゆず</t>
+          <t>ゆうじ</t>
         </is>
       </c>
       <c r="B269" t="n">
@@ -49557,19 +50404,19 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>ゆずき＆ましゅ</t>
+          <t>ゆうた</t>
         </is>
       </c>
       <c r="B270" t="n">
@@ -49577,19 +50424,19 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>ゆぴ</t>
+          <t>ゆうたん</t>
         </is>
       </c>
       <c r="B271" t="n">
@@ -49597,19 +50444,19 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>ゆり</t>
+          <t>ゆうと</t>
         </is>
       </c>
       <c r="B272" t="n">
@@ -49617,19 +50464,19 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>ゆりな</t>
+          <t>ゆうや</t>
         </is>
       </c>
       <c r="B273" t="n">
@@ -49637,19 +50484,19 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>ゆん</t>
+          <t>ゆきんこ</t>
         </is>
       </c>
       <c r="B274" t="n">
@@ -49657,19 +50504,19 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>よこい</t>
+          <t>ゆず</t>
         </is>
       </c>
       <c r="B275" t="n">
@@ -49677,19 +50524,19 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>よちお</t>
+          <t>ゆずき＆ましゅ</t>
         </is>
       </c>
       <c r="B276" t="n">
@@ -49697,19 +50544,19 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>らうら</t>
+          <t>ゆぴ</t>
         </is>
       </c>
       <c r="B277" t="n">
@@ -49717,19 +50564,19 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>らお</t>
+          <t>ゆり</t>
         </is>
       </c>
       <c r="B278" t="n">
@@ -49737,19 +50584,19 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>りえ</t>
+          <t>ゆりな</t>
         </is>
       </c>
       <c r="B279" t="n">
@@ -49757,19 +50604,19 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>りく</t>
+          <t>ゆん</t>
         </is>
       </c>
       <c r="B280" t="n">
@@ -49777,19 +50624,19 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>りさ</t>
+          <t>よこい</t>
         </is>
       </c>
       <c r="B281" t="n">
@@ -49797,19 +50644,19 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>りゅうくん</t>
+          <t>よちお</t>
         </is>
       </c>
       <c r="B282" t="n">
@@ -49817,19 +50664,19 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>りゅーちゃん</t>
+          <t>らうら</t>
         </is>
       </c>
       <c r="B283" t="n">
@@ -49837,19 +50684,19 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>りょうが</t>
+          <t>らお</t>
         </is>
       </c>
       <c r="B284" t="n">
@@ -49857,19 +50704,19 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>りょうちゃん</t>
+          <t>りえ</t>
         </is>
       </c>
       <c r="B285" t="n">
@@ -49877,19 +50724,19 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>りょーが</t>
+          <t>りく</t>
         </is>
       </c>
       <c r="B286" t="n">
@@ -49897,19 +50744,19 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>りりこ</t>
+          <t>りさ</t>
         </is>
       </c>
       <c r="B287" t="n">
@@ -49929,7 +50776,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>りん＆ゆち</t>
+          <t>りゅうくん</t>
         </is>
       </c>
       <c r="B288" t="n">
@@ -49937,19 +50784,19 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>れー</t>
+          <t>りゅーちゃん</t>
         </is>
       </c>
       <c r="B289" t="n">
@@ -49957,19 +50804,19 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>アイ</t>
+          <t>りょうが</t>
         </is>
       </c>
       <c r="B290" t="n">
@@ -49977,19 +50824,19 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>アイちゃん</t>
+          <t>りょうちゃん</t>
         </is>
       </c>
       <c r="B291" t="n">
@@ -49997,19 +50844,19 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>アキ</t>
+          <t>りょーが</t>
         </is>
       </c>
       <c r="B292" t="n">
@@ -50017,19 +50864,19 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>アナルプリンス</t>
+          <t>りりこ</t>
         </is>
       </c>
       <c r="B293" t="n">
@@ -50037,19 +50884,19 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>イエモン</t>
+          <t>りん＆ゆち</t>
         </is>
       </c>
       <c r="B294" t="n">
@@ -50057,19 +50904,19 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>オ・スー</t>
+          <t>れー</t>
         </is>
       </c>
       <c r="B295" t="n">
@@ -50077,19 +50924,19 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>カイト</t>
+          <t>アイ</t>
         </is>
       </c>
       <c r="B296" t="n">
@@ -50097,19 +50944,19 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>カズヤ</t>
+          <t>アイちゃん</t>
         </is>
       </c>
       <c r="B297" t="n">
@@ -50117,19 +50964,19 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>カミさん</t>
+          <t>アキ</t>
         </is>
       </c>
       <c r="B298" t="n">
@@ -50137,19 +50984,19 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>カモリ</t>
+          <t>アナルプリンス</t>
         </is>
       </c>
       <c r="B299" t="n">
@@ -50157,19 +51004,19 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>カー</t>
+          <t>イエモン</t>
         </is>
       </c>
       <c r="B300" t="n">
@@ -50177,19 +51024,19 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>キムさん</t>
+          <t>オ・スー</t>
         </is>
       </c>
       <c r="B301" t="n">
@@ -50197,19 +51044,19 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>キムとどえむちゃん</t>
+          <t>カイト</t>
         </is>
       </c>
       <c r="B302" t="n">
@@ -50217,19 +51064,19 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>キムとまゆ</t>
+          <t>カズヤ</t>
         </is>
       </c>
       <c r="B303" t="n">
@@ -50237,19 +51084,19 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>キムとドM女R</t>
+          <t>カミさん</t>
         </is>
       </c>
       <c r="B304" t="n">
@@ -50257,19 +51104,19 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>キムと奴隷</t>
+          <t>カモリ</t>
         </is>
       </c>
       <c r="B305" t="n">
@@ -50277,19 +51124,19 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>キムと新しい奴隷ちゃん</t>
+          <t>カー</t>
         </is>
       </c>
       <c r="B306" t="n">
@@ -50297,19 +51144,19 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>クロちゃん</t>
+          <t>キムさん</t>
         </is>
       </c>
       <c r="B307" t="n">
@@ -50317,19 +51164,19 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>ケケ</t>
+          <t>キムとどえむちゃん</t>
         </is>
       </c>
       <c r="B308" t="n">
@@ -50337,19 +51184,19 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>ゲン</t>
+          <t>キムとまゆ</t>
         </is>
       </c>
       <c r="B309" t="n">
@@ -50357,19 +51204,19 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>コオリ</t>
+          <t>キムとドM女R</t>
         </is>
       </c>
       <c r="B310" t="n">
@@ -50377,19 +51224,19 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>サトル</t>
+          <t>キムと奴隷</t>
         </is>
       </c>
       <c r="B311" t="n">
@@ -50397,19 +51244,19 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>ザッキー</t>
+          <t>キムと新しい奴隷ちゃん</t>
         </is>
       </c>
       <c r="B312" t="n">
@@ -50417,19 +51264,19 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>シゲ</t>
+          <t>クロちゃん</t>
         </is>
       </c>
       <c r="B313" t="n">
@@ -50449,7 +51296,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>シュン</t>
+          <t>ケケ</t>
         </is>
       </c>
       <c r="B314" t="n">
@@ -50457,19 +51304,19 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>シュンヤ</t>
+          <t>ゲン</t>
         </is>
       </c>
       <c r="B315" t="n">
@@ -50477,19 +51324,19 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>ジャッキー</t>
+          <t>コオリ</t>
         </is>
       </c>
       <c r="B316" t="n">
@@ -50497,19 +51344,19 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>ジョーカー</t>
+          <t>コマ</t>
         </is>
       </c>
       <c r="B317" t="n">
@@ -50517,19 +51364,19 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>タカ</t>
+          <t>サトル</t>
         </is>
       </c>
       <c r="B318" t="n">
@@ -50537,19 +51384,19 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>タカス</t>
+          <t>ザッキー</t>
         </is>
       </c>
       <c r="B319" t="n">
@@ -50557,19 +51404,19 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>タカ御一行</t>
+          <t>シゲ</t>
         </is>
       </c>
       <c r="B320" t="n">
@@ -50577,19 +51424,19 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>ダイキ</t>
+          <t>シュン</t>
         </is>
       </c>
       <c r="B321" t="n">
@@ -50597,19 +51444,19 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>ダイゴ</t>
+          <t>シュンヤ</t>
         </is>
       </c>
       <c r="B322" t="n">
@@ -50629,7 +51476,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>ダイチ</t>
+          <t>ジャッキー</t>
         </is>
       </c>
       <c r="B323" t="n">
@@ -50637,19 +51484,19 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>ツシマ</t>
+          <t>ジョーカー</t>
         </is>
       </c>
       <c r="B324" t="n">
@@ -50657,19 +51504,19 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>ツボ</t>
+          <t>タカ</t>
         </is>
       </c>
       <c r="B325" t="n">
@@ -50677,19 +51524,19 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>テクノっち</t>
+          <t>タカス</t>
         </is>
       </c>
       <c r="B326" t="n">
@@ -50697,19 +51544,19 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>テクノとポチ</t>
+          <t>タカ御一行</t>
         </is>
       </c>
       <c r="B327" t="n">
@@ -50717,19 +51564,19 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>テクノ＆てるくん＆イブオ</t>
+          <t>ダイキ</t>
         </is>
       </c>
       <c r="B328" t="n">
@@ -50737,19 +51584,19 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>トニー・トニー・チョッパー</t>
+          <t>ダイゴ</t>
         </is>
       </c>
       <c r="B329" t="n">
@@ -50757,19 +51604,19 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>ナカヤマヤ</t>
+          <t>ダイチ</t>
         </is>
       </c>
       <c r="B330" t="n">
@@ -50777,19 +51624,19 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>ニト</t>
+          <t>ツシマ</t>
         </is>
       </c>
       <c r="B331" t="n">
@@ -50797,19 +51644,19 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>ニャンまげ</t>
+          <t>ツボ</t>
         </is>
       </c>
       <c r="B332" t="n">
@@ -50817,19 +51664,19 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>ビコー</t>
+          <t>テクノとポチ</t>
         </is>
       </c>
       <c r="B333" t="n">
@@ -50837,19 +51684,19 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>フジ</t>
+          <t>テクノ＆てるくん＆イブオ</t>
         </is>
       </c>
       <c r="B334" t="n">
@@ -50857,19 +51704,19 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>ボンタ</t>
+          <t>トニー・トニー・チョッパー</t>
         </is>
       </c>
       <c r="B335" t="n">
@@ -50877,19 +51724,19 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>ポチ</t>
+          <t>ナカヤマヤ</t>
         </is>
       </c>
       <c r="B336" t="n">
@@ -50897,19 +51744,19 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>マイナス</t>
+          <t>ニト</t>
         </is>
       </c>
       <c r="B337" t="n">
@@ -50917,19 +51764,19 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>マサ</t>
+          <t>ニャンまげ</t>
         </is>
       </c>
       <c r="B338" t="n">
@@ -50937,19 +51784,19 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>マッチョ</t>
+          <t>ビコー</t>
         </is>
       </c>
       <c r="B339" t="n">
@@ -50957,19 +51804,19 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>マナティ</t>
+          <t>フジ</t>
         </is>
       </c>
       <c r="B340" t="n">
@@ -50989,7 +51836,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>ミカミと仲間たち</t>
+          <t>ボンタ</t>
         </is>
       </c>
       <c r="B341" t="n">
@@ -50997,19 +51844,19 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>ミスター工事マン</t>
+          <t>ポチ</t>
         </is>
       </c>
       <c r="B342" t="n">
@@ -51017,19 +51864,19 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>ミッシ</t>
+          <t>マイナス</t>
         </is>
       </c>
       <c r="B343" t="n">
@@ -51037,19 +51884,19 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>ミッチー</t>
+          <t>マサ</t>
         </is>
       </c>
       <c r="B344" t="n">
@@ -51057,19 +51904,19 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>ミルコ</t>
+          <t>マッチョ</t>
         </is>
       </c>
       <c r="B345" t="n">
@@ -51077,19 +51924,19 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>モジャ</t>
+          <t>マナティ</t>
         </is>
       </c>
       <c r="B346" t="n">
@@ -51097,19 +51944,19 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>ヤノちゃん</t>
+          <t>ミカミと仲間たち</t>
         </is>
       </c>
       <c r="B347" t="n">
@@ -51117,19 +51964,19 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>ヤマ</t>
+          <t>ミスター工事マン</t>
         </is>
       </c>
       <c r="B348" t="n">
@@ -51137,19 +51984,19 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>ユウ</t>
+          <t>ミッシ</t>
         </is>
       </c>
       <c r="B349" t="n">
@@ -51157,19 +52004,19 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>ユキ</t>
+          <t>ミッチー</t>
         </is>
       </c>
       <c r="B350" t="n">
@@ -51177,19 +52024,19 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>ユッキー</t>
+          <t>ミルコ</t>
         </is>
       </c>
       <c r="B351" t="n">
@@ -51197,19 +52044,19 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>ヨシヤ</t>
+          <t>モジャ</t>
         </is>
       </c>
       <c r="B352" t="n">
@@ -51217,19 +52064,19 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>リク</t>
+          <t>ヤノちゃん</t>
         </is>
       </c>
       <c r="B353" t="n">
@@ -51237,19 +52084,19 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>リョウ</t>
+          <t>ヤマ</t>
         </is>
       </c>
       <c r="B354" t="n">
@@ -51257,19 +52104,19 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>リン</t>
+          <t>ユウ</t>
         </is>
       </c>
       <c r="B355" t="n">
@@ -51277,19 +52124,19 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>ロタポジ</t>
+          <t>ユキ</t>
         </is>
       </c>
       <c r="B356" t="n">
@@ -51297,19 +52144,19 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>ローズ</t>
+          <t>ユッキー</t>
         </is>
       </c>
       <c r="B357" t="n">
@@ -51317,19 +52164,19 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>僕と私</t>
+          <t>ヨシヤ</t>
         </is>
       </c>
       <c r="B358" t="n">
@@ -51337,19 +52184,19 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>名無し</t>
+          <t>リク</t>
         </is>
       </c>
       <c r="B359" t="n">
@@ -51357,19 +52204,19 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>変態マッスル</t>
+          <t>リョウ</t>
         </is>
       </c>
       <c r="B360" t="n">
@@ -51377,19 +52224,19 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>大塚</t>
+          <t>リン</t>
         </is>
       </c>
       <c r="B361" t="n">
@@ -51397,19 +52244,19 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>天我迅</t>
+          <t>ロタポジ</t>
         </is>
       </c>
       <c r="B362" t="n">
@@ -51417,19 +52264,19 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>女子三人衆</t>
+          <t>ローズ</t>
         </is>
       </c>
       <c r="B363" t="n">
@@ -51437,19 +52284,19 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>正装しん</t>
+          <t>僕と私</t>
         </is>
       </c>
       <c r="B364" t="n">
@@ -51457,19 +52304,19 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>海砂利水魚</t>
+          <t>名無し</t>
         </is>
       </c>
       <c r="B365" t="n">
@@ -51477,19 +52324,19 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>田中</t>
+          <t>変態マッスル</t>
         </is>
       </c>
       <c r="B366" t="n">
@@ -51497,19 +52344,19 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>番</t>
+          <t>大塚</t>
         </is>
       </c>
       <c r="B367" t="n">
@@ -51517,19 +52364,19 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>絶</t>
+          <t>天我迅</t>
         </is>
       </c>
       <c r="B368" t="n">
@@ -51537,19 +52384,19 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>絶ちゃん</t>
+          <t>女子三人衆</t>
         </is>
       </c>
       <c r="B369" t="n">
@@ -51557,19 +52404,19 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>美優</t>
+          <t>正装しん</t>
         </is>
       </c>
       <c r="B370" t="n">
@@ -51577,19 +52424,19 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>赤ちゃん</t>
+          <t>海砂利水魚</t>
         </is>
       </c>
       <c r="B371" t="n">
@@ -51597,30 +52444,150 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
+          <t>田中</t>
+        </is>
+      </c>
+      <c r="B372" t="n">
+        <v>1</v>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>番</t>
+        </is>
+      </c>
+      <c r="B373" t="n">
+        <v>1</v>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>絶</t>
+        </is>
+      </c>
+      <c r="B374" t="n">
+        <v>1</v>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>絶ちゃん</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>1</v>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>美優</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>1</v>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>赤ちゃん</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>1</v>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
           <t>高田</t>
         </is>
       </c>
-      <c r="B372" t="n">
-        <v>1</v>
-      </c>
-      <c r="C372" t="inlineStr">
+      <c r="B378" t="n">
+        <v>1</v>
+      </c>
+      <c r="C378" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="D372" t="inlineStr">
+      <c r="D378" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
@@ -51677,10 +52644,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C3" t="n">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4">
@@ -51690,10 +52657,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C4" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5">
@@ -51786,10 +52753,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3">
@@ -51799,10 +52766,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C3" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4">
@@ -51812,10 +52779,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5">
@@ -51825,10 +52792,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6">
@@ -52020,10 +52987,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C20" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -52046,10 +53013,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C22" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="23">
@@ -52059,10 +53026,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C23" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24">
@@ -52150,13 +53117,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="C3" t="n">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="D3" t="n">
-        <v>153</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -52170,7 +53137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C156"/>
+  <dimension ref="A1:C160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52793,12 +53760,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>いっちゃん</t>
+          <t>ありす</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>カミさん</t>
+          <t>みやび</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -52808,12 +53775,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>いぬ</t>
+          <t>いっちゃん</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>てっちゃん</t>
+          <t>カミさん</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -52828,7 +53795,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ながとも</t>
+          <t>てっちゃん</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -52843,7 +53810,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ももたろ</t>
+          <t>ながとも</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -52858,7 +53825,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ゆきんこ</t>
+          <t>ももたろ</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -52873,7 +53840,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>マッチョ</t>
+          <t>ゆきんこ</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -52883,12 +53850,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>いぶお</t>
+          <t>いぬ</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>てる</t>
+          <t>マッチョ</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -52898,12 +53865,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>えぬ</t>
+          <t>いぶお</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>まいなちゅ</t>
+          <t>てる</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -52913,12 +53880,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>おとは</t>
+          <t>えぬ</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>さとるん</t>
+          <t>まいなちゅ</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -52933,7 +53900,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>まろ</t>
+          <t>さとるん</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -52943,12 +53910,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>おにゃん</t>
+          <t>おとは</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ひがん</t>
+          <t>まろ</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -52958,12 +53925,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>おにゃんにゃん</t>
+          <t>おにゃん</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ゆずきち</t>
+          <t>ひがん</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -52973,12 +53940,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>かい</t>
+          <t>おにゃんにゃん</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>たつ</t>
+          <t>ゆずきち</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -52988,12 +53955,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>かず</t>
+          <t>かい</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>のんのん</t>
+          <t>たつ</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -53003,12 +53970,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>かずき</t>
+          <t>かず</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>フジ</t>
+          <t>のんのん</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -53018,12 +53985,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>きむ</t>
+          <t>かずき</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>どえむちゃん</t>
+          <t>フジ</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -53038,7 +54005,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>ましゅ</t>
+          <t>どえむちゃん</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -53053,7 +54020,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>りさ</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -53063,12 +54030,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>きむさん</t>
+          <t>きむ</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ましゅ</t>
+          <t>りさ</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -53078,12 +54045,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>きょうちゃん</t>
+          <t>きむさん</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>たろー</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="C61" t="n">
@@ -53093,12 +54060,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>くま</t>
+          <t>きょうちゃん</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>とおちゃん</t>
+          <t>たろー</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -53113,7 +54080,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>まーくん</t>
+          <t>とおちゃん</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -53123,12 +54090,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>けい</t>
+          <t>くま</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>さや</t>
+          <t>まーくん</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -53138,12 +54105,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>けいちゃん</t>
+          <t>けい</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>もっち</t>
+          <t>さや</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -53153,12 +54120,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>げん</t>
+          <t>けいちゃん</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ともち</t>
+          <t>もっち</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -53168,12 +54135,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>こうた</t>
+          <t>げん</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>まゆ</t>
+          <t>ともち</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -53183,12 +54150,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ことり</t>
+          <t>こうた</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>すーたく</t>
+          <t>まゆ</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -53198,12 +54165,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ごん</t>
+          <t>ことり</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ぶりちゃん</t>
+          <t>すーたく</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -53213,12 +54180,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>さかもと</t>
+          <t>ごん</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>はんまー</t>
+          <t>ぶりちゃん</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -53233,7 +54200,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>よこい</t>
+          <t>はんまー</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -53248,7 +54215,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ビコー</t>
+          <t>よこい</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -53258,12 +54225,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>さとりゅ</t>
+          <t>さかもと</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>ひがんたん</t>
+          <t>ビコー</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -53273,12 +54240,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>さな</t>
+          <t>さとりゅ</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>とし</t>
+          <t>ひがんたん</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -53288,12 +54255,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>さない</t>
+          <t>さな</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>モジャ</t>
+          <t>とし</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -53303,12 +54270,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>しずか</t>
+          <t>さない</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>まいまい</t>
+          <t>モジャ</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -53318,12 +54285,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>しょうた</t>
+          <t>しずか</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>すーさん</t>
+          <t>まいまい</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -53333,12 +54300,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>しりゅう</t>
+          <t>しょうた</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ヤノちゃん</t>
+          <t>すーさん</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -53348,12 +54315,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>しん</t>
+          <t>しりゅう</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>たくや</t>
+          <t>ヤノちゃん</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -53368,7 +54335,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>だいざく</t>
+          <t>たくや</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -53383,7 +54350,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ゆうた</t>
+          <t>だいざく</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -53393,12 +54360,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>すず</t>
+          <t>しん</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>まいなす</t>
+          <t>ゆうた</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -53408,12 +54375,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>すー</t>
+          <t>すず</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ましゅ</t>
+          <t>まいなす</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -53423,12 +54390,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>たか</t>
+          <t>すー</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>りょうが</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -53438,12 +54405,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>たかし</t>
+          <t>たか</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>まり</t>
+          <t>りょうが</t>
         </is>
       </c>
       <c r="C85" t="n">
@@ -53453,12 +54420,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>たかやま</t>
+          <t>たかし</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ふく</t>
+          <t>まり</t>
         </is>
       </c>
       <c r="C86" t="n">
@@ -53473,7 +54440,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>ふくてゃ</t>
+          <t>ふく</t>
         </is>
       </c>
       <c r="C87" t="n">
@@ -53488,7 +54455,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>りりこ</t>
+          <t>ふくてゃ</t>
         </is>
       </c>
       <c r="C88" t="n">
@@ -53498,12 +54465,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>たく</t>
+          <t>たかやま</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>りゅう</t>
+          <t>りりこ</t>
         </is>
       </c>
       <c r="C89" t="n">
@@ -53513,12 +54480,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>たくや</t>
+          <t>たく</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>だいさく</t>
+          <t>りゅう</t>
         </is>
       </c>
       <c r="C90" t="n">
@@ -53533,7 +54500,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>だいざく</t>
+          <t>だいさく</t>
         </is>
       </c>
       <c r="C91" t="n">
@@ -53548,7 +54515,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ゆうた</t>
+          <t>だいざく</t>
         </is>
       </c>
       <c r="C92" t="n">
@@ -53558,7 +54525,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>だいざく</t>
+          <t>たくや</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -53573,12 +54540,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ちぇちぇ</t>
+          <t>だいざく</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ゆず</t>
+          <t>ゆうた</t>
         </is>
       </c>
       <c r="C94" t="n">
@@ -53588,12 +54555,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>てっちゃん</t>
+          <t>ちぇちぇ</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ながとも</t>
+          <t>ゆず</t>
         </is>
       </c>
       <c r="C95" t="n">
@@ -53608,7 +54575,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ゆきんこ</t>
+          <t>ながとも</t>
         </is>
       </c>
       <c r="C96" t="n">
@@ -53618,12 +54585,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>とおちゃん</t>
+          <t>てっちゃん</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>まーくん</t>
+          <t>ゆきんこ</t>
         </is>
       </c>
       <c r="C97" t="n">
@@ -53633,12 +54600,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>とも</t>
+          <t>とおちゃん</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>テクノ</t>
+          <t>まーくん</t>
         </is>
       </c>
       <c r="C98" t="n">
@@ -53648,12 +54615,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ともや</t>
+          <t>とも</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>シュンヤ</t>
+          <t>テクノ</t>
         </is>
       </c>
       <c r="C99" t="n">
@@ -53663,12 +54630,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>とーり</t>
+          <t>ともや</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>まや</t>
+          <t>シュンヤ</t>
         </is>
       </c>
       <c r="C100" t="n">
@@ -53678,12 +54645,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>どえむちゃん</t>
+          <t>とーり</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>ましゅ</t>
+          <t>まや</t>
         </is>
       </c>
       <c r="C101" t="n">
@@ -53693,12 +54660,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ながとも</t>
+          <t>どえむちゃん</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ゆきんこ</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="C102" t="n">
@@ -53708,12 +54675,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>なな</t>
+          <t>ながとも</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>タカ</t>
+          <t>ゆきんこ</t>
         </is>
       </c>
       <c r="C103" t="n">
@@ -53728,7 +54695,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>タク</t>
+          <t>タカ</t>
         </is>
       </c>
       <c r="C104" t="n">
@@ -53738,12 +54705,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>なべ</t>
+          <t>なな</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>シュン</t>
+          <t>タク</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -53753,12 +54720,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>なまがき</t>
+          <t>なべ</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>彩</t>
+          <t>シュン</t>
         </is>
       </c>
       <c r="C106" t="n">
@@ -53768,12 +54735,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>のんのん</t>
+          <t>なまがき</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>カズ</t>
+          <t>彩</t>
         </is>
       </c>
       <c r="C107" t="n">
@@ -53783,12 +54750,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>はんまー</t>
+          <t>のんのん</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>よこい</t>
+          <t>カズ</t>
         </is>
       </c>
       <c r="C108" t="n">
@@ -53803,7 +54770,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>ビコー</t>
+          <t>よこい</t>
         </is>
       </c>
       <c r="C109" t="n">
@@ -53813,12 +54780,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ひろとも</t>
+          <t>はんまー</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>ゆうき</t>
+          <t>ビコー</t>
         </is>
       </c>
       <c r="C110" t="n">
@@ -53828,12 +54795,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ふくちゃん</t>
+          <t>ひろし</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>まいまい</t>
+          <t>ゆうじ</t>
         </is>
       </c>
       <c r="C111" t="n">
@@ -53843,12 +54810,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ぷらぐいん</t>
+          <t>ひろし</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>れー</t>
+          <t>コマ</t>
         </is>
       </c>
       <c r="C112" t="n">
@@ -53858,12 +54825,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>まい</t>
+          <t>ひろとも</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>めい</t>
+          <t>ゆうき</t>
         </is>
       </c>
       <c r="C113" t="n">
@@ -53873,12 +54840,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>まい</t>
+          <t>ふくちゃん</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>りお</t>
+          <t>まいまい</t>
         </is>
       </c>
       <c r="C114" t="n">
@@ -53888,12 +54855,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>まいまい</t>
+          <t>ぷらぐいん</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ゆずき</t>
+          <t>れー</t>
         </is>
       </c>
       <c r="C115" t="n">
@@ -53903,12 +54870,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>まいまい</t>
+          <t>まい</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>テクノ</t>
+          <t>めい</t>
         </is>
       </c>
       <c r="C116" t="n">
@@ -53918,12 +54885,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>まいまい</t>
+          <t>まい</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>ミコト</t>
+          <t>りお</t>
         </is>
       </c>
       <c r="C117" t="n">
@@ -53933,12 +54900,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ましゅ</t>
+          <t>まいまい</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>るい</t>
+          <t>ゆずき</t>
         </is>
       </c>
       <c r="C118" t="n">
@@ -53948,12 +54915,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ましゅ</t>
+          <t>まいまい</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>カズ</t>
+          <t>テクノ</t>
         </is>
       </c>
       <c r="C119" t="n">
@@ -53963,12 +54930,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ましゅ</t>
+          <t>まいまい</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>ダイゴ</t>
+          <t>ミコト</t>
         </is>
       </c>
       <c r="C120" t="n">
@@ -53983,7 +54950,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>絶</t>
+          <t>るい</t>
         </is>
       </c>
       <c r="C121" t="n">
@@ -53993,12 +54960,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ましゅ社長</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>ゆずきち</t>
+          <t>カズ</t>
         </is>
       </c>
       <c r="C122" t="n">
@@ -54008,12 +54975,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ますみ</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>ジョーカー</t>
+          <t>ダイゴ</t>
         </is>
       </c>
       <c r="C123" t="n">
@@ -54023,12 +54990,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>まな</t>
+          <t>ましゅ</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>りゅーちゃん</t>
+          <t>絶</t>
         </is>
       </c>
       <c r="C124" t="n">
@@ -54038,12 +55005,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>まーくん</t>
+          <t>ましゅ社長</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>まーちゃん</t>
+          <t>ゆずきち</t>
         </is>
       </c>
       <c r="C125" t="n">
@@ -54053,12 +55020,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>まーくん</t>
+          <t>ますみ</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>りゅうくん</t>
+          <t>ジョーカー</t>
         </is>
       </c>
       <c r="C126" t="n">
@@ -54068,12 +55035,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>みずき</t>
+          <t>まな</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>りく</t>
+          <t>りゅーちゃん</t>
         </is>
       </c>
       <c r="C127" t="n">
@@ -54083,12 +55050,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>みずき</t>
+          <t>まーくん</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>りん</t>
+          <t>まーちゃん</t>
         </is>
       </c>
       <c r="C128" t="n">
@@ -54098,12 +55065,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>みちゃ</t>
+          <t>まーくん</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>ゆう</t>
+          <t>りゅうくん</t>
         </is>
       </c>
       <c r="C129" t="n">
@@ -54113,12 +55080,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>みちゃ</t>
+          <t>みずき</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>りょう</t>
+          <t>りく</t>
         </is>
       </c>
       <c r="C130" t="n">
@@ -54128,12 +55095,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>みゆき</t>
+          <t>みずき</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>ゆりな</t>
+          <t>りん</t>
         </is>
       </c>
       <c r="C131" t="n">
@@ -54143,12 +55110,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>みらい</t>
+          <t>みちゃ</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>ジャッキー</t>
+          <t>ゆう</t>
         </is>
       </c>
       <c r="C132" t="n">
@@ -54158,12 +55125,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>みれい</t>
+          <t>みちゃ</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>キム</t>
+          <t>りょう</t>
         </is>
       </c>
       <c r="C133" t="n">
@@ -54173,12 +55140,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>みー</t>
+          <t>みゆき</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>キム</t>
+          <t>ゆりな</t>
         </is>
       </c>
       <c r="C134" t="n">
@@ -54188,12 +55155,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ももたろ</t>
+          <t>みらい</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>マッチョ</t>
+          <t>ジャッキー</t>
         </is>
       </c>
       <c r="C135" t="n">
@@ -54203,12 +55170,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ゆう</t>
+          <t>みれい</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>りょう</t>
+          <t>キム</t>
         </is>
       </c>
       <c r="C136" t="n">
@@ -54218,12 +55185,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ゆうき</t>
+          <t>みー</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>カイト</t>
+          <t>キム</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -54233,12 +55200,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ゆうたん</t>
+          <t>ももたろ</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>カモリ</t>
+          <t>マッチョ</t>
         </is>
       </c>
       <c r="C138" t="n">
@@ -54248,12 +55215,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ゆずき</t>
+          <t>ゆう</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>田中</t>
+          <t>りょう</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -54263,12 +55230,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ゆり</t>
+          <t>ゆうき</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>りえ</t>
+          <t>カイト</t>
         </is>
       </c>
       <c r="C140" t="n">
@@ -54278,12 +55245,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>よこい</t>
+          <t>ゆうじ</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>ビコー</t>
+          <t>コマ</t>
         </is>
       </c>
       <c r="C141" t="n">
@@ -54293,12 +55260,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>よっしー</t>
+          <t>ゆうたん</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>ザッキー</t>
+          <t>カモリ</t>
         </is>
       </c>
       <c r="C142" t="n">
@@ -54308,12 +55275,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>りく</t>
+          <t>ゆずき</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>りん</t>
+          <t>田中</t>
         </is>
       </c>
       <c r="C143" t="n">
@@ -54323,12 +55290,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>アキ</t>
+          <t>ゆり</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>コオリ</t>
+          <t>りえ</t>
         </is>
       </c>
       <c r="C144" t="n">
@@ -54338,12 +55305,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>オカニー</t>
+          <t>よこい</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>ダイキ</t>
+          <t>ビコー</t>
         </is>
       </c>
       <c r="C145" t="n">
@@ -54353,12 +55320,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>オカニー</t>
+          <t>よっしー</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>ミッシ</t>
+          <t>ザッキー</t>
         </is>
       </c>
       <c r="C146" t="n">
@@ -54368,12 +55335,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>カズ</t>
+          <t>りく</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>ダイゴ</t>
+          <t>りん</t>
         </is>
       </c>
       <c r="C147" t="n">
@@ -54383,12 +55350,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>クロちゃん</t>
+          <t>アキ</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>ポチ</t>
+          <t>コオリ</t>
         </is>
       </c>
       <c r="C148" t="n">
@@ -54398,12 +55365,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ケン</t>
+          <t>オカニー</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>ツボ</t>
+          <t>ダイキ</t>
         </is>
       </c>
       <c r="C149" t="n">
@@ -54413,12 +55380,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ゲン</t>
+          <t>オカニー</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>シゲ</t>
+          <t>ミッシ</t>
         </is>
       </c>
       <c r="C150" t="n">
@@ -54428,12 +55395,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>タカ</t>
+          <t>カズ</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>タク</t>
+          <t>ダイゴ</t>
         </is>
       </c>
       <c r="C151" t="n">
@@ -54443,12 +55410,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>タカス</t>
+          <t>クロちゃん</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>マサ</t>
+          <t>ポチ</t>
         </is>
       </c>
       <c r="C152" t="n">
@@ -54458,12 +55425,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>タク</t>
+          <t>ケン</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>リョウ</t>
+          <t>ツボ</t>
         </is>
       </c>
       <c r="C153" t="n">
@@ -54473,12 +55440,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ダイキ</t>
+          <t>ゲン</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>ミッシ</t>
+          <t>シゲ</t>
         </is>
       </c>
       <c r="C154" t="n">
@@ -54488,12 +55455,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>テクノ</t>
+          <t>タカ</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>ミコト</t>
+          <t>タク</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -54503,15 +55470,75 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
+          <t>タカス</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>マサ</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>タク</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>リョウ</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>ダイキ</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>ミッシ</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>テクノ</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>ミコト</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
           <t>天我迅</t>
         </is>
       </c>
-      <c r="B156" t="inlineStr">
+      <c r="B160" t="inlineStr">
         <is>
           <t>美優</t>
         </is>
       </c>
-      <c r="C156" t="n">
+      <c r="C160" t="n">
         <v>1</v>
       </c>
     </row>

--- a/bbs_log.xlsx
+++ b/bbs_log.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H628"/>
+  <dimension ref="A1:H640"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19690,7 +19690,6 @@
           <t>ひがん</t>
         </is>
       </c>
-      <c r="E612" t="inlineStr"/>
       <c r="F612" t="inlineStr">
         <is>
           <t>オープン前に</t>
@@ -19701,7 +19700,6 @@
           <t>きました♪</t>
         </is>
       </c>
-      <c r="H612" t="inlineStr"/>
     </row>
     <row r="613">
       <c r="A613" t="n">
@@ -19722,7 +19720,6 @@
           <t>ゆずきち</t>
         </is>
       </c>
-      <c r="E613" t="inlineStr"/>
       <c r="F613" t="inlineStr">
         <is>
           <t>イベント</t>
@@ -19733,7 +19730,6 @@
           <t>ニシシ＾＾</t>
         </is>
       </c>
-      <c r="H613" t="inlineStr"/>
     </row>
     <row r="614">
       <c r="A614" t="n">
@@ -19754,7 +19750,6 @@
           <t>エーイチ</t>
         </is>
       </c>
-      <c r="E614" t="inlineStr"/>
       <c r="F614" t="inlineStr">
         <is>
           <t>初めて</t>
@@ -19765,7 +19760,6 @@
           <t>来ました</t>
         </is>
       </c>
-      <c r="H614" t="inlineStr"/>
     </row>
     <row r="615">
       <c r="A615" t="n">
@@ -19786,7 +19780,6 @@
           <t>キムとドMむい</t>
         </is>
       </c>
-      <c r="E615" t="inlineStr"/>
       <c r="F615" t="inlineStr">
         <is>
           <t>雨にも負けず</t>
@@ -19797,7 +19790,6 @@
           <t>縛って来店しようかと</t>
         </is>
       </c>
-      <c r="H615" t="inlineStr"/>
     </row>
     <row r="616">
       <c r="A616" t="n">
@@ -19818,7 +19810,6 @@
           <t>トルネードシャーク</t>
         </is>
       </c>
-      <c r="E616" t="inlineStr"/>
       <c r="F616" t="inlineStr">
         <is>
           <t>初めてですが</t>
@@ -19829,7 +19820,6 @@
           <t>今から行きます</t>
         </is>
       </c>
-      <c r="H616" t="inlineStr"/>
     </row>
     <row r="617">
       <c r="A617" t="n">
@@ -19850,7 +19840,6 @@
           <t>もっぴー、おもち</t>
         </is>
       </c>
-      <c r="E617" t="inlineStr"/>
       <c r="F617" t="inlineStr">
         <is>
           <t>妹さん連れて</t>
@@ -19861,7 +19850,6 @@
           <t>来ちゃった＾＾</t>
         </is>
       </c>
-      <c r="H617" t="inlineStr"/>
     </row>
     <row r="618">
       <c r="A618" t="n">
@@ -19882,7 +19870,6 @@
           <t>変態マッスル</t>
         </is>
       </c>
-      <c r="E618" t="inlineStr"/>
       <c r="F618" t="inlineStr">
         <is>
           <t>バースデー</t>
@@ -19893,7 +19880,6 @@
           <t>ぶりに</t>
         </is>
       </c>
-      <c r="H618" t="inlineStr"/>
     </row>
     <row r="619">
       <c r="A619" t="n">
@@ -19914,7 +19900,6 @@
           <t>N</t>
         </is>
       </c>
-      <c r="E619" t="inlineStr"/>
       <c r="F619" t="inlineStr">
         <is>
           <t>今</t>
@@ -19925,7 +19910,6 @@
           <t>きたよ♪</t>
         </is>
       </c>
-      <c r="H619" t="inlineStr"/>
     </row>
     <row r="620">
       <c r="A620" t="n">
@@ -19946,7 +19930,6 @@
           <t>たいせい</t>
         </is>
       </c>
-      <c r="E620" t="inlineStr"/>
       <c r="F620" t="inlineStr">
         <is>
           <t>雨</t>
@@ -19957,7 +19940,6 @@
           <t>やばーい</t>
         </is>
       </c>
-      <c r="H620" t="inlineStr"/>
     </row>
     <row r="621">
       <c r="A621" t="n">
@@ -19978,7 +19960,6 @@
           <t>ましゅ社長</t>
         </is>
       </c>
-      <c r="E621" t="inlineStr"/>
       <c r="F621" t="inlineStr">
         <is>
           <t>今</t>
@@ -19989,7 +19970,6 @@
           <t>きたでやんす</t>
         </is>
       </c>
-      <c r="H621" t="inlineStr"/>
     </row>
     <row r="622">
       <c r="A622" t="n">
@@ -20010,7 +19990,6 @@
           <t>キム＆むい</t>
         </is>
       </c>
-      <c r="E622" t="inlineStr"/>
       <c r="F622" t="inlineStr">
         <is>
           <t>今</t>
@@ -20021,7 +20000,6 @@
           <t>きたお</t>
         </is>
       </c>
-      <c r="H622" t="inlineStr"/>
     </row>
     <row r="623">
       <c r="A623" t="n">
@@ -20042,7 +20020,6 @@
           <t>5人衆</t>
         </is>
       </c>
-      <c r="E623" t="inlineStr"/>
       <c r="F623" t="inlineStr">
         <is>
           <t>みんなで</t>
@@ -20053,7 +20030,6 @@
           <t>きたよ♪</t>
         </is>
       </c>
-      <c r="H623" t="inlineStr"/>
     </row>
     <row r="624">
       <c r="A624" t="n">
@@ -20074,7 +20050,6 @@
           <t>カー</t>
         </is>
       </c>
-      <c r="E624" t="inlineStr"/>
       <c r="F624" t="inlineStr">
         <is>
           <t>今</t>
@@ -20085,7 +20060,6 @@
           <t>きたよー</t>
         </is>
       </c>
-      <c r="H624" t="inlineStr"/>
     </row>
     <row r="625">
       <c r="A625" t="n">
@@ -20106,7 +20080,6 @@
           <t>マイナス</t>
         </is>
       </c>
-      <c r="E625" t="inlineStr"/>
       <c r="F625" t="inlineStr">
         <is>
           <t>麻雀</t>
@@ -20117,7 +20090,6 @@
           <t>終わりに</t>
         </is>
       </c>
-      <c r="H625" t="inlineStr"/>
     </row>
     <row r="626">
       <c r="A626" t="n">
@@ -20138,7 +20110,6 @@
           <t>クアレ、ゆずき</t>
         </is>
       </c>
-      <c r="E626" t="inlineStr"/>
       <c r="F626" t="inlineStr">
         <is>
           <t>鞭を</t>
@@ -20149,7 +20120,6 @@
           <t>また受けたくて</t>
         </is>
       </c>
-      <c r="H626" t="inlineStr"/>
     </row>
     <row r="627">
       <c r="A627" t="n">
@@ -20170,7 +20140,6 @@
           <t>まいまい、こてっちゃん</t>
         </is>
       </c>
-      <c r="E627" t="inlineStr"/>
       <c r="F627" t="inlineStr">
         <is>
           <t>ビジュアル系</t>
@@ -20181,7 +20150,6 @@
           <t>カラオケ後</t>
         </is>
       </c>
-      <c r="H627" t="inlineStr"/>
     </row>
     <row r="628">
       <c r="A628" t="n">
@@ -20235,6 +20203,410 @@
         </is>
       </c>
     </row>
+    <row r="629">
+      <c r="A629" t="n">
+        <v>27985</v>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>19:06:28</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>ましゅ</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr"/>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>オープン凸</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>来ました</t>
+        </is>
+      </c>
+      <c r="H629" t="inlineStr"/>
+    </row>
+    <row r="630">
+      <c r="A630" t="n">
+        <v>27986</v>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>19:06:54</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>ひがん</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr"/>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>遊びに</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>来ました♪</t>
+        </is>
+      </c>
+      <c r="H630" t="inlineStr"/>
+    </row>
+    <row r="631">
+      <c r="A631" t="n">
+        <v>27988</v>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>19:15:22</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>ぐっちゃん（チャイマフィ）</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr"/>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>お久し</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>来ました！</t>
+        </is>
+      </c>
+      <c r="H631" t="inlineStr"/>
+    </row>
+    <row r="632">
+      <c r="A632" t="n">
+        <v>27992</v>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>20:57:58</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>えぬ</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr"/>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>まったりしに</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>いきます</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr"/>
+    </row>
+    <row r="633">
+      <c r="A633" t="n">
+        <v>27996</v>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>21:39:57</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>オリーブ</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr"/>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>はじめて</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>面白いお店探して来ました！</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr"/>
+    </row>
+    <row r="634">
+      <c r="A634" t="n">
+        <v>27998</v>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>22:02:41</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>げんき</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr"/>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>気になって</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>遊びに来てみました</t>
+        </is>
+      </c>
+      <c r="H634" t="inlineStr"/>
+    </row>
+    <row r="635">
+      <c r="A635" t="n">
+        <v>28000</v>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>22:23:55</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>えーたろ</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr"/>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>飲みに</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>来ました！</t>
+        </is>
+      </c>
+      <c r="H635" t="inlineStr"/>
+    </row>
+    <row r="636">
+      <c r="A636" t="n">
+        <v>28001</v>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>22:25:37</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>テクノ</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr"/>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>ハイボールを</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>ください</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr"/>
+    </row>
+    <row r="637">
+      <c r="A637" t="n">
+        <v>28004</v>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>22:55:40</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>大塚</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr"/>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>アゲアゲで</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>きたよーん</t>
+        </is>
+      </c>
+      <c r="H637" t="inlineStr"/>
+    </row>
+    <row r="638">
+      <c r="A638" t="n">
+        <v>28006</v>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>23:54:36</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>るい</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr"/>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>ショー帰りに</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>きたよ</t>
+        </is>
+      </c>
+      <c r="H638" t="inlineStr"/>
+    </row>
+    <row r="639">
+      <c r="A639" t="n">
+        <v>28008</v>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>02:48:31</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>ちぇちぇ＆ガールズ</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr"/>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>新規女子連れて</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>来ました！！！！</t>
+        </is>
+      </c>
+      <c r="H639" t="inlineStr"/>
+    </row>
+    <row r="640">
+      <c r="A640" t="n">
+        <v>28010</v>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>04:12:44</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>欲求不満のポコチンハンター　える</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>★☆★朝までアゲアゲの火曜日営業が始まるわよ♪★☆★</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>本日9月22日の営業時間は♪
+オープン19:00！ラスト5:00なのよ☆
+担当は
+欲求不満のポコチンハンター　える
+なのよ♪
+どんな季節でも★BAMBITCH★は色気ムンムンで暑すぎる♪
+バンビッチでおもいっきりはじけちゃって（笑）
+精力は無くても性欲がある！？
+大人の憩いと禁断サークル盛りだくさん！
+憩いと交流の魔性の遊び場バンビッチは素敵な出会いを 提供いたします（笑)☆☆
+おつまみ等の持ち込みは自由なのでみんなで持ち寄ってお近づきのきっかけにどうぞ♪
+強制や無理強いは一切ございませんので楽しく遊びましょう♪
+宇都宮市宿郷1−12−9　カサブランカビル5F</t>
+        </is>
+      </c>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>img20260922041244.jpg</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20246,7 +20618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I746"/>
+  <dimension ref="A1:I757"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52338,6 +52710,479 @@
       <c r="I746" t="inlineStr">
         <is>
           <t>カラオケ後</t>
+        </is>
+      </c>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>19:06:28</t>
+        </is>
+      </c>
+      <c r="D747" t="n">
+        <v>27985</v>
+      </c>
+      <c r="E747" t="inlineStr">
+        <is>
+          <t>ましゅ</t>
+        </is>
+      </c>
+      <c r="F747" t="n">
+        <v>14</v>
+      </c>
+      <c r="G747" t="inlineStr">
+        <is>
+          <t>ましゅ</t>
+        </is>
+      </c>
+      <c r="H747" t="inlineStr">
+        <is>
+          <t>オープン凸</t>
+        </is>
+      </c>
+      <c r="I747" t="inlineStr">
+        <is>
+          <t>来ました</t>
+        </is>
+      </c>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>19:06:54</t>
+        </is>
+      </c>
+      <c r="D748" t="n">
+        <v>27986</v>
+      </c>
+      <c r="E748" t="inlineStr">
+        <is>
+          <t>ひがん</t>
+        </is>
+      </c>
+      <c r="F748" t="n">
+        <v>22</v>
+      </c>
+      <c r="G748" t="inlineStr">
+        <is>
+          <t>ひがん</t>
+        </is>
+      </c>
+      <c r="H748" t="inlineStr">
+        <is>
+          <t>遊びに</t>
+        </is>
+      </c>
+      <c r="I748" t="inlineStr">
+        <is>
+          <t>来ました♪</t>
+        </is>
+      </c>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>19:15:22</t>
+        </is>
+      </c>
+      <c r="D749" t="n">
+        <v>27988</v>
+      </c>
+      <c r="E749" t="inlineStr">
+        <is>
+          <t>ぐっちゃん（チャイマフィ）</t>
+        </is>
+      </c>
+      <c r="F749" t="n">
+        <v>1</v>
+      </c>
+      <c r="G749" t="inlineStr">
+        <is>
+          <t>ぐっちゃん（チャイマフィ）</t>
+        </is>
+      </c>
+      <c r="H749" t="inlineStr">
+        <is>
+          <t>お久し</t>
+        </is>
+      </c>
+      <c r="I749" t="inlineStr">
+        <is>
+          <t>来ました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>20:57:58</t>
+        </is>
+      </c>
+      <c r="D750" t="n">
+        <v>27992</v>
+      </c>
+      <c r="E750" t="inlineStr">
+        <is>
+          <t>えぬ</t>
+        </is>
+      </c>
+      <c r="F750" t="n">
+        <v>3</v>
+      </c>
+      <c r="G750" t="inlineStr">
+        <is>
+          <t>えぬ</t>
+        </is>
+      </c>
+      <c r="H750" t="inlineStr">
+        <is>
+          <t>まったりしに</t>
+        </is>
+      </c>
+      <c r="I750" t="inlineStr">
+        <is>
+          <t>いきます</t>
+        </is>
+      </c>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>21:39:57</t>
+        </is>
+      </c>
+      <c r="D751" t="n">
+        <v>27996</v>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>オリーブ</t>
+        </is>
+      </c>
+      <c r="F751" t="n">
+        <v>1</v>
+      </c>
+      <c r="G751" t="inlineStr">
+        <is>
+          <t>オリーブ</t>
+        </is>
+      </c>
+      <c r="H751" t="inlineStr">
+        <is>
+          <t>はじめて</t>
+        </is>
+      </c>
+      <c r="I751" t="inlineStr">
+        <is>
+          <t>面白いお店探して来ました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>22:02:41</t>
+        </is>
+      </c>
+      <c r="D752" t="n">
+        <v>27998</v>
+      </c>
+      <c r="E752" t="inlineStr">
+        <is>
+          <t>げんき</t>
+        </is>
+      </c>
+      <c r="F752" t="n">
+        <v>1</v>
+      </c>
+      <c r="G752" t="inlineStr">
+        <is>
+          <t>げんき</t>
+        </is>
+      </c>
+      <c r="H752" t="inlineStr">
+        <is>
+          <t>気になって</t>
+        </is>
+      </c>
+      <c r="I752" t="inlineStr">
+        <is>
+          <t>遊びに来てみました</t>
+        </is>
+      </c>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>22:23:55</t>
+        </is>
+      </c>
+      <c r="D753" t="n">
+        <v>28000</v>
+      </c>
+      <c r="E753" t="inlineStr">
+        <is>
+          <t>えーたろ</t>
+        </is>
+      </c>
+      <c r="F753" t="n">
+        <v>1</v>
+      </c>
+      <c r="G753" t="inlineStr">
+        <is>
+          <t>えーたろ</t>
+        </is>
+      </c>
+      <c r="H753" t="inlineStr">
+        <is>
+          <t>飲みに</t>
+        </is>
+      </c>
+      <c r="I753" t="inlineStr">
+        <is>
+          <t>来ました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>22:25:37</t>
+        </is>
+      </c>
+      <c r="D754" t="n">
+        <v>28001</v>
+      </c>
+      <c r="E754" t="inlineStr">
+        <is>
+          <t>テクノ</t>
+        </is>
+      </c>
+      <c r="F754" t="n">
+        <v>12</v>
+      </c>
+      <c r="G754" t="inlineStr">
+        <is>
+          <t>テクノ</t>
+        </is>
+      </c>
+      <c r="H754" t="inlineStr">
+        <is>
+          <t>ハイボールを</t>
+        </is>
+      </c>
+      <c r="I754" t="inlineStr">
+        <is>
+          <t>ください</t>
+        </is>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>22:55:40</t>
+        </is>
+      </c>
+      <c r="D755" t="n">
+        <v>28004</v>
+      </c>
+      <c r="E755" t="inlineStr">
+        <is>
+          <t>大塚</t>
+        </is>
+      </c>
+      <c r="F755" t="n">
+        <v>2</v>
+      </c>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>大塚</t>
+        </is>
+      </c>
+      <c r="H755" t="inlineStr">
+        <is>
+          <t>アゲアゲで</t>
+        </is>
+      </c>
+      <c r="I755" t="inlineStr">
+        <is>
+          <t>きたよーん</t>
+        </is>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>23:54:36</t>
+        </is>
+      </c>
+      <c r="D756" t="n">
+        <v>28006</v>
+      </c>
+      <c r="E756" t="inlineStr">
+        <is>
+          <t>るい</t>
+        </is>
+      </c>
+      <c r="F756" t="n">
+        <v>5</v>
+      </c>
+      <c r="G756" t="inlineStr">
+        <is>
+          <t>るい</t>
+        </is>
+      </c>
+      <c r="H756" t="inlineStr">
+        <is>
+          <t>ショー帰りに</t>
+        </is>
+      </c>
+      <c r="I756" t="inlineStr">
+        <is>
+          <t>きたよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>02:48:31</t>
+        </is>
+      </c>
+      <c r="D757" t="n">
+        <v>28008</v>
+      </c>
+      <c r="E757" t="inlineStr">
+        <is>
+          <t>ちぇちぇ＆ガールズ</t>
+        </is>
+      </c>
+      <c r="F757" t="n">
+        <v>1</v>
+      </c>
+      <c r="G757" t="inlineStr">
+        <is>
+          <t>ちぇちぇ＆ガールズ</t>
+        </is>
+      </c>
+      <c r="H757" t="inlineStr">
+        <is>
+          <t>新規女子連れて</t>
+        </is>
+      </c>
+      <c r="I757" t="inlineStr">
+        <is>
+          <t>来ました！！！！</t>
         </is>
       </c>
     </row>
@@ -52352,7 +53197,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D414"/>
+  <dimension ref="A1:D419"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52384,7 +53229,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -52393,7 +53238,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
@@ -52404,7 +53249,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -52413,7 +53258,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
@@ -52464,7 +53309,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -52473,7 +53318,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
@@ -52860,7 +53705,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>カズ</t>
+          <t>るい</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -52873,18 +53718,18 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TKC</t>
+          <t>カズ</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -52893,14 +53738,14 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>bee</t>
+          <t>TKC</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -52913,14 +53758,14 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>かな</t>
+          <t>bee</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -52928,19 +53773,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>くれは</t>
+          <t>かな</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -52948,19 +53793,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>さとる</t>
+          <t>くれは</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -52968,19 +53813,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>すず</t>
+          <t>さとる</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -52988,19 +53833,19 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>てくのちゃん</t>
+          <t>すず</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -53008,19 +53853,19 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>でで</t>
+          <t>てくのちゃん</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -53028,7 +53873,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -53040,7 +53885,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>まいなちゅ</t>
+          <t>でで</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -53048,19 +53893,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ましゅ社長</t>
+          <t>まいなちゅ</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -53068,19 +53913,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>まーくん</t>
+          <t>ましゅ社長</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -53088,19 +53933,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ゆうき</t>
+          <t>まーくん</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -53108,19 +53953,19 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ゆずきん</t>
+          <t>ゆうき</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -53128,19 +53973,19 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>るい</t>
+          <t>ゆずきん</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -53148,12 +53993,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
@@ -53340,7 +54185,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>さと</t>
+          <t>えぬ</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -53348,19 +54193,19 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>しゅん</t>
+          <t>さと</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -53368,19 +54213,19 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>すー</t>
+          <t>しゅん</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -53388,19 +54233,19 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>すーさん</t>
+          <t>すー</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -53408,19 +54253,19 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>たかやまん</t>
+          <t>すーさん</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -53428,19 +54273,19 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>だいご</t>
+          <t>たかやまん</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -53448,19 +54293,19 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ちゃそたけ</t>
+          <t>だいご</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -53468,19 +54313,19 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>なな</t>
+          <t>ちゃそたけ</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -53488,7 +54333,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -53500,7 +54345,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ひがんたん</t>
+          <t>なな</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -53508,19 +54353,19 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ふくちゃん</t>
+          <t>ひがんたん</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -53528,19 +54373,19 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>まなみ</t>
+          <t>ふくちゃん</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -53548,19 +54393,19 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>まゆ</t>
+          <t>まなみ</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -53568,19 +54413,19 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>もっぷ</t>
+          <t>まゆ</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -53588,19 +54433,19 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>よしお</t>
+          <t>もっぷ</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -53608,19 +54453,19 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>よしおたん</t>
+          <t>よしお</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -53628,19 +54473,19 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>よしやん</t>
+          <t>よしおたん</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -53653,14 +54498,14 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>りょう</t>
+          <t>よしやん</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -53668,19 +54513,19 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>れいら</t>
+          <t>りょう</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -53688,19 +54533,19 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>カー</t>
+          <t>れいら</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -53708,19 +54553,19 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>キムとドMみい</t>
+          <t>カー</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -53728,19 +54573,19 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ケン</t>
+          <t>キムとドMみい</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -53748,19 +54593,19 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>コテッチャン</t>
+          <t>ケン</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -53768,19 +54613,19 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>タツヤ</t>
+          <t>コテッチャン</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -53793,14 +54638,14 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>マロ</t>
+          <t>タツヤ</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -53808,19 +54653,19 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ミコト</t>
+          <t>マロ</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -53828,39 +54673,39 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>ミコト</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Bee</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -53868,19 +54713,19 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>Bee</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -53893,14 +54738,14 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>あさみん</t>
+          <t>−</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -53908,19 +54753,19 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>あっくん</t>
+          <t>あさみん</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -53928,19 +54773,19 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>あゆ</t>
+          <t>あっくん</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -53948,19 +54793,19 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>あんこ</t>
+          <t>あゆ</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -53968,19 +54813,19 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>いっちゃん</t>
+          <t>あんこ</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -53988,19 +54833,19 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>いぬ</t>
+          <t>いっちゃん</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -54013,14 +54858,14 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>えぬ</t>
+          <t>いぬ</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -54028,12 +54873,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
@@ -54840,7 +55685,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>愛とスケベの戦士</t>
+          <t>大塚</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -54848,39 +55693,39 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>5人衆</t>
+          <t>愛とスケベの戦士</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>5人衆</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -54888,19 +55733,19 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>EVANS×２</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -54908,19 +55753,19 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>HGN</t>
+          <t>EVANS×２</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -54928,19 +55773,19 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>JPTR</t>
+          <t>HGN</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -54948,19 +55793,19 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>JPTR</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -54968,19 +55813,19 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>KUMA</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -54988,19 +55833,19 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>KUMA</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -55008,19 +55853,19 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -55028,19 +55873,19 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>NMGK</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -55048,19 +55893,19 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>N氏御一行</t>
+          <t>NMGK</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -55068,19 +55913,19 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>SIKUSENAチャンネルヒロキ</t>
+          <t>N氏御一行</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -55088,19 +55933,19 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>STR</t>
+          <t>SIKUSENAチャンネルヒロキ</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -55108,19 +55953,19 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>TARU</t>
+          <t>STR</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -55128,19 +55973,19 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>TARU</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -55148,19 +55993,19 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Tやま</t>
+          <t>TT</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -55168,19 +56013,19 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>Tやま</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -55188,19 +56033,19 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>YZK</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -55208,19 +56053,19 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>hikari</t>
+          <t>YZK</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -55228,19 +56073,19 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>nuri</t>
+          <t>hikari</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -55248,19 +56093,19 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>sho</t>
+          <t>nuri</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -55268,19 +56113,19 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>★Zakk★</t>
+          <t>sho</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -55288,19 +56133,19 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>あき</t>
+          <t>★Zakk★</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -55308,19 +56153,19 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>あさみ</t>
+          <t>あき</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -55328,19 +56173,19 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>あす</t>
+          <t>あさみ</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -55348,19 +56193,19 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>あにー</t>
+          <t>あす</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -55368,19 +56213,19 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>あまねちゃん</t>
+          <t>あにー</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -55388,19 +56233,19 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ありす</t>
+          <t>あまねちゃん</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -55408,19 +56253,19 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>いおり</t>
+          <t>ありす</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -55428,19 +56273,19 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>いけちゃん</t>
+          <t>いおり</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -55448,19 +56293,19 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>いぶお</t>
+          <t>いけちゃん</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -55468,19 +56313,19 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>うらら</t>
+          <t>いぶお</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -55488,19 +56333,19 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>えび</t>
+          <t>うらら</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -55508,19 +56353,19 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>おじき</t>
+          <t>えび</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -55528,19 +56373,19 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>おじきち</t>
+          <t>えーたろ</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -55548,19 +56393,19 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>おすー</t>
+          <t>おじき</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -55568,19 +56413,19 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>おちんぽベルセルク</t>
+          <t>おじきち</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -55588,19 +56433,19 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>おにゃん</t>
+          <t>おすー</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -55608,19 +56453,19 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>おにゃんにゃん</t>
+          <t>おちんぽベルセルク</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -55628,19 +56473,19 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>おばし</t>
+          <t>おにゃん</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -55648,19 +56493,19 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>おもち</t>
+          <t>おにゃんにゃん</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -55668,19 +56513,19 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>かける</t>
+          <t>おばし</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -55688,19 +56533,19 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>かずき</t>
+          <t>おもち</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -55708,19 +56553,19 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>かず＆TKC＆のんのん</t>
+          <t>かける</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -55728,19 +56573,19 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>かな(絶ちゃん</t>
+          <t>かずき</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -55748,19 +56593,19 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>かな(絶ちゃん)/おっつん</t>
+          <t>かず＆TKC＆のんのん</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -55768,19 +56613,19 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>がん</t>
+          <t>かな(絶ちゃん</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -55788,19 +56633,19 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>きむさん</t>
+          <t>かな(絶ちゃん)/おっつん</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -55808,19 +56653,19 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>きむむ</t>
+          <t>がん</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -55828,19 +56673,19 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>きむら</t>
+          <t>きむさん</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -55848,19 +56693,19 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>きょうちゃん</t>
+          <t>きむむ</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -55868,19 +56713,19 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>きんたまよ</t>
+          <t>きむら</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -55888,19 +56733,19 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>くっぱ</t>
+          <t>きょうちゃん</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -55908,19 +56753,19 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>くま</t>
+          <t>きんたまよ</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -55928,19 +56773,19 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>くり</t>
+          <t>くっぱ</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -55960,7 +56805,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ぐっちゃん</t>
+          <t>くま</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -55968,19 +56813,19 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>けい</t>
+          <t>くり</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -55988,19 +56833,19 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>けいちゃん</t>
+          <t>ぐっちゃん</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -56008,19 +56853,19 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>けんけん</t>
+          <t>ぐっちゃん（チャイマフィ）</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -56028,19 +56873,19 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>げん</t>
+          <t>けい</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -56048,19 +56893,19 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>こう</t>
+          <t>けいちゃん</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -56068,19 +56913,19 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>こうた</t>
+          <t>けんけん</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -56088,19 +56933,19 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>こてつ</t>
+          <t>げん</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -56108,19 +56953,19 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>ことねえ</t>
+          <t>げんき</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -56128,19 +56973,19 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ことり</t>
+          <t>こう</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -56148,19 +56993,19 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ごん</t>
+          <t>こうた</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -56168,19 +57013,19 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>さかもと</t>
+          <t>こてつ</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -56188,19 +57033,19 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>さくら</t>
+          <t>ことねえ</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -56208,19 +57053,19 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>さとりゅ</t>
+          <t>ことり</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -56228,19 +57073,19 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>さな</t>
+          <t>ごん</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -56248,19 +57093,19 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>さない</t>
+          <t>さかもと</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -56268,19 +57113,19 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>さや</t>
+          <t>さくら</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -56288,19 +57133,19 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>しずか</t>
+          <t>さとりゅ</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -56308,19 +57153,19 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>しりゅう</t>
+          <t>さな</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -56328,19 +57173,19 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>じん</t>
+          <t>さない</t>
         </is>
       </c>
       <c r="B200" t="n">
@@ -56348,19 +57193,19 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>せいら</t>
+          <t>さや</t>
         </is>
       </c>
       <c r="B201" t="n">
@@ -56368,19 +57213,19 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>たいせー</t>
+          <t>しずか</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -56388,19 +57233,19 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>たか</t>
+          <t>しりゅう</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -56408,19 +57253,19 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>たかし</t>
+          <t>じん</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -56440,7 +57285,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>たかち</t>
+          <t>せいら</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -56448,19 +57293,19 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>たく</t>
+          <t>たいせー</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -56468,19 +57313,19 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>たけ</t>
+          <t>たか</t>
         </is>
       </c>
       <c r="B207" t="n">
@@ -56488,19 +57333,19 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>たけし</t>
+          <t>たかし</t>
         </is>
       </c>
       <c r="B208" t="n">
@@ -56508,19 +57353,19 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>たつ</t>
+          <t>たかち</t>
         </is>
       </c>
       <c r="B209" t="n">
@@ -56528,19 +57373,19 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>たつお</t>
+          <t>たく</t>
         </is>
       </c>
       <c r="B210" t="n">
@@ -56548,19 +57393,19 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>たます</t>
+          <t>たけ</t>
         </is>
       </c>
       <c r="B211" t="n">
@@ -56568,19 +57413,19 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>たろー</t>
+          <t>たけし</t>
         </is>
       </c>
       <c r="B212" t="n">
@@ -56588,19 +57433,19 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>だいさく</t>
+          <t>たつ</t>
         </is>
       </c>
       <c r="B213" t="n">
@@ -56608,19 +57453,19 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>だいざく</t>
+          <t>たつお</t>
         </is>
       </c>
       <c r="B214" t="n">
@@ -56628,19 +57473,19 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>だいち</t>
+          <t>たます</t>
         </is>
       </c>
       <c r="B215" t="n">
@@ -56648,19 +57493,19 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>ちぇちぇ</t>
+          <t>たろー</t>
         </is>
       </c>
       <c r="B216" t="n">
@@ -56668,19 +57513,19 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>てくのっち</t>
+          <t>だいさく</t>
         </is>
       </c>
       <c r="B217" t="n">
@@ -56688,19 +57533,19 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>てっちゃん</t>
+          <t>だいざく</t>
         </is>
       </c>
       <c r="B218" t="n">
@@ -56708,19 +57553,19 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>てつ</t>
+          <t>だいち</t>
         </is>
       </c>
       <c r="B219" t="n">
@@ -56740,7 +57585,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>てつじ</t>
+          <t>ちぇちぇ</t>
         </is>
       </c>
       <c r="B220" t="n">
@@ -56748,19 +57593,19 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>てる</t>
+          <t>ちぇちぇ＆ガールズ</t>
         </is>
       </c>
       <c r="B221" t="n">
@@ -56768,19 +57613,19 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>でかかわ</t>
+          <t>てくのっち</t>
         </is>
       </c>
       <c r="B222" t="n">
@@ -56788,19 +57633,19 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>ででたゃ</t>
+          <t>てっちゃん</t>
         </is>
       </c>
       <c r="B223" t="n">
@@ -56808,19 +57653,19 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>とうや</t>
+          <t>てつ</t>
         </is>
       </c>
       <c r="B224" t="n">
@@ -56828,19 +57673,19 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>とおちゃん</t>
+          <t>てつじ</t>
         </is>
       </c>
       <c r="B225" t="n">
@@ -56848,19 +57693,19 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>とっしー</t>
+          <t>てる</t>
         </is>
       </c>
       <c r="B226" t="n">
@@ -56868,19 +57713,19 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>とも</t>
+          <t>でかかわ</t>
         </is>
       </c>
       <c r="B227" t="n">
@@ -56888,19 +57733,19 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>ともち</t>
+          <t>ででたゃ</t>
         </is>
       </c>
       <c r="B228" t="n">
@@ -56908,19 +57753,19 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>ともひろ</t>
+          <t>とうや</t>
         </is>
       </c>
       <c r="B229" t="n">
@@ -56928,19 +57773,19 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>ともや</t>
+          <t>とおちゃん</t>
         </is>
       </c>
       <c r="B230" t="n">
@@ -56948,19 +57793,19 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>ともゆき</t>
+          <t>とっしー</t>
         </is>
       </c>
       <c r="B231" t="n">
@@ -56968,19 +57813,19 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>とーり</t>
+          <t>とも</t>
         </is>
       </c>
       <c r="B232" t="n">
@@ -56988,19 +57833,19 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>どえむちゃん</t>
+          <t>ともち</t>
         </is>
       </c>
       <c r="B233" t="n">
@@ -57008,19 +57853,19 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>ながとも</t>
+          <t>ともひろ</t>
         </is>
       </c>
       <c r="B234" t="n">
@@ -57028,19 +57873,19 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>なべ</t>
+          <t>ともや</t>
         </is>
       </c>
       <c r="B235" t="n">
@@ -57048,19 +57893,19 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>にこちん</t>
+          <t>ともゆき</t>
         </is>
       </c>
       <c r="B236" t="n">
@@ -57068,19 +57913,19 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>にゃんまげ</t>
+          <t>とーり</t>
         </is>
       </c>
       <c r="B237" t="n">
@@ -57088,19 +57933,19 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>にょ</t>
+          <t>どえむちゃん</t>
         </is>
       </c>
       <c r="B238" t="n">
@@ -57108,19 +57953,19 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>ねここ</t>
+          <t>ながとも</t>
         </is>
       </c>
       <c r="B239" t="n">
@@ -57128,19 +57973,19 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>のぼ</t>
+          <t>なべ</t>
         </is>
       </c>
       <c r="B240" t="n">
@@ -57148,19 +57993,19 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>のり</t>
+          <t>にこちん</t>
         </is>
       </c>
       <c r="B241" t="n">
@@ -57168,19 +58013,19 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>はち</t>
+          <t>にゃんまげ</t>
         </is>
       </c>
       <c r="B242" t="n">
@@ -57188,19 +58033,19 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>はな</t>
+          <t>にょ</t>
         </is>
       </c>
       <c r="B243" t="n">
@@ -57208,19 +58053,19 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>はなちゃん</t>
+          <t>ねここ</t>
         </is>
       </c>
       <c r="B244" t="n">
@@ -57228,19 +58073,19 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>はなまる</t>
+          <t>のぼ</t>
         </is>
       </c>
       <c r="B245" t="n">
@@ -57248,19 +58093,19 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>はにーちゃん</t>
+          <t>のり</t>
         </is>
       </c>
       <c r="B246" t="n">
@@ -57268,19 +58113,19 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>はんまー</t>
+          <t>はち</t>
         </is>
       </c>
       <c r="B247" t="n">
@@ -57288,19 +58133,19 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>ひがんちゃん</t>
+          <t>はな</t>
         </is>
       </c>
       <c r="B248" t="n">
@@ -57308,19 +58153,19 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>ひったん</t>
+          <t>はなちゃん</t>
         </is>
       </c>
       <c r="B249" t="n">
@@ -57328,19 +58173,19 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>ひろし</t>
+          <t>はなまる</t>
         </is>
       </c>
       <c r="B250" t="n">
@@ -57348,19 +58193,19 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>ひろとも</t>
+          <t>はにーちゃん</t>
         </is>
       </c>
       <c r="B251" t="n">
@@ -57368,19 +58213,19 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>ふく</t>
+          <t>はんまー</t>
         </is>
       </c>
       <c r="B252" t="n">
@@ -57388,19 +58233,19 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>ふみ</t>
+          <t>ひがんちゃん</t>
         </is>
       </c>
       <c r="B253" t="n">
@@ -57408,19 +58253,19 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>ぷらぐいん</t>
+          <t>ひったん</t>
         </is>
       </c>
       <c r="B254" t="n">
@@ -57428,19 +58273,19 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>ぺぺ</t>
+          <t>ひろし</t>
         </is>
       </c>
       <c r="B255" t="n">
@@ -57448,19 +58293,19 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>まいまいまいまい</t>
+          <t>ひろとも</t>
         </is>
       </c>
       <c r="B256" t="n">
@@ -57468,19 +58313,19 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>まいまいん</t>
+          <t>ふく</t>
         </is>
       </c>
       <c r="B257" t="n">
@@ -57488,19 +58333,19 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>まおし</t>
+          <t>ふみ</t>
         </is>
       </c>
       <c r="B258" t="n">
@@ -57520,7 +58365,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>ます</t>
+          <t>ぷらぐいん</t>
         </is>
       </c>
       <c r="B259" t="n">
@@ -57528,19 +58373,19 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>ますみ</t>
+          <t>ぺぺ</t>
         </is>
       </c>
       <c r="B260" t="n">
@@ -57548,19 +58393,19 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>まっする</t>
+          <t>まいまいまいまい</t>
         </is>
       </c>
       <c r="B261" t="n">
@@ -57568,19 +58413,19 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>まっぴー</t>
+          <t>まいまいん</t>
         </is>
       </c>
       <c r="B262" t="n">
@@ -57588,19 +58433,19 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>まな</t>
+          <t>まおし</t>
         </is>
       </c>
       <c r="B263" t="n">
@@ -57608,19 +58453,19 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>まみ</t>
+          <t>ます</t>
         </is>
       </c>
       <c r="B264" t="n">
@@ -57628,19 +58473,19 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>まや</t>
+          <t>ますみ</t>
         </is>
       </c>
       <c r="B265" t="n">
@@ -57648,19 +58493,19 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>まり</t>
+          <t>まっする</t>
         </is>
       </c>
       <c r="B266" t="n">
@@ -57668,19 +58513,19 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>まりーな</t>
+          <t>まっぴー</t>
         </is>
       </c>
       <c r="B267" t="n">
@@ -57688,19 +58533,19 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>まー</t>
+          <t>まな</t>
         </is>
       </c>
       <c r="B268" t="n">
@@ -57708,19 +58553,19 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>まーさん</t>
+          <t>まみ</t>
         </is>
       </c>
       <c r="B269" t="n">
@@ -57728,19 +58573,19 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>まーちゃん</t>
+          <t>まや</t>
         </is>
       </c>
       <c r="B270" t="n">
@@ -57748,19 +58593,19 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>みかん</t>
+          <t>まり</t>
         </is>
       </c>
       <c r="B271" t="n">
@@ -57768,19 +58613,19 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>みずき</t>
+          <t>まりーな</t>
         </is>
       </c>
       <c r="B272" t="n">
@@ -57788,19 +58633,19 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>みちゃ</t>
+          <t>まー</t>
         </is>
       </c>
       <c r="B273" t="n">
@@ -57808,19 +58653,19 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>みっちー</t>
+          <t>まーさん</t>
         </is>
       </c>
       <c r="B274" t="n">
@@ -57828,19 +58673,19 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>みなつちん</t>
+          <t>まーちゃん</t>
         </is>
       </c>
       <c r="B275" t="n">
@@ -57848,19 +58693,19 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>みみ</t>
+          <t>みかん</t>
         </is>
       </c>
       <c r="B276" t="n">
@@ -57868,19 +58713,19 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>みやび</t>
+          <t>みずき</t>
         </is>
       </c>
       <c r="B277" t="n">
@@ -57888,19 +58733,19 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>みゆき</t>
+          <t>みちゃ</t>
         </is>
       </c>
       <c r="B278" t="n">
@@ -57908,19 +58753,19 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>みらい</t>
+          <t>みっちー</t>
         </is>
       </c>
       <c r="B279" t="n">
@@ -57928,19 +58773,19 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>みるこ</t>
+          <t>みなつちん</t>
         </is>
       </c>
       <c r="B280" t="n">
@@ -57948,19 +58793,19 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>みん</t>
+          <t>みみ</t>
         </is>
       </c>
       <c r="B281" t="n">
@@ -57968,19 +58813,19 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>みーみ</t>
+          <t>みやび</t>
         </is>
       </c>
       <c r="B282" t="n">
@@ -57988,19 +58833,19 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>もかちんぽぽ</t>
+          <t>みゆき</t>
         </is>
       </c>
       <c r="B283" t="n">
@@ -58008,19 +58853,19 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>もっち</t>
+          <t>みらい</t>
         </is>
       </c>
       <c r="B284" t="n">
@@ -58028,19 +58873,19 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>もっぴー</t>
+          <t>みるこ</t>
         </is>
       </c>
       <c r="B285" t="n">
@@ -58048,19 +58893,19 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>もと</t>
+          <t>みん</t>
         </is>
       </c>
       <c r="B286" t="n">
@@ -58068,19 +58913,19 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>ももたろ</t>
+          <t>みーみ</t>
         </is>
       </c>
       <c r="B287" t="n">
@@ -58088,19 +58933,19 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>ゆい</t>
+          <t>もかちんぽぽ</t>
         </is>
       </c>
       <c r="B288" t="n">
@@ -58108,19 +58953,19 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>ゆうじ</t>
+          <t>もっち</t>
         </is>
       </c>
       <c r="B289" t="n">
@@ -58128,19 +58973,19 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>ゆうた</t>
+          <t>もっぴー</t>
         </is>
       </c>
       <c r="B290" t="n">
@@ -58148,19 +58993,19 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>ゆうたん</t>
+          <t>もと</t>
         </is>
       </c>
       <c r="B291" t="n">
@@ -58168,19 +59013,19 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>ゆうと</t>
+          <t>ももたろ</t>
         </is>
       </c>
       <c r="B292" t="n">
@@ -58188,19 +59033,19 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>ゆうや</t>
+          <t>ゆい</t>
         </is>
       </c>
       <c r="B293" t="n">
@@ -58208,19 +59053,19 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>ゆかり</t>
+          <t>ゆうじ</t>
         </is>
       </c>
       <c r="B294" t="n">
@@ -58228,19 +59073,19 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>ゆきお</t>
+          <t>ゆうた</t>
         </is>
       </c>
       <c r="B295" t="n">
@@ -58248,19 +59093,19 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>ゆきんこ</t>
+          <t>ゆうたん</t>
         </is>
       </c>
       <c r="B296" t="n">
@@ -58268,19 +59113,19 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>ゆすき</t>
+          <t>ゆうと</t>
         </is>
       </c>
       <c r="B297" t="n">
@@ -58288,19 +59133,19 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>ゆず</t>
+          <t>ゆうや</t>
         </is>
       </c>
       <c r="B298" t="n">
@@ -58308,19 +59153,19 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>ゆずきちゃん</t>
+          <t>ゆかり</t>
         </is>
       </c>
       <c r="B299" t="n">
@@ -58328,19 +59173,19 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>ゆずき＆ましゅ</t>
+          <t>ゆきお</t>
         </is>
       </c>
       <c r="B300" t="n">
@@ -58348,19 +59193,19 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>ゆっち</t>
+          <t>ゆきんこ</t>
         </is>
       </c>
       <c r="B301" t="n">
@@ -58368,19 +59213,19 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>ゆぴ</t>
+          <t>ゆすき</t>
         </is>
       </c>
       <c r="B302" t="n">
@@ -58388,19 +59233,19 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>ゆり</t>
+          <t>ゆず</t>
         </is>
       </c>
       <c r="B303" t="n">
@@ -58420,7 +59265,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>ゆりな</t>
+          <t>ゆずきちゃん</t>
         </is>
       </c>
       <c r="B304" t="n">
@@ -58428,19 +59273,19 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>ゆん</t>
+          <t>ゆずき＆ましゅ</t>
         </is>
       </c>
       <c r="B305" t="n">
@@ -58448,19 +59293,19 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>よこい</t>
+          <t>ゆっち</t>
         </is>
       </c>
       <c r="B306" t="n">
@@ -58468,19 +59313,19 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>よちお</t>
+          <t>ゆぴ</t>
         </is>
       </c>
       <c r="B307" t="n">
@@ -58488,19 +59333,19 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>らいと</t>
+          <t>ゆり</t>
         </is>
       </c>
       <c r="B308" t="n">
@@ -58508,19 +59353,19 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>らうら</t>
+          <t>ゆりな</t>
         </is>
       </c>
       <c r="B309" t="n">
@@ -58528,19 +59373,19 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>らお</t>
+          <t>ゆん</t>
         </is>
       </c>
       <c r="B310" t="n">
@@ -58548,19 +59393,19 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>りえ</t>
+          <t>よこい</t>
         </is>
       </c>
       <c r="B311" t="n">
@@ -58568,19 +59413,19 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>りく</t>
+          <t>よちお</t>
         </is>
       </c>
       <c r="B312" t="n">
@@ -58588,19 +59433,19 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>りさ</t>
+          <t>らいと</t>
         </is>
       </c>
       <c r="B313" t="n">
@@ -58608,19 +59453,19 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>りゅうくん</t>
+          <t>らうら</t>
         </is>
       </c>
       <c r="B314" t="n">
@@ -58628,19 +59473,19 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>りゅーちゃん</t>
+          <t>らお</t>
         </is>
       </c>
       <c r="B315" t="n">
@@ -58648,19 +59493,19 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>りょうが</t>
+          <t>りえ</t>
         </is>
       </c>
       <c r="B316" t="n">
@@ -58668,19 +59513,19 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>りょうちゃん</t>
+          <t>りく</t>
         </is>
       </c>
       <c r="B317" t="n">
@@ -58688,19 +59533,19 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>りょーが</t>
+          <t>りさ</t>
         </is>
       </c>
       <c r="B318" t="n">
@@ -58708,19 +59553,19 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>りりこ</t>
+          <t>りゅうくん</t>
         </is>
       </c>
       <c r="B319" t="n">
@@ -58728,19 +59573,19 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>りん＆ゆち</t>
+          <t>りゅーちゃん</t>
         </is>
       </c>
       <c r="B320" t="n">
@@ -58748,19 +59593,19 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>れー</t>
+          <t>りょうが</t>
         </is>
       </c>
       <c r="B321" t="n">
@@ -58768,19 +59613,19 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>アイ</t>
+          <t>りょうちゃん</t>
         </is>
       </c>
       <c r="B322" t="n">
@@ -58788,19 +59633,19 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>アイちゃん</t>
+          <t>りょーが</t>
         </is>
       </c>
       <c r="B323" t="n">
@@ -58808,19 +59653,19 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>アキ</t>
+          <t>りりこ</t>
         </is>
       </c>
       <c r="B324" t="n">
@@ -58828,19 +59673,19 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>アナルプリンス</t>
+          <t>りん＆ゆち</t>
         </is>
       </c>
       <c r="B325" t="n">
@@ -58848,19 +59693,19 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>イエモン</t>
+          <t>れー</t>
         </is>
       </c>
       <c r="B326" t="n">
@@ -58868,19 +59713,19 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>イブオ</t>
+          <t>アイ</t>
         </is>
       </c>
       <c r="B327" t="n">
@@ -58888,19 +59733,19 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>エーイチ</t>
+          <t>アイちゃん</t>
         </is>
       </c>
       <c r="B328" t="n">
@@ -58908,19 +59753,19 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>オ・スー</t>
+          <t>アキ</t>
         </is>
       </c>
       <c r="B329" t="n">
@@ -58928,19 +59773,19 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>カイト</t>
+          <t>アナルプリンス</t>
         </is>
       </c>
       <c r="B330" t="n">
@@ -58948,19 +59793,19 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>カズヤ</t>
+          <t>イエモン</t>
         </is>
       </c>
       <c r="B331" t="n">
@@ -58968,19 +59813,19 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>カミさん</t>
+          <t>イブオ</t>
         </is>
       </c>
       <c r="B332" t="n">
@@ -58988,19 +59833,19 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>カモリ</t>
+          <t>エーイチ</t>
         </is>
       </c>
       <c r="B333" t="n">
@@ -59008,19 +59853,19 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>キムさん</t>
+          <t>オリーブ</t>
         </is>
       </c>
       <c r="B334" t="n">
@@ -59028,19 +59873,19 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>キムとどえむちゃん</t>
+          <t>オ・スー</t>
         </is>
       </c>
       <c r="B335" t="n">
@@ -59048,19 +59893,19 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>キムとまゆ</t>
+          <t>カイト</t>
         </is>
       </c>
       <c r="B336" t="n">
@@ -59068,19 +59913,19 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>キムとドMまいまい妹</t>
+          <t>カズヤ</t>
         </is>
       </c>
       <c r="B337" t="n">
@@ -59088,19 +59933,19 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>キムとドMむい</t>
+          <t>カミさん</t>
         </is>
       </c>
       <c r="B338" t="n">
@@ -59108,19 +59953,19 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>キムとドM女R</t>
+          <t>カモリ</t>
         </is>
       </c>
       <c r="B339" t="n">
@@ -59128,19 +59973,19 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>キムと奴隷</t>
+          <t>キムさん</t>
         </is>
       </c>
       <c r="B340" t="n">
@@ -59148,19 +59993,19 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>キムと新しい奴隷ちゃん</t>
+          <t>キムとどえむちゃん</t>
         </is>
       </c>
       <c r="B341" t="n">
@@ -59168,19 +60013,19 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>キム＆むい</t>
+          <t>キムとまゆ</t>
         </is>
       </c>
       <c r="B342" t="n">
@@ -59188,19 +60033,19 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>クアレ</t>
+          <t>キムとドMまいまい妹</t>
         </is>
       </c>
       <c r="B343" t="n">
@@ -59208,19 +60053,19 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>クロちゃん</t>
+          <t>キムとドMむい</t>
         </is>
       </c>
       <c r="B344" t="n">
@@ -59228,19 +60073,19 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>クワレ</t>
+          <t>キムとドM女R</t>
         </is>
       </c>
       <c r="B345" t="n">
@@ -59248,19 +60093,19 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>ケケ</t>
+          <t>キムと奴隷</t>
         </is>
       </c>
       <c r="B346" t="n">
@@ -59268,19 +60113,19 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>ゲン</t>
+          <t>キムと新しい奴隷ちゃん</t>
         </is>
       </c>
       <c r="B347" t="n">
@@ -59288,19 +60133,19 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>コオリ</t>
+          <t>キム＆むい</t>
         </is>
       </c>
       <c r="B348" t="n">
@@ -59308,19 +60153,19 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>コマ</t>
+          <t>クアレ</t>
         </is>
       </c>
       <c r="B349" t="n">
@@ -59328,19 +60173,19 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>サトル</t>
+          <t>クロちゃん</t>
         </is>
       </c>
       <c r="B350" t="n">
@@ -59348,19 +60193,19 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>ザッキー</t>
+          <t>クワレ</t>
         </is>
       </c>
       <c r="B351" t="n">
@@ -59368,19 +60213,19 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>シゲ</t>
+          <t>ケケ</t>
         </is>
       </c>
       <c r="B352" t="n">
@@ -59400,7 +60245,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>シュン</t>
+          <t>ゲン</t>
         </is>
       </c>
       <c r="B353" t="n">
@@ -59408,19 +60253,19 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>シュンヤ</t>
+          <t>コオリ</t>
         </is>
       </c>
       <c r="B354" t="n">
@@ -59428,19 +60273,19 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>ジャッキー</t>
+          <t>コマ</t>
         </is>
       </c>
       <c r="B355" t="n">
@@ -59448,19 +60293,19 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>ジョーカー</t>
+          <t>サトル</t>
         </is>
       </c>
       <c r="B356" t="n">
@@ -59468,19 +60313,19 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>タカス</t>
+          <t>ザッキー</t>
         </is>
       </c>
       <c r="B357" t="n">
@@ -59488,19 +60333,19 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>タカ御一行</t>
+          <t>シゲ</t>
         </is>
       </c>
       <c r="B358" t="n">
@@ -59508,19 +60353,19 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>ダイキ</t>
+          <t>シュン</t>
         </is>
       </c>
       <c r="B359" t="n">
@@ -59528,19 +60373,19 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>ダイゴ</t>
+          <t>シュンヤ</t>
         </is>
       </c>
       <c r="B360" t="n">
@@ -59560,7 +60405,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>ダイチ</t>
+          <t>ジャッキー</t>
         </is>
       </c>
       <c r="B361" t="n">
@@ -59568,19 +60413,19 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>チェスカ</t>
+          <t>ジョーカー</t>
         </is>
       </c>
       <c r="B362" t="n">
@@ -59588,19 +60433,19 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>ツシマ</t>
+          <t>タカス</t>
         </is>
       </c>
       <c r="B363" t="n">
@@ -59608,19 +60453,19 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>ツボ</t>
+          <t>タカ御一行</t>
         </is>
       </c>
       <c r="B364" t="n">
@@ -59628,19 +60473,19 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>テクノとポチ</t>
+          <t>ダイキ</t>
         </is>
       </c>
       <c r="B365" t="n">
@@ -59648,19 +60493,19 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>テクノ＆てるくん＆イブオ</t>
+          <t>ダイゴ</t>
         </is>
       </c>
       <c r="B366" t="n">
@@ -59668,19 +60513,19 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>トニー・トニー・チョッパー</t>
+          <t>ダイチ</t>
         </is>
       </c>
       <c r="B367" t="n">
@@ -59688,19 +60533,19 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>トルネードシャーク</t>
+          <t>チェスカ</t>
         </is>
       </c>
       <c r="B368" t="n">
@@ -59708,19 +60553,19 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>ナカヤマヤ</t>
+          <t>ツシマ</t>
         </is>
       </c>
       <c r="B369" t="n">
@@ -59728,19 +60573,19 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>ニト</t>
+          <t>ツボ</t>
         </is>
       </c>
       <c r="B370" t="n">
@@ -59748,19 +60593,19 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>ニャンまげ</t>
+          <t>テクノとポチ</t>
         </is>
       </c>
       <c r="B371" t="n">
@@ -59768,19 +60613,19 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>ハチ</t>
+          <t>テクノ＆てるくん＆イブオ</t>
         </is>
       </c>
       <c r="B372" t="n">
@@ -59788,19 +60633,19 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>ビコー</t>
+          <t>トニー・トニー・チョッパー</t>
         </is>
       </c>
       <c r="B373" t="n">
@@ -59808,19 +60653,19 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>フジ</t>
+          <t>トルネードシャーク</t>
         </is>
       </c>
       <c r="B374" t="n">
@@ -59828,19 +60673,19 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>ペロとペコ</t>
+          <t>ナカヤマヤ</t>
         </is>
       </c>
       <c r="B375" t="n">
@@ -59848,19 +60693,19 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>ボンタ</t>
+          <t>ニト</t>
         </is>
       </c>
       <c r="B376" t="n">
@@ -59868,19 +60713,19 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>ポチ</t>
+          <t>ニャンまげ</t>
         </is>
       </c>
       <c r="B377" t="n">
@@ -59888,19 +60733,19 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>マサ</t>
+          <t>ハチ</t>
         </is>
       </c>
       <c r="B378" t="n">
@@ -59908,19 +60753,19 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>マッチョ</t>
+          <t>ビコー</t>
         </is>
       </c>
       <c r="B379" t="n">
@@ -59928,19 +60773,19 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>ミカミと仲間たち</t>
+          <t>フジ</t>
         </is>
       </c>
       <c r="B380" t="n">
@@ -59948,19 +60793,19 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>ミスター工事マン</t>
+          <t>ペロとペコ</t>
         </is>
       </c>
       <c r="B381" t="n">
@@ -59968,19 +60813,19 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>ミッシ</t>
+          <t>ボンタ</t>
         </is>
       </c>
       <c r="B382" t="n">
@@ -59988,19 +60833,19 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>ミッチー</t>
+          <t>ポチ</t>
         </is>
       </c>
       <c r="B383" t="n">
@@ -60008,19 +60853,19 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>ミルコ</t>
+          <t>マサ</t>
         </is>
       </c>
       <c r="B384" t="n">
@@ -60028,19 +60873,19 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>ミン</t>
+          <t>マッチョ</t>
         </is>
       </c>
       <c r="B385" t="n">
@@ -60048,19 +60893,19 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>モジャ</t>
+          <t>ミカミと仲間たち</t>
         </is>
       </c>
       <c r="B386" t="n">
@@ -60068,19 +60913,19 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>ヤノちゃん</t>
+          <t>ミスター工事マン</t>
         </is>
       </c>
       <c r="B387" t="n">
@@ -60088,19 +60933,19 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>ヤマ</t>
+          <t>ミッシ</t>
         </is>
       </c>
       <c r="B388" t="n">
@@ -60108,19 +60953,19 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>ユウ</t>
+          <t>ミッチー</t>
         </is>
       </c>
       <c r="B389" t="n">
@@ -60128,19 +60973,19 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>ユキ</t>
+          <t>ミルコ</t>
         </is>
       </c>
       <c r="B390" t="n">
@@ -60148,19 +60993,19 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>ユッキー</t>
+          <t>ミン</t>
         </is>
       </c>
       <c r="B391" t="n">
@@ -60168,19 +61013,19 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>ヨシヤ</t>
+          <t>モジャ</t>
         </is>
       </c>
       <c r="B392" t="n">
@@ -60188,19 +61033,19 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>ラオ</t>
+          <t>ヤノちゃん</t>
         </is>
       </c>
       <c r="B393" t="n">
@@ -60208,19 +61053,19 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>リク</t>
+          <t>ヤマ</t>
         </is>
       </c>
       <c r="B394" t="n">
@@ -60228,19 +61073,19 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>リョウ</t>
+          <t>ユウ</t>
         </is>
       </c>
       <c r="B395" t="n">
@@ -60248,19 +61093,19 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>リン</t>
+          <t>ユキ</t>
         </is>
       </c>
       <c r="B396" t="n">
@@ -60268,19 +61113,19 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>ロタポジ</t>
+          <t>ユッキー</t>
         </is>
       </c>
       <c r="B397" t="n">
@@ -60300,7 +61145,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>ローズ</t>
+          <t>ヨシヤ</t>
         </is>
       </c>
       <c r="B398" t="n">
@@ -60308,19 +61153,19 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>偽マイマイ</t>
+          <t>ラオ</t>
         </is>
       </c>
       <c r="B399" t="n">
@@ -60328,19 +61173,19 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>僕と私</t>
+          <t>リク</t>
         </is>
       </c>
       <c r="B400" t="n">
@@ -60348,19 +61193,19 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>名無し</t>
+          <t>リョウ</t>
         </is>
       </c>
       <c r="B401" t="n">
@@ -60368,19 +61213,19 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>大塚</t>
+          <t>リン</t>
         </is>
       </c>
       <c r="B402" t="n">
@@ -60388,19 +61233,19 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>天我迅</t>
+          <t>ロタポジ</t>
         </is>
       </c>
       <c r="B403" t="n">
@@ -60408,19 +61253,19 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>女子三人衆</t>
+          <t>ローズ</t>
         </is>
       </c>
       <c r="B404" t="n">
@@ -60428,19 +61273,19 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>彩 なまがき</t>
+          <t>偽マイマイ</t>
         </is>
       </c>
       <c r="B405" t="n">
@@ -60448,19 +61293,19 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>正装しん</t>
+          <t>僕と私</t>
         </is>
       </c>
       <c r="B406" t="n">
@@ -60468,19 +61313,19 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>海砂利水魚</t>
+          <t>名無し</t>
         </is>
       </c>
       <c r="B407" t="n">
@@ -60488,19 +61333,19 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>田中</t>
+          <t>天我迅</t>
         </is>
       </c>
       <c r="B408" t="n">
@@ -60508,19 +61353,19 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>番</t>
+          <t>女子三人衆</t>
         </is>
       </c>
       <c r="B409" t="n">
@@ -60528,19 +61373,19 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>絶</t>
+          <t>彩 なまがき</t>
         </is>
       </c>
       <c r="B410" t="n">
@@ -60548,19 +61393,19 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>絶ちゃん</t>
+          <t>正装しん</t>
         </is>
       </c>
       <c r="B411" t="n">
@@ -60580,7 +61425,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>美優</t>
+          <t>海砂利水魚</t>
         </is>
       </c>
       <c r="B412" t="n">
@@ -60588,19 +61433,19 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>赤ちゃん</t>
+          <t>田中</t>
         </is>
       </c>
       <c r="B413" t="n">
@@ -60608,30 +61453,130 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
+          <t>番</t>
+        </is>
+      </c>
+      <c r="B414" t="n">
+        <v>1</v>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>絶</t>
+        </is>
+      </c>
+      <c r="B415" t="n">
+        <v>1</v>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>絶ちゃん</t>
+        </is>
+      </c>
+      <c r="B416" t="n">
+        <v>1</v>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>美優</t>
+        </is>
+      </c>
+      <c r="B417" t="n">
+        <v>1</v>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>赤ちゃん</t>
+        </is>
+      </c>
+      <c r="B418" t="n">
+        <v>1</v>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
           <t>高田</t>
         </is>
       </c>
-      <c r="B414" t="n">
-        <v>1</v>
-      </c>
-      <c r="C414" t="inlineStr">
+      <c r="B419" t="n">
+        <v>1</v>
+      </c>
+      <c r="C419" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="D414" t="inlineStr">
+      <c r="D419" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
@@ -60675,10 +61620,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="C2" t="n">
-        <v>79</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3">
@@ -60688,10 +61633,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C3" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4">
@@ -60823,10 +61768,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5">
@@ -61044,10 +61989,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C21" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
     </row>
     <row r="22">
@@ -61057,10 +62002,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C22" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23">
@@ -61070,10 +62015,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C23" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="24">
@@ -61083,10 +62028,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C24" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
     </row>
     <row r="25">
@@ -61096,10 +62041,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C25" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
   </sheetData>
@@ -61161,13 +62106,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="C3" t="n">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="D3" t="n">
-        <v>221</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>

--- a/bbs_log.xlsx
+++ b/bbs_log.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H640"/>
+  <dimension ref="A1:H652"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20222,7 +20222,6 @@
           <t>ましゅ</t>
         </is>
       </c>
-      <c r="E629" t="inlineStr"/>
       <c r="F629" t="inlineStr">
         <is>
           <t>オープン凸</t>
@@ -20233,7 +20232,6 @@
           <t>来ました</t>
         </is>
       </c>
-      <c r="H629" t="inlineStr"/>
     </row>
     <row r="630">
       <c r="A630" t="n">
@@ -20254,7 +20252,6 @@
           <t>ひがん</t>
         </is>
       </c>
-      <c r="E630" t="inlineStr"/>
       <c r="F630" t="inlineStr">
         <is>
           <t>遊びに</t>
@@ -20265,7 +20262,6 @@
           <t>来ました♪</t>
         </is>
       </c>
-      <c r="H630" t="inlineStr"/>
     </row>
     <row r="631">
       <c r="A631" t="n">
@@ -20286,7 +20282,6 @@
           <t>ぐっちゃん（チャイマフィ）</t>
         </is>
       </c>
-      <c r="E631" t="inlineStr"/>
       <c r="F631" t="inlineStr">
         <is>
           <t>お久し</t>
@@ -20297,7 +20292,6 @@
           <t>来ました！</t>
         </is>
       </c>
-      <c r="H631" t="inlineStr"/>
     </row>
     <row r="632">
       <c r="A632" t="n">
@@ -20318,7 +20312,6 @@
           <t>えぬ</t>
         </is>
       </c>
-      <c r="E632" t="inlineStr"/>
       <c r="F632" t="inlineStr">
         <is>
           <t>まったりしに</t>
@@ -20329,7 +20322,6 @@
           <t>いきます</t>
         </is>
       </c>
-      <c r="H632" t="inlineStr"/>
     </row>
     <row r="633">
       <c r="A633" t="n">
@@ -20350,7 +20342,6 @@
           <t>オリーブ</t>
         </is>
       </c>
-      <c r="E633" t="inlineStr"/>
       <c r="F633" t="inlineStr">
         <is>
           <t>はじめて</t>
@@ -20361,7 +20352,6 @@
           <t>面白いお店探して来ました！</t>
         </is>
       </c>
-      <c r="H633" t="inlineStr"/>
     </row>
     <row r="634">
       <c r="A634" t="n">
@@ -20382,7 +20372,6 @@
           <t>げんき</t>
         </is>
       </c>
-      <c r="E634" t="inlineStr"/>
       <c r="F634" t="inlineStr">
         <is>
           <t>気になって</t>
@@ -20393,7 +20382,6 @@
           <t>遊びに来てみました</t>
         </is>
       </c>
-      <c r="H634" t="inlineStr"/>
     </row>
     <row r="635">
       <c r="A635" t="n">
@@ -20414,7 +20402,6 @@
           <t>えーたろ</t>
         </is>
       </c>
-      <c r="E635" t="inlineStr"/>
       <c r="F635" t="inlineStr">
         <is>
           <t>飲みに</t>
@@ -20425,7 +20412,6 @@
           <t>来ました！</t>
         </is>
       </c>
-      <c r="H635" t="inlineStr"/>
     </row>
     <row r="636">
       <c r="A636" t="n">
@@ -20446,7 +20432,6 @@
           <t>テクノ</t>
         </is>
       </c>
-      <c r="E636" t="inlineStr"/>
       <c r="F636" t="inlineStr">
         <is>
           <t>ハイボールを</t>
@@ -20457,7 +20442,6 @@
           <t>ください</t>
         </is>
       </c>
-      <c r="H636" t="inlineStr"/>
     </row>
     <row r="637">
       <c r="A637" t="n">
@@ -20478,7 +20462,6 @@
           <t>大塚</t>
         </is>
       </c>
-      <c r="E637" t="inlineStr"/>
       <c r="F637" t="inlineStr">
         <is>
           <t>アゲアゲで</t>
@@ -20489,7 +20472,6 @@
           <t>きたよーん</t>
         </is>
       </c>
-      <c r="H637" t="inlineStr"/>
     </row>
     <row r="638">
       <c r="A638" t="n">
@@ -20510,7 +20492,6 @@
           <t>るい</t>
         </is>
       </c>
-      <c r="E638" t="inlineStr"/>
       <c r="F638" t="inlineStr">
         <is>
           <t>ショー帰りに</t>
@@ -20521,7 +20502,6 @@
           <t>きたよ</t>
         </is>
       </c>
-      <c r="H638" t="inlineStr"/>
     </row>
     <row r="639">
       <c r="A639" t="n">
@@ -20542,7 +20522,6 @@
           <t>ちぇちぇ＆ガールズ</t>
         </is>
       </c>
-      <c r="E639" t="inlineStr"/>
       <c r="F639" t="inlineStr">
         <is>
           <t>新規女子連れて</t>
@@ -20553,7 +20532,6 @@
           <t>来ました！！！！</t>
         </is>
       </c>
-      <c r="H639" t="inlineStr"/>
     </row>
     <row r="640">
       <c r="A640" t="n">
@@ -20607,6 +20585,411 @@
         </is>
       </c>
     </row>
+    <row r="641">
+      <c r="A641" t="n">
+        <v>28012</v>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>19:11:37</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>キムと超ドMみい</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr"/>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>今夜</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>来店します</t>
+        </is>
+      </c>
+      <c r="H641" t="inlineStr"/>
+    </row>
+    <row r="642">
+      <c r="A642" t="n">
+        <v>28013</v>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>19:13:36</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>ひがん</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr"/>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>オープンから</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>きちゃいました♪</t>
+        </is>
+      </c>
+      <c r="H642" t="inlineStr"/>
+    </row>
+    <row r="643">
+      <c r="A643" t="n">
+        <v>28016</v>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>19:48:09</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>ボス</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr"/>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>宇都宮</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>初来店</t>
+        </is>
+      </c>
+      <c r="H643" t="inlineStr"/>
+    </row>
+    <row r="644">
+      <c r="A644" t="n">
+        <v>28018</v>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>20:34:23</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>彩</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr"/>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>これから</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>行きます</t>
+        </is>
+      </c>
+      <c r="H644" t="inlineStr"/>
+    </row>
+    <row r="645">
+      <c r="A645" t="n">
+        <v>28021</v>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>20:45:03</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>ゆすき</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr"/>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>ストッキング師</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>来店！</t>
+        </is>
+      </c>
+      <c r="H645" t="inlineStr"/>
+    </row>
+    <row r="646">
+      <c r="A646" t="n">
+        <v>28023</v>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>21:21:55</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>キム＆みい</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr"/>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>いまきました</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>ドM凸</t>
+        </is>
+      </c>
+      <c r="H646" t="inlineStr"/>
+    </row>
+    <row r="647">
+      <c r="A647" t="n">
+        <v>28025</v>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>21:38:32</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>ニコチン</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr"/>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>来ました！</t>
+        </is>
+      </c>
+      <c r="H647" t="inlineStr"/>
+    </row>
+    <row r="648">
+      <c r="A648" t="n">
+        <v>28027</v>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>21:45:34</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>ましゅ社長</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr"/>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>只今</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>きました♪</t>
+        </is>
+      </c>
+      <c r="H648" t="inlineStr"/>
+    </row>
+    <row r="649">
+      <c r="A649" t="n">
+        <v>28029</v>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>23:22:21</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>ぽて</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr"/>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>来ました！</t>
+        </is>
+      </c>
+      <c r="H649" t="inlineStr"/>
+    </row>
+    <row r="650">
+      <c r="A650" t="n">
+        <v>28031</v>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>23:44:40</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>テクノ＆おおつか＆みこと＆もも</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr"/>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>みんなで</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>きました♪</t>
+        </is>
+      </c>
+      <c r="H650" t="inlineStr"/>
+    </row>
+    <row r="651">
+      <c r="A651" t="n">
+        <v>28033</v>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>00:48:22</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>マサ</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr"/>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>初来店</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>来ました！</t>
+        </is>
+      </c>
+      <c r="H651" t="inlineStr"/>
+    </row>
+    <row r="652">
+      <c r="A652" t="n">
+        <v>28035</v>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>04:13:54</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>ツッコミはお任せのShizu / えちえち裏垢女子のモカチ</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>★☆★朝までアゲアゲの水曜日営業が始まるわよ♪★☆★</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>本日9月23日の営業時間は♪
+オープン14:00！ラスト5:00なのよ☆
+担当は
+ツッコミはお任せのShizu
+えちえち裏垢女子のモカチ
+なのよ♪
+どんな季節でも★BAMBITCH★は色気ムンムンで暑すぎる♪
+バンビッチでおもいっきりはじけちゃって（笑）
+精力は無くても性欲がある！？
+大人の憩いと禁断サークル盛りだくさん！
+憩いと交流の魔性の遊び場バンビッチは素敵な出会いを 提供いたします（笑)☆☆
+おつまみ等の持ち込みは自由なのでみんなで持ち寄ってお近づきのきっかけにどうぞ♪
+強制や無理強いは一切ございませんので楽しく遊びましょう♪
+宇都宮市宿郷1−12−9　カサブランカビル5F</t>
+        </is>
+      </c>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>img20260923041354.jpg</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -20618,7 +21001,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I757"/>
+  <dimension ref="A1:I768"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53183,6 +53566,479 @@
       <c r="I757" t="inlineStr">
         <is>
           <t>来ました！！！！</t>
+        </is>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>19:11:37</t>
+        </is>
+      </c>
+      <c r="D758" t="n">
+        <v>28012</v>
+      </c>
+      <c r="E758" t="inlineStr">
+        <is>
+          <t>キムと超ドMみい</t>
+        </is>
+      </c>
+      <c r="F758" t="n">
+        <v>1</v>
+      </c>
+      <c r="G758" t="inlineStr">
+        <is>
+          <t>キムと超ドMみい</t>
+        </is>
+      </c>
+      <c r="H758" t="inlineStr">
+        <is>
+          <t>今夜</t>
+        </is>
+      </c>
+      <c r="I758" t="inlineStr">
+        <is>
+          <t>来店します</t>
+        </is>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>19:13:36</t>
+        </is>
+      </c>
+      <c r="D759" t="n">
+        <v>28013</v>
+      </c>
+      <c r="E759" t="inlineStr">
+        <is>
+          <t>ひがん</t>
+        </is>
+      </c>
+      <c r="F759" t="n">
+        <v>23</v>
+      </c>
+      <c r="G759" t="inlineStr">
+        <is>
+          <t>ひがん</t>
+        </is>
+      </c>
+      <c r="H759" t="inlineStr">
+        <is>
+          <t>オープンから</t>
+        </is>
+      </c>
+      <c r="I759" t="inlineStr">
+        <is>
+          <t>きちゃいました♪</t>
+        </is>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>19:48:09</t>
+        </is>
+      </c>
+      <c r="D760" t="n">
+        <v>28016</v>
+      </c>
+      <c r="E760" t="inlineStr">
+        <is>
+          <t>ボス</t>
+        </is>
+      </c>
+      <c r="F760" t="n">
+        <v>1</v>
+      </c>
+      <c r="G760" t="inlineStr">
+        <is>
+          <t>ボス</t>
+        </is>
+      </c>
+      <c r="H760" t="inlineStr">
+        <is>
+          <t>宇都宮</t>
+        </is>
+      </c>
+      <c r="I760" t="inlineStr">
+        <is>
+          <t>初来店</t>
+        </is>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>20:34:23</t>
+        </is>
+      </c>
+      <c r="D761" t="n">
+        <v>28018</v>
+      </c>
+      <c r="E761" t="inlineStr">
+        <is>
+          <t>彩</t>
+        </is>
+      </c>
+      <c r="F761" t="n">
+        <v>12</v>
+      </c>
+      <c r="G761" t="inlineStr">
+        <is>
+          <t>彩</t>
+        </is>
+      </c>
+      <c r="H761" t="inlineStr">
+        <is>
+          <t>これから</t>
+        </is>
+      </c>
+      <c r="I761" t="inlineStr">
+        <is>
+          <t>行きます</t>
+        </is>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>20:45:03</t>
+        </is>
+      </c>
+      <c r="D762" t="n">
+        <v>28021</v>
+      </c>
+      <c r="E762" t="inlineStr">
+        <is>
+          <t>ゆすき</t>
+        </is>
+      </c>
+      <c r="F762" t="n">
+        <v>2</v>
+      </c>
+      <c r="G762" t="inlineStr">
+        <is>
+          <t>ゆすき</t>
+        </is>
+      </c>
+      <c r="H762" t="inlineStr">
+        <is>
+          <t>ストッキング師</t>
+        </is>
+      </c>
+      <c r="I762" t="inlineStr">
+        <is>
+          <t>来店！</t>
+        </is>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>21:21:55</t>
+        </is>
+      </c>
+      <c r="D763" t="n">
+        <v>28023</v>
+      </c>
+      <c r="E763" t="inlineStr">
+        <is>
+          <t>キム＆みい</t>
+        </is>
+      </c>
+      <c r="F763" t="n">
+        <v>1</v>
+      </c>
+      <c r="G763" t="inlineStr">
+        <is>
+          <t>キム＆みい</t>
+        </is>
+      </c>
+      <c r="H763" t="inlineStr">
+        <is>
+          <t>いまきました</t>
+        </is>
+      </c>
+      <c r="I763" t="inlineStr">
+        <is>
+          <t>ドM凸</t>
+        </is>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>21:38:32</t>
+        </is>
+      </c>
+      <c r="D764" t="n">
+        <v>28025</v>
+      </c>
+      <c r="E764" t="inlineStr">
+        <is>
+          <t>ニコチン</t>
+        </is>
+      </c>
+      <c r="F764" t="n">
+        <v>1</v>
+      </c>
+      <c r="G764" t="inlineStr">
+        <is>
+          <t>ニコチン</t>
+        </is>
+      </c>
+      <c r="H764" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="I764" t="inlineStr">
+        <is>
+          <t>来ました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>21:45:34</t>
+        </is>
+      </c>
+      <c r="D765" t="n">
+        <v>28027</v>
+      </c>
+      <c r="E765" t="inlineStr">
+        <is>
+          <t>ましゅ社長</t>
+        </is>
+      </c>
+      <c r="F765" t="n">
+        <v>5</v>
+      </c>
+      <c r="G765" t="inlineStr">
+        <is>
+          <t>ましゅ社長</t>
+        </is>
+      </c>
+      <c r="H765" t="inlineStr">
+        <is>
+          <t>只今</t>
+        </is>
+      </c>
+      <c r="I765" t="inlineStr">
+        <is>
+          <t>きました♪</t>
+        </is>
+      </c>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>23:22:21</t>
+        </is>
+      </c>
+      <c r="D766" t="n">
+        <v>28029</v>
+      </c>
+      <c r="E766" t="inlineStr">
+        <is>
+          <t>ぽて</t>
+        </is>
+      </c>
+      <c r="F766" t="n">
+        <v>1</v>
+      </c>
+      <c r="G766" t="inlineStr">
+        <is>
+          <t>ぽて</t>
+        </is>
+      </c>
+      <c r="H766" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="I766" t="inlineStr">
+        <is>
+          <t>来ました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>23:44:40</t>
+        </is>
+      </c>
+      <c r="D767" t="n">
+        <v>28031</v>
+      </c>
+      <c r="E767" t="inlineStr">
+        <is>
+          <t>テクノ＆おおつか＆みこと＆もも</t>
+        </is>
+      </c>
+      <c r="F767" t="n">
+        <v>1</v>
+      </c>
+      <c r="G767" t="inlineStr">
+        <is>
+          <t>テクノ＆おおつか＆みこと＆もも</t>
+        </is>
+      </c>
+      <c r="H767" t="inlineStr">
+        <is>
+          <t>みんなで</t>
+        </is>
+      </c>
+      <c r="I767" t="inlineStr">
+        <is>
+          <t>きました♪</t>
+        </is>
+      </c>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>00:48:22</t>
+        </is>
+      </c>
+      <c r="D768" t="n">
+        <v>28033</v>
+      </c>
+      <c r="E768" t="inlineStr">
+        <is>
+          <t>マサ</t>
+        </is>
+      </c>
+      <c r="F768" t="n">
+        <v>2</v>
+      </c>
+      <c r="G768" t="inlineStr">
+        <is>
+          <t>マサ</t>
+        </is>
+      </c>
+      <c r="H768" t="inlineStr">
+        <is>
+          <t>初来店</t>
+        </is>
+      </c>
+      <c r="I768" t="inlineStr">
+        <is>
+          <t>来ました！</t>
         </is>
       </c>
     </row>
@@ -53197,7 +54053,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D419"/>
+  <dimension ref="A1:D425"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53229,7 +54085,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -53238,7 +54094,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
@@ -53329,7 +54185,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -53338,7 +54194,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
@@ -53685,7 +54541,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>りん</t>
+          <t>ましゅ社長</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -53693,19 +54549,19 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>るい</t>
+          <t>りん</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -53713,19 +54569,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>カズ</t>
+          <t>るい</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -53738,18 +54594,18 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TKC</t>
+          <t>カズ</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -53758,14 +54614,14 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>bee</t>
+          <t>TKC</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -53778,14 +54634,14 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>かな</t>
+          <t>bee</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -53793,19 +54649,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>くれは</t>
+          <t>かな</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -53813,19 +54669,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>さとる</t>
+          <t>くれは</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -53833,19 +54689,19 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>すず</t>
+          <t>さとる</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -53853,19 +54709,19 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>てくのちゃん</t>
+          <t>すず</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -53873,19 +54729,19 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>でで</t>
+          <t>てくのちゃん</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -53893,7 +54749,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -53905,7 +54761,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>まいなちゅ</t>
+          <t>でで</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -53913,19 +54769,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ましゅ社長</t>
+          <t>まいなちゅ</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -53933,12 +54789,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
@@ -55405,7 +56261,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>よっしー</t>
+          <t>ゆすき</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -55413,19 +56269,19 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>よっち</t>
+          <t>よっしー</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -55433,19 +56289,19 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>りお</t>
+          <t>よっち</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -55453,19 +56309,19 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
           <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>りゅう</t>
+          <t>りお</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -55473,19 +56329,19 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>オカニー</t>
+          <t>りゅう</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -55493,19 +56349,19 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>キムとドMまゆ</t>
+          <t>オカニー</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -55513,19 +56369,19 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>タカ</t>
+          <t>キムとドMまゆ</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -55533,19 +56389,19 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>タク</t>
+          <t>タカ</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -55553,19 +56409,19 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>タケ</t>
+          <t>タク</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -55573,19 +56429,19 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>テクノっち</t>
+          <t>タケ</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -55593,19 +56449,19 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>マイナス</t>
+          <t>テクノっち</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -55613,19 +56469,19 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>マッスル</t>
+          <t>マイナス</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -55633,19 +56489,19 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>マナティ</t>
+          <t>マサ</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -55653,19 +56509,19 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>変態マッスル</t>
+          <t>マッスル</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -55673,19 +56529,19 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>大塚</t>
+          <t>マナティ</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -55693,19 +56549,19 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>愛とスケベの戦士</t>
+          <t>変態マッスル</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -55713,59 +56569,59 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>5人衆</t>
+          <t>大塚</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>愛とスケベの戦士</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>EVANS×２</t>
+          <t>5人衆</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -55773,19 +56629,19 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>HGN</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -55793,19 +56649,19 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>JPTR</t>
+          <t>EVANS×２</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -55813,19 +56669,19 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>HGN</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -55833,19 +56689,19 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>KUMA</t>
+          <t>JPTR</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -55853,19 +56709,19 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -55873,19 +56729,19 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>KUMA</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -55893,19 +56749,19 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>NMGK</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -55913,19 +56769,19 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>N氏御一行</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -55933,19 +56789,19 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>SIKUSENAチャンネルヒロキ</t>
+          <t>NMGK</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -55953,19 +56809,19 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>STR</t>
+          <t>N氏御一行</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -55973,19 +56829,19 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>TARU</t>
+          <t>SIKUSENAチャンネルヒロキ</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -55993,19 +56849,19 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>STR</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -56013,19 +56869,19 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Tやま</t>
+          <t>TARU</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -56033,19 +56889,19 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>TT</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -56053,19 +56909,19 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>YZK</t>
+          <t>Tやま</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -56073,19 +56929,19 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>hikari</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -56093,19 +56949,19 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>nuri</t>
+          <t>YZK</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -56113,19 +56969,19 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>sho</t>
+          <t>hikari</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -56133,19 +56989,19 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>★Zakk★</t>
+          <t>nuri</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -56153,19 +57009,19 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>あき</t>
+          <t>sho</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -56173,19 +57029,19 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>あさみ</t>
+          <t>★Zakk★</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -56193,19 +57049,19 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>あす</t>
+          <t>あき</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -56213,19 +57069,19 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>あにー</t>
+          <t>あさみ</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -56233,19 +57089,19 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>あまねちゃん</t>
+          <t>あす</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -56265,7 +57121,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ありす</t>
+          <t>あにー</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -56273,19 +57129,19 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>いおり</t>
+          <t>あまねちゃん</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -56293,19 +57149,19 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>いけちゃん</t>
+          <t>ありす</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -56313,19 +57169,19 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>いぶお</t>
+          <t>いおり</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -56333,19 +57189,19 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>うらら</t>
+          <t>いけちゃん</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -56353,19 +57209,19 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>えび</t>
+          <t>いぶお</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -56373,19 +57229,19 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>えーたろ</t>
+          <t>うらら</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -56393,19 +57249,19 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>おじき</t>
+          <t>えび</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -56413,19 +57269,19 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>おじきち</t>
+          <t>えーたろ</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -56433,19 +57289,19 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>おすー</t>
+          <t>おじき</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -56453,19 +57309,19 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>おちんぽベルセルク</t>
+          <t>おじきち</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -56473,19 +57329,19 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>おにゃん</t>
+          <t>おすー</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -56493,19 +57349,19 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>おにゃんにゃん</t>
+          <t>おちんぽベルセルク</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -56513,19 +57369,19 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>おばし</t>
+          <t>おにゃん</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -56533,19 +57389,19 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>おもち</t>
+          <t>おにゃんにゃん</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -56553,19 +57409,19 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>かける</t>
+          <t>おばし</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -56573,19 +57429,19 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>かずき</t>
+          <t>おもち</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -56593,19 +57449,19 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>かず＆TKC＆のんのん</t>
+          <t>かける</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -56613,19 +57469,19 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>かな(絶ちゃん</t>
+          <t>かずき</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -56633,19 +57489,19 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>かな(絶ちゃん)/おっつん</t>
+          <t>かず＆TKC＆のんのん</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -56653,19 +57509,19 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>がん</t>
+          <t>かな(絶ちゃん</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -56673,19 +57529,19 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>きむさん</t>
+          <t>かな(絶ちゃん)/おっつん</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -56693,19 +57549,19 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>きむむ</t>
+          <t>がん</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -56713,19 +57569,19 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>きむら</t>
+          <t>きむさん</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -56733,19 +57589,19 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>きょうちゃん</t>
+          <t>きむむ</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -56753,19 +57609,19 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>きんたまよ</t>
+          <t>きむら</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -56773,19 +57629,19 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>くっぱ</t>
+          <t>きょうちゃん</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -56793,19 +57649,19 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>くま</t>
+          <t>きんたまよ</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -56813,19 +57669,19 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>くり</t>
+          <t>くっぱ</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -56845,7 +57701,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>ぐっちゃん</t>
+          <t>くま</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -56853,19 +57709,19 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ぐっちゃん（チャイマフィ）</t>
+          <t>くり</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -56873,19 +57729,19 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>けい</t>
+          <t>ぐっちゃん</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -56893,19 +57749,19 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>けいちゃん</t>
+          <t>ぐっちゃん（チャイマフィ）</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -56913,19 +57769,19 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>けんけん</t>
+          <t>けい</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -56933,19 +57789,19 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>げん</t>
+          <t>けいちゃん</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -56953,19 +57809,19 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>げんき</t>
+          <t>けんけん</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -56973,19 +57829,19 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>こう</t>
+          <t>げん</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -56993,19 +57849,19 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>こうた</t>
+          <t>げんき</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -57013,19 +57869,19 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>こてつ</t>
+          <t>こう</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -57045,7 +57901,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>ことねえ</t>
+          <t>こうた</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -57053,19 +57909,19 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>ことり</t>
+          <t>こてつ</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -57073,19 +57929,19 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>ごん</t>
+          <t>ことねえ</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -57093,19 +57949,19 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>さかもと</t>
+          <t>ことり</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -57113,19 +57969,19 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>さくら</t>
+          <t>ごん</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -57133,19 +57989,19 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>さとりゅ</t>
+          <t>さかもと</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -57153,19 +58009,19 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>さな</t>
+          <t>さくら</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -57173,19 +58029,19 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>さない</t>
+          <t>さとりゅ</t>
         </is>
       </c>
       <c r="B200" t="n">
@@ -57193,19 +58049,19 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>さや</t>
+          <t>さな</t>
         </is>
       </c>
       <c r="B201" t="n">
@@ -57213,19 +58069,19 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>しずか</t>
+          <t>さない</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -57233,19 +58089,19 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>しりゅう</t>
+          <t>さや</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -57253,19 +58109,19 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>じん</t>
+          <t>しずか</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -57273,19 +58129,19 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>せいら</t>
+          <t>しりゅう</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -57293,19 +58149,19 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>たいせー</t>
+          <t>じん</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -57313,19 +58169,19 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>たか</t>
+          <t>せいら</t>
         </is>
       </c>
       <c r="B207" t="n">
@@ -57333,19 +58189,19 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>たかし</t>
+          <t>たいせー</t>
         </is>
       </c>
       <c r="B208" t="n">
@@ -57353,19 +58209,19 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>たかち</t>
+          <t>たか</t>
         </is>
       </c>
       <c r="B209" t="n">
@@ -57373,19 +58229,19 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>たく</t>
+          <t>たかし</t>
         </is>
       </c>
       <c r="B210" t="n">
@@ -57393,19 +58249,19 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>たけ</t>
+          <t>たかち</t>
         </is>
       </c>
       <c r="B211" t="n">
@@ -57413,19 +58269,19 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>たけし</t>
+          <t>たく</t>
         </is>
       </c>
       <c r="B212" t="n">
@@ -57433,19 +58289,19 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>たつ</t>
+          <t>たけ</t>
         </is>
       </c>
       <c r="B213" t="n">
@@ -57453,19 +58309,19 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>たつお</t>
+          <t>たけし</t>
         </is>
       </c>
       <c r="B214" t="n">
@@ -57473,19 +58329,19 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>たます</t>
+          <t>たつ</t>
         </is>
       </c>
       <c r="B215" t="n">
@@ -57493,19 +58349,19 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>たろー</t>
+          <t>たつお</t>
         </is>
       </c>
       <c r="B216" t="n">
@@ -57513,19 +58369,19 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>だいさく</t>
+          <t>たます</t>
         </is>
       </c>
       <c r="B217" t="n">
@@ -57533,19 +58389,19 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>だいざく</t>
+          <t>たろー</t>
         </is>
       </c>
       <c r="B218" t="n">
@@ -57553,19 +58409,19 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>だいち</t>
+          <t>だいさく</t>
         </is>
       </c>
       <c r="B219" t="n">
@@ -57573,19 +58429,19 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>ちぇちぇ</t>
+          <t>だいざく</t>
         </is>
       </c>
       <c r="B220" t="n">
@@ -57593,19 +58449,19 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>ちぇちぇ＆ガールズ</t>
+          <t>だいち</t>
         </is>
       </c>
       <c r="B221" t="n">
@@ -57613,19 +58469,19 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>てくのっち</t>
+          <t>ちぇちぇ</t>
         </is>
       </c>
       <c r="B222" t="n">
@@ -57633,19 +58489,19 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>てっちゃん</t>
+          <t>ちぇちぇ＆ガールズ</t>
         </is>
       </c>
       <c r="B223" t="n">
@@ -57653,19 +58509,19 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>てつ</t>
+          <t>てくのっち</t>
         </is>
       </c>
       <c r="B224" t="n">
@@ -57673,19 +58529,19 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>てつじ</t>
+          <t>てっちゃん</t>
         </is>
       </c>
       <c r="B225" t="n">
@@ -57693,19 +58549,19 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>てる</t>
+          <t>てつ</t>
         </is>
       </c>
       <c r="B226" t="n">
@@ -57713,19 +58569,19 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>でかかわ</t>
+          <t>てつじ</t>
         </is>
       </c>
       <c r="B227" t="n">
@@ -57733,19 +58589,19 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>ででたゃ</t>
+          <t>てる</t>
         </is>
       </c>
       <c r="B228" t="n">
@@ -57753,19 +58609,19 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>とうや</t>
+          <t>でかかわ</t>
         </is>
       </c>
       <c r="B229" t="n">
@@ -57773,19 +58629,19 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>とおちゃん</t>
+          <t>ででたゃ</t>
         </is>
       </c>
       <c r="B230" t="n">
@@ -57793,19 +58649,19 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>とっしー</t>
+          <t>とうや</t>
         </is>
       </c>
       <c r="B231" t="n">
@@ -57813,19 +58669,19 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>とも</t>
+          <t>とおちゃん</t>
         </is>
       </c>
       <c r="B232" t="n">
@@ -57833,19 +58689,19 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>ともち</t>
+          <t>とっしー</t>
         </is>
       </c>
       <c r="B233" t="n">
@@ -57853,19 +58709,19 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>ともひろ</t>
+          <t>とも</t>
         </is>
       </c>
       <c r="B234" t="n">
@@ -57873,19 +58729,19 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>ともや</t>
+          <t>ともち</t>
         </is>
       </c>
       <c r="B235" t="n">
@@ -57893,19 +58749,19 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>ともゆき</t>
+          <t>ともひろ</t>
         </is>
       </c>
       <c r="B236" t="n">
@@ -57913,19 +58769,19 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>とーり</t>
+          <t>ともや</t>
         </is>
       </c>
       <c r="B237" t="n">
@@ -57933,19 +58789,19 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>どえむちゃん</t>
+          <t>ともゆき</t>
         </is>
       </c>
       <c r="B238" t="n">
@@ -57953,19 +58809,19 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>ながとも</t>
+          <t>とーり</t>
         </is>
       </c>
       <c r="B239" t="n">
@@ -57973,19 +58829,19 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>なべ</t>
+          <t>どえむちゃん</t>
         </is>
       </c>
       <c r="B240" t="n">
@@ -57993,19 +58849,19 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>にこちん</t>
+          <t>ながとも</t>
         </is>
       </c>
       <c r="B241" t="n">
@@ -58025,7 +58881,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>にゃんまげ</t>
+          <t>なべ</t>
         </is>
       </c>
       <c r="B242" t="n">
@@ -58033,19 +58889,19 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>にょ</t>
+          <t>にこちん</t>
         </is>
       </c>
       <c r="B243" t="n">
@@ -58053,19 +58909,19 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>ねここ</t>
+          <t>にゃんまげ</t>
         </is>
       </c>
       <c r="B244" t="n">
@@ -58073,19 +58929,19 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>のぼ</t>
+          <t>にょ</t>
         </is>
       </c>
       <c r="B245" t="n">
@@ -58093,19 +58949,19 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>のり</t>
+          <t>ねここ</t>
         </is>
       </c>
       <c r="B246" t="n">
@@ -58113,19 +58969,19 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>はち</t>
+          <t>のぼ</t>
         </is>
       </c>
       <c r="B247" t="n">
@@ -58133,19 +58989,19 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>はな</t>
+          <t>のり</t>
         </is>
       </c>
       <c r="B248" t="n">
@@ -58153,19 +59009,19 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>はなちゃん</t>
+          <t>はち</t>
         </is>
       </c>
       <c r="B249" t="n">
@@ -58173,19 +59029,19 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>はなまる</t>
+          <t>はな</t>
         </is>
       </c>
       <c r="B250" t="n">
@@ -58193,19 +59049,19 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>はにーちゃん</t>
+          <t>はなちゃん</t>
         </is>
       </c>
       <c r="B251" t="n">
@@ -58213,19 +59069,19 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>はんまー</t>
+          <t>はなまる</t>
         </is>
       </c>
       <c r="B252" t="n">
@@ -58233,19 +59089,19 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>ひがんちゃん</t>
+          <t>はにーちゃん</t>
         </is>
       </c>
       <c r="B253" t="n">
@@ -58253,19 +59109,19 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>ひったん</t>
+          <t>はんまー</t>
         </is>
       </c>
       <c r="B254" t="n">
@@ -58273,19 +59129,19 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>ひろし</t>
+          <t>ひがんちゃん</t>
         </is>
       </c>
       <c r="B255" t="n">
@@ -58293,19 +59149,19 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>ひろとも</t>
+          <t>ひったん</t>
         </is>
       </c>
       <c r="B256" t="n">
@@ -58313,19 +59169,19 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>ふく</t>
+          <t>ひろし</t>
         </is>
       </c>
       <c r="B257" t="n">
@@ -58333,19 +59189,19 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>ふみ</t>
+          <t>ひろとも</t>
         </is>
       </c>
       <c r="B258" t="n">
@@ -58353,19 +59209,19 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>ぷらぐいん</t>
+          <t>ふく</t>
         </is>
       </c>
       <c r="B259" t="n">
@@ -58373,19 +59229,19 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>ぺぺ</t>
+          <t>ふみ</t>
         </is>
       </c>
       <c r="B260" t="n">
@@ -58393,19 +59249,19 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>まいまいまいまい</t>
+          <t>ぷらぐいん</t>
         </is>
       </c>
       <c r="B261" t="n">
@@ -58413,19 +59269,19 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>まいまいん</t>
+          <t>ぺぺ</t>
         </is>
       </c>
       <c r="B262" t="n">
@@ -58433,19 +59289,19 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>まおし</t>
+          <t>ぽて</t>
         </is>
       </c>
       <c r="B263" t="n">
@@ -58453,19 +59309,19 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>ます</t>
+          <t>まいまいまいまい</t>
         </is>
       </c>
       <c r="B264" t="n">
@@ -58473,19 +59329,19 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>ますみ</t>
+          <t>まいまいん</t>
         </is>
       </c>
       <c r="B265" t="n">
@@ -58493,19 +59349,19 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>まっする</t>
+          <t>まおし</t>
         </is>
       </c>
       <c r="B266" t="n">
@@ -58513,19 +59369,19 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>まっぴー</t>
+          <t>ます</t>
         </is>
       </c>
       <c r="B267" t="n">
@@ -58533,19 +59389,19 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>まな</t>
+          <t>ますみ</t>
         </is>
       </c>
       <c r="B268" t="n">
@@ -58553,19 +59409,19 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>まみ</t>
+          <t>まっする</t>
         </is>
       </c>
       <c r="B269" t="n">
@@ -58573,19 +59429,19 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>まや</t>
+          <t>まっぴー</t>
         </is>
       </c>
       <c r="B270" t="n">
@@ -58593,19 +59449,19 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>まり</t>
+          <t>まな</t>
         </is>
       </c>
       <c r="B271" t="n">
@@ -58625,7 +59481,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>まりーな</t>
+          <t>まみ</t>
         </is>
       </c>
       <c r="B272" t="n">
@@ -58633,19 +59489,19 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>まー</t>
+          <t>まや</t>
         </is>
       </c>
       <c r="B273" t="n">
@@ -58653,19 +59509,19 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>まーさん</t>
+          <t>まり</t>
         </is>
       </c>
       <c r="B274" t="n">
@@ -58673,19 +59529,19 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>まーちゃん</t>
+          <t>まりーな</t>
         </is>
       </c>
       <c r="B275" t="n">
@@ -58693,19 +59549,19 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>みかん</t>
+          <t>まー</t>
         </is>
       </c>
       <c r="B276" t="n">
@@ -58713,19 +59569,19 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>みずき</t>
+          <t>まーさん</t>
         </is>
       </c>
       <c r="B277" t="n">
@@ -58733,19 +59589,19 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>みちゃ</t>
+          <t>まーちゃん</t>
         </is>
       </c>
       <c r="B278" t="n">
@@ -58753,19 +59609,19 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>みっちー</t>
+          <t>みかん</t>
         </is>
       </c>
       <c r="B279" t="n">
@@ -58773,19 +59629,19 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>みなつちん</t>
+          <t>みずき</t>
         </is>
       </c>
       <c r="B280" t="n">
@@ -58805,7 +59661,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>みみ</t>
+          <t>みちゃ</t>
         </is>
       </c>
       <c r="B281" t="n">
@@ -58813,19 +59669,19 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>みやび</t>
+          <t>みっちー</t>
         </is>
       </c>
       <c r="B282" t="n">
@@ -58833,19 +59689,19 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>みゆき</t>
+          <t>みなつちん</t>
         </is>
       </c>
       <c r="B283" t="n">
@@ -58853,19 +59709,19 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>みらい</t>
+          <t>みみ</t>
         </is>
       </c>
       <c r="B284" t="n">
@@ -58873,19 +59729,19 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>みるこ</t>
+          <t>みやび</t>
         </is>
       </c>
       <c r="B285" t="n">
@@ -58893,19 +59749,19 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>みん</t>
+          <t>みゆき</t>
         </is>
       </c>
       <c r="B286" t="n">
@@ -58913,19 +59769,19 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>みーみ</t>
+          <t>みらい</t>
         </is>
       </c>
       <c r="B287" t="n">
@@ -58933,19 +59789,19 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>もかちんぽぽ</t>
+          <t>みるこ</t>
         </is>
       </c>
       <c r="B288" t="n">
@@ -58953,19 +59809,19 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>もっち</t>
+          <t>みん</t>
         </is>
       </c>
       <c r="B289" t="n">
@@ -58973,19 +59829,19 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>もっぴー</t>
+          <t>みーみ</t>
         </is>
       </c>
       <c r="B290" t="n">
@@ -58993,19 +59849,19 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>もと</t>
+          <t>もかちんぽぽ</t>
         </is>
       </c>
       <c r="B291" t="n">
@@ -59013,19 +59869,19 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>ももたろ</t>
+          <t>もっち</t>
         </is>
       </c>
       <c r="B292" t="n">
@@ -59033,19 +59889,19 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>ゆい</t>
+          <t>もっぴー</t>
         </is>
       </c>
       <c r="B293" t="n">
@@ -59053,19 +59909,19 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>ゆうじ</t>
+          <t>もと</t>
         </is>
       </c>
       <c r="B294" t="n">
@@ -59073,19 +59929,19 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>ゆうた</t>
+          <t>ももたろ</t>
         </is>
       </c>
       <c r="B295" t="n">
@@ -59093,19 +59949,19 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>ゆうたん</t>
+          <t>ゆい</t>
         </is>
       </c>
       <c r="B296" t="n">
@@ -59113,19 +59969,19 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>ゆうと</t>
+          <t>ゆうじ</t>
         </is>
       </c>
       <c r="B297" t="n">
@@ -59133,19 +59989,19 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>ゆうや</t>
+          <t>ゆうた</t>
         </is>
       </c>
       <c r="B298" t="n">
@@ -59153,19 +60009,19 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>ゆかり</t>
+          <t>ゆうたん</t>
         </is>
       </c>
       <c r="B299" t="n">
@@ -59173,19 +60029,19 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>ゆきお</t>
+          <t>ゆうと</t>
         </is>
       </c>
       <c r="B300" t="n">
@@ -59193,19 +60049,19 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>ゆきんこ</t>
+          <t>ゆうや</t>
         </is>
       </c>
       <c r="B301" t="n">
@@ -59213,19 +60069,19 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>ゆすき</t>
+          <t>ゆかり</t>
         </is>
       </c>
       <c r="B302" t="n">
@@ -59233,19 +60089,19 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>ゆず</t>
+          <t>ゆきお</t>
         </is>
       </c>
       <c r="B303" t="n">
@@ -59253,19 +60109,19 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>ゆずきちゃん</t>
+          <t>ゆきんこ</t>
         </is>
       </c>
       <c r="B304" t="n">
@@ -59273,19 +60129,19 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>ゆずき＆ましゅ</t>
+          <t>ゆず</t>
         </is>
       </c>
       <c r="B305" t="n">
@@ -59293,19 +60149,19 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>ゆっち</t>
+          <t>ゆずきちゃん</t>
         </is>
       </c>
       <c r="B306" t="n">
@@ -59313,19 +60169,19 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>ゆぴ</t>
+          <t>ゆずき＆ましゅ</t>
         </is>
       </c>
       <c r="B307" t="n">
@@ -59333,19 +60189,19 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>ゆり</t>
+          <t>ゆっち</t>
         </is>
       </c>
       <c r="B308" t="n">
@@ -59353,19 +60209,19 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>ゆりな</t>
+          <t>ゆぴ</t>
         </is>
       </c>
       <c r="B309" t="n">
@@ -59373,19 +60229,19 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>ゆん</t>
+          <t>ゆり</t>
         </is>
       </c>
       <c r="B310" t="n">
@@ -59393,19 +60249,19 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>よこい</t>
+          <t>ゆりな</t>
         </is>
       </c>
       <c r="B311" t="n">
@@ -59413,19 +60269,19 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>よちお</t>
+          <t>ゆん</t>
         </is>
       </c>
       <c r="B312" t="n">
@@ -59433,19 +60289,19 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>らいと</t>
+          <t>よこい</t>
         </is>
       </c>
       <c r="B313" t="n">
@@ -59453,19 +60309,19 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>らうら</t>
+          <t>よちお</t>
         </is>
       </c>
       <c r="B314" t="n">
@@ -59473,19 +60329,19 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>らお</t>
+          <t>らいと</t>
         </is>
       </c>
       <c r="B315" t="n">
@@ -59493,19 +60349,19 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>りえ</t>
+          <t>らうら</t>
         </is>
       </c>
       <c r="B316" t="n">
@@ -59513,19 +60369,19 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>りく</t>
+          <t>らお</t>
         </is>
       </c>
       <c r="B317" t="n">
@@ -59533,19 +60389,19 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>りさ</t>
+          <t>りえ</t>
         </is>
       </c>
       <c r="B318" t="n">
@@ -59553,19 +60409,19 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>りゅうくん</t>
+          <t>りく</t>
         </is>
       </c>
       <c r="B319" t="n">
@@ -59573,19 +60429,19 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>りゅーちゃん</t>
+          <t>りさ</t>
         </is>
       </c>
       <c r="B320" t="n">
@@ -59593,19 +60449,19 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>りょうが</t>
+          <t>りゅうくん</t>
         </is>
       </c>
       <c r="B321" t="n">
@@ -59613,19 +60469,19 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>りょうちゃん</t>
+          <t>りゅーちゃん</t>
         </is>
       </c>
       <c r="B322" t="n">
@@ -59633,19 +60489,19 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>りょーが</t>
+          <t>りょうが</t>
         </is>
       </c>
       <c r="B323" t="n">
@@ -59653,19 +60509,19 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>りりこ</t>
+          <t>りょうちゃん</t>
         </is>
       </c>
       <c r="B324" t="n">
@@ -59673,19 +60529,19 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>りん＆ゆち</t>
+          <t>りょーが</t>
         </is>
       </c>
       <c r="B325" t="n">
@@ -59693,19 +60549,19 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>れー</t>
+          <t>りりこ</t>
         </is>
       </c>
       <c r="B326" t="n">
@@ -59713,19 +60569,19 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>アイ</t>
+          <t>りん＆ゆち</t>
         </is>
       </c>
       <c r="B327" t="n">
@@ -59733,19 +60589,19 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>アイちゃん</t>
+          <t>れー</t>
         </is>
       </c>
       <c r="B328" t="n">
@@ -59753,19 +60609,19 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>アキ</t>
+          <t>アイ</t>
         </is>
       </c>
       <c r="B329" t="n">
@@ -59773,19 +60629,19 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>アナルプリンス</t>
+          <t>アイちゃん</t>
         </is>
       </c>
       <c r="B330" t="n">
@@ -59793,19 +60649,19 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>イエモン</t>
+          <t>アキ</t>
         </is>
       </c>
       <c r="B331" t="n">
@@ -59813,19 +60669,19 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>イブオ</t>
+          <t>アナルプリンス</t>
         </is>
       </c>
       <c r="B332" t="n">
@@ -59833,19 +60689,19 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>エーイチ</t>
+          <t>イエモン</t>
         </is>
       </c>
       <c r="B333" t="n">
@@ -59853,19 +60709,19 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>オリーブ</t>
+          <t>イブオ</t>
         </is>
       </c>
       <c r="B334" t="n">
@@ -59873,19 +60729,19 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>オ・スー</t>
+          <t>エーイチ</t>
         </is>
       </c>
       <c r="B335" t="n">
@@ -59893,19 +60749,19 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>カイト</t>
+          <t>オリーブ</t>
         </is>
       </c>
       <c r="B336" t="n">
@@ -59913,19 +60769,19 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>カズヤ</t>
+          <t>オ・スー</t>
         </is>
       </c>
       <c r="B337" t="n">
@@ -59933,19 +60789,19 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>カミさん</t>
+          <t>カイト</t>
         </is>
       </c>
       <c r="B338" t="n">
@@ -59953,19 +60809,19 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>カモリ</t>
+          <t>カズヤ</t>
         </is>
       </c>
       <c r="B339" t="n">
@@ -59973,19 +60829,19 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>キムさん</t>
+          <t>カミさん</t>
         </is>
       </c>
       <c r="B340" t="n">
@@ -59993,19 +60849,19 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>キムとどえむちゃん</t>
+          <t>カモリ</t>
         </is>
       </c>
       <c r="B341" t="n">
@@ -60013,19 +60869,19 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>キムとまゆ</t>
+          <t>キムさん</t>
         </is>
       </c>
       <c r="B342" t="n">
@@ -60033,19 +60889,19 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>キムとドMまいまい妹</t>
+          <t>キムとどえむちゃん</t>
         </is>
       </c>
       <c r="B343" t="n">
@@ -60053,19 +60909,19 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>キムとドMむい</t>
+          <t>キムとまゆ</t>
         </is>
       </c>
       <c r="B344" t="n">
@@ -60073,19 +60929,19 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>キムとドM女R</t>
+          <t>キムとドMまいまい妹</t>
         </is>
       </c>
       <c r="B345" t="n">
@@ -60093,19 +60949,19 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>キムと奴隷</t>
+          <t>キムとドMむい</t>
         </is>
       </c>
       <c r="B346" t="n">
@@ -60113,19 +60969,19 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>キムと新しい奴隷ちゃん</t>
+          <t>キムとドM女R</t>
         </is>
       </c>
       <c r="B347" t="n">
@@ -60133,19 +60989,19 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>キム＆むい</t>
+          <t>キムと奴隷</t>
         </is>
       </c>
       <c r="B348" t="n">
@@ -60153,19 +61009,19 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>クアレ</t>
+          <t>キムと新しい奴隷ちゃん</t>
         </is>
       </c>
       <c r="B349" t="n">
@@ -60173,19 +61029,19 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>クロちゃん</t>
+          <t>キムと超ドMみい</t>
         </is>
       </c>
       <c r="B350" t="n">
@@ -60193,19 +61049,19 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>クワレ</t>
+          <t>キム＆みい</t>
         </is>
       </c>
       <c r="B351" t="n">
@@ -60213,19 +61069,19 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>ケケ</t>
+          <t>キム＆むい</t>
         </is>
       </c>
       <c r="B352" t="n">
@@ -60233,19 +61089,19 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>ゲン</t>
+          <t>クアレ</t>
         </is>
       </c>
       <c r="B353" t="n">
@@ -60253,19 +61109,19 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>コオリ</t>
+          <t>クロちゃん</t>
         </is>
       </c>
       <c r="B354" t="n">
@@ -60273,19 +61129,19 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>コマ</t>
+          <t>クワレ</t>
         </is>
       </c>
       <c r="B355" t="n">
@@ -60293,19 +61149,19 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>サトル</t>
+          <t>ケケ</t>
         </is>
       </c>
       <c r="B356" t="n">
@@ -60313,19 +61169,19 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>ザッキー</t>
+          <t>ゲン</t>
         </is>
       </c>
       <c r="B357" t="n">
@@ -60333,19 +61189,19 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>シゲ</t>
+          <t>コオリ</t>
         </is>
       </c>
       <c r="B358" t="n">
@@ -60353,19 +61209,19 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>シュン</t>
+          <t>コマ</t>
         </is>
       </c>
       <c r="B359" t="n">
@@ -60373,19 +61229,19 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>シュンヤ</t>
+          <t>サトル</t>
         </is>
       </c>
       <c r="B360" t="n">
@@ -60393,19 +61249,19 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>ジャッキー</t>
+          <t>ザッキー</t>
         </is>
       </c>
       <c r="B361" t="n">
@@ -60413,19 +61269,19 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>ジョーカー</t>
+          <t>シゲ</t>
         </is>
       </c>
       <c r="B362" t="n">
@@ -60433,19 +61289,19 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>タカス</t>
+          <t>シュン</t>
         </is>
       </c>
       <c r="B363" t="n">
@@ -60453,19 +61309,19 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>タカ御一行</t>
+          <t>シュンヤ</t>
         </is>
       </c>
       <c r="B364" t="n">
@@ -60473,19 +61329,19 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>ダイキ</t>
+          <t>ジャッキー</t>
         </is>
       </c>
       <c r="B365" t="n">
@@ -60493,19 +61349,19 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>ダイゴ</t>
+          <t>ジョーカー</t>
         </is>
       </c>
       <c r="B366" t="n">
@@ -60513,19 +61369,19 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>ダイチ</t>
+          <t>タカス</t>
         </is>
       </c>
       <c r="B367" t="n">
@@ -60533,19 +61389,19 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>チェスカ</t>
+          <t>タカ御一行</t>
         </is>
       </c>
       <c r="B368" t="n">
@@ -60553,19 +61409,19 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>ツシマ</t>
+          <t>ダイキ</t>
         </is>
       </c>
       <c r="B369" t="n">
@@ -60573,19 +61429,19 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>ツボ</t>
+          <t>ダイゴ</t>
         </is>
       </c>
       <c r="B370" t="n">
@@ -60593,19 +61449,19 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>テクノとポチ</t>
+          <t>ダイチ</t>
         </is>
       </c>
       <c r="B371" t="n">
@@ -60613,19 +61469,19 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>テクノ＆てるくん＆イブオ</t>
+          <t>チェスカ</t>
         </is>
       </c>
       <c r="B372" t="n">
@@ -60633,19 +61489,19 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>トニー・トニー・チョッパー</t>
+          <t>ツシマ</t>
         </is>
       </c>
       <c r="B373" t="n">
@@ -60653,19 +61509,19 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>トルネードシャーク</t>
+          <t>ツボ</t>
         </is>
       </c>
       <c r="B374" t="n">
@@ -60673,19 +61529,19 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>ナカヤマヤ</t>
+          <t>テクノとポチ</t>
         </is>
       </c>
       <c r="B375" t="n">
@@ -60693,19 +61549,19 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>ニト</t>
+          <t>テクノ＆おおつか＆みこと＆もも</t>
         </is>
       </c>
       <c r="B376" t="n">
@@ -60713,19 +61569,19 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>ニャンまげ</t>
+          <t>テクノ＆てるくん＆イブオ</t>
         </is>
       </c>
       <c r="B377" t="n">
@@ -60733,19 +61589,19 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>ハチ</t>
+          <t>トニー・トニー・チョッパー</t>
         </is>
       </c>
       <c r="B378" t="n">
@@ -60753,19 +61609,19 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>ビコー</t>
+          <t>トルネードシャーク</t>
         </is>
       </c>
       <c r="B379" t="n">
@@ -60773,19 +61629,19 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>フジ</t>
+          <t>ナカヤマヤ</t>
         </is>
       </c>
       <c r="B380" t="n">
@@ -60793,19 +61649,19 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>ペロとペコ</t>
+          <t>ニコチン</t>
         </is>
       </c>
       <c r="B381" t="n">
@@ -60813,19 +61669,19 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>ボンタ</t>
+          <t>ニト</t>
         </is>
       </c>
       <c r="B382" t="n">
@@ -60833,19 +61689,19 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>ポチ</t>
+          <t>ニャンまげ</t>
         </is>
       </c>
       <c r="B383" t="n">
@@ -60853,19 +61709,19 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>マサ</t>
+          <t>ハチ</t>
         </is>
       </c>
       <c r="B384" t="n">
@@ -60873,19 +61729,19 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>マッチョ</t>
+          <t>ビコー</t>
         </is>
       </c>
       <c r="B385" t="n">
@@ -60893,19 +61749,19 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>ミカミと仲間たち</t>
+          <t>フジ</t>
         </is>
       </c>
       <c r="B386" t="n">
@@ -60913,19 +61769,19 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>ミスター工事マン</t>
+          <t>ペロとペコ</t>
         </is>
       </c>
       <c r="B387" t="n">
@@ -60933,19 +61789,19 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>ミッシ</t>
+          <t>ボス</t>
         </is>
       </c>
       <c r="B388" t="n">
@@ -60953,19 +61809,19 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>ミッチー</t>
+          <t>ボンタ</t>
         </is>
       </c>
       <c r="B389" t="n">
@@ -60973,19 +61829,19 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>ミルコ</t>
+          <t>ポチ</t>
         </is>
       </c>
       <c r="B390" t="n">
@@ -60993,19 +61849,19 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>ミン</t>
+          <t>マッチョ</t>
         </is>
       </c>
       <c r="B391" t="n">
@@ -61013,19 +61869,19 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>モジャ</t>
+          <t>ミカミと仲間たち</t>
         </is>
       </c>
       <c r="B392" t="n">
@@ -61033,19 +61889,19 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>ヤノちゃん</t>
+          <t>ミスター工事マン</t>
         </is>
       </c>
       <c r="B393" t="n">
@@ -61053,19 +61909,19 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>ヤマ</t>
+          <t>ミッシ</t>
         </is>
       </c>
       <c r="B394" t="n">
@@ -61073,19 +61929,19 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>ユウ</t>
+          <t>ミッチー</t>
         </is>
       </c>
       <c r="B395" t="n">
@@ -61093,19 +61949,19 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>ユキ</t>
+          <t>ミルコ</t>
         </is>
       </c>
       <c r="B396" t="n">
@@ -61113,19 +61969,19 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>ユッキー</t>
+          <t>ミン</t>
         </is>
       </c>
       <c r="B397" t="n">
@@ -61133,19 +61989,19 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>ヨシヤ</t>
+          <t>モジャ</t>
         </is>
       </c>
       <c r="B398" t="n">
@@ -61153,19 +62009,19 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>ラオ</t>
+          <t>ヤノちゃん</t>
         </is>
       </c>
       <c r="B399" t="n">
@@ -61173,19 +62029,19 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>リク</t>
+          <t>ヤマ</t>
         </is>
       </c>
       <c r="B400" t="n">
@@ -61193,19 +62049,19 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>リョウ</t>
+          <t>ユウ</t>
         </is>
       </c>
       <c r="B401" t="n">
@@ -61213,19 +62069,19 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>リン</t>
+          <t>ユキ</t>
         </is>
       </c>
       <c r="B402" t="n">
@@ -61233,19 +62089,19 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>ロタポジ</t>
+          <t>ユッキー</t>
         </is>
       </c>
       <c r="B403" t="n">
@@ -61265,7 +62121,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>ローズ</t>
+          <t>ヨシヤ</t>
         </is>
       </c>
       <c r="B404" t="n">
@@ -61273,19 +62129,19 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>偽マイマイ</t>
+          <t>ラオ</t>
         </is>
       </c>
       <c r="B405" t="n">
@@ -61293,19 +62149,19 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>僕と私</t>
+          <t>リク</t>
         </is>
       </c>
       <c r="B406" t="n">
@@ -61313,19 +62169,19 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>名無し</t>
+          <t>リョウ</t>
         </is>
       </c>
       <c r="B407" t="n">
@@ -61333,19 +62189,19 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>天我迅</t>
+          <t>リン</t>
         </is>
       </c>
       <c r="B408" t="n">
@@ -61353,19 +62209,19 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>女子三人衆</t>
+          <t>ロタポジ</t>
         </is>
       </c>
       <c r="B409" t="n">
@@ -61373,19 +62229,19 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>彩 なまがき</t>
+          <t>ローズ</t>
         </is>
       </c>
       <c r="B410" t="n">
@@ -61393,19 +62249,19 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>正装しん</t>
+          <t>偽マイマイ</t>
         </is>
       </c>
       <c r="B411" t="n">
@@ -61413,19 +62269,19 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>海砂利水魚</t>
+          <t>僕と私</t>
         </is>
       </c>
       <c r="B412" t="n">
@@ -61433,19 +62289,19 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>田中</t>
+          <t>名無し</t>
         </is>
       </c>
       <c r="B413" t="n">
@@ -61453,19 +62309,19 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>番</t>
+          <t>天我迅</t>
         </is>
       </c>
       <c r="B414" t="n">
@@ -61473,19 +62329,19 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>絶</t>
+          <t>女子三人衆</t>
         </is>
       </c>
       <c r="B415" t="n">
@@ -61493,19 +62349,19 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>絶ちゃん</t>
+          <t>彩 なまがき</t>
         </is>
       </c>
       <c r="B416" t="n">
@@ -61513,19 +62369,19 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>美優</t>
+          <t>正装しん</t>
         </is>
       </c>
       <c r="B417" t="n">
@@ -61533,19 +62389,19 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>赤ちゃん</t>
+          <t>海砂利水魚</t>
         </is>
       </c>
       <c r="B418" t="n">
@@ -61553,30 +62409,150 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
+          <t>田中</t>
+        </is>
+      </c>
+      <c r="B419" t="n">
+        <v>1</v>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>番</t>
+        </is>
+      </c>
+      <c r="B420" t="n">
+        <v>1</v>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>絶</t>
+        </is>
+      </c>
+      <c r="B421" t="n">
+        <v>1</v>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>絶ちゃん</t>
+        </is>
+      </c>
+      <c r="B422" t="n">
+        <v>1</v>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>美優</t>
+        </is>
+      </c>
+      <c r="B423" t="n">
+        <v>1</v>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>赤ちゃん</t>
+        </is>
+      </c>
+      <c r="B424" t="n">
+        <v>1</v>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
           <t>高田</t>
         </is>
       </c>
-      <c r="B419" t="n">
-        <v>1</v>
-      </c>
-      <c r="C419" t="inlineStr">
+      <c r="B425" t="n">
+        <v>1</v>
+      </c>
+      <c r="C425" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="D419" t="inlineStr">
+      <c r="D425" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
@@ -61633,10 +62609,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="C3" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4">
@@ -61646,10 +62622,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C4" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="5">
@@ -61742,10 +62718,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3">
@@ -61989,10 +62965,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C21" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
     </row>
     <row r="22">
@@ -62002,10 +62978,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C22" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="23">
@@ -62015,10 +62991,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C23" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="24">
@@ -62041,10 +63017,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C25" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -62106,13 +63082,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="C3" t="n">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="D3" t="n">
-        <v>227</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>

--- a/bbs_log.xlsx
+++ b/bbs_log.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H730"/>
+  <dimension ref="A1:H741"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22616,7 +22616,6 @@
           <t>ひがん</t>
         </is>
       </c>
-      <c r="E705" t="inlineStr"/>
       <c r="F705" t="inlineStr">
         <is>
           <t>はやめに</t>
@@ -22627,7 +22626,6 @@
           <t>きたよん</t>
         </is>
       </c>
-      <c r="H705" t="inlineStr"/>
     </row>
     <row r="706">
       <c r="A706" t="n">
@@ -22648,7 +22646,6 @@
           <t>さとる</t>
         </is>
       </c>
-      <c r="E706" t="inlineStr"/>
       <c r="F706" t="inlineStr">
         <is>
           <t>今</t>
@@ -22659,7 +22656,6 @@
           <t>きたよ！！</t>
         </is>
       </c>
-      <c r="H706" t="inlineStr"/>
     </row>
     <row r="707">
       <c r="A707" t="n">
@@ -22680,7 +22676,6 @@
           <t>まろ</t>
         </is>
       </c>
-      <c r="E707" t="inlineStr"/>
       <c r="F707" t="inlineStr">
         <is>
           <t>今</t>
@@ -22691,7 +22686,6 @@
           <t>きた！</t>
         </is>
       </c>
-      <c r="H707" t="inlineStr"/>
     </row>
     <row r="708">
       <c r="A708" t="n">
@@ -22712,7 +22706,6 @@
           <t>スズ</t>
         </is>
       </c>
-      <c r="E708" t="inlineStr"/>
       <c r="F708" t="inlineStr">
         <is>
           <t>今</t>
@@ -22723,7 +22716,6 @@
           <t>来ました！</t>
         </is>
       </c>
-      <c r="H708" t="inlineStr"/>
     </row>
     <row r="709">
       <c r="A709" t="n">
@@ -22744,7 +22736,6 @@
           <t>たかやま、ふくちゃん</t>
         </is>
       </c>
-      <c r="E709" t="inlineStr"/>
       <c r="F709" t="inlineStr">
         <is>
           <t>めがねーず</t>
@@ -22755,7 +22746,6 @@
           <t>きちゃ</t>
         </is>
       </c>
-      <c r="H709" t="inlineStr"/>
     </row>
     <row r="710">
       <c r="A710" t="n">
@@ -22776,7 +22766,6 @@
           <t>まーさん</t>
         </is>
       </c>
-      <c r="E710" t="inlineStr"/>
       <c r="F710" t="inlineStr">
         <is>
           <t>さっき</t>
@@ -22787,7 +22776,6 @@
           <t>きましたよ</t>
         </is>
       </c>
-      <c r="H710" t="inlineStr"/>
     </row>
     <row r="711">
       <c r="A711" t="n">
@@ -22808,7 +22796,6 @@
           <t>変態まっする</t>
         </is>
       </c>
-      <c r="E711" t="inlineStr"/>
       <c r="F711" t="inlineStr">
         <is>
           <t>今</t>
@@ -22819,7 +22806,6 @@
           <t>きましたぜ</t>
         </is>
       </c>
-      <c r="H711" t="inlineStr"/>
     </row>
     <row r="712">
       <c r="A712" t="n">
@@ -22840,7 +22826,6 @@
           <t>サト、コテッチャン</t>
         </is>
       </c>
-      <c r="E712" t="inlineStr"/>
       <c r="F712" t="inlineStr">
         <is>
           <t>いっしょに</t>
@@ -22851,7 +22836,6 @@
           <t>きまんた</t>
         </is>
       </c>
-      <c r="H712" t="inlineStr"/>
     </row>
     <row r="713">
       <c r="A713" t="n">
@@ -22872,7 +22856,6 @@
           <t>ねむねむ</t>
         </is>
       </c>
-      <c r="E713" t="inlineStr"/>
       <c r="F713" t="inlineStr">
         <is>
           <t>お休みだけど</t>
@@ -22883,7 +22866,6 @@
           <t>遊びに来たよ！</t>
         </is>
       </c>
-      <c r="H713" t="inlineStr"/>
     </row>
     <row r="714">
       <c r="A714" t="n">
@@ -22904,7 +22886,6 @@
           <t>ゆずきぴ</t>
         </is>
       </c>
-      <c r="E714" t="inlineStr"/>
       <c r="F714" t="inlineStr">
         <is>
           <t>師範代</t>
@@ -22915,7 +22896,6 @@
           <t>きました</t>
         </is>
       </c>
-      <c r="H714" t="inlineStr"/>
     </row>
     <row r="715">
       <c r="A715" t="n">
@@ -22936,7 +22916,6 @@
           <t>キム、みい</t>
         </is>
       </c>
-      <c r="E715" t="inlineStr"/>
       <c r="F715" t="inlineStr">
         <is>
           <t>いま</t>
@@ -22947,7 +22926,6 @@
           <t>きました！！！</t>
         </is>
       </c>
-      <c r="H715" t="inlineStr"/>
     </row>
     <row r="716">
       <c r="A716" t="n">
@@ -22968,7 +22946,6 @@
           <t>ゆう</t>
         </is>
       </c>
-      <c r="E716" t="inlineStr"/>
       <c r="F716" t="inlineStr">
         <is>
           <t>今</t>
@@ -22979,7 +22956,6 @@
           <t>きました！</t>
         </is>
       </c>
-      <c r="H716" t="inlineStr"/>
     </row>
     <row r="717">
       <c r="A717" t="n">
@@ -23000,7 +22976,6 @@
           <t>まいまい</t>
         </is>
       </c>
-      <c r="E717" t="inlineStr"/>
       <c r="F717" t="inlineStr">
         <is>
           <t>3回目</t>
@@ -23011,7 +22986,6 @@
           <t>きました</t>
         </is>
       </c>
-      <c r="H717" t="inlineStr"/>
     </row>
     <row r="718">
       <c r="A718" t="n">
@@ -23032,7 +23006,6 @@
           <t>ましゅ会長</t>
         </is>
       </c>
-      <c r="E718" t="inlineStr"/>
       <c r="F718" t="inlineStr">
         <is>
           <t>いま</t>
@@ -23043,7 +23016,6 @@
           <t>登場</t>
         </is>
       </c>
-      <c r="H718" t="inlineStr"/>
     </row>
     <row r="719">
       <c r="A719" t="n">
@@ -23064,7 +23036,6 @@
           <t>碧咲</t>
         </is>
       </c>
-      <c r="E719" t="inlineStr"/>
       <c r="F719" t="inlineStr">
         <is>
           <t>ねむい</t>
@@ -23075,7 +23046,6 @@
           <t>これから行きます</t>
         </is>
       </c>
-      <c r="H719" t="inlineStr"/>
     </row>
     <row r="720">
       <c r="A720" t="n">
@@ -23096,7 +23066,6 @@
           <t>カズヤ</t>
         </is>
       </c>
-      <c r="E720" t="inlineStr"/>
       <c r="F720" t="inlineStr">
         <is>
           <t>今</t>
@@ -23107,7 +23076,6 @@
           <t>きました！</t>
         </is>
       </c>
-      <c r="H720" t="inlineStr"/>
     </row>
     <row r="721">
       <c r="A721" t="n">
@@ -23128,7 +23096,6 @@
           <t>よしやん、かな</t>
         </is>
       </c>
-      <c r="E721" t="inlineStr"/>
       <c r="F721" t="inlineStr">
         <is>
           <t>今週も</t>
@@ -23139,7 +23106,6 @@
           <t>きたたたたたたた</t>
         </is>
       </c>
-      <c r="H721" t="inlineStr"/>
     </row>
     <row r="722">
       <c r="A722" t="n">
@@ -23160,7 +23126,6 @@
           <t>えいたろう</t>
         </is>
       </c>
-      <c r="E722" t="inlineStr"/>
       <c r="F722" t="inlineStr">
         <is>
           <t>今</t>
@@ -23171,7 +23136,6 @@
           <t>きました！！！</t>
         </is>
       </c>
-      <c r="H722" t="inlineStr"/>
     </row>
     <row r="723">
       <c r="A723" t="n">
@@ -23192,7 +23156,6 @@
           <t>たいせい</t>
         </is>
       </c>
-      <c r="E723" t="inlineStr"/>
       <c r="F723" t="inlineStr">
         <is>
           <t>今日は遅めに</t>
@@ -23203,7 +23166,6 @@
           <t>きましたよ！！！</t>
         </is>
       </c>
-      <c r="H723" t="inlineStr"/>
     </row>
     <row r="724">
       <c r="A724" t="n">
@@ -23224,7 +23186,6 @@
           <t>ちほ</t>
         </is>
       </c>
-      <c r="E724" t="inlineStr"/>
       <c r="F724" t="inlineStr">
         <is>
           <t>今</t>
@@ -23235,7 +23196,6 @@
           <t>きたよん</t>
         </is>
       </c>
-      <c r="H724" t="inlineStr"/>
     </row>
     <row r="725">
       <c r="A725" t="n">
@@ -23256,7 +23216,6 @@
           <t>けいご、びん、しょう</t>
         </is>
       </c>
-      <c r="E725" t="inlineStr"/>
       <c r="F725" t="inlineStr">
         <is>
           <t>はじめて</t>
@@ -23267,7 +23226,6 @@
           <t>きまんた</t>
         </is>
       </c>
-      <c r="H725" t="inlineStr"/>
     </row>
     <row r="726">
       <c r="A726" t="n">
@@ -23288,7 +23246,6 @@
           <t>みっちー、クワレ</t>
         </is>
       </c>
-      <c r="E726" t="inlineStr"/>
       <c r="F726" t="inlineStr">
         <is>
           <t>今</t>
@@ -23299,7 +23256,6 @@
           <t>きました</t>
         </is>
       </c>
-      <c r="H726" t="inlineStr"/>
     </row>
     <row r="727">
       <c r="A727" t="n">
@@ -23320,7 +23276,6 @@
           <t>ぽちゃりす組</t>
         </is>
       </c>
-      <c r="E727" t="inlineStr"/>
       <c r="F727" t="inlineStr">
         <is>
           <t>仕事終わり</t>
@@ -23331,7 +23286,6 @@
           <t>来ました！</t>
         </is>
       </c>
-      <c r="H727" t="inlineStr"/>
     </row>
     <row r="728">
       <c r="A728" t="n">
@@ -23352,7 +23306,6 @@
           <t>カズ、ダイゴ、シン</t>
         </is>
       </c>
-      <c r="E728" t="inlineStr"/>
       <c r="F728" t="inlineStr">
         <is>
           <t>3人で</t>
@@ -23363,7 +23316,6 @@
           <t>来ました！</t>
         </is>
       </c>
-      <c r="H728" t="inlineStr"/>
     </row>
     <row r="729">
       <c r="A729" t="n">
@@ -23384,7 +23336,6 @@
           <t>TKC,るい</t>
         </is>
       </c>
-      <c r="E729" t="inlineStr"/>
       <c r="F729" t="inlineStr">
         <is>
           <t>すこし</t>
@@ -23395,7 +23346,6 @@
           <t>きました！</t>
         </is>
       </c>
-      <c r="H729" t="inlineStr"/>
     </row>
     <row r="730">
       <c r="A730" t="n">
@@ -23449,6 +23399,378 @@
         </is>
       </c>
     </row>
+    <row r="731">
+      <c r="A731" t="n">
+        <v>28197</v>
+      </c>
+      <c r="B731" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>17:11:27</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>キムと超ドMみい</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr"/>
+      <c r="F731" t="inlineStr">
+        <is>
+          <t>今夜は縛って</t>
+        </is>
+      </c>
+      <c r="G731" t="inlineStr">
+        <is>
+          <t>来店します</t>
+        </is>
+      </c>
+      <c r="H731" t="inlineStr"/>
+    </row>
+    <row r="732">
+      <c r="A732" t="n">
+        <v>28199</v>
+      </c>
+      <c r="B732" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>19:07:07</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>とうや</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr"/>
+      <c r="F732" t="inlineStr">
+        <is>
+          <t>宮コン</t>
+        </is>
+      </c>
+      <c r="G732" t="inlineStr">
+        <is>
+          <t>終わりに</t>
+        </is>
+      </c>
+      <c r="H732" t="inlineStr"/>
+    </row>
+    <row r="733">
+      <c r="A733" t="n">
+        <v>28200</v>
+      </c>
+      <c r="B733" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>19:07:35</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>キム＆みー</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr"/>
+      <c r="F733" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G733" t="inlineStr">
+        <is>
+          <t>来たよ！</t>
+        </is>
+      </c>
+      <c r="H733" t="inlineStr"/>
+    </row>
+    <row r="734">
+      <c r="A734" t="n">
+        <v>28203</v>
+      </c>
+      <c r="B734" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>19:46:13</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>ましゅ会長</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr"/>
+      <c r="F734" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G734" t="inlineStr">
+        <is>
+          <t>きたんご＾＾</t>
+        </is>
+      </c>
+      <c r="H734" t="inlineStr"/>
+    </row>
+    <row r="735">
+      <c r="A735" t="n">
+        <v>28205</v>
+      </c>
+      <c r="B735" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>20:15:20</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>カズヤ</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr"/>
+      <c r="F735" t="inlineStr">
+        <is>
+          <t>今日も</t>
+        </is>
+      </c>
+      <c r="G735" t="inlineStr">
+        <is>
+          <t>きたよー</t>
+        </is>
+      </c>
+      <c r="H735" t="inlineStr"/>
+    </row>
+    <row r="736">
+      <c r="A736" t="n">
+        <v>28212</v>
+      </c>
+      <c r="B736" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>21:13:11</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>ゆずきち</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr"/>
+      <c r="F736" t="inlineStr">
+        <is>
+          <t>ライブ</t>
+        </is>
+      </c>
+      <c r="G736" t="inlineStr">
+        <is>
+          <t>終わり</t>
+        </is>
+      </c>
+      <c r="H736" t="inlineStr"/>
+    </row>
+    <row r="737">
+      <c r="A737" t="n">
+        <v>28213</v>
+      </c>
+      <c r="B737" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>21:13:16</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>彩</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr"/>
+      <c r="F737" t="inlineStr">
+        <is>
+          <t>いま</t>
+        </is>
+      </c>
+      <c r="G737" t="inlineStr">
+        <is>
+          <t>来たよ</t>
+        </is>
+      </c>
+      <c r="H737" t="inlineStr"/>
+    </row>
+    <row r="738">
+      <c r="A738" t="n">
+        <v>28214</v>
+      </c>
+      <c r="B738" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>21:13:44</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>ひがんたん</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr"/>
+      <c r="F738" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G738" t="inlineStr">
+        <is>
+          <t>きたんたん</t>
+        </is>
+      </c>
+      <c r="H738" t="inlineStr"/>
+    </row>
+    <row r="739">
+      <c r="A739" t="n">
+        <v>28218</v>
+      </c>
+      <c r="B739" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>23:44:01</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>ふくちゃん</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr"/>
+      <c r="F739" t="inlineStr">
+        <is>
+          <t>休憩</t>
+        </is>
+      </c>
+      <c r="G739" t="inlineStr">
+        <is>
+          <t>しにきたよ</t>
+        </is>
+      </c>
+      <c r="H739" t="inlineStr"/>
+    </row>
+    <row r="740">
+      <c r="A740" t="n">
+        <v>28220</v>
+      </c>
+      <c r="B740" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>00:50:57</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>マロ</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr"/>
+      <c r="F740" t="inlineStr">
+        <is>
+          <t>シースー持って</t>
+        </is>
+      </c>
+      <c r="G740" t="inlineStr">
+        <is>
+          <t>今から行くにょ</t>
+        </is>
+      </c>
+      <c r="H740" t="inlineStr"/>
+    </row>
+    <row r="741">
+      <c r="A741" t="n">
+        <v>28222</v>
+      </c>
+      <c r="B741" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>05:42:14</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr">
+        <is>
+          <t>新妻マゾヒストのミコト</t>
+        </is>
+      </c>
+      <c r="F741" t="inlineStr">
+        <is>
+          <t>★☆★朝までアゲアゲの月曜日営業が始まるわよ♪★☆★</t>
+        </is>
+      </c>
+      <c r="G741" t="inlineStr">
+        <is>
+          <t>本日9月28日の営業時間は♪
+オープン19:00！ラスト5:00なのよ☆
+担当は
+新妻マゾヒストのミコト
+なのよ♪
+どんな季節でも★BAMBITCH★は色気ムンムンで暑すぎる♪
+バンビッチでおもいっきりはじけちゃって（笑）
+精力は無くても性欲がある！？
+大人の憩いと禁断サークル盛りだくさん！
+憩いと交流の魔性の遊び場バンビッチは素敵な出会いを 提供いたします（笑)☆☆
+おつまみ等の持ち込みは自由なのでみんなで持ち寄ってお近づきのきっかけにどうぞ♪
+強制や無理強いは一切ございませんので楽しく遊びましょう♪
+宇都宮市宿郷1−12−9　カサブランカビル5F</t>
+        </is>
+      </c>
+      <c r="H741" t="inlineStr">
+        <is>
+          <t>img20260928054214.jpg</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23460,7 +23782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I859"/>
+  <dimension ref="A1:I869"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60412,6 +60734,436 @@
       <c r="I859" t="inlineStr">
         <is>
           <t>きました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B860" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C860" t="inlineStr">
+        <is>
+          <t>17:11:27</t>
+        </is>
+      </c>
+      <c r="D860" t="n">
+        <v>28197</v>
+      </c>
+      <c r="E860" t="inlineStr">
+        <is>
+          <t>キムと超ドMみい</t>
+        </is>
+      </c>
+      <c r="F860" t="n">
+        <v>4</v>
+      </c>
+      <c r="G860" t="inlineStr">
+        <is>
+          <t>キムと超ドMみい</t>
+        </is>
+      </c>
+      <c r="H860" t="inlineStr">
+        <is>
+          <t>今夜は縛って</t>
+        </is>
+      </c>
+      <c r="I860" t="inlineStr">
+        <is>
+          <t>来店します</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B861" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C861" t="inlineStr">
+        <is>
+          <t>19:07:07</t>
+        </is>
+      </c>
+      <c r="D861" t="n">
+        <v>28199</v>
+      </c>
+      <c r="E861" t="inlineStr">
+        <is>
+          <t>とうや</t>
+        </is>
+      </c>
+      <c r="F861" t="n">
+        <v>2</v>
+      </c>
+      <c r="G861" t="inlineStr">
+        <is>
+          <t>とうや</t>
+        </is>
+      </c>
+      <c r="H861" t="inlineStr">
+        <is>
+          <t>宮コン</t>
+        </is>
+      </c>
+      <c r="I861" t="inlineStr">
+        <is>
+          <t>終わりに</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B862" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C862" t="inlineStr">
+        <is>
+          <t>19:07:35</t>
+        </is>
+      </c>
+      <c r="D862" t="n">
+        <v>28200</v>
+      </c>
+      <c r="E862" t="inlineStr">
+        <is>
+          <t>キム＆みー</t>
+        </is>
+      </c>
+      <c r="F862" t="n">
+        <v>1</v>
+      </c>
+      <c r="G862" t="inlineStr">
+        <is>
+          <t>キム＆みー</t>
+        </is>
+      </c>
+      <c r="H862" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="I862" t="inlineStr">
+        <is>
+          <t>来たよ！</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B863" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C863" t="inlineStr">
+        <is>
+          <t>19:46:13</t>
+        </is>
+      </c>
+      <c r="D863" t="n">
+        <v>28203</v>
+      </c>
+      <c r="E863" t="inlineStr">
+        <is>
+          <t>ましゅ会長</t>
+        </is>
+      </c>
+      <c r="F863" t="n">
+        <v>2</v>
+      </c>
+      <c r="G863" t="inlineStr">
+        <is>
+          <t>ましゅ会長</t>
+        </is>
+      </c>
+      <c r="H863" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="I863" t="inlineStr">
+        <is>
+          <t>きたんご＾＾</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B864" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C864" t="inlineStr">
+        <is>
+          <t>20:15:20</t>
+        </is>
+      </c>
+      <c r="D864" t="n">
+        <v>28205</v>
+      </c>
+      <c r="E864" t="inlineStr">
+        <is>
+          <t>カズヤ</t>
+        </is>
+      </c>
+      <c r="F864" t="n">
+        <v>3</v>
+      </c>
+      <c r="G864" t="inlineStr">
+        <is>
+          <t>カズヤ</t>
+        </is>
+      </c>
+      <c r="H864" t="inlineStr">
+        <is>
+          <t>今日も</t>
+        </is>
+      </c>
+      <c r="I864" t="inlineStr">
+        <is>
+          <t>きたよー</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B865" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C865" t="inlineStr">
+        <is>
+          <t>21:13:11</t>
+        </is>
+      </c>
+      <c r="D865" t="n">
+        <v>28212</v>
+      </c>
+      <c r="E865" t="inlineStr">
+        <is>
+          <t>ゆずきち</t>
+        </is>
+      </c>
+      <c r="F865" t="n">
+        <v>10</v>
+      </c>
+      <c r="G865" t="inlineStr">
+        <is>
+          <t>ゆずきち</t>
+        </is>
+      </c>
+      <c r="H865" t="inlineStr">
+        <is>
+          <t>ライブ</t>
+        </is>
+      </c>
+      <c r="I865" t="inlineStr">
+        <is>
+          <t>終わり</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B866" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C866" t="inlineStr">
+        <is>
+          <t>21:13:16</t>
+        </is>
+      </c>
+      <c r="D866" t="n">
+        <v>28213</v>
+      </c>
+      <c r="E866" t="inlineStr">
+        <is>
+          <t>彩</t>
+        </is>
+      </c>
+      <c r="F866" t="n">
+        <v>13</v>
+      </c>
+      <c r="G866" t="inlineStr">
+        <is>
+          <t>彩</t>
+        </is>
+      </c>
+      <c r="H866" t="inlineStr">
+        <is>
+          <t>いま</t>
+        </is>
+      </c>
+      <c r="I866" t="inlineStr">
+        <is>
+          <t>来たよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B867" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C867" t="inlineStr">
+        <is>
+          <t>21:13:44</t>
+        </is>
+      </c>
+      <c r="D867" t="n">
+        <v>28214</v>
+      </c>
+      <c r="E867" t="inlineStr">
+        <is>
+          <t>ひがんたん</t>
+        </is>
+      </c>
+      <c r="F867" t="n">
+        <v>4</v>
+      </c>
+      <c r="G867" t="inlineStr">
+        <is>
+          <t>ひがんたん</t>
+        </is>
+      </c>
+      <c r="H867" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="I867" t="inlineStr">
+        <is>
+          <t>きたんたん</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B868" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C868" t="inlineStr">
+        <is>
+          <t>23:44:01</t>
+        </is>
+      </c>
+      <c r="D868" t="n">
+        <v>28218</v>
+      </c>
+      <c r="E868" t="inlineStr">
+        <is>
+          <t>ふくちゃん</t>
+        </is>
+      </c>
+      <c r="F868" t="n">
+        <v>5</v>
+      </c>
+      <c r="G868" t="inlineStr">
+        <is>
+          <t>ふくちゃん</t>
+        </is>
+      </c>
+      <c r="H868" t="inlineStr">
+        <is>
+          <t>休憩</t>
+        </is>
+      </c>
+      <c r="I868" t="inlineStr">
+        <is>
+          <t>しにきたよ</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B869" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C869" t="inlineStr">
+        <is>
+          <t>00:50:57</t>
+        </is>
+      </c>
+      <c r="D869" t="n">
+        <v>28220</v>
+      </c>
+      <c r="E869" t="inlineStr">
+        <is>
+          <t>マロ</t>
+        </is>
+      </c>
+      <c r="F869" t="n">
+        <v>4</v>
+      </c>
+      <c r="G869" t="inlineStr">
+        <is>
+          <t>マロ</t>
+        </is>
+      </c>
+      <c r="H869" t="inlineStr">
+        <is>
+          <t>シースー持って</t>
+        </is>
+      </c>
+      <c r="I869" t="inlineStr">
+        <is>
+          <t>今から行くにょ</t>
         </is>
       </c>
     </row>
@@ -60426,7 +61178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D462"/>
+  <dimension ref="A1:D463"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60558,7 +61310,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -60567,7 +61319,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -60594,27 +61346,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>なお</t>
+          <t>ゆずきち</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ゆずきち</t>
+          <t>なお</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -60622,12 +61374,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
@@ -60974,7 +61726,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ふくてゃ</t>
+          <t>ふくちゃん</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -60982,19 +61734,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>まいなす</t>
+          <t>ふくてゃ</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -61002,19 +61754,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ましゅ社長</t>
+          <t>まいなす</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -61022,19 +61774,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
           <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>りん</t>
+          <t>ましゅ社長</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -61042,19 +61794,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ろくじ</t>
+          <t>りん</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -61062,19 +61814,19 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>キム</t>
+          <t>ろくじ</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -61082,39 +61834,39 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>bee</t>
+          <t>キム</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>くれは</t>
+          <t>bee</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -61122,19 +61874,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>すず</t>
+          <t>くれは</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -61142,19 +61894,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ちゃそたけ</t>
+          <t>すず</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -61162,19 +61914,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>てくのちゃん</t>
+          <t>ちゃそたけ</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -61182,19 +61934,19 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>でで</t>
+          <t>てくのちゃん</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -61202,7 +61954,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -61214,7 +61966,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ふくちゃん</t>
+          <t>でで</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -61222,19 +61974,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>まいなちゅ</t>
+          <t>ひがんたん</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -61242,19 +61994,19 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>まなみ</t>
+          <t>まいなちゅ</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -61262,19 +62014,19 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>まーくん</t>
+          <t>まなみ</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -61282,19 +62034,19 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ゆうき</t>
+          <t>まーくん</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -61302,19 +62054,19 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ゆずきん</t>
+          <t>ゆうき</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -61322,19 +62074,19 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>よしお</t>
+          <t>ゆずきん</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -61342,19 +62094,19 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>よしやん</t>
+          <t>よしお</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -61362,19 +62114,19 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>コテッチャン</t>
+          <t>よしやん</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -61382,7 +62134,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -61394,67 +62146,67 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>キムと超ドMみい</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>コテッチャン</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>マロ</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -61462,19 +62214,19 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>T山</t>
+          <t>R</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -61482,19 +62234,19 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -61502,19 +62254,19 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>あいちゃん</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -61522,19 +62274,19 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>あや</t>
+          <t>T山</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -61542,19 +62294,19 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>えぬ</t>
+          <t>−</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -61562,19 +62314,19 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>さと</t>
+          <t>あいちゃん</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -61582,19 +62334,19 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>しゅん</t>
+          <t>あや</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -61602,19 +62354,19 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>すー</t>
+          <t>えぬ</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -61622,19 +62374,19 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>すーさん</t>
+          <t>さと</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -61642,19 +62394,19 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>たかやまん</t>
+          <t>しゅん</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -61662,19 +62414,19 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>たつや</t>
+          <t>すー</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -61682,19 +62434,19 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>だいご</t>
+          <t>すーさん</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -61702,19 +62454,19 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>なな</t>
+          <t>たかやまん</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -61722,19 +62474,19 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>なまがき</t>
+          <t>たつや</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -61742,7 +62494,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -61754,7 +62506,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ひがんたん</t>
+          <t>だいご</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -61762,19 +62514,19 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ぽちゃりす組</t>
+          <t>なな</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -61782,19 +62534,19 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>まゆ</t>
+          <t>なまがき</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -61802,19 +62554,19 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>まろ</t>
+          <t>ぽちゃりす組</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -61822,19 +62574,19 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>もっぷ</t>
+          <t>まゆ</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -61842,19 +62594,19 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>よしおたん</t>
+          <t>まろ</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -61862,19 +62614,19 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>りょう</t>
+          <t>もっぷ</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -61882,19 +62634,19 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>れいら</t>
+          <t>よしおたん</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -61902,19 +62654,19 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>カー</t>
+          <t>りょう</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -61922,19 +62674,19 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>キムとドMみい</t>
+          <t>れいら</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -61942,19 +62694,19 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>キムと超ドMみい</t>
+          <t>カズヤ</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -61962,19 +62714,19 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ケン</t>
+          <t>カー</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -61982,19 +62734,19 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>タツヤ</t>
+          <t>キムとドMみい</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -62002,19 +62754,19 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>マロ</t>
+          <t>ケン</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -62022,19 +62774,19 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ミコト</t>
+          <t>タツヤ</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -62042,19 +62794,19 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>愛とスケベの戦士</t>
+          <t>ミコト</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -62062,39 +62814,39 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>愛とスケベの戦士</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Bee</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -62102,19 +62854,19 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>YZK</t>
+          <t>Bee</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -62122,19 +62874,19 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>あさみん</t>
+          <t>YZK</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -62142,19 +62894,19 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>あっくん</t>
+          <t>あさみん</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -62162,19 +62914,19 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>あゆ</t>
+          <t>あっくん</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -62182,19 +62934,19 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>あんこ</t>
+          <t>あゆ</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -62202,19 +62954,19 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>いっちゃん</t>
+          <t>あんこ</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -62222,19 +62974,19 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>いぬ</t>
+          <t>いっちゃん</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -62247,14 +62999,14 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>える</t>
+          <t>いぬ</t>
         </is>
       </c>
       <c r="B92" t="n">
@@ -62262,19 +63014,19 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>おでで</t>
+          <t>える</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -62282,19 +63034,19 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>かい</t>
+          <t>おでで</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -62302,19 +63054,19 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>きむ</t>
+          <t>かい</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -62322,19 +63074,19 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>けん</t>
+          <t>きむ</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -62342,19 +63094,19 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
           <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>こーだい</t>
+          <t>けん</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -62362,19 +63114,19 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>さとるん</t>
+          <t>こーだい</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -62382,19 +63134,19 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>しょうた</t>
+          <t>さとるん</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -62402,19 +63154,19 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>しーたん</t>
+          <t>しょうた</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -62422,19 +63174,19 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>すーたく</t>
+          <t>しーたん</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -62447,14 +63199,14 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>たくや</t>
+          <t>すーたく</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -62462,7 +63214,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -62474,7 +63226,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>たつ</t>
+          <t>たくや</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -62482,19 +63234,19 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ちぇちぇ</t>
+          <t>たつ</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -62502,7 +63254,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -62514,7 +63266,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ちっち</t>
+          <t>ちぇちぇ</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -62522,19 +63274,19 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>てつじ</t>
+          <t>ちっち</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -62542,19 +63294,19 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>とし</t>
+          <t>てつじ</t>
         </is>
       </c>
       <c r="B107" t="n">
@@ -62562,19 +63314,19 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ねむねむ</t>
+          <t>とうや</t>
         </is>
       </c>
       <c r="B108" t="n">
@@ -62582,19 +63334,19 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ひがんちゃん</t>
+          <t>とし</t>
         </is>
       </c>
       <c r="B109" t="n">
@@ -62602,19 +63354,19 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ふく</t>
+          <t>ねむねむ</t>
         </is>
       </c>
       <c r="B110" t="n">
@@ -62622,19 +63374,19 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ぶりちゃん</t>
+          <t>ひがんちゃん</t>
         </is>
       </c>
       <c r="B111" t="n">
@@ -62642,19 +63394,19 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>べー</t>
+          <t>ふく</t>
         </is>
       </c>
       <c r="B112" t="n">
@@ -62662,19 +63414,19 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>まい</t>
+          <t>ぶりちゃん</t>
         </is>
       </c>
       <c r="B113" t="n">
@@ -62687,14 +63439,14 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>まりん</t>
+          <t>べー</t>
         </is>
       </c>
       <c r="B114" t="n">
@@ -62702,19 +63454,19 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>まーさん</t>
+          <t>まい</t>
         </is>
       </c>
       <c r="B115" t="n">
@@ -62722,19 +63474,19 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>みっちー</t>
+          <t>ましゅ会長</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -62742,7 +63494,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -62754,7 +63506,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>みれい</t>
+          <t>まりん</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -62762,19 +63514,19 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>みー</t>
+          <t>まーさん</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -62782,19 +63534,19 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>めい</t>
+          <t>みっちー</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -62802,19 +63554,19 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>やえ</t>
+          <t>みれい</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -62822,19 +63574,19 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ゆうくん</t>
+          <t>みー</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -62842,19 +63594,19 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ゆすき</t>
+          <t>めい</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -62862,19 +63614,19 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>よっしー</t>
+          <t>やえ</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -62882,19 +63634,19 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>よっち</t>
+          <t>ゆうくん</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -62902,19 +63654,19 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>りお</t>
+          <t>ゆすき</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -62922,19 +63674,19 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>りゅう</t>
+          <t>よっしー</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -62942,19 +63694,19 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>オカニー</t>
+          <t>よっち</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -62962,19 +63714,19 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>カズヤ</t>
+          <t>りお</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -62982,19 +63734,19 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>キムとドMまゆ</t>
+          <t>りゅう</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -63002,19 +63754,19 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>クワレ</t>
+          <t>オカニー</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -63022,19 +63774,19 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>タカ</t>
+          <t>キムとドMまゆ</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -63042,19 +63794,19 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>タク</t>
+          <t>クワレ</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -63062,19 +63814,19 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>タケ</t>
+          <t>タカ</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -63082,19 +63834,19 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ダイゴ</t>
+          <t>タク</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -63102,19 +63854,19 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>テクノっち</t>
+          <t>タケ</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -63122,19 +63874,19 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>マイナス</t>
+          <t>ダイゴ</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -63142,19 +63894,19 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>マサ</t>
+          <t>テクノっち</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -63162,19 +63914,19 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>マッスル</t>
+          <t>マイナス</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -63182,19 +63934,19 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>マナティ</t>
+          <t>マサ</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -63202,19 +63954,19 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>リン</t>
+          <t>マッスル</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -63222,19 +63974,19 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>変態マッスル</t>
+          <t>マナティ</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -63242,19 +63994,19 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>大塚</t>
+          <t>リン</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -63262,19 +64014,19 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>高田</t>
+          <t>変態マッスル</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -63282,59 +64034,59 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>5人衆</t>
+          <t>大塚</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>高田</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>EVANS×２</t>
+          <t>5人衆</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -63342,19 +64094,19 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>HGN</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -63362,19 +64114,19 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>JPTR</t>
+          <t>EVANS×２</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -63382,19 +64134,19 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>HGN</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -63402,19 +64154,19 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>KSK</t>
+          <t>JPTR</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -63422,19 +64174,19 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>KUMA</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -63442,19 +64194,19 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>KSK</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -63462,19 +64214,19 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>KUMA</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -63482,19 +64234,19 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>NMGK</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -63502,19 +64254,19 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>N氏御一行</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -63522,19 +64274,19 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>SIKUSENAチャンネルヒロキ</t>
+          <t>NMGK</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -63542,19 +64294,19 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>STR</t>
+          <t>N氏御一行</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -63562,19 +64314,19 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>TARU</t>
+          <t>SIKUSENAチャンネルヒロキ</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -63582,19 +64334,19 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>STR</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -63602,19 +64354,19 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Tやま</t>
+          <t>TARU</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -63622,19 +64374,19 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>TT</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -63642,19 +64394,19 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>hikari</t>
+          <t>Tやま</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -63662,19 +64414,19 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>nuri</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -63682,19 +64434,19 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>sho</t>
+          <t>hikari</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -63702,19 +64454,19 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>taka</t>
+          <t>nuri</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -63722,19 +64474,19 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>★Zakk★</t>
+          <t>sho</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -63742,19 +64494,19 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>あき</t>
+          <t>taka</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -63762,19 +64514,19 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>あさみ</t>
+          <t>★Zakk★</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -63782,19 +64534,19 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>あす</t>
+          <t>あき</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -63802,19 +64554,19 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>あにー</t>
+          <t>あさみ</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -63822,19 +64574,19 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>あまねちゃん</t>
+          <t>あす</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -63854,7 +64606,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>ありす</t>
+          <t>あにー</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -63862,19 +64614,19 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>いおり</t>
+          <t>あまねちゃん</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -63882,19 +64634,19 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>いけちゃん</t>
+          <t>ありす</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -63902,19 +64654,19 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>いぶお</t>
+          <t>いおり</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -63922,19 +64674,19 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>うらら</t>
+          <t>いけちゃん</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -63942,19 +64694,19 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>えいたろう</t>
+          <t>いぶお</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -63962,19 +64714,19 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>えび</t>
+          <t>うらら</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -63982,19 +64734,19 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>えーたろ</t>
+          <t>えいたろう</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -64002,19 +64754,19 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>おじき</t>
+          <t>えび</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -64022,19 +64774,19 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>おじきち</t>
+          <t>えーたろ</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -64042,19 +64794,19 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>おすー</t>
+          <t>おじき</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -64062,19 +64814,19 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>おちんぽベルセルク</t>
+          <t>おじきち</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -64082,19 +64834,19 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>おにゃん</t>
+          <t>おすー</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -64102,19 +64854,19 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>おにゃんにゃん</t>
+          <t>おちんぽベルセルク</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -64122,19 +64874,19 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>おばし</t>
+          <t>おにゃん</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -64142,19 +64894,19 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>おもち</t>
+          <t>おにゃんにゃん</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -64162,19 +64914,19 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>かける</t>
+          <t>おばし</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -64182,19 +64934,19 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>かずき</t>
+          <t>おもち</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -64202,19 +64954,19 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>かず＆TKC＆のんのん</t>
+          <t>かける</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -64222,19 +64974,19 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>かつ</t>
+          <t>かずき</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -64242,19 +64994,19 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>かな(絶ちゃん</t>
+          <t>かず＆TKC＆のんのん</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -64274,7 +65026,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>かな(絶ちゃん)/おっつん</t>
+          <t>かつ</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -64282,19 +65034,19 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>がん</t>
+          <t>かな(絶ちゃん</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -64302,19 +65054,19 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>きむさん</t>
+          <t>かな(絶ちゃん)/おっつん</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -64322,19 +65074,19 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>きむむ</t>
+          <t>がん</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -64342,19 +65094,19 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>きむら</t>
+          <t>きむさん</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -64362,19 +65114,19 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>きょうちゃん</t>
+          <t>きむむ</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -64382,19 +65134,19 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>きんたまよ</t>
+          <t>きむら</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -64402,19 +65154,19 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>くっぱ</t>
+          <t>きょうちゃん</t>
         </is>
       </c>
       <c r="B200" t="n">
@@ -64422,19 +65174,19 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>くま</t>
+          <t>きんたまよ</t>
         </is>
       </c>
       <c r="B201" t="n">
@@ -64442,19 +65194,19 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>くり</t>
+          <t>くっぱ</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -64474,7 +65226,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>ぐっちゃん</t>
+          <t>くま</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -64482,19 +65234,19 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>ぐっちゃん（チャイマフィ）</t>
+          <t>くり</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -64502,19 +65254,19 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>けい</t>
+          <t>ぐっちゃん</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -64522,19 +65274,19 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>けいご</t>
+          <t>ぐっちゃん（チャイマフィ）</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -64542,19 +65294,19 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>けいちゃん</t>
+          <t>けい</t>
         </is>
       </c>
       <c r="B207" t="n">
@@ -64562,19 +65314,19 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>けんけん</t>
+          <t>けいご</t>
         </is>
       </c>
       <c r="B208" t="n">
@@ -64582,19 +65334,19 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>げん</t>
+          <t>けいちゃん</t>
         </is>
       </c>
       <c r="B209" t="n">
@@ -64602,19 +65354,19 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>げんき</t>
+          <t>けんけん</t>
         </is>
       </c>
       <c r="B210" t="n">
@@ -64622,19 +65374,19 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>こう</t>
+          <t>げん</t>
         </is>
       </c>
       <c r="B211" t="n">
@@ -64642,19 +65394,19 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>こうた</t>
+          <t>げんき</t>
         </is>
       </c>
       <c r="B212" t="n">
@@ -64662,19 +65414,19 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>こてつ</t>
+          <t>こう</t>
         </is>
       </c>
       <c r="B213" t="n">
@@ -64694,7 +65446,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>ことねえ</t>
+          <t>こうた</t>
         </is>
       </c>
       <c r="B214" t="n">
@@ -64702,19 +65454,19 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>ことり</t>
+          <t>こてつ</t>
         </is>
       </c>
       <c r="B215" t="n">
@@ -64722,19 +65474,19 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>ごん</t>
+          <t>ことねえ</t>
         </is>
       </c>
       <c r="B216" t="n">
@@ -64742,19 +65494,19 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>さかもと</t>
+          <t>ことり</t>
         </is>
       </c>
       <c r="B217" t="n">
@@ -64762,19 +65514,19 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>さくら</t>
+          <t>ごん</t>
         </is>
       </c>
       <c r="B218" t="n">
@@ -64782,19 +65534,19 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>さとりゅ</t>
+          <t>さかもと</t>
         </is>
       </c>
       <c r="B219" t="n">
@@ -64802,19 +65554,19 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>さな</t>
+          <t>さくら</t>
         </is>
       </c>
       <c r="B220" t="n">
@@ -64822,19 +65574,19 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>さない</t>
+          <t>さとりゅ</t>
         </is>
       </c>
       <c r="B221" t="n">
@@ -64842,19 +65594,19 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>さや</t>
+          <t>さな</t>
         </is>
       </c>
       <c r="B222" t="n">
@@ -64862,19 +65614,19 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>しずか</t>
+          <t>さない</t>
         </is>
       </c>
       <c r="B223" t="n">
@@ -64882,19 +65634,19 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>しょう</t>
+          <t>さや</t>
         </is>
       </c>
       <c r="B224" t="n">
@@ -64902,19 +65654,19 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>しょー</t>
+          <t>しずか</t>
         </is>
       </c>
       <c r="B225" t="n">
@@ -64922,19 +65674,19 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>しりゅう</t>
+          <t>しょう</t>
         </is>
       </c>
       <c r="B226" t="n">
@@ -64942,19 +65694,19 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>じん</t>
+          <t>しょー</t>
         </is>
       </c>
       <c r="B227" t="n">
@@ -64962,19 +65714,19 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>せいら</t>
+          <t>しりゅう</t>
         </is>
       </c>
       <c r="B228" t="n">
@@ -64982,19 +65734,19 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>ぜっちゃん＆おっつん</t>
+          <t>じん</t>
         </is>
       </c>
       <c r="B229" t="n">
@@ -65002,19 +65754,19 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>たいせー</t>
+          <t>せいら</t>
         </is>
       </c>
       <c r="B230" t="n">
@@ -65022,19 +65774,19 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>たか</t>
+          <t>ぜっちゃん＆おっつん</t>
         </is>
       </c>
       <c r="B231" t="n">
@@ -65042,19 +65794,19 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>たかし</t>
+          <t>たいせー</t>
         </is>
       </c>
       <c r="B232" t="n">
@@ -65062,19 +65814,19 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>たかち</t>
+          <t>たか</t>
         </is>
       </c>
       <c r="B233" t="n">
@@ -65082,19 +65834,19 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>たく</t>
+          <t>たかし</t>
         </is>
       </c>
       <c r="B234" t="n">
@@ -65102,19 +65854,19 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>たけ</t>
+          <t>たかち</t>
         </is>
       </c>
       <c r="B235" t="n">
@@ -65122,19 +65874,19 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>たけし</t>
+          <t>たく</t>
         </is>
       </c>
       <c r="B236" t="n">
@@ -65142,19 +65894,19 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>たつお</t>
+          <t>たけ</t>
         </is>
       </c>
       <c r="B237" t="n">
@@ -65162,19 +65914,19 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>たます</t>
+          <t>たけし</t>
         </is>
       </c>
       <c r="B238" t="n">
@@ -65182,19 +65934,19 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>たろー</t>
+          <t>たつお</t>
         </is>
       </c>
       <c r="B239" t="n">
@@ -65202,19 +65954,19 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>だいさく</t>
+          <t>たます</t>
         </is>
       </c>
       <c r="B240" t="n">
@@ -65222,19 +65974,19 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>だいざく</t>
+          <t>たろー</t>
         </is>
       </c>
       <c r="B241" t="n">
@@ -65242,19 +65994,19 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>だいち</t>
+          <t>だいさく</t>
         </is>
       </c>
       <c r="B242" t="n">
@@ -65262,19 +66014,19 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>ちぇちぇ＆ガールズ</t>
+          <t>だいざく</t>
         </is>
       </c>
       <c r="B243" t="n">
@@ -65282,19 +66034,19 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>ちほ</t>
+          <t>だいち</t>
         </is>
       </c>
       <c r="B244" t="n">
@@ -65302,19 +66054,19 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>つかさ</t>
+          <t>ちぇちぇ＆ガールズ</t>
         </is>
       </c>
       <c r="B245" t="n">
@@ -65322,19 +66074,19 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>てくのちん</t>
+          <t>ちほ</t>
         </is>
       </c>
       <c r="B246" t="n">
@@ -65342,19 +66094,19 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>てくのっち</t>
+          <t>つかさ</t>
         </is>
       </c>
       <c r="B247" t="n">
@@ -65362,19 +66114,19 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>てっちゃん</t>
+          <t>てくのちん</t>
         </is>
       </c>
       <c r="B248" t="n">
@@ -65382,19 +66134,19 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>てつ</t>
+          <t>てくのっち</t>
         </is>
       </c>
       <c r="B249" t="n">
@@ -65402,19 +66154,19 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>てる</t>
+          <t>てっちゃん</t>
         </is>
       </c>
       <c r="B250" t="n">
@@ -65422,19 +66174,19 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>でかかわ</t>
+          <t>てつ</t>
         </is>
       </c>
       <c r="B251" t="n">
@@ -65442,19 +66194,19 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>ででたゃ</t>
+          <t>てる</t>
         </is>
       </c>
       <c r="B252" t="n">
@@ -65462,19 +66214,19 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>とうや</t>
+          <t>でかかわ</t>
         </is>
       </c>
       <c r="B253" t="n">
@@ -65482,19 +66234,19 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>とおちゃん</t>
+          <t>ででたゃ</t>
         </is>
       </c>
       <c r="B254" t="n">
@@ -65502,19 +66254,19 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>とっしー</t>
+          <t>とおちゃん</t>
         </is>
       </c>
       <c r="B255" t="n">
@@ -65522,19 +66274,19 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>とも</t>
+          <t>とっしー</t>
         </is>
       </c>
       <c r="B256" t="n">
@@ -65542,19 +66294,19 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>ともち</t>
+          <t>とも</t>
         </is>
       </c>
       <c r="B257" t="n">
@@ -65562,19 +66314,19 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>ともひろ</t>
+          <t>ともち</t>
         </is>
       </c>
       <c r="B258" t="n">
@@ -65582,19 +66334,19 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>ともや</t>
+          <t>ともひろ</t>
         </is>
       </c>
       <c r="B259" t="n">
@@ -65602,19 +66354,19 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>ともゆき</t>
+          <t>ともや</t>
         </is>
       </c>
       <c r="B260" t="n">
@@ -65622,19 +66374,19 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>とーり</t>
+          <t>ともゆき</t>
         </is>
       </c>
       <c r="B261" t="n">
@@ -65642,19 +66394,19 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>どえむちゃん</t>
+          <t>とーり</t>
         </is>
       </c>
       <c r="B262" t="n">
@@ -65662,19 +66414,19 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>ながとも</t>
+          <t>どえむちゃん</t>
         </is>
       </c>
       <c r="B263" t="n">
@@ -65682,19 +66434,19 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>なべ</t>
+          <t>ながとも</t>
         </is>
       </c>
       <c r="B264" t="n">
@@ -65702,19 +66454,19 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>にこちん</t>
+          <t>なべ</t>
         </is>
       </c>
       <c r="B265" t="n">
@@ -65722,19 +66474,19 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>にゃんまげ</t>
+          <t>にこちん</t>
         </is>
       </c>
       <c r="B266" t="n">
@@ -65742,19 +66494,19 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>にょ</t>
+          <t>にゃんまげ</t>
         </is>
       </c>
       <c r="B267" t="n">
@@ -65762,19 +66514,19 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>ねここ</t>
+          <t>にょ</t>
         </is>
       </c>
       <c r="B268" t="n">
@@ -65782,19 +66534,19 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>のぼ</t>
+          <t>ねここ</t>
         </is>
       </c>
       <c r="B269" t="n">
@@ -65802,19 +66554,19 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>のり</t>
+          <t>のぼ</t>
         </is>
       </c>
       <c r="B270" t="n">
@@ -65822,19 +66574,19 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>はち</t>
+          <t>のり</t>
         </is>
       </c>
       <c r="B271" t="n">
@@ -65842,19 +66594,19 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>はな</t>
+          <t>はち</t>
         </is>
       </c>
       <c r="B272" t="n">
@@ -65862,19 +66614,19 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>はなちゃん</t>
+          <t>はな</t>
         </is>
       </c>
       <c r="B273" t="n">
@@ -65882,19 +66634,19 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>はなまる</t>
+          <t>はなちゃん</t>
         </is>
       </c>
       <c r="B274" t="n">
@@ -65902,19 +66654,19 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>はにーちゃん</t>
+          <t>はなまる</t>
         </is>
       </c>
       <c r="B275" t="n">
@@ -65922,19 +66674,19 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>はんまー</t>
+          <t>はにーちゃん</t>
         </is>
       </c>
       <c r="B276" t="n">
@@ -65942,19 +66694,19 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>ひったん</t>
+          <t>はんまー</t>
         </is>
       </c>
       <c r="B277" t="n">
@@ -65962,19 +66714,19 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>ひろし</t>
+          <t>ひったん</t>
         </is>
       </c>
       <c r="B278" t="n">
@@ -65982,19 +66734,19 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>ひろとも</t>
+          <t>ひろし</t>
         </is>
       </c>
       <c r="B279" t="n">
@@ -66002,19 +66754,19 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>びん</t>
+          <t>ひろとも</t>
         </is>
       </c>
       <c r="B280" t="n">
@@ -66022,19 +66774,19 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>ふみ</t>
+          <t>びん</t>
         </is>
       </c>
       <c r="B281" t="n">
@@ -66042,19 +66794,19 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>ぷらぐいん</t>
+          <t>ふみ</t>
         </is>
       </c>
       <c r="B282" t="n">
@@ -66062,19 +66814,19 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>ぺぺ</t>
+          <t>ぷらぐいん</t>
         </is>
       </c>
       <c r="B283" t="n">
@@ -66094,7 +66846,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>ぽて</t>
+          <t>ぺぺ</t>
         </is>
       </c>
       <c r="B284" t="n">
@@ -66102,19 +66854,19 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>まいまいまいまい</t>
+          <t>ぽて</t>
         </is>
       </c>
       <c r="B285" t="n">
@@ -66122,19 +66874,19 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>まいまいん</t>
+          <t>まいまいまいまい</t>
         </is>
       </c>
       <c r="B286" t="n">
@@ -66142,19 +66894,19 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>まおし</t>
+          <t>まいまいん</t>
         </is>
       </c>
       <c r="B287" t="n">
@@ -66174,7 +66926,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>ましゅ会長</t>
+          <t>まおし</t>
         </is>
       </c>
       <c r="B288" t="n">
@@ -66182,12 +66934,12 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
@@ -67954,7 +68706,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>キム＆むい</t>
+          <t>キム＆みー</t>
         </is>
       </c>
       <c r="B377" t="n">
@@ -67962,19 +68714,19 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>キング</t>
+          <t>キム＆むい</t>
         </is>
       </c>
       <c r="B378" t="n">
@@ -67982,19 +68734,19 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>クアレ</t>
+          <t>キング</t>
         </is>
       </c>
       <c r="B379" t="n">
@@ -68002,19 +68754,19 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>クロちゃん</t>
+          <t>クアレ</t>
         </is>
       </c>
       <c r="B380" t="n">
@@ -68022,19 +68774,19 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>ケケ</t>
+          <t>クロちゃん</t>
         </is>
       </c>
       <c r="B381" t="n">
@@ -68054,7 +68806,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>ゲン</t>
+          <t>ケケ</t>
         </is>
       </c>
       <c r="B382" t="n">
@@ -68074,7 +68826,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>コオリ</t>
+          <t>ゲン</t>
         </is>
       </c>
       <c r="B383" t="n">
@@ -68082,19 +68834,19 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>コマ</t>
+          <t>コオリ</t>
         </is>
       </c>
       <c r="B384" t="n">
@@ -68102,19 +68854,19 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>サクヤ</t>
+          <t>コマ</t>
         </is>
       </c>
       <c r="B385" t="n">
@@ -68122,19 +68874,19 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>サト</t>
+          <t>サクヤ</t>
         </is>
       </c>
       <c r="B386" t="n">
@@ -68142,19 +68894,19 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>サトル</t>
+          <t>サト</t>
         </is>
       </c>
       <c r="B387" t="n">
@@ -68162,19 +68914,19 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>ザッキー</t>
+          <t>サトル</t>
         </is>
       </c>
       <c r="B388" t="n">
@@ -68182,19 +68934,19 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>シゲ</t>
+          <t>ザッキー</t>
         </is>
       </c>
       <c r="B389" t="n">
@@ -68202,19 +68954,19 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>シュウ</t>
+          <t>シゲ</t>
         </is>
       </c>
       <c r="B390" t="n">
@@ -68222,19 +68974,19 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>シュン</t>
+          <t>シュウ</t>
         </is>
       </c>
       <c r="B391" t="n">
@@ -68242,19 +68994,19 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>シュンヤ</t>
+          <t>シュン</t>
         </is>
       </c>
       <c r="B392" t="n">
@@ -68262,19 +69014,19 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>シン</t>
+          <t>シュンヤ</t>
         </is>
       </c>
       <c r="B393" t="n">
@@ -68282,19 +69034,19 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>シン変質者</t>
+          <t>シン</t>
         </is>
       </c>
       <c r="B394" t="n">
@@ -68302,19 +69054,19 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>ジャッキー</t>
+          <t>シン変質者</t>
         </is>
       </c>
       <c r="B395" t="n">
@@ -68322,19 +69074,19 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>ジョーカー</t>
+          <t>ジャッキー</t>
         </is>
       </c>
       <c r="B396" t="n">
@@ -68342,19 +69094,19 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>スズ</t>
+          <t>ジョーカー</t>
         </is>
       </c>
       <c r="B397" t="n">
@@ -68362,19 +69114,19 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>タイガ</t>
+          <t>スズ</t>
         </is>
       </c>
       <c r="B398" t="n">
@@ -68394,7 +69146,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>タカス</t>
+          <t>タイガ</t>
         </is>
       </c>
       <c r="B399" t="n">
@@ -68402,19 +69154,19 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>タカ御一行</t>
+          <t>タカス</t>
         </is>
       </c>
       <c r="B400" t="n">
@@ -68422,19 +69174,19 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>ダイキ</t>
+          <t>タカ御一行</t>
         </is>
       </c>
       <c r="B401" t="n">
@@ -68442,19 +69194,19 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>ダイチ</t>
+          <t>ダイキ</t>
         </is>
       </c>
       <c r="B402" t="n">
@@ -68462,19 +69214,19 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>チェスカ</t>
+          <t>ダイチ</t>
         </is>
       </c>
       <c r="B403" t="n">
@@ -68482,19 +69234,19 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>ツシマ</t>
+          <t>チェスカ</t>
         </is>
       </c>
       <c r="B404" t="n">
@@ -68502,19 +69254,19 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>ツボ</t>
+          <t>ツシマ</t>
         </is>
       </c>
       <c r="B405" t="n">
@@ -68522,19 +69274,19 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>テクノとポチ</t>
+          <t>ツボ</t>
         </is>
       </c>
       <c r="B406" t="n">
@@ -68542,19 +69294,19 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>テクノ＆おおつか＆みこと＆もも</t>
+          <t>テクノとポチ</t>
         </is>
       </c>
       <c r="B407" t="n">
@@ -68562,19 +69314,19 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>テクノ＆てるくん＆イブオ</t>
+          <t>テクノ＆おおつか＆みこと＆もも</t>
         </is>
       </c>
       <c r="B408" t="n">
@@ -68582,19 +69334,19 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>トニー・トニー・チョッパー</t>
+          <t>テクノ＆てるくん＆イブオ</t>
         </is>
       </c>
       <c r="B409" t="n">
@@ -68602,19 +69354,19 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>トルネードシャーク</t>
+          <t>トニー・トニー・チョッパー</t>
         </is>
       </c>
       <c r="B410" t="n">
@@ -68622,19 +69374,19 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>ナカヤマヤ</t>
+          <t>トルネードシャーク</t>
         </is>
       </c>
       <c r="B411" t="n">
@@ -68642,19 +69394,19 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>ニコチン</t>
+          <t>ナカヤマヤ</t>
         </is>
       </c>
       <c r="B412" t="n">
@@ -68662,19 +69414,19 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>ニト</t>
+          <t>ニコチン</t>
         </is>
       </c>
       <c r="B413" t="n">
@@ -68682,19 +69434,19 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>ニャンまげ</t>
+          <t>ニト</t>
         </is>
       </c>
       <c r="B414" t="n">
@@ -68702,19 +69454,19 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>ハチ</t>
+          <t>ニャンまげ</t>
         </is>
       </c>
       <c r="B415" t="n">
@@ -68722,19 +69474,19 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>ヒロ</t>
+          <t>ハチ</t>
         </is>
       </c>
       <c r="B416" t="n">
@@ -68742,19 +69494,19 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>ヒロシ</t>
+          <t>ヒロ</t>
         </is>
       </c>
       <c r="B417" t="n">
@@ -68762,19 +69514,19 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>ビコー</t>
+          <t>ヒロシ</t>
         </is>
       </c>
       <c r="B418" t="n">
@@ -68782,19 +69534,19 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>フジ</t>
+          <t>ビコー</t>
         </is>
       </c>
       <c r="B419" t="n">
@@ -68802,19 +69554,19 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>ペロとペコ</t>
+          <t>フジ</t>
         </is>
       </c>
       <c r="B420" t="n">
@@ -68822,19 +69574,19 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>ボス</t>
+          <t>ペロとペコ</t>
         </is>
       </c>
       <c r="B421" t="n">
@@ -68842,19 +69594,19 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>ボンタ</t>
+          <t>ボス</t>
         </is>
       </c>
       <c r="B422" t="n">
@@ -68862,19 +69614,19 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>ポチ</t>
+          <t>ボンタ</t>
         </is>
       </c>
       <c r="B423" t="n">
@@ -68882,19 +69634,19 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>マッチョ</t>
+          <t>ポチ</t>
         </is>
       </c>
       <c r="B424" t="n">
@@ -68902,19 +69654,19 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>ミカミと仲間たち</t>
+          <t>マッチョ</t>
         </is>
       </c>
       <c r="B425" t="n">
@@ -68922,19 +69674,19 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>ミスター工事マン</t>
+          <t>ミカミと仲間たち</t>
         </is>
       </c>
       <c r="B426" t="n">
@@ -68942,19 +69694,19 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>ミッシ</t>
+          <t>ミスター工事マン</t>
         </is>
       </c>
       <c r="B427" t="n">
@@ -68962,19 +69714,19 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>ミッチー</t>
+          <t>ミッシ</t>
         </is>
       </c>
       <c r="B428" t="n">
@@ -68982,19 +69734,19 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>ミルコ</t>
+          <t>ミッチー</t>
         </is>
       </c>
       <c r="B429" t="n">
@@ -69014,7 +69766,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>ミン</t>
+          <t>ミルコ</t>
         </is>
       </c>
       <c r="B430" t="n">
@@ -69022,19 +69774,19 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>モジャ</t>
+          <t>ミン</t>
         </is>
       </c>
       <c r="B431" t="n">
@@ -69042,19 +69794,19 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>ヤノちゃん</t>
+          <t>モジャ</t>
         </is>
       </c>
       <c r="B432" t="n">
@@ -69062,19 +69814,19 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>ヤマ</t>
+          <t>ヤノちゃん</t>
         </is>
       </c>
       <c r="B433" t="n">
@@ -69082,19 +69834,19 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>ユウ</t>
+          <t>ヤマ</t>
         </is>
       </c>
       <c r="B434" t="n">
@@ -69102,19 +69854,19 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>ユキ</t>
+          <t>ユウ</t>
         </is>
       </c>
       <c r="B435" t="n">
@@ -69122,19 +69874,19 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>ユッキー</t>
+          <t>ユキ</t>
         </is>
       </c>
       <c r="B436" t="n">
@@ -69142,19 +69894,19 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>ヨシヤ</t>
+          <t>ユッキー</t>
         </is>
       </c>
       <c r="B437" t="n">
@@ -69162,19 +69914,19 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>ラオ</t>
+          <t>ヨシヤ</t>
         </is>
       </c>
       <c r="B438" t="n">
@@ -69182,19 +69934,19 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>リク</t>
+          <t>ラオ</t>
         </is>
       </c>
       <c r="B439" t="n">
@@ -69202,19 +69954,19 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>リョウ</t>
+          <t>リク</t>
         </is>
       </c>
       <c r="B440" t="n">
@@ -69222,19 +69974,19 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>レオ</t>
+          <t>リョウ</t>
         </is>
       </c>
       <c r="B441" t="n">
@@ -69242,19 +69994,19 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>ロタポジ</t>
+          <t>レオ</t>
         </is>
       </c>
       <c r="B442" t="n">
@@ -69262,19 +70014,19 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>ローズ</t>
+          <t>ロタポジ</t>
         </is>
       </c>
       <c r="B443" t="n">
@@ -69282,19 +70034,19 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>偽マイマイ</t>
+          <t>ローズ</t>
         </is>
       </c>
       <c r="B444" t="n">
@@ -69302,19 +70054,19 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>僕と私</t>
+          <t>偽マイマイ</t>
         </is>
       </c>
       <c r="B445" t="n">
@@ -69322,19 +70074,19 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>名無し</t>
+          <t>僕と私</t>
         </is>
       </c>
       <c r="B446" t="n">
@@ -69354,7 +70106,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>変態まっする</t>
+          <t>名無し</t>
         </is>
       </c>
       <c r="B447" t="n">
@@ -69362,19 +70114,19 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>変態マッソー</t>
+          <t>変態まっする</t>
         </is>
       </c>
       <c r="B448" t="n">
@@ -69382,19 +70134,19 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>天我迅</t>
+          <t>変態マッソー</t>
         </is>
       </c>
       <c r="B449" t="n">
@@ -69402,19 +70154,19 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>女子三人衆</t>
+          <t>天我迅</t>
         </is>
       </c>
       <c r="B450" t="n">
@@ -69422,19 +70174,19 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>彩 なまがき</t>
+          <t>女子三人衆</t>
         </is>
       </c>
       <c r="B451" t="n">
@@ -69442,19 +70194,19 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>正装しん</t>
+          <t>彩 なまがき</t>
         </is>
       </c>
       <c r="B452" t="n">
@@ -69462,19 +70214,19 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>海砂利水魚</t>
+          <t>正装しん</t>
         </is>
       </c>
       <c r="B453" t="n">
@@ -69482,19 +70234,19 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>田中</t>
+          <t>海砂利水魚</t>
         </is>
       </c>
       <c r="B454" t="n">
@@ -69502,19 +70254,19 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>番</t>
+          <t>田中</t>
         </is>
       </c>
       <c r="B455" t="n">
@@ -69522,19 +70274,19 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>碧咲</t>
+          <t>番</t>
         </is>
       </c>
       <c r="B456" t="n">
@@ -69542,19 +70294,19 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>絶</t>
+          <t>碧咲</t>
         </is>
       </c>
       <c r="B457" t="n">
@@ -69562,19 +70314,19 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>絶ちゃん</t>
+          <t>絶</t>
         </is>
       </c>
       <c r="B458" t="n">
@@ -69582,19 +70334,19 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>美優</t>
+          <t>絶ちゃん</t>
         </is>
       </c>
       <c r="B459" t="n">
@@ -69602,19 +70354,19 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>赤ちゃん</t>
+          <t>美優</t>
         </is>
       </c>
       <c r="B460" t="n">
@@ -69622,19 +70374,19 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>赤井ヱビス</t>
+          <t>赤ちゃん</t>
         </is>
       </c>
       <c r="B461" t="n">
@@ -69642,30 +70394,50 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
+          <t>赤井ヱビス</t>
+        </is>
+      </c>
+      <c r="B462" t="n">
+        <v>1</v>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
           <t>雅-miyabi-/とも</t>
         </is>
       </c>
-      <c r="B462" t="n">
-        <v>1</v>
-      </c>
-      <c r="C462" t="inlineStr">
+      <c r="B463" t="n">
+        <v>1</v>
+      </c>
+      <c r="C463" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="D462" t="inlineStr">
+      <c r="D463" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -69709,10 +70481,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="3">
@@ -69787,10 +70559,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="C8" t="n">
-        <v>149</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -69831,10 +70603,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C2" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3">
@@ -70052,10 +70824,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -70078,10 +70850,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C21" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="22">
@@ -70091,10 +70863,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C22" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23">
@@ -70104,10 +70876,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C23" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
     </row>
     <row r="24">
@@ -70130,10 +70902,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C25" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -70195,13 +70967,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="C3" t="n">
-        <v>434</v>
+        <v>444</v>
       </c>
       <c r="D3" t="n">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
   </sheetData>

--- a/bbs_log.xlsx
+++ b/bbs_log.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H780"/>
+  <dimension ref="A1:H787"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24625,7 +24625,6 @@
           <t>c</t>
         </is>
       </c>
-      <c r="E769" t="inlineStr"/>
       <c r="F769" t="inlineStr">
         <is>
           <t>今日も</t>
@@ -24636,7 +24635,6 @@
           <t>いきマス</t>
         </is>
       </c>
-      <c r="H769" t="inlineStr"/>
     </row>
     <row r="770">
       <c r="A770" t="n">
@@ -24657,7 +24655,6 @@
           <t>さとる</t>
         </is>
       </c>
-      <c r="E770" t="inlineStr"/>
       <c r="F770" t="inlineStr">
         <is>
           <t>肉買って</t>
@@ -24668,7 +24665,6 @@
           <t>きました！食べよう！</t>
         </is>
       </c>
-      <c r="H770" t="inlineStr"/>
     </row>
     <row r="771">
       <c r="A771" t="n">
@@ -24689,7 +24685,6 @@
           <t>M</t>
         </is>
       </c>
-      <c r="E771" t="inlineStr"/>
       <c r="F771" t="inlineStr">
         <is>
           <t>わたしも</t>
@@ -24700,7 +24695,6 @@
           <t>いく！</t>
         </is>
       </c>
-      <c r="H771" t="inlineStr"/>
     </row>
     <row r="772">
       <c r="A772" t="n">
@@ -24721,7 +24715,6 @@
           <t>彩</t>
         </is>
       </c>
-      <c r="E772" t="inlineStr"/>
       <c r="F772" t="inlineStr">
         <is>
           <t>食べに</t>
@@ -24732,7 +24725,6 @@
           <t>きました！</t>
         </is>
       </c>
-      <c r="H772" t="inlineStr"/>
     </row>
     <row r="773">
       <c r="A773" t="n">
@@ -24753,7 +24745,6 @@
           <t>ねむ</t>
         </is>
       </c>
-      <c r="E773" t="inlineStr"/>
       <c r="F773" t="inlineStr">
         <is>
           <t>お腹へった</t>
@@ -24764,7 +24755,6 @@
           <t>きた！</t>
         </is>
       </c>
-      <c r="H773" t="inlineStr"/>
     </row>
     <row r="774">
       <c r="A774" t="n">
@@ -24785,7 +24775,6 @@
           <t>べー</t>
         </is>
       </c>
-      <c r="E774" t="inlineStr"/>
       <c r="F774" t="inlineStr">
         <is>
           <t>昨日に引き続き</t>
@@ -24796,7 +24785,6 @@
           <t>きました！</t>
         </is>
       </c>
-      <c r="H774" t="inlineStr"/>
     </row>
     <row r="775">
       <c r="A775" t="n">
@@ -24817,7 +24805,6 @@
           <t>よしおたん</t>
         </is>
       </c>
-      <c r="E775" t="inlineStr"/>
       <c r="F775" t="inlineStr">
         <is>
           <t>代行まち</t>
@@ -24828,7 +24815,6 @@
           <t>きました！</t>
         </is>
       </c>
-      <c r="H775" t="inlineStr"/>
     </row>
     <row r="776">
       <c r="A776" t="n">
@@ -24849,7 +24835,6 @@
           <t>あいちゃん</t>
         </is>
       </c>
-      <c r="E776" t="inlineStr"/>
       <c r="F776" t="inlineStr">
         <is>
           <t>今</t>
@@ -24860,7 +24845,6 @@
           <t>きました！</t>
         </is>
       </c>
-      <c r="H776" t="inlineStr"/>
     </row>
     <row r="777">
       <c r="A777" t="n">
@@ -24881,7 +24865,6 @@
           <t>カネキヨ、くろちゃん、ぽち</t>
         </is>
       </c>
-      <c r="E777" t="inlineStr"/>
       <c r="F777" t="inlineStr">
         <is>
           <t>今</t>
@@ -24892,7 +24875,6 @@
           <t>久々に！！！</t>
         </is>
       </c>
-      <c r="H777" t="inlineStr"/>
     </row>
     <row r="778">
       <c r="A778" t="n">
@@ -24913,7 +24895,6 @@
           <t>わいちゃん</t>
         </is>
       </c>
-      <c r="E778" t="inlineStr"/>
       <c r="F778" t="inlineStr">
         <is>
           <t>飲んで</t>
@@ -24924,7 +24905,6 @@
           <t>きたんご</t>
         </is>
       </c>
-      <c r="H778" t="inlineStr"/>
     </row>
     <row r="779">
       <c r="A779" t="n">
@@ -24945,7 +24925,6 @@
           <t>ひがん</t>
         </is>
       </c>
-      <c r="E779" t="inlineStr"/>
       <c r="F779" t="inlineStr">
         <is>
           <t>しごおわ</t>
@@ -24956,7 +24935,6 @@
           <t>きちゃ</t>
         </is>
       </c>
-      <c r="H779" t="inlineStr"/>
     </row>
     <row r="780">
       <c r="A780" t="n">
@@ -25011,6 +24989,250 @@
         </is>
       </c>
     </row>
+    <row r="781">
+      <c r="A781" t="n">
+        <v>28307</v>
+      </c>
+      <c r="B781" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>19:36:53</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>彩</t>
+        </is>
+      </c>
+      <c r="E781" t="inlineStr"/>
+      <c r="F781" t="inlineStr">
+        <is>
+          <t>いま</t>
+        </is>
+      </c>
+      <c r="G781" t="inlineStr">
+        <is>
+          <t>来ました</t>
+        </is>
+      </c>
+      <c r="H781" t="inlineStr"/>
+    </row>
+    <row r="782">
+      <c r="A782" t="n">
+        <v>28309</v>
+      </c>
+      <c r="B782" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>20:24:35</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>らお</t>
+        </is>
+      </c>
+      <c r="E782" t="inlineStr"/>
+      <c r="F782" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G782" t="inlineStr">
+        <is>
+          <t>来ました</t>
+        </is>
+      </c>
+      <c r="H782" t="inlineStr"/>
+    </row>
+    <row r="783">
+      <c r="A783" t="n">
+        <v>28311</v>
+      </c>
+      <c r="B783" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>21:56:22</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>あい</t>
+        </is>
+      </c>
+      <c r="E783" t="inlineStr"/>
+      <c r="F783" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G783" t="inlineStr">
+        <is>
+          <t>来ました♪</t>
+        </is>
+      </c>
+      <c r="H783" t="inlineStr"/>
+    </row>
+    <row r="784">
+      <c r="A784" t="n">
+        <v>28313</v>
+      </c>
+      <c r="B784" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>23:05:59</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>福ちゃん</t>
+        </is>
+      </c>
+      <c r="E784" t="inlineStr"/>
+      <c r="F784" t="inlineStr">
+        <is>
+          <t>そろそろ</t>
+        </is>
+      </c>
+      <c r="G784" t="inlineStr">
+        <is>
+          <t>行きます！</t>
+        </is>
+      </c>
+      <c r="H784" t="inlineStr"/>
+    </row>
+    <row r="785">
+      <c r="A785" t="n">
+        <v>28316</v>
+      </c>
+      <c r="B785" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>00:30:48</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>ひがん</t>
+        </is>
+      </c>
+      <c r="E785" t="inlineStr"/>
+      <c r="F785" t="inlineStr">
+        <is>
+          <t>しごおわー</t>
+        </is>
+      </c>
+      <c r="G785" t="inlineStr">
+        <is>
+          <t>きたよー</t>
+        </is>
+      </c>
+      <c r="H785" t="inlineStr"/>
+    </row>
+    <row r="786">
+      <c r="A786" t="n">
+        <v>28318</v>
+      </c>
+      <c r="B786" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>01:55:48</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>にこちん</t>
+        </is>
+      </c>
+      <c r="E786" t="inlineStr"/>
+      <c r="F786" t="inlineStr">
+        <is>
+          <t>さっき</t>
+        </is>
+      </c>
+      <c r="G786" t="inlineStr">
+        <is>
+          <t>来たよ</t>
+        </is>
+      </c>
+      <c r="H786" t="inlineStr"/>
+    </row>
+    <row r="787">
+      <c r="A787" t="n">
+        <v>28320</v>
+      </c>
+      <c r="B787" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>04:54:05</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E787" t="inlineStr">
+        <is>
+          <t>天然の100人ネキねむ</t>
+        </is>
+      </c>
+      <c r="F787" t="inlineStr">
+        <is>
+          <t>★☆★朝までアゲアゲの金曜日営業が始まるわよ♪★☆★</t>
+        </is>
+      </c>
+      <c r="G787" t="inlineStr">
+        <is>
+          <t>本日10月1日の営業時間は♪
+オープン19:00！ラスト5:00なのよ☆
+担当は
+天然の100人ネキねむ
+なのよ♪
+どんな季節でも★BAMBITCH★は色気ムンムンで暑すぎる♪
+バンビッチでおもいっきりはじけちゃって（笑）
+精力は無くても性欲がある！？
+大人の憩いと禁断サークル盛りだくさん！
+憩いと交流の魔性の遊び場バンビッチは素敵な出会いを 提供いたします（笑)☆☆
+おつまみ等の持ち込みは自由なのでみんなで持ち寄ってお近づきのきっかけにどうぞ♪
+強制や無理強いは一切ございませんので楽しく遊びましょう♪
+宇都宮市宿郷1−12−9　カサブランカビル5F</t>
+        </is>
+      </c>
+      <c r="H787" t="inlineStr">
+        <is>
+          <t>img20261002045405.jpg</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25022,7 +25244,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I911"/>
+  <dimension ref="A1:I917"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64210,6 +64432,264 @@
       <c r="I911" t="inlineStr">
         <is>
           <t>きちゃ</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B912" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C912" t="inlineStr">
+        <is>
+          <t>19:36:53</t>
+        </is>
+      </c>
+      <c r="D912" t="n">
+        <v>28307</v>
+      </c>
+      <c r="E912" t="inlineStr">
+        <is>
+          <t>彩</t>
+        </is>
+      </c>
+      <c r="F912" t="n">
+        <v>15</v>
+      </c>
+      <c r="G912" t="inlineStr">
+        <is>
+          <t>彩</t>
+        </is>
+      </c>
+      <c r="H912" t="inlineStr">
+        <is>
+          <t>いま</t>
+        </is>
+      </c>
+      <c r="I912" t="inlineStr">
+        <is>
+          <t>来ました</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B913" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C913" t="inlineStr">
+        <is>
+          <t>20:24:35</t>
+        </is>
+      </c>
+      <c r="D913" t="n">
+        <v>28309</v>
+      </c>
+      <c r="E913" t="inlineStr">
+        <is>
+          <t>らお</t>
+        </is>
+      </c>
+      <c r="F913" t="n">
+        <v>2</v>
+      </c>
+      <c r="G913" t="inlineStr">
+        <is>
+          <t>らお</t>
+        </is>
+      </c>
+      <c r="H913" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="I913" t="inlineStr">
+        <is>
+          <t>来ました</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B914" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C914" t="inlineStr">
+        <is>
+          <t>21:56:22</t>
+        </is>
+      </c>
+      <c r="D914" t="n">
+        <v>28311</v>
+      </c>
+      <c r="E914" t="inlineStr">
+        <is>
+          <t>あい</t>
+        </is>
+      </c>
+      <c r="F914" t="n">
+        <v>1</v>
+      </c>
+      <c r="G914" t="inlineStr">
+        <is>
+          <t>あい</t>
+        </is>
+      </c>
+      <c r="H914" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="I914" t="inlineStr">
+        <is>
+          <t>来ました♪</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B915" t="inlineStr">
+        <is>
+          <t>木</t>
+        </is>
+      </c>
+      <c r="C915" t="inlineStr">
+        <is>
+          <t>23:05:59</t>
+        </is>
+      </c>
+      <c r="D915" t="n">
+        <v>28313</v>
+      </c>
+      <c r="E915" t="inlineStr">
+        <is>
+          <t>福ちゃん</t>
+        </is>
+      </c>
+      <c r="F915" t="n">
+        <v>1</v>
+      </c>
+      <c r="G915" t="inlineStr">
+        <is>
+          <t>福ちゃん</t>
+        </is>
+      </c>
+      <c r="H915" t="inlineStr">
+        <is>
+          <t>そろそろ</t>
+        </is>
+      </c>
+      <c r="I915" t="inlineStr">
+        <is>
+          <t>行きます！</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B916" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C916" t="inlineStr">
+        <is>
+          <t>00:30:48</t>
+        </is>
+      </c>
+      <c r="D916" t="n">
+        <v>28316</v>
+      </c>
+      <c r="E916" t="inlineStr">
+        <is>
+          <t>ひがん</t>
+        </is>
+      </c>
+      <c r="F916" t="n">
+        <v>29</v>
+      </c>
+      <c r="G916" t="inlineStr">
+        <is>
+          <t>ひがん</t>
+        </is>
+      </c>
+      <c r="H916" t="inlineStr">
+        <is>
+          <t>しごおわー</t>
+        </is>
+      </c>
+      <c r="I916" t="inlineStr">
+        <is>
+          <t>きたよー</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>金</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>01:55:48</t>
+        </is>
+      </c>
+      <c r="D917" t="n">
+        <v>28318</v>
+      </c>
+      <c r="E917" t="inlineStr">
+        <is>
+          <t>にこちん</t>
+        </is>
+      </c>
+      <c r="F917" t="n">
+        <v>2</v>
+      </c>
+      <c r="G917" t="inlineStr">
+        <is>
+          <t>にこちん</t>
+        </is>
+      </c>
+      <c r="H917" t="inlineStr">
+        <is>
+          <t>さっき</t>
+        </is>
+      </c>
+      <c r="I917" t="inlineStr">
+        <is>
+          <t>来たよ</t>
         </is>
       </c>
     </row>
@@ -64224,7 +64704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D480"/>
+  <dimension ref="A1:D482"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64256,7 +64736,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -64265,7 +64745,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
     </row>
@@ -64292,27 +64772,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>まいまい</t>
+          <t>彩</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ゆずき</t>
+          <t>まいまい</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -64320,19 +64800,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>彩</t>
+          <t>ゆずき</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -64340,12 +64820,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
@@ -66532,7 +67012,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ねむねむ</t>
+          <t>にこちん</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -66540,19 +67020,19 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-02</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ふく</t>
+          <t>ねむねむ</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -66560,19 +67040,19 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ぶりちゃん</t>
+          <t>ふく</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -66580,19 +67060,19 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>まい</t>
+          <t>ぶりちゃん</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -66605,14 +67085,14 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ましゅ会長</t>
+          <t>まい</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -66620,19 +67100,19 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>まりん</t>
+          <t>ましゅ会長</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -66640,19 +67120,19 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>まーさん</t>
+          <t>まりん</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -66660,19 +67140,19 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>みっちー</t>
+          <t>まーさん</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -66680,19 +67160,19 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>みれい</t>
+          <t>みっちー</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -66700,19 +67180,19 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>みー</t>
+          <t>みれい</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -66720,19 +67200,19 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>めい</t>
+          <t>みー</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -66740,19 +67220,19 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>やえ</t>
+          <t>めい</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -66760,19 +67240,19 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ゆうくん</t>
+          <t>やえ</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -66780,19 +67260,19 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ゆすき</t>
+          <t>ゆうくん</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -66800,19 +67280,19 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>よっしー</t>
+          <t>ゆすき</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -66820,19 +67300,19 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>よっち</t>
+          <t>よっしー</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -66840,19 +67320,19 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>りお</t>
+          <t>よっち</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -66860,19 +67340,19 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
           <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>アキ</t>
+          <t>らお</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -66880,19 +67360,19 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>オカニー</t>
+          <t>りお</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -66900,19 +67380,19 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>キムとドMまゆ</t>
+          <t>アキ</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -66920,19 +67400,19 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>クワレ</t>
+          <t>オカニー</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -66940,19 +67420,19 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>タカ</t>
+          <t>キムとドMまゆ</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -66960,19 +67440,19 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>タク</t>
+          <t>クワレ</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -66980,19 +67460,19 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>タケ</t>
+          <t>タカ</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -67000,19 +67480,19 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ダイゴ</t>
+          <t>タク</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -67020,19 +67500,19 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>マイナス</t>
+          <t>タケ</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -67040,19 +67520,19 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>マサ</t>
+          <t>ダイゴ</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -67060,19 +67540,19 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>マッスル</t>
+          <t>マイナス</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -67080,19 +67560,19 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>マナティ</t>
+          <t>マサ</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -67100,19 +67580,19 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>リン</t>
+          <t>マッスル</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -67120,19 +67600,19 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>変態マッスル</t>
+          <t>マナティ</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -67140,19 +67620,19 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>大塚</t>
+          <t>リン</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -67160,19 +67640,19 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>高田</t>
+          <t>変態マッスル</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -67180,59 +67660,59 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>5人衆</t>
+          <t>大塚</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>高田</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>EVANS×２</t>
+          <t>5人衆</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -67240,19 +67720,19 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>HGN</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -67260,19 +67740,19 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>JPTR</t>
+          <t>EVANS×２</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -67280,19 +67760,19 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>HGN</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -67300,19 +67780,19 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>KSK</t>
+          <t>JPTR</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -67320,19 +67800,19 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>KUMA</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -67340,19 +67820,19 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>KSK</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -67360,19 +67840,19 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>KUMA</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -67380,19 +67860,19 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>NMGK</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -67400,19 +67880,19 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>N氏御一行</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -67420,19 +67900,19 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>SIKUSENAチャンネルヒロキ</t>
+          <t>NMGK</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -67440,19 +67920,19 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>STR</t>
+          <t>N氏御一行</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -67460,19 +67940,19 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>TARU</t>
+          <t>SIKUSENAチャンネルヒロキ</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -67480,19 +67960,19 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>STR</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -67500,19 +67980,19 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Tやま</t>
+          <t>TARU</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -67520,19 +68000,19 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>TT</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -67540,19 +68020,19 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Tやま</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -67560,19 +68040,19 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>hikari</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -67580,19 +68060,19 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>nuri</t>
+          <t>c</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -67600,19 +68080,19 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>sho</t>
+          <t>hikari</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -67620,19 +68100,19 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>taka</t>
+          <t>nuri</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -67640,19 +68120,19 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>★Zakk★</t>
+          <t>sho</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -67660,19 +68140,19 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>あき</t>
+          <t>taka</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -67680,19 +68160,19 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>あさみ</t>
+          <t>★Zakk★</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -67700,19 +68180,19 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>あす</t>
+          <t>あい</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -67720,19 +68200,19 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>あにー</t>
+          <t>あき</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -67740,19 +68220,19 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>あまねちゃん</t>
+          <t>あさみ</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -67760,19 +68240,19 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>ありす</t>
+          <t>あす</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -67780,19 +68260,19 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>いおり</t>
+          <t>あにー</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -67800,19 +68280,19 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>いけちゃん</t>
+          <t>あまねちゃん</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -67820,19 +68300,19 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>いぶお</t>
+          <t>ありす</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -67840,19 +68320,19 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>うらら</t>
+          <t>いおり</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -67860,19 +68340,19 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>えいたろう</t>
+          <t>いけちゃん</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -67880,19 +68360,19 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>えび</t>
+          <t>いぶお</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -67900,19 +68380,19 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>えーたろ</t>
+          <t>うらら</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -67920,19 +68400,19 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>おじき</t>
+          <t>えいたろう</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -67940,19 +68420,19 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>おじきち</t>
+          <t>えび</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -67960,19 +68440,19 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>おすー</t>
+          <t>えーたろ</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -67980,19 +68460,19 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>おちんぽベルセルク</t>
+          <t>おじき</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -68000,19 +68480,19 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>おにゃん</t>
+          <t>おじきち</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -68020,19 +68500,19 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>おにゃんにゃん</t>
+          <t>おすー</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -68052,7 +68532,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>おばし</t>
+          <t>おちんぽベルセルク</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -68060,19 +68540,19 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>おもち</t>
+          <t>おにゃん</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -68080,19 +68560,19 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>かける</t>
+          <t>おにゃんにゃん</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -68100,19 +68580,19 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>かずき</t>
+          <t>おばし</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -68120,19 +68600,19 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>かず＆TKC＆のんのん</t>
+          <t>おもち</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -68140,19 +68620,19 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>かつ</t>
+          <t>かける</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -68160,19 +68640,19 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>かな(絶ちゃん</t>
+          <t>かずき</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -68180,19 +68660,19 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>かな(絶ちゃん)/おっつん</t>
+          <t>かず＆TKC＆のんのん</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -68200,19 +68680,19 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>がん</t>
+          <t>かつ</t>
         </is>
       </c>
       <c r="B200" t="n">
@@ -68220,19 +68700,19 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>きむさん</t>
+          <t>かな(絶ちゃん</t>
         </is>
       </c>
       <c r="B201" t="n">
@@ -68240,19 +68720,19 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>きむむ</t>
+          <t>かな(絶ちゃん)/おっつん</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -68260,19 +68740,19 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>きむら</t>
+          <t>がん</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -68280,19 +68760,19 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>きょうちゃん</t>
+          <t>きむさん</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -68300,19 +68780,19 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>きんたまよ</t>
+          <t>きむむ</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -68320,19 +68800,19 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>くっぱ</t>
+          <t>きむら</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -68340,19 +68820,19 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>くま</t>
+          <t>きょうちゃん</t>
         </is>
       </c>
       <c r="B207" t="n">
@@ -68360,19 +68840,19 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>くり</t>
+          <t>きんたまよ</t>
         </is>
       </c>
       <c r="B208" t="n">
@@ -68380,19 +68860,19 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>くろちゃん</t>
+          <t>くっぱ</t>
         </is>
       </c>
       <c r="B209" t="n">
@@ -68400,19 +68880,19 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>ぐっちゃん</t>
+          <t>くま</t>
         </is>
       </c>
       <c r="B210" t="n">
@@ -68420,19 +68900,19 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>ぐっちゃん（チャイマフィ）</t>
+          <t>くり</t>
         </is>
       </c>
       <c r="B211" t="n">
@@ -68440,19 +68920,19 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>けい</t>
+          <t>くろちゃん</t>
         </is>
       </c>
       <c r="B212" t="n">
@@ -68460,19 +68940,19 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>けいご</t>
+          <t>ぐっちゃん</t>
         </is>
       </c>
       <c r="B213" t="n">
@@ -68480,19 +68960,19 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>けいちゃん</t>
+          <t>ぐっちゃん（チャイマフィ）</t>
         </is>
       </c>
       <c r="B214" t="n">
@@ -68500,19 +68980,19 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>けんけん</t>
+          <t>けい</t>
         </is>
       </c>
       <c r="B215" t="n">
@@ -68520,19 +69000,19 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>げん</t>
+          <t>けいご</t>
         </is>
       </c>
       <c r="B216" t="n">
@@ -68540,19 +69020,19 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>げんき</t>
+          <t>けいちゃん</t>
         </is>
       </c>
       <c r="B217" t="n">
@@ -68560,19 +69040,19 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>こう</t>
+          <t>けんけん</t>
         </is>
       </c>
       <c r="B218" t="n">
@@ -68580,19 +69060,19 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>こうた</t>
+          <t>げん</t>
         </is>
       </c>
       <c r="B219" t="n">
@@ -68600,19 +69080,19 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>こてつ</t>
+          <t>げんき</t>
         </is>
       </c>
       <c r="B220" t="n">
@@ -68620,19 +69100,19 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>ことねえ</t>
+          <t>こう</t>
         </is>
       </c>
       <c r="B221" t="n">
@@ -68640,19 +69120,19 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>ことり</t>
+          <t>こうた</t>
         </is>
       </c>
       <c r="B222" t="n">
@@ -68660,19 +69140,19 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>ごん</t>
+          <t>こてつ</t>
         </is>
       </c>
       <c r="B223" t="n">
@@ -68680,19 +69160,19 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>さかもと</t>
+          <t>ことねえ</t>
         </is>
       </c>
       <c r="B224" t="n">
@@ -68700,19 +69180,19 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>さくら</t>
+          <t>ことり</t>
         </is>
       </c>
       <c r="B225" t="n">
@@ -68720,19 +69200,19 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>さとりゅ</t>
+          <t>ごん</t>
         </is>
       </c>
       <c r="B226" t="n">
@@ -68740,19 +69220,19 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>さな</t>
+          <t>さかもと</t>
         </is>
       </c>
       <c r="B227" t="n">
@@ -68760,19 +69240,19 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>さない</t>
+          <t>さくら</t>
         </is>
       </c>
       <c r="B228" t="n">
@@ -68780,19 +69260,19 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>さや</t>
+          <t>さとりゅ</t>
         </is>
       </c>
       <c r="B229" t="n">
@@ -68800,19 +69280,19 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>しずか</t>
+          <t>さな</t>
         </is>
       </c>
       <c r="B230" t="n">
@@ -68820,19 +69300,19 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>しょう</t>
+          <t>さない</t>
         </is>
       </c>
       <c r="B231" t="n">
@@ -68840,19 +69320,19 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>しょー</t>
+          <t>さや</t>
         </is>
       </c>
       <c r="B232" t="n">
@@ -68860,19 +69340,19 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>しりゅう</t>
+          <t>しずか</t>
         </is>
       </c>
       <c r="B233" t="n">
@@ -68880,19 +69360,19 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>じん</t>
+          <t>しょう</t>
         </is>
       </c>
       <c r="B234" t="n">
@@ -68900,19 +69380,19 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>せいら</t>
+          <t>しょー</t>
         </is>
       </c>
       <c r="B235" t="n">
@@ -68920,19 +69400,19 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>ぜっちゃん＆おっつん</t>
+          <t>しりゅう</t>
         </is>
       </c>
       <c r="B236" t="n">
@@ -68940,19 +69420,19 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>たいせー</t>
+          <t>じん</t>
         </is>
       </c>
       <c r="B237" t="n">
@@ -68960,19 +69440,19 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>たかし</t>
+          <t>せいら</t>
         </is>
       </c>
       <c r="B238" t="n">
@@ -68980,19 +69460,19 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>たかち</t>
+          <t>ぜっちゃん＆おっつん</t>
         </is>
       </c>
       <c r="B239" t="n">
@@ -69000,19 +69480,19 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>たく</t>
+          <t>たいせー</t>
         </is>
       </c>
       <c r="B240" t="n">
@@ -69020,19 +69500,19 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>たけし</t>
+          <t>たかし</t>
         </is>
       </c>
       <c r="B241" t="n">
@@ -69040,19 +69520,19 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>たつお</t>
+          <t>たかち</t>
         </is>
       </c>
       <c r="B242" t="n">
@@ -69060,19 +69540,19 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>たます</t>
+          <t>たく</t>
         </is>
       </c>
       <c r="B243" t="n">
@@ -69080,19 +69560,19 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>たろー</t>
+          <t>たけし</t>
         </is>
       </c>
       <c r="B244" t="n">
@@ -69100,19 +69580,19 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>たー</t>
+          <t>たつお</t>
         </is>
       </c>
       <c r="B245" t="n">
@@ -69120,19 +69600,19 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>だいさく</t>
+          <t>たます</t>
         </is>
       </c>
       <c r="B246" t="n">
@@ -69140,19 +69620,19 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>だいざく</t>
+          <t>たろー</t>
         </is>
       </c>
       <c r="B247" t="n">
@@ -69160,19 +69640,19 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>だいち</t>
+          <t>たー</t>
         </is>
       </c>
       <c r="B248" t="n">
@@ -69180,19 +69660,19 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>ちぇちぇ＆ガールズ</t>
+          <t>だいさく</t>
         </is>
       </c>
       <c r="B249" t="n">
@@ -69200,19 +69680,19 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>ちっちてゃ</t>
+          <t>だいざく</t>
         </is>
       </c>
       <c r="B250" t="n">
@@ -69220,19 +69700,19 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>ちほ</t>
+          <t>だいち</t>
         </is>
       </c>
       <c r="B251" t="n">
@@ -69240,19 +69720,19 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>つかさ</t>
+          <t>ちぇちぇ＆ガールズ</t>
         </is>
       </c>
       <c r="B252" t="n">
@@ -69260,19 +69740,19 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>てくのちん</t>
+          <t>ちっちてゃ</t>
         </is>
       </c>
       <c r="B253" t="n">
@@ -69280,19 +69760,19 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>てくのっち</t>
+          <t>ちほ</t>
         </is>
       </c>
       <c r="B254" t="n">
@@ -69300,19 +69780,19 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>てっちゃん</t>
+          <t>つかさ</t>
         </is>
       </c>
       <c r="B255" t="n">
@@ -69320,19 +69800,19 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>てつ</t>
+          <t>てくのちん</t>
         </is>
       </c>
       <c r="B256" t="n">
@@ -69340,19 +69820,19 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>てる</t>
+          <t>てくのっち</t>
         </is>
       </c>
       <c r="B257" t="n">
@@ -69360,19 +69840,19 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>でかかわ</t>
+          <t>てっちゃん</t>
         </is>
       </c>
       <c r="B258" t="n">
@@ -69380,19 +69860,19 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>ででたゃ</t>
+          <t>てつ</t>
         </is>
       </c>
       <c r="B259" t="n">
@@ -69400,19 +69880,19 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>とおちゃん</t>
+          <t>てる</t>
         </is>
       </c>
       <c r="B260" t="n">
@@ -69420,19 +69900,19 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>とっしー</t>
+          <t>でかかわ</t>
         </is>
       </c>
       <c r="B261" t="n">
@@ -69440,19 +69920,19 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>とも</t>
+          <t>ででたゃ</t>
         </is>
       </c>
       <c r="B262" t="n">
@@ -69460,19 +69940,19 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>ともち</t>
+          <t>とおちゃん</t>
         </is>
       </c>
       <c r="B263" t="n">
@@ -69480,19 +69960,19 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>ともひろ</t>
+          <t>とっしー</t>
         </is>
       </c>
       <c r="B264" t="n">
@@ -69500,19 +69980,19 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>ともや</t>
+          <t>とも</t>
         </is>
       </c>
       <c r="B265" t="n">
@@ -69520,19 +70000,19 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>ともゆき</t>
+          <t>ともち</t>
         </is>
       </c>
       <c r="B266" t="n">
@@ -69540,19 +70020,19 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>とーり</t>
+          <t>ともひろ</t>
         </is>
       </c>
       <c r="B267" t="n">
@@ -69560,19 +70040,19 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>どえむちゃん</t>
+          <t>ともや</t>
         </is>
       </c>
       <c r="B268" t="n">
@@ -69580,19 +70060,19 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>ながとも</t>
+          <t>ともゆき</t>
         </is>
       </c>
       <c r="B269" t="n">
@@ -69600,19 +70080,19 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>なべ</t>
+          <t>とーり</t>
         </is>
       </c>
       <c r="B270" t="n">
@@ -69620,19 +70100,19 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>にこちん</t>
+          <t>どえむちゃん</t>
         </is>
       </c>
       <c r="B271" t="n">
@@ -69640,19 +70120,19 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>にゃんまげ</t>
+          <t>ながとも</t>
         </is>
       </c>
       <c r="B272" t="n">
@@ -69660,19 +70140,19 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>にょ</t>
+          <t>なべ</t>
         </is>
       </c>
       <c r="B273" t="n">
@@ -69680,19 +70160,19 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>ねここ</t>
+          <t>にゃんまげ</t>
         </is>
       </c>
       <c r="B274" t="n">
@@ -69700,19 +70180,19 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>ねむ</t>
+          <t>にょ</t>
         </is>
       </c>
       <c r="B275" t="n">
@@ -69720,19 +70200,19 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>のぼ</t>
+          <t>ねここ</t>
         </is>
       </c>
       <c r="B276" t="n">
@@ -69740,19 +70220,19 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>のり</t>
+          <t>ねむ</t>
         </is>
       </c>
       <c r="B277" t="n">
@@ -69760,19 +70240,19 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>はち</t>
+          <t>のぼ</t>
         </is>
       </c>
       <c r="B278" t="n">
@@ -69780,19 +70260,19 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>はな</t>
+          <t>のり</t>
         </is>
       </c>
       <c r="B279" t="n">
@@ -69800,19 +70280,19 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>はなちゃん</t>
+          <t>はち</t>
         </is>
       </c>
       <c r="B280" t="n">
@@ -69820,19 +70300,19 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>はなまる</t>
+          <t>はな</t>
         </is>
       </c>
       <c r="B281" t="n">
@@ -69840,19 +70320,19 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>はにーちゃん</t>
+          <t>はなちゃん</t>
         </is>
       </c>
       <c r="B282" t="n">
@@ -69860,19 +70340,19 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>はんまー</t>
+          <t>はなまる</t>
         </is>
       </c>
       <c r="B283" t="n">
@@ -69880,19 +70360,19 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>ひったん</t>
+          <t>はにーちゃん</t>
         </is>
       </c>
       <c r="B284" t="n">
@@ -69900,19 +70380,19 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>ひろし</t>
+          <t>はんまー</t>
         </is>
       </c>
       <c r="B285" t="n">
@@ -69920,19 +70400,19 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>ひろとも</t>
+          <t>ひったん</t>
         </is>
       </c>
       <c r="B286" t="n">
@@ -69940,19 +70420,19 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>びん</t>
+          <t>ひろし</t>
         </is>
       </c>
       <c r="B287" t="n">
@@ -69960,19 +70440,19 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>ぴよ</t>
+          <t>ひろとも</t>
         </is>
       </c>
       <c r="B288" t="n">
@@ -69980,19 +70460,19 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>ふみ</t>
+          <t>びん</t>
         </is>
       </c>
       <c r="B289" t="n">
@@ -70000,19 +70480,19 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>ぷらぐいん</t>
+          <t>ぴよ</t>
         </is>
       </c>
       <c r="B290" t="n">
@@ -70020,19 +70500,19 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>ぺぺ</t>
+          <t>ふみ</t>
         </is>
       </c>
       <c r="B291" t="n">
@@ -70040,19 +70520,19 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>ぽち</t>
+          <t>ぷらぐいん</t>
         </is>
       </c>
       <c r="B292" t="n">
@@ -70060,19 +70540,19 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>ぽて</t>
+          <t>ぺぺ</t>
         </is>
       </c>
       <c r="B293" t="n">
@@ -70080,19 +70560,19 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>まいまいまいまい</t>
+          <t>ぽち</t>
         </is>
       </c>
       <c r="B294" t="n">
@@ -70100,19 +70580,19 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>まいまいん</t>
+          <t>ぽて</t>
         </is>
       </c>
       <c r="B295" t="n">
@@ -70120,19 +70600,19 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>まおし</t>
+          <t>まいまいまいまい</t>
         </is>
       </c>
       <c r="B296" t="n">
@@ -70140,19 +70620,19 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>ます</t>
+          <t>まいまいん</t>
         </is>
       </c>
       <c r="B297" t="n">
@@ -70160,19 +70640,19 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>ますみ</t>
+          <t>まおし</t>
         </is>
       </c>
       <c r="B298" t="n">
@@ -70180,19 +70660,19 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>まっする</t>
+          <t>ます</t>
         </is>
       </c>
       <c r="B299" t="n">
@@ -70200,19 +70680,19 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>まっぴー</t>
+          <t>ますみ</t>
         </is>
       </c>
       <c r="B300" t="n">
@@ -70220,19 +70700,19 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>まな</t>
+          <t>まっする</t>
         </is>
       </c>
       <c r="B301" t="n">
@@ -70240,19 +70720,19 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>まみ</t>
+          <t>まっぴー</t>
         </is>
       </c>
       <c r="B302" t="n">
@@ -70260,19 +70740,19 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>まや</t>
+          <t>まな</t>
         </is>
       </c>
       <c r="B303" t="n">
@@ -70280,19 +70760,19 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>まり</t>
+          <t>まみ</t>
         </is>
       </c>
       <c r="B304" t="n">
@@ -70300,19 +70780,19 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>まりーな</t>
+          <t>まや</t>
         </is>
       </c>
       <c r="B305" t="n">
@@ -70320,19 +70800,19 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>まー</t>
+          <t>まり</t>
         </is>
       </c>
       <c r="B306" t="n">
@@ -70340,19 +70820,19 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>まーちゃん</t>
+          <t>まりーな</t>
         </is>
       </c>
       <c r="B307" t="n">
@@ -70360,19 +70840,19 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>みい</t>
+          <t>まー</t>
         </is>
       </c>
       <c r="B308" t="n">
@@ -70380,19 +70860,19 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>みかん</t>
+          <t>まーちゃん</t>
         </is>
       </c>
       <c r="B309" t="n">
@@ -70400,19 +70880,19 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>みけけ</t>
+          <t>みい</t>
         </is>
       </c>
       <c r="B310" t="n">
@@ -70420,19 +70900,19 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>みずき</t>
+          <t>みかん</t>
         </is>
       </c>
       <c r="B311" t="n">
@@ -70452,7 +70932,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>みちゃ</t>
+          <t>みけけ</t>
         </is>
       </c>
       <c r="B312" t="n">
@@ -70460,19 +70940,19 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>みなつちん</t>
+          <t>みずき</t>
         </is>
       </c>
       <c r="B313" t="n">
@@ -70492,7 +70972,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>みみ</t>
+          <t>みちゃ</t>
         </is>
       </c>
       <c r="B314" t="n">
@@ -70500,19 +70980,19 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>みやび</t>
+          <t>みなつちん</t>
         </is>
       </c>
       <c r="B315" t="n">
@@ -70520,19 +71000,19 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>みゆき</t>
+          <t>みみ</t>
         </is>
       </c>
       <c r="B316" t="n">
@@ -70540,19 +71020,19 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>みらい</t>
+          <t>みやび</t>
         </is>
       </c>
       <c r="B317" t="n">
@@ -70560,19 +71040,19 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>みるこ</t>
+          <t>みゆき</t>
         </is>
       </c>
       <c r="B318" t="n">
@@ -70580,19 +71060,19 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>みん</t>
+          <t>みらい</t>
         </is>
       </c>
       <c r="B319" t="n">
@@ -70600,19 +71080,19 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>みんみん</t>
+          <t>みるこ</t>
         </is>
       </c>
       <c r="B320" t="n">
@@ -70620,19 +71100,19 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>みーみ</t>
+          <t>みん</t>
         </is>
       </c>
       <c r="B321" t="n">
@@ -70640,19 +71120,19 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>もかちんぽぽ</t>
+          <t>みんみん</t>
         </is>
       </c>
       <c r="B322" t="n">
@@ -70660,19 +71140,19 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>もっち</t>
+          <t>みーみ</t>
         </is>
       </c>
       <c r="B323" t="n">
@@ -70680,19 +71160,19 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>もっぴっぴ</t>
+          <t>もかちんぽぽ</t>
         </is>
       </c>
       <c r="B324" t="n">
@@ -70700,19 +71180,19 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>もっぴー</t>
+          <t>もっち</t>
         </is>
       </c>
       <c r="B325" t="n">
@@ -70720,19 +71200,19 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>もと</t>
+          <t>もっぴっぴ</t>
         </is>
       </c>
       <c r="B326" t="n">
@@ -70740,19 +71220,19 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>ももたろ</t>
+          <t>もっぴー</t>
         </is>
       </c>
       <c r="B327" t="n">
@@ -70760,19 +71240,19 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>やす</t>
+          <t>もと</t>
         </is>
       </c>
       <c r="B328" t="n">
@@ -70780,19 +71260,19 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>ゆい</t>
+          <t>ももたろ</t>
         </is>
       </c>
       <c r="B329" t="n">
@@ -70800,19 +71280,19 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>ゆうじ</t>
+          <t>やす</t>
         </is>
       </c>
       <c r="B330" t="n">
@@ -70820,19 +71300,19 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>ゆうた</t>
+          <t>ゆい</t>
         </is>
       </c>
       <c r="B331" t="n">
@@ -70840,19 +71320,19 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>ゆうたん</t>
+          <t>ゆうじ</t>
         </is>
       </c>
       <c r="B332" t="n">
@@ -70860,19 +71340,19 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>ゆうと</t>
+          <t>ゆうた</t>
         </is>
       </c>
       <c r="B333" t="n">
@@ -70880,19 +71360,19 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>ゆうや</t>
+          <t>ゆうたん</t>
         </is>
       </c>
       <c r="B334" t="n">
@@ -70900,19 +71380,19 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>ゆかり</t>
+          <t>ゆうと</t>
         </is>
       </c>
       <c r="B335" t="n">
@@ -70920,19 +71400,19 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>ゆきお</t>
+          <t>ゆうや</t>
         </is>
       </c>
       <c r="B336" t="n">
@@ -70940,19 +71420,19 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>ゆきんこ</t>
+          <t>ゆかり</t>
         </is>
       </c>
       <c r="B337" t="n">
@@ -70960,19 +71440,19 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>ゆず</t>
+          <t>ゆきお</t>
         </is>
       </c>
       <c r="B338" t="n">
@@ -70980,19 +71460,19 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>ゆずきちくん</t>
+          <t>ゆきんこ</t>
         </is>
       </c>
       <c r="B339" t="n">
@@ -71000,19 +71480,19 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>ゆずきちゃん</t>
+          <t>ゆず</t>
         </is>
       </c>
       <c r="B340" t="n">
@@ -71020,19 +71500,19 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>ゆずきぴ</t>
+          <t>ゆずきちくん</t>
         </is>
       </c>
       <c r="B341" t="n">
@@ -71040,19 +71520,19 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>ゆずき＆ましゅ</t>
+          <t>ゆずきちゃん</t>
         </is>
       </c>
       <c r="B342" t="n">
@@ -71060,19 +71540,19 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>ゆっち</t>
+          <t>ゆずきぴ</t>
         </is>
       </c>
       <c r="B343" t="n">
@@ -71080,19 +71560,19 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>ゆぴ</t>
+          <t>ゆずき＆ましゅ</t>
         </is>
       </c>
       <c r="B344" t="n">
@@ -71100,19 +71580,19 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>ゆり</t>
+          <t>ゆっち</t>
         </is>
       </c>
       <c r="B345" t="n">
@@ -71120,19 +71600,19 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>ゆりな</t>
+          <t>ゆぴ</t>
         </is>
       </c>
       <c r="B346" t="n">
@@ -71140,19 +71620,19 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>ゆん</t>
+          <t>ゆり</t>
         </is>
       </c>
       <c r="B347" t="n">
@@ -71160,19 +71640,19 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>ゆんゆん</t>
+          <t>ゆりな</t>
         </is>
       </c>
       <c r="B348" t="n">
@@ -71180,19 +71660,19 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>よこい</t>
+          <t>ゆん</t>
         </is>
       </c>
       <c r="B349" t="n">
@@ -71200,19 +71680,19 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>よちお</t>
+          <t>ゆんゆん</t>
         </is>
       </c>
       <c r="B350" t="n">
@@ -71220,19 +71700,19 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>らいと</t>
+          <t>よこい</t>
         </is>
       </c>
       <c r="B351" t="n">
@@ -71240,19 +71720,19 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>らうら</t>
+          <t>よちお</t>
         </is>
       </c>
       <c r="B352" t="n">
@@ -71260,19 +71740,19 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>らお</t>
+          <t>らいと</t>
         </is>
       </c>
       <c r="B353" t="n">
@@ -71280,19 +71760,19 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>りえ</t>
+          <t>らうら</t>
         </is>
       </c>
       <c r="B354" t="n">
@@ -71300,19 +71780,19 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>りく</t>
+          <t>りえ</t>
         </is>
       </c>
       <c r="B355" t="n">
@@ -71320,19 +71800,19 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>りさ</t>
+          <t>りく</t>
         </is>
       </c>
       <c r="B356" t="n">
@@ -71340,19 +71820,19 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>りゅうくん</t>
+          <t>りさ</t>
         </is>
       </c>
       <c r="B357" t="n">
@@ -71360,19 +71840,19 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>りゅーちゃん</t>
+          <t>りゅうくん</t>
         </is>
       </c>
       <c r="B358" t="n">
@@ -71380,19 +71860,19 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>りょうが</t>
+          <t>りゅーちゃん</t>
         </is>
       </c>
       <c r="B359" t="n">
@@ -71412,7 +71892,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>りょうちゃん</t>
+          <t>りょうが</t>
         </is>
       </c>
       <c r="B360" t="n">
@@ -71420,19 +71900,19 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>りょーが</t>
+          <t>りょうちゃん</t>
         </is>
       </c>
       <c r="B361" t="n">
@@ -71440,19 +71920,19 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>りりこ</t>
+          <t>りょーが</t>
         </is>
       </c>
       <c r="B362" t="n">
@@ -71460,19 +71940,19 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>りん＆ゆち</t>
+          <t>りりこ</t>
         </is>
       </c>
       <c r="B363" t="n">
@@ -71480,19 +71960,19 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>れい</t>
+          <t>りん＆ゆち</t>
         </is>
       </c>
       <c r="B364" t="n">
@@ -71500,19 +71980,19 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>れー</t>
+          <t>れい</t>
         </is>
       </c>
       <c r="B365" t="n">
@@ -71520,19 +72000,19 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>わいちゃん</t>
+          <t>れー</t>
         </is>
       </c>
       <c r="B366" t="n">
@@ -71540,19 +72020,19 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>わんころ</t>
+          <t>わいちゃん</t>
         </is>
       </c>
       <c r="B367" t="n">
@@ -71560,19 +72040,19 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>アイ</t>
+          <t>わんころ</t>
         </is>
       </c>
       <c r="B368" t="n">
@@ -71580,19 +72060,19 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>アイちゃん</t>
+          <t>アイ</t>
         </is>
       </c>
       <c r="B369" t="n">
@@ -71600,19 +72080,19 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>アナルプリンス</t>
+          <t>アイちゃん</t>
         </is>
       </c>
       <c r="B370" t="n">
@@ -71620,19 +72100,19 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>イエモン</t>
+          <t>アナルプリンス</t>
         </is>
       </c>
       <c r="B371" t="n">
@@ -71640,19 +72120,19 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>イブオ</t>
+          <t>イエモン</t>
         </is>
       </c>
       <c r="B372" t="n">
@@ -71660,19 +72140,19 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>エーイチ</t>
+          <t>イブオ</t>
         </is>
       </c>
       <c r="B373" t="n">
@@ -71680,19 +72160,19 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>オリーブ</t>
+          <t>エーイチ</t>
         </is>
       </c>
       <c r="B374" t="n">
@@ -71700,19 +72180,19 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>オ・スー</t>
+          <t>オリーブ</t>
         </is>
       </c>
       <c r="B375" t="n">
@@ -71720,19 +72200,19 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>カイト</t>
+          <t>オ・スー</t>
         </is>
       </c>
       <c r="B376" t="n">
@@ -71740,19 +72220,19 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>カイトウ・キッド</t>
+          <t>カイト</t>
         </is>
       </c>
       <c r="B377" t="n">
@@ -71760,19 +72240,19 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>カネキヨ</t>
+          <t>カイトウ・キッド</t>
         </is>
       </c>
       <c r="B378" t="n">
@@ -71780,19 +72260,19 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>カミさん</t>
+          <t>カネキヨ</t>
         </is>
       </c>
       <c r="B379" t="n">
@@ -71800,19 +72280,19 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>カモリ</t>
+          <t>カミさん</t>
         </is>
       </c>
       <c r="B380" t="n">
@@ -71820,19 +72300,19 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>キムさん</t>
+          <t>カモリ</t>
         </is>
       </c>
       <c r="B381" t="n">
@@ -71840,19 +72320,19 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>キムとどえむちゃん</t>
+          <t>キムさん</t>
         </is>
       </c>
       <c r="B382" t="n">
@@ -71860,19 +72340,19 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>キムとまゆ</t>
+          <t>キムとどえむちゃん</t>
         </is>
       </c>
       <c r="B383" t="n">
@@ -71880,19 +72360,19 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>キムとドMまいまい妹</t>
+          <t>キムとまゆ</t>
         </is>
       </c>
       <c r="B384" t="n">
@@ -71900,19 +72380,19 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>キムとドMむい</t>
+          <t>キムとドMまいまい妹</t>
         </is>
       </c>
       <c r="B385" t="n">
@@ -71920,19 +72400,19 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>キムとドM女R</t>
+          <t>キムとドMむい</t>
         </is>
       </c>
       <c r="B386" t="n">
@@ -71940,19 +72420,19 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>キムと奴隷</t>
+          <t>キムとドM女R</t>
         </is>
       </c>
       <c r="B387" t="n">
@@ -71960,19 +72440,19 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>キムと新しい奴隷ちゃん</t>
+          <t>キムと奴隷</t>
         </is>
       </c>
       <c r="B388" t="n">
@@ -71980,19 +72460,19 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>キムラ</t>
+          <t>キムと新しい奴隷ちゃん</t>
         </is>
       </c>
       <c r="B389" t="n">
@@ -72000,19 +72480,19 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>キム＆みい</t>
+          <t>キムラ</t>
         </is>
       </c>
       <c r="B390" t="n">
@@ -72020,19 +72500,19 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>キム＆みー</t>
+          <t>キム＆みい</t>
         </is>
       </c>
       <c r="B391" t="n">
@@ -72040,19 +72520,19 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>キム＆むい</t>
+          <t>キム＆みー</t>
         </is>
       </c>
       <c r="B392" t="n">
@@ -72060,19 +72540,19 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>キング</t>
+          <t>キム＆むい</t>
         </is>
       </c>
       <c r="B393" t="n">
@@ -72080,19 +72560,19 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>クアレ</t>
+          <t>キング</t>
         </is>
       </c>
       <c r="B394" t="n">
@@ -72100,19 +72580,19 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>クロちゃん</t>
+          <t>クアレ</t>
         </is>
       </c>
       <c r="B395" t="n">
@@ -72120,19 +72600,19 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>ケケ</t>
+          <t>クロちゃん</t>
         </is>
       </c>
       <c r="B396" t="n">
@@ -72152,7 +72632,7 @@
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>ゲン</t>
+          <t>ケケ</t>
         </is>
       </c>
       <c r="B397" t="n">
@@ -72172,7 +72652,7 @@
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>コオリ</t>
+          <t>ゲン</t>
         </is>
       </c>
       <c r="B398" t="n">
@@ -72180,19 +72660,19 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>コマ</t>
+          <t>コオリ</t>
         </is>
       </c>
       <c r="B399" t="n">
@@ -72200,19 +72680,19 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>サクヤ</t>
+          <t>コマ</t>
         </is>
       </c>
       <c r="B400" t="n">
@@ -72220,19 +72700,19 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>サト</t>
+          <t>サクヤ</t>
         </is>
       </c>
       <c r="B401" t="n">
@@ -72240,19 +72720,19 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>サトル</t>
+          <t>サト</t>
         </is>
       </c>
       <c r="B402" t="n">
@@ -72260,19 +72740,19 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>ザッキー</t>
+          <t>サトル</t>
         </is>
       </c>
       <c r="B403" t="n">
@@ -72280,19 +72760,19 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>シゲ</t>
+          <t>ザッキー</t>
         </is>
       </c>
       <c r="B404" t="n">
@@ -72300,19 +72780,19 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>シュウ</t>
+          <t>シゲ</t>
         </is>
       </c>
       <c r="B405" t="n">
@@ -72320,19 +72800,19 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>シュン</t>
+          <t>シュウ</t>
         </is>
       </c>
       <c r="B406" t="n">
@@ -72340,19 +72820,19 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>シュンヤ</t>
+          <t>シュン</t>
         </is>
       </c>
       <c r="B407" t="n">
@@ -72360,19 +72840,19 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>シン</t>
+          <t>シュンヤ</t>
         </is>
       </c>
       <c r="B408" t="n">
@@ -72380,19 +72860,19 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>シン変質者</t>
+          <t>シン</t>
         </is>
       </c>
       <c r="B409" t="n">
@@ -72400,19 +72880,19 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>ジャッキー</t>
+          <t>シン変質者</t>
         </is>
       </c>
       <c r="B410" t="n">
@@ -72420,19 +72900,19 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>ジョーカー</t>
+          <t>ジャッキー</t>
         </is>
       </c>
       <c r="B411" t="n">
@@ -72440,19 +72920,19 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>スズ</t>
+          <t>ジョーカー</t>
         </is>
       </c>
       <c r="B412" t="n">
@@ -72460,19 +72940,19 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>ソルト</t>
+          <t>スズ</t>
         </is>
       </c>
       <c r="B413" t="n">
@@ -72480,19 +72960,19 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>タイガ</t>
+          <t>ソルト</t>
         </is>
       </c>
       <c r="B414" t="n">
@@ -72500,19 +72980,19 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>タカス</t>
+          <t>タイガ</t>
         </is>
       </c>
       <c r="B415" t="n">
@@ -72520,19 +73000,19 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>タカ御一行</t>
+          <t>タカス</t>
         </is>
       </c>
       <c r="B416" t="n">
@@ -72540,19 +73020,19 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>ダイキ</t>
+          <t>タカ御一行</t>
         </is>
       </c>
       <c r="B417" t="n">
@@ -72560,19 +73040,19 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>ダイチ</t>
+          <t>ダイキ</t>
         </is>
       </c>
       <c r="B418" t="n">
@@ -72580,19 +73060,19 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>チェスカ</t>
+          <t>ダイチ</t>
         </is>
       </c>
       <c r="B419" t="n">
@@ -72600,19 +73080,19 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>ツシマ</t>
+          <t>チェスカ</t>
         </is>
       </c>
       <c r="B420" t="n">
@@ -72620,19 +73100,19 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>ツボ</t>
+          <t>ツシマ</t>
         </is>
       </c>
       <c r="B421" t="n">
@@ -72640,19 +73120,19 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>テクノとポチ</t>
+          <t>ツボ</t>
         </is>
       </c>
       <c r="B422" t="n">
@@ -72660,19 +73140,19 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>テクノ＆おおつか＆みこと＆もも</t>
+          <t>テクノとポチ</t>
         </is>
       </c>
       <c r="B423" t="n">
@@ -72680,19 +73160,19 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>テクノ＆てるくん＆イブオ</t>
+          <t>テクノ＆おおつか＆みこと＆もも</t>
         </is>
       </c>
       <c r="B424" t="n">
@@ -72700,19 +73180,19 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>トニー・トニー・チョッパー</t>
+          <t>テクノ＆てるくん＆イブオ</t>
         </is>
       </c>
       <c r="B425" t="n">
@@ -72720,19 +73200,19 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>トム</t>
+          <t>トニー・トニー・チョッパー</t>
         </is>
       </c>
       <c r="B426" t="n">
@@ -72740,19 +73220,19 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>トルネードシャーク</t>
+          <t>トム</t>
         </is>
       </c>
       <c r="B427" t="n">
@@ -72760,19 +73240,19 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>ナカヤマヤ</t>
+          <t>トルネードシャーク</t>
         </is>
       </c>
       <c r="B428" t="n">
@@ -72780,19 +73260,19 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>ニコチン</t>
+          <t>ナカヤマヤ</t>
         </is>
       </c>
       <c r="B429" t="n">
@@ -72800,19 +73280,19 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>ニト</t>
+          <t>ニコチン</t>
         </is>
       </c>
       <c r="B430" t="n">
@@ -72820,19 +73300,19 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>ニャンまげ</t>
+          <t>ニト</t>
         </is>
       </c>
       <c r="B431" t="n">
@@ -72840,19 +73320,19 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>ハチ</t>
+          <t>ニャンまげ</t>
         </is>
       </c>
       <c r="B432" t="n">
@@ -72860,19 +73340,19 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>ヒロ</t>
+          <t>ハチ</t>
         </is>
       </c>
       <c r="B433" t="n">
@@ -72880,19 +73360,19 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>ヒロシ</t>
+          <t>ヒロ</t>
         </is>
       </c>
       <c r="B434" t="n">
@@ -72900,19 +73380,19 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>ビコー</t>
+          <t>ヒロシ</t>
         </is>
       </c>
       <c r="B435" t="n">
@@ -72920,19 +73400,19 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>フジ</t>
+          <t>ビコー</t>
         </is>
       </c>
       <c r="B436" t="n">
@@ -72940,19 +73420,19 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>ペロとペコ</t>
+          <t>フジ</t>
         </is>
       </c>
       <c r="B437" t="n">
@@ -72960,19 +73440,19 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>ボス</t>
+          <t>ペロとペコ</t>
         </is>
       </c>
       <c r="B438" t="n">
@@ -72980,19 +73460,19 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>ボンタ</t>
+          <t>ボス</t>
         </is>
       </c>
       <c r="B439" t="n">
@@ -73000,19 +73480,19 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>ポチ</t>
+          <t>ボンタ</t>
         </is>
       </c>
       <c r="B440" t="n">
@@ -73020,19 +73500,19 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>マッチョ</t>
+          <t>ポチ</t>
         </is>
       </c>
       <c r="B441" t="n">
@@ -73040,19 +73520,19 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>ミカミと仲間たち</t>
+          <t>マッチョ</t>
         </is>
       </c>
       <c r="B442" t="n">
@@ -73060,19 +73540,19 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>ミスター工事マン</t>
+          <t>ミカミと仲間たち</t>
         </is>
       </c>
       <c r="B443" t="n">
@@ -73080,19 +73560,19 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>ミッシ</t>
+          <t>ミスター工事マン</t>
         </is>
       </c>
       <c r="B444" t="n">
@@ -73100,19 +73580,19 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>ミッチー</t>
+          <t>ミッシ</t>
         </is>
       </c>
       <c r="B445" t="n">
@@ -73120,19 +73600,19 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>ミルコ</t>
+          <t>ミッチー</t>
         </is>
       </c>
       <c r="B446" t="n">
@@ -73152,7 +73632,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>ミン</t>
+          <t>ミルコ</t>
         </is>
       </c>
       <c r="B447" t="n">
@@ -73160,19 +73640,19 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>モジャ</t>
+          <t>ミン</t>
         </is>
       </c>
       <c r="B448" t="n">
@@ -73180,19 +73660,19 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>ヤノちゃん</t>
+          <t>モジャ</t>
         </is>
       </c>
       <c r="B449" t="n">
@@ -73200,19 +73680,19 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>ヤマ</t>
+          <t>ヤノちゃん</t>
         </is>
       </c>
       <c r="B450" t="n">
@@ -73220,19 +73700,19 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>ユウ</t>
+          <t>ヤマ</t>
         </is>
       </c>
       <c r="B451" t="n">
@@ -73240,19 +73720,19 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>ユキ</t>
+          <t>ユウ</t>
         </is>
       </c>
       <c r="B452" t="n">
@@ -73260,19 +73740,19 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>ユッキー</t>
+          <t>ユキ</t>
         </is>
       </c>
       <c r="B453" t="n">
@@ -73280,19 +73760,19 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>ヨシヤ</t>
+          <t>ユッキー</t>
         </is>
       </c>
       <c r="B454" t="n">
@@ -73300,19 +73780,19 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>ラオ</t>
+          <t>ヨシヤ</t>
         </is>
       </c>
       <c r="B455" t="n">
@@ -73320,19 +73800,19 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>リク</t>
+          <t>ラオ</t>
         </is>
       </c>
       <c r="B456" t="n">
@@ -73340,19 +73820,19 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>リョウ</t>
+          <t>リク</t>
         </is>
       </c>
       <c r="B457" t="n">
@@ -73360,19 +73840,19 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>レオ</t>
+          <t>リョウ</t>
         </is>
       </c>
       <c r="B458" t="n">
@@ -73380,19 +73860,19 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>ロタポジ</t>
+          <t>レオ</t>
         </is>
       </c>
       <c r="B459" t="n">
@@ -73400,19 +73880,19 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>ローズ</t>
+          <t>ロタポジ</t>
         </is>
       </c>
       <c r="B460" t="n">
@@ -73420,19 +73900,19 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>偽マイマイ</t>
+          <t>ローズ</t>
         </is>
       </c>
       <c r="B461" t="n">
@@ -73440,19 +73920,19 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>僕と私</t>
+          <t>偽マイマイ</t>
         </is>
       </c>
       <c r="B462" t="n">
@@ -73460,19 +73940,19 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>光一</t>
+          <t>僕と私</t>
         </is>
       </c>
       <c r="B463" t="n">
@@ -73480,19 +73960,19 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>名無し</t>
+          <t>光一</t>
         </is>
       </c>
       <c r="B464" t="n">
@@ -73500,19 +73980,19 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>変態まっする</t>
+          <t>名無し</t>
         </is>
       </c>
       <c r="B465" t="n">
@@ -73520,19 +74000,19 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>変態マッソー</t>
+          <t>変態まっする</t>
         </is>
       </c>
       <c r="B466" t="n">
@@ -73540,19 +74020,19 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>天我迅</t>
+          <t>変態マッソー</t>
         </is>
       </c>
       <c r="B467" t="n">
@@ -73560,19 +74040,19 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>女子三人衆</t>
+          <t>天我迅</t>
         </is>
       </c>
       <c r="B468" t="n">
@@ -73580,19 +74060,19 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>彩 なまがき</t>
+          <t>女子三人衆</t>
         </is>
       </c>
       <c r="B469" t="n">
@@ -73600,19 +74080,19 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>正装しん</t>
+          <t>彩 なまがき</t>
         </is>
       </c>
       <c r="B470" t="n">
@@ -73620,19 +74100,19 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>海砂利水魚</t>
+          <t>正装しん</t>
         </is>
       </c>
       <c r="B471" t="n">
@@ -73640,19 +74120,19 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>田中</t>
+          <t>海砂利水魚</t>
         </is>
       </c>
       <c r="B472" t="n">
@@ -73660,19 +74140,19 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>番</t>
+          <t>田中</t>
         </is>
       </c>
       <c r="B473" t="n">
@@ -73680,19 +74160,19 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>碧咲</t>
+          <t>番</t>
         </is>
       </c>
       <c r="B474" t="n">
@@ -73700,19 +74180,19 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>絶</t>
+          <t>碧咲</t>
         </is>
       </c>
       <c r="B475" t="n">
@@ -73720,19 +74200,19 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>絶ちゃん</t>
+          <t>福ちゃん</t>
         </is>
       </c>
       <c r="B476" t="n">
@@ -73740,19 +74220,19 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>美優</t>
+          <t>絶</t>
         </is>
       </c>
       <c r="B477" t="n">
@@ -73760,19 +74240,19 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>赤ちゃん</t>
+          <t>絶ちゃん</t>
         </is>
       </c>
       <c r="B478" t="n">
@@ -73780,19 +74260,19 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>赤井ヱビス</t>
+          <t>美優</t>
         </is>
       </c>
       <c r="B479" t="n">
@@ -73800,30 +74280,70 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
+          <t>赤ちゃん</t>
+        </is>
+      </c>
+      <c r="B480" t="n">
+        <v>1</v>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>赤井ヱビス</t>
+        </is>
+      </c>
+      <c r="B481" t="n">
+        <v>1</v>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
           <t>雅-miyabi-/とも</t>
         </is>
       </c>
-      <c r="B480" t="n">
-        <v>1</v>
-      </c>
-      <c r="C480" t="inlineStr">
+      <c r="B482" t="n">
+        <v>1</v>
+      </c>
+      <c r="C482" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="D480" t="inlineStr">
+      <c r="D482" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -73906,10 +74426,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C5" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6">
@@ -73919,10 +74439,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="7">
@@ -73989,10 +74509,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C2" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3">
@@ -74002,10 +74522,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C3" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4">
@@ -74236,10 +74756,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C21" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="22">
@@ -74249,10 +74769,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C22" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="23">
@@ -74262,10 +74782,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C23" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24">
@@ -74288,10 +74808,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C25" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -74369,13 +74889,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/bbs_log.xlsx
+++ b/bbs_log.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H821"/>
+  <dimension ref="A1:H828"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25592,7 +25592,6 @@
           <t>キムとローズ</t>
         </is>
       </c>
-      <c r="E799" t="inlineStr"/>
       <c r="F799" t="inlineStr">
         <is>
           <t>本日</t>
@@ -25603,7 +25602,6 @@
           <t>乳縛りで来店します</t>
         </is>
       </c>
-      <c r="H799" t="inlineStr"/>
     </row>
     <row r="800">
       <c r="A800" t="n">
@@ -25624,7 +25622,6 @@
           <t>たかやま、ふくちゃん</t>
         </is>
       </c>
-      <c r="E800" t="inlineStr"/>
       <c r="F800" t="inlineStr">
         <is>
           <t>めがねーず</t>
@@ -25635,7 +25632,6 @@
           <t>きまんこ</t>
         </is>
       </c>
-      <c r="H800" t="inlineStr"/>
     </row>
     <row r="801">
       <c r="A801" t="n">
@@ -25656,7 +25652,6 @@
           <t>ミコト</t>
         </is>
       </c>
-      <c r="E801" t="inlineStr"/>
       <c r="F801" t="inlineStr">
         <is>
           <t>今</t>
@@ -25667,7 +25662,6 @@
           <t>遊びに来ましたよ♪</t>
         </is>
       </c>
-      <c r="H801" t="inlineStr"/>
     </row>
     <row r="802">
       <c r="A802" t="n">
@@ -25688,7 +25682,6 @@
           <t>さとる、ましゅ</t>
         </is>
       </c>
-      <c r="E802" t="inlineStr"/>
       <c r="F802" t="inlineStr">
         <is>
           <t>いっしょに</t>
@@ -25699,7 +25692,6 @@
           <t>きまんた</t>
         </is>
       </c>
-      <c r="H802" t="inlineStr"/>
     </row>
     <row r="803">
       <c r="A803" t="n">
@@ -25720,7 +25712,6 @@
           <t>クワレ</t>
         </is>
       </c>
-      <c r="E803" t="inlineStr"/>
       <c r="F803" t="inlineStr">
         <is>
           <t>いきます</t>
@@ -25731,7 +25722,6 @@
           <t>ひとりで</t>
         </is>
       </c>
-      <c r="H803" t="inlineStr"/>
     </row>
     <row r="804">
       <c r="A804" t="n">
@@ -25752,7 +25742,6 @@
           <t>おまする</t>
         </is>
       </c>
-      <c r="E804" t="inlineStr"/>
       <c r="F804" t="inlineStr">
         <is>
           <t>今</t>
@@ -25763,7 +25752,6 @@
           <t>飯食ってきた！</t>
         </is>
       </c>
-      <c r="H804" t="inlineStr"/>
     </row>
     <row r="805">
       <c r="A805" t="n">
@@ -25784,7 +25772,6 @@
           <t>カシワ</t>
         </is>
       </c>
-      <c r="E805" t="inlineStr"/>
       <c r="F805" t="inlineStr">
         <is>
           <t>はじめて</t>
@@ -25795,7 +25782,6 @@
           <t>きまんた</t>
         </is>
       </c>
-      <c r="H805" t="inlineStr"/>
     </row>
     <row r="806">
       <c r="A806" t="n">
@@ -25816,7 +25802,6 @@
           <t>おでで</t>
         </is>
       </c>
-      <c r="E806" t="inlineStr"/>
       <c r="F806" t="inlineStr">
         <is>
           <t>今</t>
@@ -25827,7 +25812,6 @@
           <t>きちゃ！</t>
         </is>
       </c>
-      <c r="H806" t="inlineStr"/>
     </row>
     <row r="807">
       <c r="A807" t="n">
@@ -25848,7 +25832,6 @@
           <t>みなっち</t>
         </is>
       </c>
-      <c r="E807" t="inlineStr"/>
       <c r="F807" t="inlineStr">
         <is>
           <t>ちょっとだけ</t>
@@ -25859,7 +25842,6 @@
           <t>顔出すわん</t>
         </is>
       </c>
-      <c r="H807" t="inlineStr"/>
     </row>
     <row r="808">
       <c r="A808" t="n">
@@ -25880,7 +25862,6 @@
           <t>しりゅう、ヤノ</t>
         </is>
       </c>
-      <c r="E808" t="inlineStr"/>
       <c r="F808" t="inlineStr">
         <is>
           <t>ひさびさ</t>
@@ -25891,7 +25872,6 @@
           <t>きまんた</t>
         </is>
       </c>
-      <c r="H808" t="inlineStr"/>
     </row>
     <row r="809">
       <c r="A809" t="n">
@@ -25912,7 +25892,6 @@
           <t>あいちゃん</t>
         </is>
       </c>
-      <c r="E809" t="inlineStr"/>
       <c r="F809" t="inlineStr">
         <is>
           <t>ちょっと</t>
@@ -25923,7 +25902,6 @@
           <t>きたよ！！</t>
         </is>
       </c>
-      <c r="H809" t="inlineStr"/>
     </row>
     <row r="810">
       <c r="A810" t="n">
@@ -25944,7 +25922,6 @@
           <t>たなか</t>
         </is>
       </c>
-      <c r="E810" t="inlineStr"/>
       <c r="F810" t="inlineStr">
         <is>
           <t>今</t>
@@ -25955,7 +25932,6 @@
           <t>はじめてきました</t>
         </is>
       </c>
-      <c r="H810" t="inlineStr"/>
     </row>
     <row r="811">
       <c r="A811" t="n">
@@ -25976,7 +25952,6 @@
           <t>まちゃん、えね</t>
         </is>
       </c>
-      <c r="E811" t="inlineStr"/>
       <c r="F811" t="inlineStr">
         <is>
           <t>今</t>
@@ -25987,7 +25962,6 @@
           <t>きまんた</t>
         </is>
       </c>
-      <c r="H811" t="inlineStr"/>
     </row>
     <row r="812">
       <c r="A812" t="n">
@@ -26008,7 +25982,6 @@
           <t>キング</t>
         </is>
       </c>
-      <c r="E812" t="inlineStr"/>
       <c r="F812" t="inlineStr">
         <is>
           <t>今</t>
@@ -26019,7 +25992,6 @@
           <t>きました！！！</t>
         </is>
       </c>
-      <c r="H812" t="inlineStr"/>
     </row>
     <row r="813">
       <c r="A813" t="n">
@@ -26040,7 +26012,6 @@
           <t>じゅきや</t>
         </is>
       </c>
-      <c r="E813" t="inlineStr"/>
       <c r="F813" t="inlineStr">
         <is>
           <t>いま</t>
@@ -26051,7 +26022,6 @@
           <t>きたよ！</t>
         </is>
       </c>
-      <c r="H813" t="inlineStr"/>
     </row>
     <row r="814">
       <c r="A814" t="n">
@@ -26072,7 +26042,6 @@
           <t>すーたく</t>
         </is>
       </c>
-      <c r="E814" t="inlineStr"/>
       <c r="F814" t="inlineStr">
         <is>
           <t>今</t>
@@ -26083,7 +26052,6 @@
           <t>きまきま</t>
         </is>
       </c>
-      <c r="H814" t="inlineStr"/>
     </row>
     <row r="815">
       <c r="A815" t="n">
@@ -26104,7 +26072,6 @@
           <t>メンズ5人組</t>
         </is>
       </c>
-      <c r="E815" t="inlineStr"/>
       <c r="F815" t="inlineStr">
         <is>
           <t>初めて</t>
@@ -26115,7 +26082,6 @@
           <t>きました！</t>
         </is>
       </c>
-      <c r="H815" t="inlineStr"/>
     </row>
     <row r="816">
       <c r="A816" t="n">
@@ -26136,7 +26102,6 @@
           <t>りょう</t>
         </is>
       </c>
-      <c r="E816" t="inlineStr"/>
       <c r="F816" t="inlineStr">
         <is>
           <t>初めて</t>
@@ -26147,7 +26112,6 @@
           <t>きました！</t>
         </is>
       </c>
-      <c r="H816" t="inlineStr"/>
     </row>
     <row r="817">
       <c r="A817" t="n">
@@ -26168,7 +26132,6 @@
           <t>あんこちゃん</t>
         </is>
       </c>
-      <c r="E817" t="inlineStr"/>
       <c r="F817" t="inlineStr">
         <is>
           <t>しごおわ</t>
@@ -26179,7 +26142,6 @@
           <t>きちゃ！</t>
         </is>
       </c>
-      <c r="H817" t="inlineStr"/>
     </row>
     <row r="818">
       <c r="A818" t="n">
@@ -26200,7 +26162,6 @@
           <t>サカモト、かな、部長</t>
         </is>
       </c>
-      <c r="E818" t="inlineStr"/>
       <c r="F818" t="inlineStr">
         <is>
           <t>新規さん連れて</t>
@@ -26211,7 +26172,6 @@
           <t>きました</t>
         </is>
       </c>
-      <c r="H818" t="inlineStr"/>
     </row>
     <row r="819">
       <c r="A819" t="n">
@@ -26232,7 +26192,6 @@
           <t>ラ王</t>
         </is>
       </c>
-      <c r="E819" t="inlineStr"/>
       <c r="F819" t="inlineStr">
         <is>
           <t>今</t>
@@ -26243,7 +26202,6 @@
           <t>きました</t>
         </is>
       </c>
-      <c r="H819" t="inlineStr"/>
     </row>
     <row r="820">
       <c r="A820" t="n">
@@ -26264,7 +26222,6 @@
           <t>あきと</t>
         </is>
       </c>
-      <c r="E820" t="inlineStr"/>
       <c r="F820" t="inlineStr">
         <is>
           <t>はじめて</t>
@@ -26275,7 +26232,6 @@
           <t>きました</t>
         </is>
       </c>
-      <c r="H820" t="inlineStr"/>
     </row>
     <row r="821">
       <c r="A821" t="n">
@@ -26329,6 +26285,250 @@
         </is>
       </c>
     </row>
+    <row r="822">
+      <c r="A822" t="n">
+        <v>28393</v>
+      </c>
+      <c r="B822" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>18:58:33</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>ゆずき</t>
+        </is>
+      </c>
+      <c r="E822" t="inlineStr"/>
+      <c r="F822" t="inlineStr">
+        <is>
+          <t>おーぷんまえに</t>
+        </is>
+      </c>
+      <c r="G822" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+      <c r="H822" t="inlineStr"/>
+    </row>
+    <row r="823">
+      <c r="A823" t="n">
+        <v>28395</v>
+      </c>
+      <c r="B823" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>19:06:58</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>ひがんたん</t>
+        </is>
+      </c>
+      <c r="E823" t="inlineStr"/>
+      <c r="F823" t="inlineStr">
+        <is>
+          <t>今日は</t>
+        </is>
+      </c>
+      <c r="G823" t="inlineStr">
+        <is>
+          <t>クールに</t>
+        </is>
+      </c>
+      <c r="H823" t="inlineStr"/>
+    </row>
+    <row r="824">
+      <c r="A824" t="n">
+        <v>28397</v>
+      </c>
+      <c r="B824" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>19:53:02</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>らん、カルマ、ポポ</t>
+        </is>
+      </c>
+      <c r="E824" t="inlineStr"/>
+      <c r="F824" t="inlineStr">
+        <is>
+          <t>久しぶり＆新規連れて</t>
+        </is>
+      </c>
+      <c r="G824" t="inlineStr">
+        <is>
+          <t>来ました</t>
+        </is>
+      </c>
+      <c r="H824" t="inlineStr"/>
+    </row>
+    <row r="825">
+      <c r="A825" t="n">
+        <v>28399</v>
+      </c>
+      <c r="B825" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>21:37:38</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>てる</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr"/>
+      <c r="F825" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G825" t="inlineStr">
+        <is>
+          <t>きたよー</t>
+        </is>
+      </c>
+      <c r="H825" t="inlineStr"/>
+    </row>
+    <row r="826">
+      <c r="A826" t="n">
+        <v>28401</v>
+      </c>
+      <c r="B826" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>00:48:13</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>さとるん</t>
+        </is>
+      </c>
+      <c r="E826" t="inlineStr"/>
+      <c r="F826" t="inlineStr">
+        <is>
+          <t>久々</t>
+        </is>
+      </c>
+      <c r="G826" t="inlineStr">
+        <is>
+          <t>日曜日に</t>
+        </is>
+      </c>
+      <c r="H826" t="inlineStr"/>
+    </row>
+    <row r="827">
+      <c r="A827" t="n">
+        <v>28403</v>
+      </c>
+      <c r="B827" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>02:06:14</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>まいまい</t>
+        </is>
+      </c>
+      <c r="E827" t="inlineStr"/>
+      <c r="F827" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G827" t="inlineStr">
+        <is>
+          <t>きたんご</t>
+        </is>
+      </c>
+      <c r="H827" t="inlineStr"/>
+    </row>
+    <row r="828">
+      <c r="A828" t="n">
+        <v>28405</v>
+      </c>
+      <c r="B828" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>05:20:54</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E828" t="inlineStr">
+        <is>
+          <t>新妻マゾヒストのミコト</t>
+        </is>
+      </c>
+      <c r="F828" t="inlineStr">
+        <is>
+          <t>★☆★朝までアゲアゲの月曜日営業が始まるわよ♪★☆★</t>
+        </is>
+      </c>
+      <c r="G828" t="inlineStr">
+        <is>
+          <t>本日10月5日の営業時間は♪
+オープン19:00！ラスト5:00なのよ☆
+担当は
+新妻マゾヒストのミコト
+なのよ♪
+どんな季節でも★BAMBITCH★は色気ムンムンで暑すぎる♪
+バンビッチでおもいっきりはじけちゃって（笑）
+精力は無くても性欲がある！？
+大人の憩いと禁断サークル盛りだくさん！
+憩いと交流の魔性の遊び場バンビッチは素敵な出会いを 提供いたします（笑)☆☆
+おつまみ等の持ち込みは自由なのでみんなで持ち寄ってお近づきのきっかけにどうぞ♪
+強制や無理強いは一切ございませんので楽しく遊びましょう♪
+宇都宮市宿郷1−12−9　カサブランカビル5F</t>
+        </is>
+      </c>
+      <c r="H828" t="inlineStr">
+        <is>
+          <t>img20261005052054.jpg</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26340,7 +26540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I957"/>
+  <dimension ref="A1:I965"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67506,6 +67706,350 @@
       <c r="I957" t="inlineStr">
         <is>
           <t>きました</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>18:58:33</t>
+        </is>
+      </c>
+      <c r="D958" t="n">
+        <v>28393</v>
+      </c>
+      <c r="E958" t="inlineStr">
+        <is>
+          <t>ゆずき</t>
+        </is>
+      </c>
+      <c r="F958" t="n">
+        <v>15</v>
+      </c>
+      <c r="G958" t="inlineStr">
+        <is>
+          <t>ゆずき</t>
+        </is>
+      </c>
+      <c r="H958" t="inlineStr">
+        <is>
+          <t>おーぷんまえに</t>
+        </is>
+      </c>
+      <c r="I958" t="inlineStr">
+        <is>
+          <t>きました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>19:06:58</t>
+        </is>
+      </c>
+      <c r="D959" t="n">
+        <v>28395</v>
+      </c>
+      <c r="E959" t="inlineStr">
+        <is>
+          <t>ひがんたん</t>
+        </is>
+      </c>
+      <c r="F959" t="n">
+        <v>5</v>
+      </c>
+      <c r="G959" t="inlineStr">
+        <is>
+          <t>ひがんたん</t>
+        </is>
+      </c>
+      <c r="H959" t="inlineStr">
+        <is>
+          <t>今日は</t>
+        </is>
+      </c>
+      <c r="I959" t="inlineStr">
+        <is>
+          <t>クールに</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>19:53:02</t>
+        </is>
+      </c>
+      <c r="D960" t="n">
+        <v>28397</v>
+      </c>
+      <c r="E960" t="inlineStr">
+        <is>
+          <t>らん</t>
+        </is>
+      </c>
+      <c r="F960" t="n">
+        <v>1</v>
+      </c>
+      <c r="G960" t="inlineStr">
+        <is>
+          <t>らん、カルマ、ポポ</t>
+        </is>
+      </c>
+      <c r="H960" t="inlineStr">
+        <is>
+          <t>久しぶり＆新規連れて</t>
+        </is>
+      </c>
+      <c r="I960" t="inlineStr">
+        <is>
+          <t>来ました</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>19:53:02</t>
+        </is>
+      </c>
+      <c r="D961" t="n">
+        <v>28397</v>
+      </c>
+      <c r="E961" t="inlineStr">
+        <is>
+          <t>カルマ</t>
+        </is>
+      </c>
+      <c r="F961" t="n">
+        <v>1</v>
+      </c>
+      <c r="G961" t="inlineStr">
+        <is>
+          <t>らん、カルマ、ポポ</t>
+        </is>
+      </c>
+      <c r="H961" t="inlineStr">
+        <is>
+          <t>久しぶり＆新規連れて</t>
+        </is>
+      </c>
+      <c r="I961" t="inlineStr">
+        <is>
+          <t>来ました</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>19:53:02</t>
+        </is>
+      </c>
+      <c r="D962" t="n">
+        <v>28397</v>
+      </c>
+      <c r="E962" t="inlineStr">
+        <is>
+          <t>ポポ</t>
+        </is>
+      </c>
+      <c r="F962" t="n">
+        <v>1</v>
+      </c>
+      <c r="G962" t="inlineStr">
+        <is>
+          <t>らん、カルマ、ポポ</t>
+        </is>
+      </c>
+      <c r="H962" t="inlineStr">
+        <is>
+          <t>久しぶり＆新規連れて</t>
+        </is>
+      </c>
+      <c r="I962" t="inlineStr">
+        <is>
+          <t>来ました</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>21:37:38</t>
+        </is>
+      </c>
+      <c r="D963" t="n">
+        <v>28399</v>
+      </c>
+      <c r="E963" t="inlineStr">
+        <is>
+          <t>てる</t>
+        </is>
+      </c>
+      <c r="F963" t="n">
+        <v>2</v>
+      </c>
+      <c r="G963" t="inlineStr">
+        <is>
+          <t>てる</t>
+        </is>
+      </c>
+      <c r="H963" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="I963" t="inlineStr">
+        <is>
+          <t>きたよー</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>00:48:13</t>
+        </is>
+      </c>
+      <c r="D964" t="n">
+        <v>28401</v>
+      </c>
+      <c r="E964" t="inlineStr">
+        <is>
+          <t>さとるん</t>
+        </is>
+      </c>
+      <c r="F964" t="n">
+        <v>3</v>
+      </c>
+      <c r="G964" t="inlineStr">
+        <is>
+          <t>さとるん</t>
+        </is>
+      </c>
+      <c r="H964" t="inlineStr">
+        <is>
+          <t>久々</t>
+        </is>
+      </c>
+      <c r="I964" t="inlineStr">
+        <is>
+          <t>日曜日に</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>02:06:14</t>
+        </is>
+      </c>
+      <c r="D965" t="n">
+        <v>28403</v>
+      </c>
+      <c r="E965" t="inlineStr">
+        <is>
+          <t>まいまい</t>
+        </is>
+      </c>
+      <c r="F965" t="n">
+        <v>15</v>
+      </c>
+      <c r="G965" t="inlineStr">
+        <is>
+          <t>まいまい</t>
+        </is>
+      </c>
+      <c r="H965" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="I965" t="inlineStr">
+        <is>
+          <t>きたんご</t>
         </is>
       </c>
     </row>
@@ -67520,7 +68064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D500"/>
+  <dimension ref="A1:D503"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67588,7 +68132,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>彩</t>
+          <t>まいまい</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -67596,52 +68140,52 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>まいまい</t>
+          <t>ゆずき</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ゆずき</t>
+          <t>彩</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -68168,7 +68712,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ふくてゃ</t>
+          <t>ひがんたん</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -68176,19 +68720,19 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>べー</t>
+          <t>ふくてゃ</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -68196,19 +68740,19 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>まいなす</t>
+          <t>べー</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -68216,19 +68760,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ましゅ社長</t>
+          <t>まいなす</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -68236,19 +68780,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
           <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>よしやん</t>
+          <t>ましゅ社長</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -68256,19 +68800,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>りん</t>
+          <t>よしやん</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -68276,19 +68820,19 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-10-02</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>キム</t>
+          <t>りん</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -68301,14 +68845,14 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>コテッチャン</t>
+          <t>キム</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -68316,19 +68860,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ミコト</t>
+          <t>コテッチャン</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -68336,39 +68880,39 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-02</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>くれは</t>
+          <t>ミコト</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>しゅん</t>
+          <t>くれは</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -68376,19 +68920,19 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>すず</t>
+          <t>しゅん</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -68396,19 +68940,19 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ちゃそたけ</t>
+          <t>すず</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -68416,19 +68960,19 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>てくのちゃん</t>
+          <t>ちゃそたけ</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -68436,19 +68980,19 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>でで</t>
+          <t>てくのちゃん</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -68456,7 +69000,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -68468,7 +69012,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ひがんたん</t>
+          <t>でで</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -68476,12 +69020,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -68908,7 +69452,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>すー</t>
+          <t>さとるん</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -68916,19 +69460,19 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>すーさん</t>
+          <t>すー</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -68936,19 +69480,19 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>すーたく</t>
+          <t>すーさん</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -68956,19 +69500,19 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>たけ</t>
+          <t>すーたく</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -68976,19 +69520,19 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>たつや</t>
+          <t>たけ</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -68996,19 +69540,19 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-02</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>だいご</t>
+          <t>たつや</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -69021,14 +69565,14 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>なな</t>
+          <t>だいご</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -69036,19 +69580,19 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>なまがき</t>
+          <t>なな</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -69056,19 +69600,19 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ひがんちゃん</t>
+          <t>なまがき</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -69076,19 +69620,19 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ぽちゃりす組</t>
+          <t>ひがんちゃん</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -69096,19 +69640,19 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>まゆ</t>
+          <t>ぽちゃりす組</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -69116,19 +69660,19 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>まろ</t>
+          <t>まゆ</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -69136,19 +69680,19 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>もっぷ</t>
+          <t>まろ</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -69156,19 +69700,19 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>りゅう</t>
+          <t>もっぷ</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -69176,19 +69720,19 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>れいら</t>
+          <t>りゅう</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -69196,19 +69740,19 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>カズヤ</t>
+          <t>れいら</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -69216,19 +69760,19 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>カー</t>
+          <t>カズヤ</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -69236,19 +69780,19 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>キムとドMみい</t>
+          <t>カー</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -69256,19 +69800,19 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ケン</t>
+          <t>キムとドMみい</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -69276,19 +69820,19 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>タツヤ</t>
+          <t>ケン</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -69296,19 +69840,19 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>テクノっち</t>
+          <t>タツヤ</t>
         </is>
       </c>
       <c r="B90" t="n">
@@ -69316,19 +69860,19 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>愛とスケベの戦士</t>
+          <t>テクノっち</t>
         </is>
       </c>
       <c r="B91" t="n">
@@ -69336,39 +69880,39 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>愛とスケベの戦士</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Bee</t>
+          <t>A</t>
         </is>
       </c>
       <c r="B93" t="n">
@@ -69376,19 +69920,19 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>YZK</t>
+          <t>Bee</t>
         </is>
       </c>
       <c r="B94" t="n">
@@ -69396,19 +69940,19 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>あさみん</t>
+          <t>YZK</t>
         </is>
       </c>
       <c r="B95" t="n">
@@ -69416,19 +69960,19 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>あっくん</t>
+          <t>あさみん</t>
         </is>
       </c>
       <c r="B96" t="n">
@@ -69436,19 +69980,19 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>あゆ</t>
+          <t>あっくん</t>
         </is>
       </c>
       <c r="B97" t="n">
@@ -69456,19 +70000,19 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>あんこ</t>
+          <t>あゆ</t>
         </is>
       </c>
       <c r="B98" t="n">
@@ -69476,19 +70020,19 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>いっちゃん</t>
+          <t>あんこ</t>
         </is>
       </c>
       <c r="B99" t="n">
@@ -69496,19 +70040,19 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>いぬ</t>
+          <t>いっちゃん</t>
         </is>
       </c>
       <c r="B100" t="n">
@@ -69521,14 +70065,14 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>える</t>
+          <t>いぬ</t>
         </is>
       </c>
       <c r="B101" t="n">
@@ -69536,19 +70080,19 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>かい</t>
+          <t>える</t>
         </is>
       </c>
       <c r="B102" t="n">
@@ -69556,19 +70100,19 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>きむ</t>
+          <t>かい</t>
         </is>
       </c>
       <c r="B103" t="n">
@@ -69576,19 +70120,19 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>けん</t>
+          <t>きむ</t>
         </is>
       </c>
       <c r="B104" t="n">
@@ -69596,19 +70140,19 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
           <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>こーだい</t>
+          <t>けん</t>
         </is>
       </c>
       <c r="B105" t="n">
@@ -69616,19 +70160,19 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>さとるん</t>
+          <t>こーだい</t>
         </is>
       </c>
       <c r="B106" t="n">
@@ -69636,12 +70180,12 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
@@ -69828,7 +70372,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>とうや</t>
+          <t>てる</t>
         </is>
       </c>
       <c r="B116" t="n">
@@ -69836,19 +70380,19 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>とし</t>
+          <t>とうや</t>
         </is>
       </c>
       <c r="B117" t="n">
@@ -69856,19 +70400,19 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>にこちん</t>
+          <t>とし</t>
         </is>
       </c>
       <c r="B118" t="n">
@@ -69876,19 +70420,19 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ねむねむ</t>
+          <t>にこちん</t>
         </is>
       </c>
       <c r="B119" t="n">
@@ -69896,19 +70440,19 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-02</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ふく</t>
+          <t>ねむねむ</t>
         </is>
       </c>
       <c r="B120" t="n">
@@ -69916,19 +70460,19 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ぶりちゃん</t>
+          <t>ふく</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -69936,19 +70480,19 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>まい</t>
+          <t>ぶりちゃん</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -69961,14 +70505,14 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>まいまいまいまい</t>
+          <t>まい</t>
         </is>
       </c>
       <c r="B123" t="n">
@@ -69976,19 +70520,19 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ましゅ会長</t>
+          <t>まいまいまいまい</t>
         </is>
       </c>
       <c r="B124" t="n">
@@ -69996,19 +70540,19 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>まりん</t>
+          <t>ましゅ会長</t>
         </is>
       </c>
       <c r="B125" t="n">
@@ -70016,19 +70560,19 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>まーさん</t>
+          <t>まりん</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -70036,19 +70580,19 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>みっちー</t>
+          <t>まーさん</t>
         </is>
       </c>
       <c r="B127" t="n">
@@ -70056,19 +70600,19 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>みれい</t>
+          <t>みっちー</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -70076,19 +70620,19 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>みー</t>
+          <t>みれい</t>
         </is>
       </c>
       <c r="B129" t="n">
@@ -70096,19 +70640,19 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>めい</t>
+          <t>みー</t>
         </is>
       </c>
       <c r="B130" t="n">
@@ -70116,19 +70660,19 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>やえ</t>
+          <t>めい</t>
         </is>
       </c>
       <c r="B131" t="n">
@@ -70136,19 +70680,19 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ゆうくん</t>
+          <t>やえ</t>
         </is>
       </c>
       <c r="B132" t="n">
@@ -70156,19 +70700,19 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ゆすき</t>
+          <t>ゆうくん</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -70176,19 +70720,19 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ゆずきちくん</t>
+          <t>ゆすき</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -70196,19 +70740,19 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>よっしー</t>
+          <t>ゆずきちくん</t>
         </is>
       </c>
       <c r="B135" t="n">
@@ -70216,19 +70760,19 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-10-02</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>よっち</t>
+          <t>よっしー</t>
         </is>
       </c>
       <c r="B136" t="n">
@@ -70236,19 +70780,19 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>らお</t>
+          <t>よっち</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -70256,19 +70800,19 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>りお</t>
+          <t>らお</t>
         </is>
       </c>
       <c r="B138" t="n">
@@ -70276,19 +70820,19 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>アキ</t>
+          <t>りお</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -70296,19 +70840,19 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>オカニー</t>
+          <t>アキ</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -70316,19 +70860,19 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>キムとドMまゆ</t>
+          <t>オカニー</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -70336,19 +70880,19 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>キング</t>
+          <t>キムとドMまゆ</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -70356,19 +70900,19 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>タカ</t>
+          <t>キング</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -70376,19 +70920,19 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>タク</t>
+          <t>タカ</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -70396,19 +70940,19 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>タケ</t>
+          <t>タク</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -70416,19 +70960,19 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ダイゴ</t>
+          <t>タケ</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -70436,19 +70980,19 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>マイナス</t>
+          <t>ダイゴ</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -70456,19 +71000,19 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>マサ</t>
+          <t>マイナス</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -70476,19 +71020,19 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>マッスル</t>
+          <t>マサ</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -70496,19 +71040,19 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>マナティ</t>
+          <t>マッスル</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -70521,14 +71065,14 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>リン</t>
+          <t>マナティ</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -70536,19 +71080,19 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>変態マッスル</t>
+          <t>リン</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -70556,19 +71100,19 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>大塚</t>
+          <t>変態マッスル</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -70576,19 +71120,19 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>高田</t>
+          <t>大塚</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -70596,39 +71140,39 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>5人衆</t>
+          <t>高田</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>5人衆</t>
         </is>
       </c>
       <c r="B156" t="n">
@@ -70636,19 +71180,19 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>EVANS×２</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -70656,19 +71200,19 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>HGN</t>
+          <t>EVANS×２</t>
         </is>
       </c>
       <c r="B158" t="n">
@@ -70676,19 +71220,19 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>JPTR</t>
+          <t>HGN</t>
         </is>
       </c>
       <c r="B159" t="n">
@@ -70696,19 +71240,19 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>KO</t>
+          <t>JPTR</t>
         </is>
       </c>
       <c r="B160" t="n">
@@ -70716,19 +71260,19 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>KSK</t>
+          <t>KO</t>
         </is>
       </c>
       <c r="B161" t="n">
@@ -70736,19 +71280,19 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>KUMA</t>
+          <t>KSK</t>
         </is>
       </c>
       <c r="B162" t="n">
@@ -70756,19 +71300,19 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>KUMA</t>
         </is>
       </c>
       <c r="B163" t="n">
@@ -70776,19 +71320,19 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="B164" t="n">
@@ -70796,19 +71340,19 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>NMGK</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -70816,19 +71360,19 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>N氏御一行</t>
+          <t>NMGK</t>
         </is>
       </c>
       <c r="B166" t="n">
@@ -70836,19 +71380,19 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>SIKUSENAチャンネルヒロキ</t>
+          <t>N氏御一行</t>
         </is>
       </c>
       <c r="B167" t="n">
@@ -70856,19 +71400,19 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>STR</t>
+          <t>SIKUSENAチャンネルヒロキ</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -70876,19 +71420,19 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>TARU</t>
+          <t>STR</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -70896,19 +71440,19 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>TT</t>
+          <t>TARU</t>
         </is>
       </c>
       <c r="B170" t="n">
@@ -70916,19 +71460,19 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Tやま</t>
+          <t>TT</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -70936,19 +71480,19 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>Tやま</t>
         </is>
       </c>
       <c r="B172" t="n">
@@ -70956,19 +71500,19 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="B173" t="n">
@@ -70976,19 +71520,19 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>hikari</t>
+          <t>c</t>
         </is>
       </c>
       <c r="B174" t="n">
@@ -70996,19 +71540,19 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>nuri</t>
+          <t>hikari</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -71016,19 +71560,19 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>sho</t>
+          <t>nuri</t>
         </is>
       </c>
       <c r="B176" t="n">
@@ -71036,19 +71580,19 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>taka</t>
+          <t>sho</t>
         </is>
       </c>
       <c r="B177" t="n">
@@ -71056,19 +71600,19 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>★Zakk★</t>
+          <t>taka</t>
         </is>
       </c>
       <c r="B178" t="n">
@@ -71076,19 +71620,19 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>あい</t>
+          <t>★Zakk★</t>
         </is>
       </c>
       <c r="B179" t="n">
@@ -71096,19 +71640,19 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>あき</t>
+          <t>あい</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -71116,19 +71660,19 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>あきと</t>
+          <t>あき</t>
         </is>
       </c>
       <c r="B181" t="n">
@@ -71136,19 +71680,19 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>あさみ</t>
+          <t>あきと</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -71156,19 +71700,19 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>あす</t>
+          <t>あさみ</t>
         </is>
       </c>
       <c r="B183" t="n">
@@ -71176,19 +71720,19 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>あにー</t>
+          <t>あす</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -71196,19 +71740,19 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>あまねちゃん</t>
+          <t>あにー</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -71216,19 +71760,19 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>ありす</t>
+          <t>あまねちゃん</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -71236,19 +71780,19 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>あんこちゃん</t>
+          <t>ありす</t>
         </is>
       </c>
       <c r="B187" t="n">
@@ -71256,19 +71800,19 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>いおり</t>
+          <t>あんこちゃん</t>
         </is>
       </c>
       <c r="B188" t="n">
@@ -71276,19 +71820,19 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>いけちゃん</t>
+          <t>いおり</t>
         </is>
       </c>
       <c r="B189" t="n">
@@ -71296,19 +71840,19 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>いぶお</t>
+          <t>いけちゃん</t>
         </is>
       </c>
       <c r="B190" t="n">
@@ -71316,19 +71860,19 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>うらら</t>
+          <t>いぶお</t>
         </is>
       </c>
       <c r="B191" t="n">
@@ -71336,19 +71880,19 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>えいたろう</t>
+          <t>うらら</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -71356,19 +71900,19 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>えね</t>
+          <t>えいたろう</t>
         </is>
       </c>
       <c r="B193" t="n">
@@ -71376,19 +71920,19 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>えび</t>
+          <t>えね</t>
         </is>
       </c>
       <c r="B194" t="n">
@@ -71396,19 +71940,19 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>えーたろ</t>
+          <t>えび</t>
         </is>
       </c>
       <c r="B195" t="n">
@@ -71416,19 +71960,19 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>おじき</t>
+          <t>えーたろ</t>
         </is>
       </c>
       <c r="B196" t="n">
@@ -71436,19 +71980,19 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>おじきち</t>
+          <t>おじき</t>
         </is>
       </c>
       <c r="B197" t="n">
@@ -71456,19 +72000,19 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>おすー</t>
+          <t>おじきち</t>
         </is>
       </c>
       <c r="B198" t="n">
@@ -71476,19 +72020,19 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>おちんぽベルセルク</t>
+          <t>おすー</t>
         </is>
       </c>
       <c r="B199" t="n">
@@ -71496,19 +72040,19 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>おにゃん</t>
+          <t>おちんぽベルセルク</t>
         </is>
       </c>
       <c r="B200" t="n">
@@ -71516,19 +72060,19 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>おにゃんにゃん</t>
+          <t>おにゃん</t>
         </is>
       </c>
       <c r="B201" t="n">
@@ -71536,19 +72080,19 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>おばし</t>
+          <t>おにゃんにゃん</t>
         </is>
       </c>
       <c r="B202" t="n">
@@ -71556,19 +72100,19 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>おまする</t>
+          <t>おばし</t>
         </is>
       </c>
       <c r="B203" t="n">
@@ -71576,19 +72120,19 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>おもち</t>
+          <t>おまする</t>
         </is>
       </c>
       <c r="B204" t="n">
@@ -71596,19 +72140,19 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>かける</t>
+          <t>おもち</t>
         </is>
       </c>
       <c r="B205" t="n">
@@ -71616,19 +72160,19 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>かずき</t>
+          <t>かける</t>
         </is>
       </c>
       <c r="B206" t="n">
@@ -71636,19 +72180,19 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>かず＆TKC＆のんのん</t>
+          <t>かずき</t>
         </is>
       </c>
       <c r="B207" t="n">
@@ -71656,19 +72200,19 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>かつ</t>
+          <t>かず＆TKC＆のんのん</t>
         </is>
       </c>
       <c r="B208" t="n">
@@ -71676,19 +72220,19 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>かな(絶ちゃん</t>
+          <t>かつ</t>
         </is>
       </c>
       <c r="B209" t="n">
@@ -71696,19 +72240,19 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>かな(絶ちゃん)/おっつん</t>
+          <t>かな(絶ちゃん</t>
         </is>
       </c>
       <c r="B210" t="n">
@@ -71716,19 +72260,19 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>がん</t>
+          <t>かな(絶ちゃん)/おっつん</t>
         </is>
       </c>
       <c r="B211" t="n">
@@ -71736,19 +72280,19 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>きむさん</t>
+          <t>がん</t>
         </is>
       </c>
       <c r="B212" t="n">
@@ -71756,19 +72300,19 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>きむむ</t>
+          <t>きむさん</t>
         </is>
       </c>
       <c r="B213" t="n">
@@ -71776,19 +72320,19 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>きむら</t>
+          <t>きむむ</t>
         </is>
       </c>
       <c r="B214" t="n">
@@ -71796,19 +72340,19 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>きょうちゃん</t>
+          <t>きむら</t>
         </is>
       </c>
       <c r="B215" t="n">
@@ -71816,19 +72360,19 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>きんたまよ</t>
+          <t>きょうちゃん</t>
         </is>
       </c>
       <c r="B216" t="n">
@@ -71836,19 +72380,19 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>くっぱ</t>
+          <t>きんたまよ</t>
         </is>
       </c>
       <c r="B217" t="n">
@@ -71856,19 +72400,19 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>くま</t>
+          <t>くっぱ</t>
         </is>
       </c>
       <c r="B218" t="n">
@@ -71876,19 +72420,19 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>くり</t>
+          <t>くま</t>
         </is>
       </c>
       <c r="B219" t="n">
@@ -71896,19 +72440,19 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>くろちゃん</t>
+          <t>くり</t>
         </is>
       </c>
       <c r="B220" t="n">
@@ -71916,19 +72460,19 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>ぐっちゃん</t>
+          <t>くろちゃん</t>
         </is>
       </c>
       <c r="B221" t="n">
@@ -71936,19 +72480,19 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>ぐっちゃん（チャイマフィ）</t>
+          <t>ぐっちゃん</t>
         </is>
       </c>
       <c r="B222" t="n">
@@ -71956,19 +72500,19 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>けい</t>
+          <t>ぐっちゃん（チャイマフィ）</t>
         </is>
       </c>
       <c r="B223" t="n">
@@ -71976,19 +72520,19 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>けいご</t>
+          <t>けい</t>
         </is>
       </c>
       <c r="B224" t="n">
@@ -71996,19 +72540,19 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>けいちゃん</t>
+          <t>けいご</t>
         </is>
       </c>
       <c r="B225" t="n">
@@ -72016,19 +72560,19 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>けんけん</t>
+          <t>けいちゃん</t>
         </is>
       </c>
       <c r="B226" t="n">
@@ -72036,19 +72580,19 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>げん</t>
+          <t>けんけん</t>
         </is>
       </c>
       <c r="B227" t="n">
@@ -72056,19 +72600,19 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>げんき</t>
+          <t>げん</t>
         </is>
       </c>
       <c r="B228" t="n">
@@ -72076,19 +72620,19 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>こう</t>
+          <t>げんき</t>
         </is>
       </c>
       <c r="B229" t="n">
@@ -72096,19 +72640,19 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>こうた</t>
+          <t>こう</t>
         </is>
       </c>
       <c r="B230" t="n">
@@ -72116,19 +72660,19 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>こてつ</t>
+          <t>こうた</t>
         </is>
       </c>
       <c r="B231" t="n">
@@ -72136,19 +72680,19 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>ことねえ</t>
+          <t>こてつ</t>
         </is>
       </c>
       <c r="B232" t="n">
@@ -72156,19 +72700,19 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>ことり</t>
+          <t>ことねえ</t>
         </is>
       </c>
       <c r="B233" t="n">
@@ -72176,19 +72720,19 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>ごん</t>
+          <t>ことり</t>
         </is>
       </c>
       <c r="B234" t="n">
@@ -72196,19 +72740,19 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>さかもと</t>
+          <t>ごん</t>
         </is>
       </c>
       <c r="B235" t="n">
@@ -72216,19 +72760,19 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>さくら</t>
+          <t>さかもと</t>
         </is>
       </c>
       <c r="B236" t="n">
@@ -72236,19 +72780,19 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>さとりゅ</t>
+          <t>さくら</t>
         </is>
       </c>
       <c r="B237" t="n">
@@ -72256,19 +72800,19 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>さな</t>
+          <t>さとりゅ</t>
         </is>
       </c>
       <c r="B238" t="n">
@@ -72276,19 +72820,19 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>さない</t>
+          <t>さな</t>
         </is>
       </c>
       <c r="B239" t="n">
@@ -72296,19 +72840,19 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>さや</t>
+          <t>さない</t>
         </is>
       </c>
       <c r="B240" t="n">
@@ -72316,19 +72860,19 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>しずか</t>
+          <t>さや</t>
         </is>
       </c>
       <c r="B241" t="n">
@@ -72336,19 +72880,19 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>しょう</t>
+          <t>しずか</t>
         </is>
       </c>
       <c r="B242" t="n">
@@ -72356,19 +72900,19 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>しょー</t>
+          <t>しょう</t>
         </is>
       </c>
       <c r="B243" t="n">
@@ -72376,19 +72920,19 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>じゅきや</t>
+          <t>しょー</t>
         </is>
       </c>
       <c r="B244" t="n">
@@ -72396,19 +72940,19 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>じん</t>
+          <t>じゅきや</t>
         </is>
       </c>
       <c r="B245" t="n">
@@ -72416,19 +72960,19 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>せいら</t>
+          <t>じん</t>
         </is>
       </c>
       <c r="B246" t="n">
@@ -72436,19 +72980,19 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>ぜっちゃん＆おっつん</t>
+          <t>せいら</t>
         </is>
       </c>
       <c r="B247" t="n">
@@ -72456,19 +73000,19 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>たいせー</t>
+          <t>ぜっちゃん＆おっつん</t>
         </is>
       </c>
       <c r="B248" t="n">
@@ -72476,19 +73020,19 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>たかし</t>
+          <t>たいせー</t>
         </is>
       </c>
       <c r="B249" t="n">
@@ -72496,19 +73040,19 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>たかち</t>
+          <t>たかし</t>
         </is>
       </c>
       <c r="B250" t="n">
@@ -72516,19 +73060,19 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>たく</t>
+          <t>たかち</t>
         </is>
       </c>
       <c r="B251" t="n">
@@ -72536,19 +73080,19 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>たけし</t>
+          <t>たく</t>
         </is>
       </c>
       <c r="B252" t="n">
@@ -72556,19 +73100,19 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>たつお</t>
+          <t>たけし</t>
         </is>
       </c>
       <c r="B253" t="n">
@@ -72576,19 +73120,19 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>たなか</t>
+          <t>たつお</t>
         </is>
       </c>
       <c r="B254" t="n">
@@ -72596,19 +73140,19 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>たます</t>
+          <t>たなか</t>
         </is>
       </c>
       <c r="B255" t="n">
@@ -72616,19 +73160,19 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>たろー</t>
+          <t>たます</t>
         </is>
       </c>
       <c r="B256" t="n">
@@ -72636,19 +73180,19 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>たー</t>
+          <t>たろー</t>
         </is>
       </c>
       <c r="B257" t="n">
@@ -72656,19 +73200,19 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>だいさく</t>
+          <t>たー</t>
         </is>
       </c>
       <c r="B258" t="n">
@@ -72676,19 +73220,19 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>だいざく</t>
+          <t>だいさく</t>
         </is>
       </c>
       <c r="B259" t="n">
@@ -72696,19 +73240,19 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>だいち</t>
+          <t>だいざく</t>
         </is>
       </c>
       <c r="B260" t="n">
@@ -72716,19 +73260,19 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>ちぇちぇ＆ガールズ</t>
+          <t>だいち</t>
         </is>
       </c>
       <c r="B261" t="n">
@@ -72736,19 +73280,19 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>ちっちてゃ</t>
+          <t>ちぇちぇ＆ガールズ</t>
         </is>
       </c>
       <c r="B262" t="n">
@@ -72756,19 +73300,19 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>ちほ</t>
+          <t>ちっちてゃ</t>
         </is>
       </c>
       <c r="B263" t="n">
@@ -72776,19 +73320,19 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>つかさ</t>
+          <t>ちほ</t>
         </is>
       </c>
       <c r="B264" t="n">
@@ -72796,19 +73340,19 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>てくのちん</t>
+          <t>つかさ</t>
         </is>
       </c>
       <c r="B265" t="n">
@@ -72816,19 +73360,19 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>てくのっち</t>
+          <t>てくのちん</t>
         </is>
       </c>
       <c r="B266" t="n">
@@ -72836,19 +73380,19 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>てっちゃん</t>
+          <t>てくのっち</t>
         </is>
       </c>
       <c r="B267" t="n">
@@ -72856,19 +73400,19 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>てつ</t>
+          <t>てっちゃん</t>
         </is>
       </c>
       <c r="B268" t="n">
@@ -72876,19 +73420,19 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>てる</t>
+          <t>てつ</t>
         </is>
       </c>
       <c r="B269" t="n">
@@ -72896,12 +73440,12 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
@@ -74808,7 +75352,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>りえ</t>
+          <t>らん</t>
         </is>
       </c>
       <c r="B365" t="n">
@@ -74816,19 +75360,19 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>りく</t>
+          <t>りえ</t>
         </is>
       </c>
       <c r="B366" t="n">
@@ -74836,19 +75380,19 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>りさ</t>
+          <t>りく</t>
         </is>
       </c>
       <c r="B367" t="n">
@@ -74856,19 +75400,19 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>りゅうくん</t>
+          <t>りさ</t>
         </is>
       </c>
       <c r="B368" t="n">
@@ -74876,19 +75420,19 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>りゅーちゃん</t>
+          <t>りゅうくん</t>
         </is>
       </c>
       <c r="B369" t="n">
@@ -74896,19 +75440,19 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>りょうが</t>
+          <t>りゅーちゃん</t>
         </is>
       </c>
       <c r="B370" t="n">
@@ -74928,7 +75472,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>りょうちゃん</t>
+          <t>りょうが</t>
         </is>
       </c>
       <c r="B371" t="n">
@@ -74936,19 +75480,19 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>りょーが</t>
+          <t>りょうちゃん</t>
         </is>
       </c>
       <c r="B372" t="n">
@@ -74956,19 +75500,19 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>りりこ</t>
+          <t>りょーが</t>
         </is>
       </c>
       <c r="B373" t="n">
@@ -74976,19 +75520,19 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>りん＆ゆち</t>
+          <t>りりこ</t>
         </is>
       </c>
       <c r="B374" t="n">
@@ -74996,19 +75540,19 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>れい</t>
+          <t>りん＆ゆち</t>
         </is>
       </c>
       <c r="B375" t="n">
@@ -75016,19 +75560,19 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>れー</t>
+          <t>れい</t>
         </is>
       </c>
       <c r="B376" t="n">
@@ -75036,19 +75580,19 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>わいちゃん</t>
+          <t>れー</t>
         </is>
       </c>
       <c r="B377" t="n">
@@ -75056,19 +75600,19 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>わんころ</t>
+          <t>わいちゃん</t>
         </is>
       </c>
       <c r="B378" t="n">
@@ -75076,19 +75620,19 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>アイ</t>
+          <t>わんころ</t>
         </is>
       </c>
       <c r="B379" t="n">
@@ -75096,19 +75640,19 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>アイちゃん</t>
+          <t>アイ</t>
         </is>
       </c>
       <c r="B380" t="n">
@@ -75116,19 +75660,19 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>アナルプリンス</t>
+          <t>アイちゃん</t>
         </is>
       </c>
       <c r="B381" t="n">
@@ -75136,19 +75680,19 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>イエモン</t>
+          <t>アナルプリンス</t>
         </is>
       </c>
       <c r="B382" t="n">
@@ -75156,19 +75700,19 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>イブオ</t>
+          <t>イエモン</t>
         </is>
       </c>
       <c r="B383" t="n">
@@ -75176,19 +75720,19 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>エーイチ</t>
+          <t>イブオ</t>
         </is>
       </c>
       <c r="B384" t="n">
@@ -75196,19 +75740,19 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>オリーブ</t>
+          <t>エーイチ</t>
         </is>
       </c>
       <c r="B385" t="n">
@@ -75216,19 +75760,19 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>オ・スー</t>
+          <t>オリーブ</t>
         </is>
       </c>
       <c r="B386" t="n">
@@ -75236,19 +75780,19 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>カイト</t>
+          <t>オ・スー</t>
         </is>
       </c>
       <c r="B387" t="n">
@@ -75256,19 +75800,19 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>カイトウ・キッド</t>
+          <t>カイト</t>
         </is>
       </c>
       <c r="B388" t="n">
@@ -75276,19 +75820,19 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>カシワ</t>
+          <t>カイトウ・キッド</t>
         </is>
       </c>
       <c r="B389" t="n">
@@ -75296,19 +75840,19 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>カナ</t>
+          <t>カシワ</t>
         </is>
       </c>
       <c r="B390" t="n">
@@ -75316,19 +75860,19 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>カネキヨ</t>
+          <t>カナ</t>
         </is>
       </c>
       <c r="B391" t="n">
@@ -75336,19 +75880,19 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>カミさん</t>
+          <t>カネキヨ</t>
         </is>
       </c>
       <c r="B392" t="n">
@@ -75356,19 +75900,19 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>カモリ</t>
+          <t>カミさん</t>
         </is>
       </c>
       <c r="B393" t="n">
@@ -75376,19 +75920,19 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>キムさん</t>
+          <t>カモリ</t>
         </is>
       </c>
       <c r="B394" t="n">
@@ -75396,19 +75940,19 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>キムとどえむちゃん</t>
+          <t>カルマ</t>
         </is>
       </c>
       <c r="B395" t="n">
@@ -75416,19 +75960,19 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>キムとまゆ</t>
+          <t>キムさん</t>
         </is>
       </c>
       <c r="B396" t="n">
@@ -75436,19 +75980,19 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>キムとドMまいまい妹</t>
+          <t>キムとどえむちゃん</t>
         </is>
       </c>
       <c r="B397" t="n">
@@ -75456,19 +76000,19 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>キムとドMむい</t>
+          <t>キムとまゆ</t>
         </is>
       </c>
       <c r="B398" t="n">
@@ -75476,19 +76020,19 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>キムとドM女R</t>
+          <t>キムとドMまいまい妹</t>
         </is>
       </c>
       <c r="B399" t="n">
@@ -75496,19 +76040,19 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>キムとローズ</t>
+          <t>キムとドMむい</t>
         </is>
       </c>
       <c r="B400" t="n">
@@ -75516,19 +76060,19 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>キムと奴隷</t>
+          <t>キムとドM女R</t>
         </is>
       </c>
       <c r="B401" t="n">
@@ -75536,19 +76080,19 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>キムと新しい奴隷ちゃん</t>
+          <t>キムとローズ</t>
         </is>
       </c>
       <c r="B402" t="n">
@@ -75556,19 +76100,19 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>キムラ</t>
+          <t>キムと奴隷</t>
         </is>
       </c>
       <c r="B403" t="n">
@@ -75576,19 +76120,19 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>キム＆みい</t>
+          <t>キムと新しい奴隷ちゃん</t>
         </is>
       </c>
       <c r="B404" t="n">
@@ -75596,19 +76140,19 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>キム＆みー</t>
+          <t>キムラ</t>
         </is>
       </c>
       <c r="B405" t="n">
@@ -75616,19 +76160,19 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>キム＆むい</t>
+          <t>キム＆みい</t>
         </is>
       </c>
       <c r="B406" t="n">
@@ -75636,19 +76180,19 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>クアレ</t>
+          <t>キム＆みー</t>
         </is>
       </c>
       <c r="B407" t="n">
@@ -75656,19 +76200,19 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>クロちゃん</t>
+          <t>キム＆むい</t>
         </is>
       </c>
       <c r="B408" t="n">
@@ -75676,19 +76220,19 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>ケケ</t>
+          <t>クアレ</t>
         </is>
       </c>
       <c r="B409" t="n">
@@ -75696,19 +76240,19 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>ゲン</t>
+          <t>クロちゃん</t>
         </is>
       </c>
       <c r="B410" t="n">
@@ -75728,7 +76272,7 @@
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>コオリ</t>
+          <t>ケケ</t>
         </is>
       </c>
       <c r="B411" t="n">
@@ -75736,19 +76280,19 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>コマ</t>
+          <t>ゲン</t>
         </is>
       </c>
       <c r="B412" t="n">
@@ -75756,19 +76300,19 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>サカモト</t>
+          <t>コオリ</t>
         </is>
       </c>
       <c r="B413" t="n">
@@ -75776,19 +76320,19 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>サクヤ</t>
+          <t>コマ</t>
         </is>
       </c>
       <c r="B414" t="n">
@@ -75796,19 +76340,19 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>サト</t>
+          <t>サカモト</t>
         </is>
       </c>
       <c r="B415" t="n">
@@ -75816,19 +76360,19 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>サトル</t>
+          <t>サクヤ</t>
         </is>
       </c>
       <c r="B416" t="n">
@@ -75836,19 +76380,19 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>ザッキー</t>
+          <t>サト</t>
         </is>
       </c>
       <c r="B417" t="n">
@@ -75856,19 +76400,19 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>シゲ</t>
+          <t>サトル</t>
         </is>
       </c>
       <c r="B418" t="n">
@@ -75876,19 +76420,19 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>シマ</t>
+          <t>ザッキー</t>
         </is>
       </c>
       <c r="B419" t="n">
@@ -75896,19 +76440,19 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>シュウ</t>
+          <t>シゲ</t>
         </is>
       </c>
       <c r="B420" t="n">
@@ -75916,19 +76460,19 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>シュン</t>
+          <t>シマ</t>
         </is>
       </c>
       <c r="B421" t="n">
@@ -75936,19 +76480,19 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-10-02</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>シュンヤ</t>
+          <t>シュウ</t>
         </is>
       </c>
       <c r="B422" t="n">
@@ -75956,19 +76500,19 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>シン</t>
+          <t>シュン</t>
         </is>
       </c>
       <c r="B423" t="n">
@@ -75976,19 +76520,19 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>シン変質者</t>
+          <t>シュンヤ</t>
         </is>
       </c>
       <c r="B424" t="n">
@@ -75996,19 +76540,19 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>ジャッキー</t>
+          <t>シン</t>
         </is>
       </c>
       <c r="B425" t="n">
@@ -76016,19 +76560,19 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>ジョーカー</t>
+          <t>シン変質者</t>
         </is>
       </c>
       <c r="B426" t="n">
@@ -76036,19 +76580,19 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>スズ</t>
+          <t>ジャッキー</t>
         </is>
       </c>
       <c r="B427" t="n">
@@ -76056,19 +76600,19 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>ソルト</t>
+          <t>ジョーカー</t>
         </is>
       </c>
       <c r="B428" t="n">
@@ -76076,19 +76620,19 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>タイガ</t>
+          <t>スズ</t>
         </is>
       </c>
       <c r="B429" t="n">
@@ -76108,7 +76652,7 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>タカス</t>
+          <t>ソルト</t>
         </is>
       </c>
       <c r="B430" t="n">
@@ -76116,19 +76660,19 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>タカ御一行</t>
+          <t>タイガ</t>
         </is>
       </c>
       <c r="B431" t="n">
@@ -76136,19 +76680,19 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>ダイキ</t>
+          <t>タカス</t>
         </is>
       </c>
       <c r="B432" t="n">
@@ -76156,19 +76700,19 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>ダイチ</t>
+          <t>タカ御一行</t>
         </is>
       </c>
       <c r="B433" t="n">
@@ -76176,19 +76720,19 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>チェスカ</t>
+          <t>ダイキ</t>
         </is>
       </c>
       <c r="B434" t="n">
@@ -76196,19 +76740,19 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>ツシマ</t>
+          <t>ダイチ</t>
         </is>
       </c>
       <c r="B435" t="n">
@@ -76216,19 +76760,19 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>ツボ</t>
+          <t>チェスカ</t>
         </is>
       </c>
       <c r="B436" t="n">
@@ -76236,19 +76780,19 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>テクノとポチ</t>
+          <t>ツシマ</t>
         </is>
       </c>
       <c r="B437" t="n">
@@ -76256,19 +76800,19 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>テクノ＆おおつか＆みこと＆もも</t>
+          <t>ツボ</t>
         </is>
       </c>
       <c r="B438" t="n">
@@ -76276,19 +76820,19 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>テクノ＆てるくん＆イブオ</t>
+          <t>テクノとポチ</t>
         </is>
       </c>
       <c r="B439" t="n">
@@ -76296,19 +76840,19 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>トニー・トニー・チョッパー</t>
+          <t>テクノ＆おおつか＆みこと＆もも</t>
         </is>
       </c>
       <c r="B440" t="n">
@@ -76316,19 +76860,19 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>トム</t>
+          <t>テクノ＆てるくん＆イブオ</t>
         </is>
       </c>
       <c r="B441" t="n">
@@ -76336,19 +76880,19 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>トルネードシャーク</t>
+          <t>トニー・トニー・チョッパー</t>
         </is>
       </c>
       <c r="B442" t="n">
@@ -76356,19 +76900,19 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>ナカヤマヤ</t>
+          <t>トム</t>
         </is>
       </c>
       <c r="B443" t="n">
@@ -76376,19 +76920,19 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>ニコチン</t>
+          <t>トルネードシャーク</t>
         </is>
       </c>
       <c r="B444" t="n">
@@ -76396,19 +76940,19 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>ニト</t>
+          <t>ナカヤマヤ</t>
         </is>
       </c>
       <c r="B445" t="n">
@@ -76416,19 +76960,19 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>ニャンまげ</t>
+          <t>ニコチン</t>
         </is>
       </c>
       <c r="B446" t="n">
@@ -76436,19 +76980,19 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>ハチ</t>
+          <t>ニト</t>
         </is>
       </c>
       <c r="B447" t="n">
@@ -76456,19 +77000,19 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>ヒロ</t>
+          <t>ニャンまげ</t>
         </is>
       </c>
       <c r="B448" t="n">
@@ -76476,19 +77020,19 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>ヒロシ</t>
+          <t>ハチ</t>
         </is>
       </c>
       <c r="B449" t="n">
@@ -76496,19 +77040,19 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>ビコー</t>
+          <t>ヒロ</t>
         </is>
       </c>
       <c r="B450" t="n">
@@ -76516,19 +77060,19 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>フジ</t>
+          <t>ヒロシ</t>
         </is>
       </c>
       <c r="B451" t="n">
@@ -76536,19 +77080,19 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>ペロとペコ</t>
+          <t>ビコー</t>
         </is>
       </c>
       <c r="B452" t="n">
@@ -76556,19 +77100,19 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>ボス</t>
+          <t>フジ</t>
         </is>
       </c>
       <c r="B453" t="n">
@@ -76576,19 +77120,19 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>ボンタ</t>
+          <t>ペロとペコ</t>
         </is>
       </c>
       <c r="B454" t="n">
@@ -76596,19 +77140,19 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>ポチ</t>
+          <t>ボス</t>
         </is>
       </c>
       <c r="B455" t="n">
@@ -76616,19 +77160,19 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>マッチョ</t>
+          <t>ボンタ</t>
         </is>
       </c>
       <c r="B456" t="n">
@@ -76648,7 +77192,7 @@
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>ミカミと仲間たち</t>
+          <t>ポチ</t>
         </is>
       </c>
       <c r="B457" t="n">
@@ -76656,19 +77200,19 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>ミスター工事マン</t>
+          <t>ポポ</t>
         </is>
       </c>
       <c r="B458" t="n">
@@ -76676,19 +77220,19 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>ミッシ</t>
+          <t>マッチョ</t>
         </is>
       </c>
       <c r="B459" t="n">
@@ -76696,19 +77240,19 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>ミッチー</t>
+          <t>ミカミと仲間たち</t>
         </is>
       </c>
       <c r="B460" t="n">
@@ -76716,19 +77260,19 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>ミルコ</t>
+          <t>ミスター工事マン</t>
         </is>
       </c>
       <c r="B461" t="n">
@@ -76736,19 +77280,19 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>ミン</t>
+          <t>ミッシ</t>
         </is>
       </c>
       <c r="B462" t="n">
@@ -76756,19 +77300,19 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>メンズ5人組</t>
+          <t>ミッチー</t>
         </is>
       </c>
       <c r="B463" t="n">
@@ -76776,19 +77320,19 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>モジャ</t>
+          <t>ミルコ</t>
         </is>
       </c>
       <c r="B464" t="n">
@@ -76796,19 +77340,19 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>ヤノ</t>
+          <t>ミン</t>
         </is>
       </c>
       <c r="B465" t="n">
@@ -76816,19 +77360,19 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>ヤノちゃん</t>
+          <t>メンズ5人組</t>
         </is>
       </c>
       <c r="B466" t="n">
@@ -76836,19 +77380,19 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>ヤマ</t>
+          <t>モジャ</t>
         </is>
       </c>
       <c r="B467" t="n">
@@ -76856,19 +77400,19 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>ユウ</t>
+          <t>ヤノ</t>
         </is>
       </c>
       <c r="B468" t="n">
@@ -76876,19 +77420,19 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>ユキ</t>
+          <t>ヤノちゃん</t>
         </is>
       </c>
       <c r="B469" t="n">
@@ -76896,19 +77440,19 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>ユッキー</t>
+          <t>ヤマ</t>
         </is>
       </c>
       <c r="B470" t="n">
@@ -76916,19 +77460,19 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>ヨシヤ</t>
+          <t>ユウ</t>
         </is>
       </c>
       <c r="B471" t="n">
@@ -76936,19 +77480,19 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>ラオ</t>
+          <t>ユキ</t>
         </is>
       </c>
       <c r="B472" t="n">
@@ -76956,19 +77500,19 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>ラ王</t>
+          <t>ユッキー</t>
         </is>
       </c>
       <c r="B473" t="n">
@@ -76976,19 +77520,19 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>リク</t>
+          <t>ヨシヤ</t>
         </is>
       </c>
       <c r="B474" t="n">
@@ -76996,19 +77540,19 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>リョウ</t>
+          <t>ラオ</t>
         </is>
       </c>
       <c r="B475" t="n">
@@ -77016,19 +77560,19 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>レオ</t>
+          <t>ラ王</t>
         </is>
       </c>
       <c r="B476" t="n">
@@ -77036,19 +77580,19 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>ロタポジ</t>
+          <t>リク</t>
         </is>
       </c>
       <c r="B477" t="n">
@@ -77056,19 +77600,19 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>ローズ</t>
+          <t>リョウ</t>
         </is>
       </c>
       <c r="B478" t="n">
@@ -77076,19 +77620,19 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>偽マイマイ</t>
+          <t>レオ</t>
         </is>
       </c>
       <c r="B479" t="n">
@@ -77096,19 +77640,19 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>僕と私</t>
+          <t>ロタポジ</t>
         </is>
       </c>
       <c r="B480" t="n">
@@ -77116,19 +77660,19 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>光一</t>
+          <t>ローズ</t>
         </is>
       </c>
       <c r="B481" t="n">
@@ -77136,19 +77680,19 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>名無し</t>
+          <t>偽マイマイ</t>
         </is>
       </c>
       <c r="B482" t="n">
@@ -77156,19 +77700,19 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>変態まっする</t>
+          <t>僕と私</t>
         </is>
       </c>
       <c r="B483" t="n">
@@ -77176,19 +77720,19 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>変態マッソー</t>
+          <t>光一</t>
         </is>
       </c>
       <c r="B484" t="n">
@@ -77196,19 +77740,19 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>天我迅</t>
+          <t>名無し</t>
         </is>
       </c>
       <c r="B485" t="n">
@@ -77216,19 +77760,19 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>女子三人衆</t>
+          <t>変態まっする</t>
         </is>
       </c>
       <c r="B486" t="n">
@@ -77236,19 +77780,19 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>彩 なまがき</t>
+          <t>変態マッソー</t>
         </is>
       </c>
       <c r="B487" t="n">
@@ -77256,19 +77800,19 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>正装しん</t>
+          <t>天我迅</t>
         </is>
       </c>
       <c r="B488" t="n">
@@ -77276,19 +77820,19 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>海砂利水魚</t>
+          <t>女子三人衆</t>
         </is>
       </c>
       <c r="B489" t="n">
@@ -77296,19 +77840,19 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>田中</t>
+          <t>彩 なまがき</t>
         </is>
       </c>
       <c r="B490" t="n">
@@ -77316,19 +77860,19 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>番</t>
+          <t>正装しん</t>
         </is>
       </c>
       <c r="B491" t="n">
@@ -77336,19 +77880,19 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>碧咲</t>
+          <t>海砂利水魚</t>
         </is>
       </c>
       <c r="B492" t="n">
@@ -77356,19 +77900,19 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>福ちゃん</t>
+          <t>田中</t>
         </is>
       </c>
       <c r="B493" t="n">
@@ -77376,19 +77920,19 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>絶</t>
+          <t>番</t>
         </is>
       </c>
       <c r="B494" t="n">
@@ -77396,19 +77940,19 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>絶ちゃん</t>
+          <t>碧咲</t>
         </is>
       </c>
       <c r="B495" t="n">
@@ -77416,19 +77960,19 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>美優</t>
+          <t>福ちゃん</t>
         </is>
       </c>
       <c r="B496" t="n">
@@ -77436,19 +77980,19 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>赤ちゃん</t>
+          <t>絶</t>
         </is>
       </c>
       <c r="B497" t="n">
@@ -77456,19 +78000,19 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>赤井ヱビス</t>
+          <t>絶ちゃん</t>
         </is>
       </c>
       <c r="B498" t="n">
@@ -77476,19 +78020,19 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>部長</t>
+          <t>美優</t>
         </is>
       </c>
       <c r="B499" t="n">
@@ -77496,30 +78040,90 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
+          <t>赤ちゃん</t>
+        </is>
+      </c>
+      <c r="B500" t="n">
+        <v>1</v>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>赤井ヱビス</t>
+        </is>
+      </c>
+      <c r="B501" t="n">
+        <v>1</v>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>部長</t>
+        </is>
+      </c>
+      <c r="B502" t="n">
+        <v>1</v>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
           <t>雅-miyabi-/とも</t>
         </is>
       </c>
-      <c r="B500" t="n">
-        <v>1</v>
-      </c>
-      <c r="C500" t="inlineStr">
+      <c r="B503" t="n">
+        <v>1</v>
+      </c>
+      <c r="C503" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="D500" t="inlineStr">
+      <c r="D503" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -77563,10 +78167,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C2" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3">
@@ -77641,10 +78245,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C8" t="n">
-        <v>167</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -77685,10 +78289,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C2" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3">
@@ -77711,10 +78315,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C4" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
@@ -77919,10 +78523,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C20" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21">
@@ -77932,10 +78536,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C21" t="n">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="22">
@@ -77958,10 +78562,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C23" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="24">
@@ -78065,13 +78669,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C4" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D4" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -78085,7 +78689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C215"/>
+  <dimension ref="A1:C218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -81003,12 +81607,12 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>りく</t>
+          <t>らん</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>りん</t>
+          <t>カルマ</t>
         </is>
       </c>
       <c r="C195" t="n">
@@ -81018,12 +81622,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>アキ</t>
+          <t>らん</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>コオリ</t>
+          <t>ポポ</t>
         </is>
       </c>
       <c r="C196" t="n">
@@ -81033,12 +81637,12 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>オカニー</t>
+          <t>りく</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>ダイキ</t>
+          <t>りん</t>
         </is>
       </c>
       <c r="C197" t="n">
@@ -81048,12 +81652,12 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>オカニー</t>
+          <t>アキ</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>ミッシ</t>
+          <t>コオリ</t>
         </is>
       </c>
       <c r="C198" t="n">
@@ -81063,12 +81667,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>カズ</t>
+          <t>オカニー</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>シン</t>
+          <t>ダイキ</t>
         </is>
       </c>
       <c r="C199" t="n">
@@ -81078,12 +81682,12 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>キム</t>
+          <t>オカニー</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>偽マイマイ</t>
+          <t>ミッシ</t>
         </is>
       </c>
       <c r="C200" t="n">
@@ -81093,12 +81697,12 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>キムラ</t>
+          <t>カズ</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>キング</t>
+          <t>シン</t>
         </is>
       </c>
       <c r="C201" t="n">
@@ -81108,12 +81712,12 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>クロちゃん</t>
+          <t>カルマ</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>ポチ</t>
+          <t>ポポ</t>
         </is>
       </c>
       <c r="C202" t="n">
@@ -81123,12 +81727,12 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>ケン</t>
+          <t>キム</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>ツボ</t>
+          <t>偽マイマイ</t>
         </is>
       </c>
       <c r="C203" t="n">
@@ -81138,12 +81742,12 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>ゲン</t>
+          <t>キムラ</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>シゲ</t>
+          <t>キング</t>
         </is>
       </c>
       <c r="C204" t="n">
@@ -81153,12 +81757,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>コテッチャン</t>
+          <t>クロちゃん</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>サト</t>
+          <t>ポチ</t>
         </is>
       </c>
       <c r="C205" t="n">
@@ -81168,12 +81772,12 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>サカモト</t>
+          <t>ケン</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>部長</t>
+          <t>ツボ</t>
         </is>
       </c>
       <c r="C206" t="n">
@@ -81183,12 +81787,12 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>シュウ</t>
+          <t>ゲン</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>タイガ</t>
+          <t>シゲ</t>
         </is>
       </c>
       <c r="C207" t="n">
@@ -81198,12 +81802,12 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>シン</t>
+          <t>コテッチャン</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>ダイゴ</t>
+          <t>サト</t>
         </is>
       </c>
       <c r="C208" t="n">
@@ -81213,12 +81817,12 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>ソルト</t>
+          <t>サカモト</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>トム</t>
+          <t>部長</t>
         </is>
       </c>
       <c r="C209" t="n">
@@ -81228,12 +81832,12 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>タカ</t>
+          <t>シュウ</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>タク</t>
+          <t>タイガ</t>
         </is>
       </c>
       <c r="C210" t="n">
@@ -81243,12 +81847,12 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>タカス</t>
+          <t>シン</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>マサ</t>
+          <t>ダイゴ</t>
         </is>
       </c>
       <c r="C211" t="n">
@@ -81258,12 +81862,12 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>タク</t>
+          <t>ソルト</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>リョウ</t>
+          <t>トム</t>
         </is>
       </c>
       <c r="C212" t="n">
@@ -81273,12 +81877,12 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>ダイキ</t>
+          <t>タカ</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>ミッシ</t>
+          <t>タク</t>
         </is>
       </c>
       <c r="C213" t="n">
@@ -81288,12 +81892,12 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>テクノ</t>
+          <t>タカス</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>ミコト</t>
+          <t>マサ</t>
         </is>
       </c>
       <c r="C214" t="n">
@@ -81303,15 +81907,60 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
+          <t>タク</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>リョウ</t>
+        </is>
+      </c>
+      <c r="C215" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>ダイキ</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>ミッシ</t>
+        </is>
+      </c>
+      <c r="C216" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>テクノ</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>ミコト</t>
+        </is>
+      </c>
+      <c r="C217" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
           <t>天我迅</t>
         </is>
       </c>
-      <c r="B215" t="inlineStr">
+      <c r="B218" t="inlineStr">
         <is>
           <t>美優</t>
         </is>
       </c>
-      <c r="C215" t="n">
+      <c r="C218" t="n">
         <v>1</v>
       </c>
     </row>

--- a/bbs_log.xlsx
+++ b/bbs_log.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H828"/>
+  <dimension ref="A1:H836"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26304,7 +26304,6 @@
           <t>ゆずき</t>
         </is>
       </c>
-      <c r="E822" t="inlineStr"/>
       <c r="F822" t="inlineStr">
         <is>
           <t>おーぷんまえに</t>
@@ -26315,7 +26314,6 @@
           <t>きました！</t>
         </is>
       </c>
-      <c r="H822" t="inlineStr"/>
     </row>
     <row r="823">
       <c r="A823" t="n">
@@ -26336,7 +26334,6 @@
           <t>ひがんたん</t>
         </is>
       </c>
-      <c r="E823" t="inlineStr"/>
       <c r="F823" t="inlineStr">
         <is>
           <t>今日は</t>
@@ -26347,7 +26344,6 @@
           <t>クールに</t>
         </is>
       </c>
-      <c r="H823" t="inlineStr"/>
     </row>
     <row r="824">
       <c r="A824" t="n">
@@ -26368,7 +26364,6 @@
           <t>らん、カルマ、ポポ</t>
         </is>
       </c>
-      <c r="E824" t="inlineStr"/>
       <c r="F824" t="inlineStr">
         <is>
           <t>久しぶり＆新規連れて</t>
@@ -26379,7 +26374,6 @@
           <t>来ました</t>
         </is>
       </c>
-      <c r="H824" t="inlineStr"/>
     </row>
     <row r="825">
       <c r="A825" t="n">
@@ -26400,7 +26394,6 @@
           <t>てる</t>
         </is>
       </c>
-      <c r="E825" t="inlineStr"/>
       <c r="F825" t="inlineStr">
         <is>
           <t>今</t>
@@ -26411,7 +26404,6 @@
           <t>きたよー</t>
         </is>
       </c>
-      <c r="H825" t="inlineStr"/>
     </row>
     <row r="826">
       <c r="A826" t="n">
@@ -26432,7 +26424,6 @@
           <t>さとるん</t>
         </is>
       </c>
-      <c r="E826" t="inlineStr"/>
       <c r="F826" t="inlineStr">
         <is>
           <t>久々</t>
@@ -26443,7 +26434,6 @@
           <t>日曜日に</t>
         </is>
       </c>
-      <c r="H826" t="inlineStr"/>
     </row>
     <row r="827">
       <c r="A827" t="n">
@@ -26464,7 +26454,6 @@
           <t>まいまい</t>
         </is>
       </c>
-      <c r="E827" t="inlineStr"/>
       <c r="F827" t="inlineStr">
         <is>
           <t>今</t>
@@ -26475,7 +26464,6 @@
           <t>きたんご</t>
         </is>
       </c>
-      <c r="H827" t="inlineStr"/>
     </row>
     <row r="828">
       <c r="A828" t="n">
@@ -26529,6 +26517,283 @@
         </is>
       </c>
     </row>
+    <row r="829">
+      <c r="A829" t="n">
+        <v>28407</v>
+      </c>
+      <c r="B829" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>12:41:45</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>たかの</t>
+        </is>
+      </c>
+      <c r="E829" t="inlineStr"/>
+      <c r="F829" t="inlineStr">
+        <is>
+          <t>初めて</t>
+        </is>
+      </c>
+      <c r="G829" t="inlineStr">
+        <is>
+          <t>明日、行こうかと。
+初めましてなので、緊張。</t>
+        </is>
+      </c>
+      <c r="H829" t="inlineStr"/>
+    </row>
+    <row r="830">
+      <c r="A830" t="n">
+        <v>28409</v>
+      </c>
+      <c r="B830" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>19:37:04</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>ろくじ</t>
+        </is>
+      </c>
+      <c r="E830" t="inlineStr"/>
+      <c r="F830" t="inlineStr">
+        <is>
+          <t>本日も</t>
+        </is>
+      </c>
+      <c r="G830" t="inlineStr">
+        <is>
+          <t>マゾ活に来た</t>
+        </is>
+      </c>
+      <c r="H830" t="inlineStr"/>
+    </row>
+    <row r="831">
+      <c r="A831" t="n">
+        <v>28411</v>
+      </c>
+      <c r="B831" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>20:30:03</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>カズ</t>
+        </is>
+      </c>
+      <c r="E831" t="inlineStr"/>
+      <c r="F831" t="inlineStr">
+        <is>
+          <t>北海道から</t>
+        </is>
+      </c>
+      <c r="G831" t="inlineStr">
+        <is>
+          <t>初めて来ました</t>
+        </is>
+      </c>
+      <c r="H831" t="inlineStr"/>
+    </row>
+    <row r="832">
+      <c r="A832" t="n">
+        <v>28413</v>
+      </c>
+      <c r="B832" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>21:07:47</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>ひがん</t>
+        </is>
+      </c>
+      <c r="E832" t="inlineStr"/>
+      <c r="F832" t="inlineStr">
+        <is>
+          <t>遊びに</t>
+        </is>
+      </c>
+      <c r="G832" t="inlineStr">
+        <is>
+          <t>きたよー♪</t>
+        </is>
+      </c>
+      <c r="H832" t="inlineStr"/>
+    </row>
+    <row r="833">
+      <c r="A833" t="n">
+        <v>28415</v>
+      </c>
+      <c r="B833" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C833" t="inlineStr">
+        <is>
+          <t>21:35:43</t>
+        </is>
+      </c>
+      <c r="D833" t="inlineStr">
+        <is>
+          <t>かなちゃん＆おっつん</t>
+        </is>
+      </c>
+      <c r="E833" t="inlineStr"/>
+      <c r="F833" t="inlineStr">
+        <is>
+          <t>ちょっと</t>
+        </is>
+      </c>
+      <c r="G833" t="inlineStr">
+        <is>
+          <t>遊びキタ！</t>
+        </is>
+      </c>
+      <c r="H833" t="inlineStr"/>
+    </row>
+    <row r="834">
+      <c r="A834" t="n">
+        <v>28417</v>
+      </c>
+      <c r="B834" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C834" t="inlineStr">
+        <is>
+          <t>22:55:42</t>
+        </is>
+      </c>
+      <c r="D834" t="inlineStr">
+        <is>
+          <t>コテッチャン</t>
+        </is>
+      </c>
+      <c r="E834" t="inlineStr"/>
+      <c r="F834" t="inlineStr">
+        <is>
+          <t>少し</t>
+        </is>
+      </c>
+      <c r="G834" t="inlineStr">
+        <is>
+          <t>来ました</t>
+        </is>
+      </c>
+      <c r="H834" t="inlineStr"/>
+    </row>
+    <row r="835">
+      <c r="A835" t="n">
+        <v>28419</v>
+      </c>
+      <c r="B835" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="C835" t="inlineStr">
+        <is>
+          <t>23:40:54</t>
+        </is>
+      </c>
+      <c r="D835" t="inlineStr">
+        <is>
+          <t>ケン</t>
+        </is>
+      </c>
+      <c r="E835" t="inlineStr"/>
+      <c r="F835" t="inlineStr">
+        <is>
+          <t>初めてです</t>
+        </is>
+      </c>
+      <c r="G835" t="inlineStr">
+        <is>
+          <t>来てみました！</t>
+        </is>
+      </c>
+      <c r="H835" t="inlineStr"/>
+    </row>
+    <row r="836">
+      <c r="A836" t="n">
+        <v>28421</v>
+      </c>
+      <c r="B836" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="C836" t="inlineStr">
+        <is>
+          <t>04:08:13</t>
+        </is>
+      </c>
+      <c r="D836" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E836" t="inlineStr">
+        <is>
+          <t>欲求不満のポコチンハンター　える</t>
+        </is>
+      </c>
+      <c r="F836" t="inlineStr">
+        <is>
+          <t>★☆★朝までアゲアゲの火曜日営業が始まるわよ♪★☆★</t>
+        </is>
+      </c>
+      <c r="G836" t="inlineStr">
+        <is>
+          <t>本日10月6日の営業時間は♪
+オープン19:00！ラスト5:00なのよ☆
+担当は
+欲求不満のポコチンハンター　える
+なのよ♪
+どんな季節でも★BAMBITCH★は色気ムンムンで暑すぎる♪
+バンビッチでおもいっきりはじけちゃって（笑）
+精力は無くても性欲がある！？
+大人の憩いと禁断サークル盛りだくさん！
+憩いと交流の魔性の遊び場バンビッチは素敵な出会いを 提供いたします（笑)☆☆
+おつまみ等の持ち込みは自由なのでみんなで持ち寄ってお近づきのきっかけにどうぞ♪
+強制や無理強いは一切ございませんので楽しく遊びましょう♪
+宇都宮市宿郷1−12−9　カサブランカビル5F</t>
+        </is>
+      </c>
+      <c r="H836" t="inlineStr">
+        <is>
+          <t>img20261006040813.jpg</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -26540,7 +26805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I965"/>
+  <dimension ref="A1:I972"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68050,6 +68315,308 @@
       <c r="I965" t="inlineStr">
         <is>
           <t>きたんご</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>12:41:45</t>
+        </is>
+      </c>
+      <c r="D966" t="n">
+        <v>28407</v>
+      </c>
+      <c r="E966" t="inlineStr">
+        <is>
+          <t>たかの</t>
+        </is>
+      </c>
+      <c r="F966" t="n">
+        <v>1</v>
+      </c>
+      <c r="G966" t="inlineStr">
+        <is>
+          <t>たかの</t>
+        </is>
+      </c>
+      <c r="H966" t="inlineStr">
+        <is>
+          <t>初めて</t>
+        </is>
+      </c>
+      <c r="I966" t="inlineStr">
+        <is>
+          <t>明日、行こうかと。
+初めましてなので、緊張。</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>19:37:04</t>
+        </is>
+      </c>
+      <c r="D967" t="n">
+        <v>28409</v>
+      </c>
+      <c r="E967" t="inlineStr">
+        <is>
+          <t>ろくじ</t>
+        </is>
+      </c>
+      <c r="F967" t="n">
+        <v>7</v>
+      </c>
+      <c r="G967" t="inlineStr">
+        <is>
+          <t>ろくじ</t>
+        </is>
+      </c>
+      <c r="H967" t="inlineStr">
+        <is>
+          <t>本日も</t>
+        </is>
+      </c>
+      <c r="I967" t="inlineStr">
+        <is>
+          <t>マゾ活に来た</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>20:30:03</t>
+        </is>
+      </c>
+      <c r="D968" t="n">
+        <v>28411</v>
+      </c>
+      <c r="E968" t="inlineStr">
+        <is>
+          <t>カズ</t>
+        </is>
+      </c>
+      <c r="F968" t="n">
+        <v>7</v>
+      </c>
+      <c r="G968" t="inlineStr">
+        <is>
+          <t>カズ</t>
+        </is>
+      </c>
+      <c r="H968" t="inlineStr">
+        <is>
+          <t>北海道から</t>
+        </is>
+      </c>
+      <c r="I968" t="inlineStr">
+        <is>
+          <t>初めて来ました</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>21:07:47</t>
+        </is>
+      </c>
+      <c r="D969" t="n">
+        <v>28413</v>
+      </c>
+      <c r="E969" t="inlineStr">
+        <is>
+          <t>ひがん</t>
+        </is>
+      </c>
+      <c r="F969" t="n">
+        <v>30</v>
+      </c>
+      <c r="G969" t="inlineStr">
+        <is>
+          <t>ひがん</t>
+        </is>
+      </c>
+      <c r="H969" t="inlineStr">
+        <is>
+          <t>遊びに</t>
+        </is>
+      </c>
+      <c r="I969" t="inlineStr">
+        <is>
+          <t>きたよー♪</t>
+        </is>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>21:35:43</t>
+        </is>
+      </c>
+      <c r="D970" t="n">
+        <v>28415</v>
+      </c>
+      <c r="E970" t="inlineStr">
+        <is>
+          <t>かなちゃん＆おっつん</t>
+        </is>
+      </c>
+      <c r="F970" t="n">
+        <v>1</v>
+      </c>
+      <c r="G970" t="inlineStr">
+        <is>
+          <t>かなちゃん＆おっつん</t>
+        </is>
+      </c>
+      <c r="H970" t="inlineStr">
+        <is>
+          <t>ちょっと</t>
+        </is>
+      </c>
+      <c r="I970" t="inlineStr">
+        <is>
+          <t>遊びキタ！</t>
+        </is>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>22:55:42</t>
+        </is>
+      </c>
+      <c r="D971" t="n">
+        <v>28417</v>
+      </c>
+      <c r="E971" t="inlineStr">
+        <is>
+          <t>コテッチャン</t>
+        </is>
+      </c>
+      <c r="F971" t="n">
+        <v>6</v>
+      </c>
+      <c r="G971" t="inlineStr">
+        <is>
+          <t>コテッチャン</t>
+        </is>
+      </c>
+      <c r="H971" t="inlineStr">
+        <is>
+          <t>少し</t>
+        </is>
+      </c>
+      <c r="I971" t="inlineStr">
+        <is>
+          <t>来ました</t>
+        </is>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>23:40:54</t>
+        </is>
+      </c>
+      <c r="D972" t="n">
+        <v>28419</v>
+      </c>
+      <c r="E972" t="inlineStr">
+        <is>
+          <t>ケン</t>
+        </is>
+      </c>
+      <c r="F972" t="n">
+        <v>4</v>
+      </c>
+      <c r="G972" t="inlineStr">
+        <is>
+          <t>ケン</t>
+        </is>
+      </c>
+      <c r="H972" t="inlineStr">
+        <is>
+          <t>初めてです</t>
+        </is>
+      </c>
+      <c r="I972" t="inlineStr">
+        <is>
+          <t>来てみました！</t>
         </is>
       </c>
     </row>
@@ -68064,7 +68631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D503"/>
+  <dimension ref="A1:D505"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -68096,7 +68663,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -68105,7 +68672,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
@@ -68432,31 +68999,31 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>ろくじ</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TKC</t>
+          <t>カズ</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -68465,14 +69032,14 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>かず</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -68480,19 +69047,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>かな</t>
+          <t>TKC</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -68500,19 +69067,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ふくちゃん</t>
+          <t>かず</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -68520,19 +69087,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ろくじ</t>
+          <t>かな</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -68540,19 +69107,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>カズ</t>
+          <t>ふくちゃん</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -68560,39 +69127,39 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>コテッチャン</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>K</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -68600,7 +69167,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -68612,7 +69179,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>bee</t>
+          <t>N</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -68620,19 +69187,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>あいちゃん</t>
+          <t>bee</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -68640,19 +69207,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>こてっちゃん</t>
+          <t>あいちゃん</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -68660,19 +69227,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>しん</t>
+          <t>こてっちゃん</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -68680,19 +69247,19 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>たかやまん</t>
+          <t>しん</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -68700,19 +69267,19 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ひがんたん</t>
+          <t>たかやまん</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -68720,19 +69287,19 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ふくてゃ</t>
+          <t>ひがんたん</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -68740,19 +69307,19 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>べー</t>
+          <t>ふくてゃ</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -68760,19 +69327,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>まいなす</t>
+          <t>べー</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -68780,19 +69347,19 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ましゅ社長</t>
+          <t>まいなす</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -68800,19 +69367,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
           <t>2026-09-12</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>よしやん</t>
+          <t>ましゅ社長</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -68820,19 +69387,19 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>りん</t>
+          <t>よしやん</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -68840,19 +69407,19 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-10-02</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>キム</t>
+          <t>りん</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -68865,14 +69432,14 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>コテッチャン</t>
+          <t>キム</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -68880,12 +69447,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
@@ -69232,7 +69799,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>マロ</t>
+          <t>ケン</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -69240,23 +69807,23 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>H</t>
+          <t>マロ</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -69265,14 +69832,14 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>H</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -69280,19 +69847,19 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>R</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -69300,19 +69867,19 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>S</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -69320,19 +69887,19 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>T山</t>
+          <t>T</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -69340,19 +69907,19 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>−</t>
+          <t>T山</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -69365,14 +69932,14 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>あや</t>
+          <t>−</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -69380,19 +69947,19 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>えぬ</t>
+          <t>あや</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -69400,19 +69967,19 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>おでで</t>
+          <t>えぬ</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -69420,19 +69987,19 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>さと</t>
+          <t>おでで</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -69445,14 +70012,14 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>さとるん</t>
+          <t>さと</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -69465,14 +70032,14 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>すー</t>
+          <t>さとるん</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -69480,19 +70047,19 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>すーさん</t>
+          <t>すー</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -69500,19 +70067,19 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>すーたく</t>
+          <t>すーさん</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -69520,19 +70087,19 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>たけ</t>
+          <t>すーたく</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -69540,19 +70107,19 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>たつや</t>
+          <t>たけ</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -69560,19 +70127,19 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-02</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>だいご</t>
+          <t>たつや</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -69585,14 +70152,14 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>なな</t>
+          <t>だいご</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -69600,19 +70167,19 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>なまがき</t>
+          <t>なな</t>
         </is>
       </c>
       <c r="B78" t="n">
@@ -69620,19 +70187,19 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ひがんちゃん</t>
+          <t>なまがき</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -69640,19 +70207,19 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ぽちゃりす組</t>
+          <t>ひがんちゃん</t>
         </is>
       </c>
       <c r="B80" t="n">
@@ -69660,19 +70227,19 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>まゆ</t>
+          <t>ぽちゃりす組</t>
         </is>
       </c>
       <c r="B81" t="n">
@@ -69680,19 +70247,19 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>まろ</t>
+          <t>まゆ</t>
         </is>
       </c>
       <c r="B82" t="n">
@@ -69700,19 +70267,19 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>もっぷ</t>
+          <t>まろ</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -69720,19 +70287,19 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>りゅう</t>
+          <t>もっぷ</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -69740,19 +70307,19 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>れいら</t>
+          <t>りゅう</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -69760,19 +70327,19 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>カズヤ</t>
+          <t>れいら</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -69780,19 +70347,19 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>カー</t>
+          <t>カズヤ</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -69800,19 +70367,19 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>キムとドMみい</t>
+          <t>カー</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -69820,19 +70387,19 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ケン</t>
+          <t>キムとドMみい</t>
         </is>
       </c>
       <c r="B89" t="n">
@@ -69840,12 +70407,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -72292,7 +72859,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>がん</t>
+          <t>かなちゃん＆おっつん</t>
         </is>
       </c>
       <c r="B212" t="n">
@@ -72300,19 +72867,19 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>きむさん</t>
+          <t>がん</t>
         </is>
       </c>
       <c r="B213" t="n">
@@ -72320,19 +72887,19 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>きむむ</t>
+          <t>きむさん</t>
         </is>
       </c>
       <c r="B214" t="n">
@@ -72340,19 +72907,19 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>きむら</t>
+          <t>きむむ</t>
         </is>
       </c>
       <c r="B215" t="n">
@@ -72360,19 +72927,19 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>きょうちゃん</t>
+          <t>きむら</t>
         </is>
       </c>
       <c r="B216" t="n">
@@ -72380,19 +72947,19 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>きんたまよ</t>
+          <t>きょうちゃん</t>
         </is>
       </c>
       <c r="B217" t="n">
@@ -72400,19 +72967,19 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>くっぱ</t>
+          <t>きんたまよ</t>
         </is>
       </c>
       <c r="B218" t="n">
@@ -72420,19 +72987,19 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>くま</t>
+          <t>くっぱ</t>
         </is>
       </c>
       <c r="B219" t="n">
@@ -72440,19 +73007,19 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>くり</t>
+          <t>くま</t>
         </is>
       </c>
       <c r="B220" t="n">
@@ -72460,19 +73027,19 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>くろちゃん</t>
+          <t>くり</t>
         </is>
       </c>
       <c r="B221" t="n">
@@ -72480,19 +73047,19 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>ぐっちゃん</t>
+          <t>くろちゃん</t>
         </is>
       </c>
       <c r="B222" t="n">
@@ -72500,19 +73067,19 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>ぐっちゃん（チャイマフィ）</t>
+          <t>ぐっちゃん</t>
         </is>
       </c>
       <c r="B223" t="n">
@@ -72520,19 +73087,19 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>けい</t>
+          <t>ぐっちゃん（チャイマフィ）</t>
         </is>
       </c>
       <c r="B224" t="n">
@@ -72540,19 +73107,19 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>けいご</t>
+          <t>けい</t>
         </is>
       </c>
       <c r="B225" t="n">
@@ -72560,19 +73127,19 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>けいちゃん</t>
+          <t>けいご</t>
         </is>
       </c>
       <c r="B226" t="n">
@@ -72580,19 +73147,19 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>けんけん</t>
+          <t>けいちゃん</t>
         </is>
       </c>
       <c r="B227" t="n">
@@ -72600,19 +73167,19 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>げん</t>
+          <t>けんけん</t>
         </is>
       </c>
       <c r="B228" t="n">
@@ -72620,19 +73187,19 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>げんき</t>
+          <t>げん</t>
         </is>
       </c>
       <c r="B229" t="n">
@@ -72640,19 +73207,19 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>こう</t>
+          <t>げんき</t>
         </is>
       </c>
       <c r="B230" t="n">
@@ -72660,19 +73227,19 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>こうた</t>
+          <t>こう</t>
         </is>
       </c>
       <c r="B231" t="n">
@@ -72680,19 +73247,19 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>こてつ</t>
+          <t>こうた</t>
         </is>
       </c>
       <c r="B232" t="n">
@@ -72700,19 +73267,19 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>ことねえ</t>
+          <t>こてつ</t>
         </is>
       </c>
       <c r="B233" t="n">
@@ -72720,19 +73287,19 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>ことり</t>
+          <t>ことねえ</t>
         </is>
       </c>
       <c r="B234" t="n">
@@ -72740,19 +73307,19 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>ごん</t>
+          <t>ことり</t>
         </is>
       </c>
       <c r="B235" t="n">
@@ -72760,19 +73327,19 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>さかもと</t>
+          <t>ごん</t>
         </is>
       </c>
       <c r="B236" t="n">
@@ -72780,19 +73347,19 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>さくら</t>
+          <t>さかもと</t>
         </is>
       </c>
       <c r="B237" t="n">
@@ -72800,19 +73367,19 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>さとりゅ</t>
+          <t>さくら</t>
         </is>
       </c>
       <c r="B238" t="n">
@@ -72820,19 +73387,19 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>さな</t>
+          <t>さとりゅ</t>
         </is>
       </c>
       <c r="B239" t="n">
@@ -72840,19 +73407,19 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>さない</t>
+          <t>さな</t>
         </is>
       </c>
       <c r="B240" t="n">
@@ -72860,19 +73427,19 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>さや</t>
+          <t>さない</t>
         </is>
       </c>
       <c r="B241" t="n">
@@ -72880,19 +73447,19 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>しずか</t>
+          <t>さや</t>
         </is>
       </c>
       <c r="B242" t="n">
@@ -72900,19 +73467,19 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>しょう</t>
+          <t>しずか</t>
         </is>
       </c>
       <c r="B243" t="n">
@@ -72920,19 +73487,19 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>しょー</t>
+          <t>しょう</t>
         </is>
       </c>
       <c r="B244" t="n">
@@ -72940,19 +73507,19 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>じゅきや</t>
+          <t>しょー</t>
         </is>
       </c>
       <c r="B245" t="n">
@@ -72960,19 +73527,19 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>じん</t>
+          <t>じゅきや</t>
         </is>
       </c>
       <c r="B246" t="n">
@@ -72980,19 +73547,19 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>せいら</t>
+          <t>じん</t>
         </is>
       </c>
       <c r="B247" t="n">
@@ -73000,19 +73567,19 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>ぜっちゃん＆おっつん</t>
+          <t>せいら</t>
         </is>
       </c>
       <c r="B248" t="n">
@@ -73020,19 +73587,19 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>たいせー</t>
+          <t>ぜっちゃん＆おっつん</t>
         </is>
       </c>
       <c r="B249" t="n">
@@ -73040,19 +73607,19 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>たかし</t>
+          <t>たいせー</t>
         </is>
       </c>
       <c r="B250" t="n">
@@ -73060,19 +73627,19 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>たかち</t>
+          <t>たかし</t>
         </is>
       </c>
       <c r="B251" t="n">
@@ -73080,19 +73647,19 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>たく</t>
+          <t>たかち</t>
         </is>
       </c>
       <c r="B252" t="n">
@@ -73100,19 +73667,19 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>たけし</t>
+          <t>たかの</t>
         </is>
       </c>
       <c r="B253" t="n">
@@ -73120,19 +73687,19 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>たつお</t>
+          <t>たく</t>
         </is>
       </c>
       <c r="B254" t="n">
@@ -73140,19 +73707,19 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>たなか</t>
+          <t>たけし</t>
         </is>
       </c>
       <c r="B255" t="n">
@@ -73160,19 +73727,19 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>たます</t>
+          <t>たつお</t>
         </is>
       </c>
       <c r="B256" t="n">
@@ -73180,19 +73747,19 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>たろー</t>
+          <t>たなか</t>
         </is>
       </c>
       <c r="B257" t="n">
@@ -73200,19 +73767,19 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>たー</t>
+          <t>たます</t>
         </is>
       </c>
       <c r="B258" t="n">
@@ -73220,19 +73787,19 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>だいさく</t>
+          <t>たろー</t>
         </is>
       </c>
       <c r="B259" t="n">
@@ -73240,19 +73807,19 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>だいざく</t>
+          <t>たー</t>
         </is>
       </c>
       <c r="B260" t="n">
@@ -73260,19 +73827,19 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>だいち</t>
+          <t>だいさく</t>
         </is>
       </c>
       <c r="B261" t="n">
@@ -73280,19 +73847,19 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>ちぇちぇ＆ガールズ</t>
+          <t>だいざく</t>
         </is>
       </c>
       <c r="B262" t="n">
@@ -73300,19 +73867,19 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>ちっちてゃ</t>
+          <t>だいち</t>
         </is>
       </c>
       <c r="B263" t="n">
@@ -73320,19 +73887,19 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>ちほ</t>
+          <t>ちぇちぇ＆ガールズ</t>
         </is>
       </c>
       <c r="B264" t="n">
@@ -73340,19 +73907,19 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>つかさ</t>
+          <t>ちっちてゃ</t>
         </is>
       </c>
       <c r="B265" t="n">
@@ -73360,19 +73927,19 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>てくのちん</t>
+          <t>ちほ</t>
         </is>
       </c>
       <c r="B266" t="n">
@@ -73380,19 +73947,19 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>てくのっち</t>
+          <t>つかさ</t>
         </is>
       </c>
       <c r="B267" t="n">
@@ -73400,19 +73967,19 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>てっちゃん</t>
+          <t>てくのちん</t>
         </is>
       </c>
       <c r="B268" t="n">
@@ -73420,19 +73987,19 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>てつ</t>
+          <t>てくのっち</t>
         </is>
       </c>
       <c r="B269" t="n">
@@ -73440,19 +74007,19 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>でかかわ</t>
+          <t>てっちゃん</t>
         </is>
       </c>
       <c r="B270" t="n">
@@ -73460,19 +74027,19 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>ででたゃ</t>
+          <t>てつ</t>
         </is>
       </c>
       <c r="B271" t="n">
@@ -73480,19 +74047,19 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>とおちゃん</t>
+          <t>でかかわ</t>
         </is>
       </c>
       <c r="B272" t="n">
@@ -73500,19 +74067,19 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>とっしー</t>
+          <t>ででたゃ</t>
         </is>
       </c>
       <c r="B273" t="n">
@@ -73520,19 +74087,19 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>とも</t>
+          <t>とおちゃん</t>
         </is>
       </c>
       <c r="B274" t="n">
@@ -73540,19 +74107,19 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>ともち</t>
+          <t>とっしー</t>
         </is>
       </c>
       <c r="B275" t="n">
@@ -73560,19 +74127,19 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>ともひろ</t>
+          <t>とも</t>
         </is>
       </c>
       <c r="B276" t="n">
@@ -73580,19 +74147,19 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>ともや</t>
+          <t>ともち</t>
         </is>
       </c>
       <c r="B277" t="n">
@@ -73600,19 +74167,19 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>ともゆき</t>
+          <t>ともひろ</t>
         </is>
       </c>
       <c r="B278" t="n">
@@ -73620,19 +74187,19 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>とーり</t>
+          <t>ともや</t>
         </is>
       </c>
       <c r="B279" t="n">
@@ -73640,19 +74207,19 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>どえむちゃん</t>
+          <t>ともゆき</t>
         </is>
       </c>
       <c r="B280" t="n">
@@ -73660,19 +74227,19 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>ながとも</t>
+          <t>とーり</t>
         </is>
       </c>
       <c r="B281" t="n">
@@ -73680,19 +74247,19 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>なっちゃん</t>
+          <t>どえむちゃん</t>
         </is>
       </c>
       <c r="B282" t="n">
@@ -73700,19 +74267,19 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>なべ</t>
+          <t>ながとも</t>
         </is>
       </c>
       <c r="B283" t="n">
@@ -73720,19 +74287,19 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>にゃんまげ</t>
+          <t>なっちゃん</t>
         </is>
       </c>
       <c r="B284" t="n">
@@ -73740,19 +74307,19 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>にょ</t>
+          <t>なべ</t>
         </is>
       </c>
       <c r="B285" t="n">
@@ -73760,19 +74327,19 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>ねここ</t>
+          <t>にゃんまげ</t>
         </is>
       </c>
       <c r="B286" t="n">
@@ -73780,19 +74347,19 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>ねむ</t>
+          <t>にょ</t>
         </is>
       </c>
       <c r="B287" t="n">
@@ -73800,19 +74367,19 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>のぼ</t>
+          <t>ねここ</t>
         </is>
       </c>
       <c r="B288" t="n">
@@ -73820,19 +74387,19 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>のり</t>
+          <t>ねむ</t>
         </is>
       </c>
       <c r="B289" t="n">
@@ -73840,19 +74407,19 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>はち</t>
+          <t>のぼ</t>
         </is>
       </c>
       <c r="B290" t="n">
@@ -73860,19 +74427,19 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>はな</t>
+          <t>のり</t>
         </is>
       </c>
       <c r="B291" t="n">
@@ -73880,19 +74447,19 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>はなちゃん</t>
+          <t>はち</t>
         </is>
       </c>
       <c r="B292" t="n">
@@ -73900,19 +74467,19 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>はなまる</t>
+          <t>はな</t>
         </is>
       </c>
       <c r="B293" t="n">
@@ -73920,19 +74487,19 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>はにーちゃん</t>
+          <t>はなちゃん</t>
         </is>
       </c>
       <c r="B294" t="n">
@@ -73940,19 +74507,19 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>はんまー</t>
+          <t>はなまる</t>
         </is>
       </c>
       <c r="B295" t="n">
@@ -73960,19 +74527,19 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>ひったん</t>
+          <t>はにーちゃん</t>
         </is>
       </c>
       <c r="B296" t="n">
@@ -73980,19 +74547,19 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>ひろし</t>
+          <t>はんまー</t>
         </is>
       </c>
       <c r="B297" t="n">
@@ -74000,19 +74567,19 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>ひろとも</t>
+          <t>ひったん</t>
         </is>
       </c>
       <c r="B298" t="n">
@@ -74020,19 +74587,19 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>びん</t>
+          <t>ひろし</t>
         </is>
       </c>
       <c r="B299" t="n">
@@ -74040,19 +74607,19 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>ぴよ</t>
+          <t>ひろとも</t>
         </is>
       </c>
       <c r="B300" t="n">
@@ -74060,19 +74627,19 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>ふみ</t>
+          <t>びん</t>
         </is>
       </c>
       <c r="B301" t="n">
@@ -74080,19 +74647,19 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>ぷらぐいん</t>
+          <t>ぴよ</t>
         </is>
       </c>
       <c r="B302" t="n">
@@ -74100,19 +74667,19 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>ぺぺ</t>
+          <t>ふみ</t>
         </is>
       </c>
       <c r="B303" t="n">
@@ -74120,19 +74687,19 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>ぽち</t>
+          <t>ぷらぐいん</t>
         </is>
       </c>
       <c r="B304" t="n">
@@ -74140,19 +74707,19 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>ぽて</t>
+          <t>ぺぺ</t>
         </is>
       </c>
       <c r="B305" t="n">
@@ -74160,19 +74727,19 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>まいまいん</t>
+          <t>ぽち</t>
         </is>
       </c>
       <c r="B306" t="n">
@@ -74180,19 +74747,19 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>まおし</t>
+          <t>ぽて</t>
         </is>
       </c>
       <c r="B307" t="n">
@@ -74200,19 +74767,19 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>ます</t>
+          <t>まいまいん</t>
         </is>
       </c>
       <c r="B308" t="n">
@@ -74220,19 +74787,19 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>ますみ</t>
+          <t>まおし</t>
         </is>
       </c>
       <c r="B309" t="n">
@@ -74240,19 +74807,19 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>まちゃん</t>
+          <t>ます</t>
         </is>
       </c>
       <c r="B310" t="n">
@@ -74260,19 +74827,19 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>まっする</t>
+          <t>ますみ</t>
         </is>
       </c>
       <c r="B311" t="n">
@@ -74280,19 +74847,19 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>まっぴー</t>
+          <t>まちゃん</t>
         </is>
       </c>
       <c r="B312" t="n">
@@ -74300,19 +74867,19 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>まな</t>
+          <t>まっする</t>
         </is>
       </c>
       <c r="B313" t="n">
@@ -74320,19 +74887,19 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>まみ</t>
+          <t>まっぴー</t>
         </is>
       </c>
       <c r="B314" t="n">
@@ -74340,19 +74907,19 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>まや</t>
+          <t>まな</t>
         </is>
       </c>
       <c r="B315" t="n">
@@ -74360,19 +74927,19 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>まり</t>
+          <t>まみ</t>
         </is>
       </c>
       <c r="B316" t="n">
@@ -74380,19 +74947,19 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>まりーな</t>
+          <t>まや</t>
         </is>
       </c>
       <c r="B317" t="n">
@@ -74400,19 +74967,19 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>まー</t>
+          <t>まり</t>
         </is>
       </c>
       <c r="B318" t="n">
@@ -74420,19 +74987,19 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>まーちゃん</t>
+          <t>まりーな</t>
         </is>
       </c>
       <c r="B319" t="n">
@@ -74440,19 +75007,19 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>みい</t>
+          <t>まー</t>
         </is>
       </c>
       <c r="B320" t="n">
@@ -74460,19 +75027,19 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>みかん</t>
+          <t>まーちゃん</t>
         </is>
       </c>
       <c r="B321" t="n">
@@ -74480,19 +75047,19 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>みけけ</t>
+          <t>みい</t>
         </is>
       </c>
       <c r="B322" t="n">
@@ -74500,19 +75067,19 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>みずき</t>
+          <t>みかん</t>
         </is>
       </c>
       <c r="B323" t="n">
@@ -74532,7 +75099,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>みちゃ</t>
+          <t>みけけ</t>
         </is>
       </c>
       <c r="B324" t="n">
@@ -74540,19 +75107,19 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>みなつちん</t>
+          <t>みずき</t>
         </is>
       </c>
       <c r="B325" t="n">
@@ -74572,7 +75139,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>みみ</t>
+          <t>みちゃ</t>
         </is>
       </c>
       <c r="B326" t="n">
@@ -74580,19 +75147,19 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>みやび</t>
+          <t>みなつちん</t>
         </is>
       </c>
       <c r="B327" t="n">
@@ -74600,19 +75167,19 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>みゆき</t>
+          <t>みみ</t>
         </is>
       </c>
       <c r="B328" t="n">
@@ -74620,19 +75187,19 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>みらい</t>
+          <t>みやび</t>
         </is>
       </c>
       <c r="B329" t="n">
@@ -74640,19 +75207,19 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>みるこ</t>
+          <t>みゆき</t>
         </is>
       </c>
       <c r="B330" t="n">
@@ -74660,19 +75227,19 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>みん</t>
+          <t>みらい</t>
         </is>
       </c>
       <c r="B331" t="n">
@@ -74680,19 +75247,19 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>みんみん</t>
+          <t>みるこ</t>
         </is>
       </c>
       <c r="B332" t="n">
@@ -74700,19 +75267,19 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>みーみ</t>
+          <t>みん</t>
         </is>
       </c>
       <c r="B333" t="n">
@@ -74720,19 +75287,19 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>もかちんぽぽ</t>
+          <t>みんみん</t>
         </is>
       </c>
       <c r="B334" t="n">
@@ -74740,19 +75307,19 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>もっきー</t>
+          <t>みーみ</t>
         </is>
       </c>
       <c r="B335" t="n">
@@ -74760,19 +75327,19 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>もっち</t>
+          <t>もかちんぽぽ</t>
         </is>
       </c>
       <c r="B336" t="n">
@@ -74780,19 +75347,19 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>もっぴっぴ</t>
+          <t>もっきー</t>
         </is>
       </c>
       <c r="B337" t="n">
@@ -74800,19 +75367,19 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-02</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>もっぴー</t>
+          <t>もっち</t>
         </is>
       </c>
       <c r="B338" t="n">
@@ -74820,19 +75387,19 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>もと</t>
+          <t>もっぴっぴ</t>
         </is>
       </c>
       <c r="B339" t="n">
@@ -74840,19 +75407,19 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>ももたろ</t>
+          <t>もっぴー</t>
         </is>
       </c>
       <c r="B340" t="n">
@@ -74860,19 +75427,19 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>やす</t>
+          <t>もと</t>
         </is>
       </c>
       <c r="B341" t="n">
@@ -74880,19 +75447,19 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>ゆい</t>
+          <t>ももたろ</t>
         </is>
       </c>
       <c r="B342" t="n">
@@ -74900,19 +75467,19 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>ゆうじ</t>
+          <t>やす</t>
         </is>
       </c>
       <c r="B343" t="n">
@@ -74920,19 +75487,19 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>ゆうた</t>
+          <t>ゆい</t>
         </is>
       </c>
       <c r="B344" t="n">
@@ -74940,19 +75507,19 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>ゆうたん</t>
+          <t>ゆうじ</t>
         </is>
       </c>
       <c r="B345" t="n">
@@ -74960,19 +75527,19 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>ゆうと</t>
+          <t>ゆうた</t>
         </is>
       </c>
       <c r="B346" t="n">
@@ -74980,19 +75547,19 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>ゆうや</t>
+          <t>ゆうたん</t>
         </is>
       </c>
       <c r="B347" t="n">
@@ -75000,19 +75567,19 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>ゆかり</t>
+          <t>ゆうと</t>
         </is>
       </c>
       <c r="B348" t="n">
@@ -75020,19 +75587,19 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>ゆきお</t>
+          <t>ゆうや</t>
         </is>
       </c>
       <c r="B349" t="n">
@@ -75040,19 +75607,19 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>ゆきんこ</t>
+          <t>ゆかり</t>
         </is>
       </c>
       <c r="B350" t="n">
@@ -75060,19 +75627,19 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>ゆず</t>
+          <t>ゆきお</t>
         </is>
       </c>
       <c r="B351" t="n">
@@ -75080,19 +75647,19 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>ゆずきちゃん</t>
+          <t>ゆきんこ</t>
         </is>
       </c>
       <c r="B352" t="n">
@@ -75100,19 +75667,19 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>ゆずきぴ</t>
+          <t>ゆず</t>
         </is>
       </c>
       <c r="B353" t="n">
@@ -75120,19 +75687,19 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>ゆずき＆ましゅ</t>
+          <t>ゆずきちゃん</t>
         </is>
       </c>
       <c r="B354" t="n">
@@ -75140,19 +75707,19 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>ゆっち</t>
+          <t>ゆずきぴ</t>
         </is>
       </c>
       <c r="B355" t="n">
@@ -75160,19 +75727,19 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>ゆぴ</t>
+          <t>ゆずき＆ましゅ</t>
         </is>
       </c>
       <c r="B356" t="n">
@@ -75180,19 +75747,19 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>ゆり</t>
+          <t>ゆっち</t>
         </is>
       </c>
       <c r="B357" t="n">
@@ -75200,19 +75767,19 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>ゆりな</t>
+          <t>ゆぴ</t>
         </is>
       </c>
       <c r="B358" t="n">
@@ -75220,19 +75787,19 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>ゆん</t>
+          <t>ゆり</t>
         </is>
       </c>
       <c r="B359" t="n">
@@ -75240,19 +75807,19 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>ゆんゆん</t>
+          <t>ゆりな</t>
         </is>
       </c>
       <c r="B360" t="n">
@@ -75260,19 +75827,19 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>よこい</t>
+          <t>ゆん</t>
         </is>
       </c>
       <c r="B361" t="n">
@@ -75280,19 +75847,19 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>よちお</t>
+          <t>ゆんゆん</t>
         </is>
       </c>
       <c r="B362" t="n">
@@ -75300,19 +75867,19 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>らいと</t>
+          <t>よこい</t>
         </is>
       </c>
       <c r="B363" t="n">
@@ -75320,19 +75887,19 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>らうら</t>
+          <t>よちお</t>
         </is>
       </c>
       <c r="B364" t="n">
@@ -75340,19 +75907,19 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>らん</t>
+          <t>らいと</t>
         </is>
       </c>
       <c r="B365" t="n">
@@ -75360,19 +75927,19 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>りえ</t>
+          <t>らうら</t>
         </is>
       </c>
       <c r="B366" t="n">
@@ -75380,19 +75947,19 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>りく</t>
+          <t>らん</t>
         </is>
       </c>
       <c r="B367" t="n">
@@ -75400,19 +75967,19 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>りさ</t>
+          <t>りえ</t>
         </is>
       </c>
       <c r="B368" t="n">
@@ -75420,19 +75987,19 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>りゅうくん</t>
+          <t>りく</t>
         </is>
       </c>
       <c r="B369" t="n">
@@ -75440,19 +76007,19 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>りゅーちゃん</t>
+          <t>りさ</t>
         </is>
       </c>
       <c r="B370" t="n">
@@ -75460,19 +76027,19 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>りょうが</t>
+          <t>りゅうくん</t>
         </is>
       </c>
       <c r="B371" t="n">
@@ -75480,19 +76047,19 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>りょうちゃん</t>
+          <t>りゅーちゃん</t>
         </is>
       </c>
       <c r="B372" t="n">
@@ -75500,19 +76067,19 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>りょーが</t>
+          <t>りょうが</t>
         </is>
       </c>
       <c r="B373" t="n">
@@ -75520,19 +76087,19 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>りりこ</t>
+          <t>りょうちゃん</t>
         </is>
       </c>
       <c r="B374" t="n">
@@ -75540,19 +76107,19 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>りん＆ゆち</t>
+          <t>りょーが</t>
         </is>
       </c>
       <c r="B375" t="n">
@@ -75560,19 +76127,19 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>れい</t>
+          <t>りりこ</t>
         </is>
       </c>
       <c r="B376" t="n">
@@ -75580,19 +76147,19 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>れー</t>
+          <t>りん＆ゆち</t>
         </is>
       </c>
       <c r="B377" t="n">
@@ -75600,19 +76167,19 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>わいちゃん</t>
+          <t>れい</t>
         </is>
       </c>
       <c r="B378" t="n">
@@ -75620,19 +76187,19 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>わんころ</t>
+          <t>れー</t>
         </is>
       </c>
       <c r="B379" t="n">
@@ -75640,19 +76207,19 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>アイ</t>
+          <t>わいちゃん</t>
         </is>
       </c>
       <c r="B380" t="n">
@@ -75660,19 +76227,19 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>アイちゃん</t>
+          <t>わんころ</t>
         </is>
       </c>
       <c r="B381" t="n">
@@ -75680,19 +76247,19 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>アナルプリンス</t>
+          <t>アイ</t>
         </is>
       </c>
       <c r="B382" t="n">
@@ -75700,19 +76267,19 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>イエモン</t>
+          <t>アイちゃん</t>
         </is>
       </c>
       <c r="B383" t="n">
@@ -75720,19 +76287,19 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>イブオ</t>
+          <t>アナルプリンス</t>
         </is>
       </c>
       <c r="B384" t="n">
@@ -75740,19 +76307,19 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>エーイチ</t>
+          <t>イエモン</t>
         </is>
       </c>
       <c r="B385" t="n">
@@ -75760,19 +76327,19 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>オリーブ</t>
+          <t>イブオ</t>
         </is>
       </c>
       <c r="B386" t="n">
@@ -75780,19 +76347,19 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>オ・スー</t>
+          <t>エーイチ</t>
         </is>
       </c>
       <c r="B387" t="n">
@@ -75800,19 +76367,19 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>カイト</t>
+          <t>オリーブ</t>
         </is>
       </c>
       <c r="B388" t="n">
@@ -75820,19 +76387,19 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>カイトウ・キッド</t>
+          <t>オ・スー</t>
         </is>
       </c>
       <c r="B389" t="n">
@@ -75840,19 +76407,19 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>カシワ</t>
+          <t>カイト</t>
         </is>
       </c>
       <c r="B390" t="n">
@@ -75860,19 +76427,19 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>カナ</t>
+          <t>カイトウ・キッド</t>
         </is>
       </c>
       <c r="B391" t="n">
@@ -75880,19 +76447,19 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>カネキヨ</t>
+          <t>カシワ</t>
         </is>
       </c>
       <c r="B392" t="n">
@@ -75900,19 +76467,19 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>カミさん</t>
+          <t>カナ</t>
         </is>
       </c>
       <c r="B393" t="n">
@@ -75920,19 +76487,19 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-10-02</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>カモリ</t>
+          <t>カネキヨ</t>
         </is>
       </c>
       <c r="B394" t="n">
@@ -75940,19 +76507,19 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>カルマ</t>
+          <t>カミさん</t>
         </is>
       </c>
       <c r="B395" t="n">
@@ -75960,19 +76527,19 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>キムさん</t>
+          <t>カモリ</t>
         </is>
       </c>
       <c r="B396" t="n">
@@ -75980,19 +76547,19 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>キムとどえむちゃん</t>
+          <t>カルマ</t>
         </is>
       </c>
       <c r="B397" t="n">
@@ -76000,19 +76567,19 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>キムとまゆ</t>
+          <t>キムさん</t>
         </is>
       </c>
       <c r="B398" t="n">
@@ -76020,19 +76587,19 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>キムとドMまいまい妹</t>
+          <t>キムとどえむちゃん</t>
         </is>
       </c>
       <c r="B399" t="n">
@@ -76040,19 +76607,19 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>キムとドMむい</t>
+          <t>キムとまゆ</t>
         </is>
       </c>
       <c r="B400" t="n">
@@ -76060,19 +76627,19 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-08</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>キムとドM女R</t>
+          <t>キムとドMまいまい妹</t>
         </is>
       </c>
       <c r="B401" t="n">
@@ -76080,19 +76647,19 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>キムとローズ</t>
+          <t>キムとドMむい</t>
         </is>
       </c>
       <c r="B402" t="n">
@@ -76100,19 +76667,19 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>キムと奴隷</t>
+          <t>キムとドM女R</t>
         </is>
       </c>
       <c r="B403" t="n">
@@ -76120,19 +76687,19 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>キムと新しい奴隷ちゃん</t>
+          <t>キムとローズ</t>
         </is>
       </c>
       <c r="B404" t="n">
@@ -76140,19 +76707,19 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>キムラ</t>
+          <t>キムと奴隷</t>
         </is>
       </c>
       <c r="B405" t="n">
@@ -76160,19 +76727,19 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>キム＆みい</t>
+          <t>キムと新しい奴隷ちゃん</t>
         </is>
       </c>
       <c r="B406" t="n">
@@ -76180,19 +76747,19 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>キム＆みー</t>
+          <t>キムラ</t>
         </is>
       </c>
       <c r="B407" t="n">
@@ -76200,19 +76767,19 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>キム＆むい</t>
+          <t>キム＆みい</t>
         </is>
       </c>
       <c r="B408" t="n">
@@ -76220,19 +76787,19 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>クアレ</t>
+          <t>キム＆みー</t>
         </is>
       </c>
       <c r="B409" t="n">
@@ -76240,19 +76807,19 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>クロちゃん</t>
+          <t>キム＆むい</t>
         </is>
       </c>
       <c r="B410" t="n">
@@ -76260,19 +76827,19 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>ケケ</t>
+          <t>クアレ</t>
         </is>
       </c>
       <c r="B411" t="n">
@@ -76280,19 +76847,19 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>ゲン</t>
+          <t>クロちゃん</t>
         </is>
       </c>
       <c r="B412" t="n">
@@ -76312,7 +76879,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>コオリ</t>
+          <t>ケケ</t>
         </is>
       </c>
       <c r="B413" t="n">
@@ -76320,19 +76887,19 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>コマ</t>
+          <t>ゲン</t>
         </is>
       </c>
       <c r="B414" t="n">
@@ -76340,19 +76907,19 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>サカモト</t>
+          <t>コオリ</t>
         </is>
       </c>
       <c r="B415" t="n">
@@ -76360,19 +76927,19 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>サクヤ</t>
+          <t>コマ</t>
         </is>
       </c>
       <c r="B416" t="n">
@@ -76380,19 +76947,19 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>サト</t>
+          <t>サカモト</t>
         </is>
       </c>
       <c r="B417" t="n">
@@ -76400,19 +76967,19 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>サトル</t>
+          <t>サクヤ</t>
         </is>
       </c>
       <c r="B418" t="n">
@@ -76420,19 +76987,19 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>ザッキー</t>
+          <t>サト</t>
         </is>
       </c>
       <c r="B419" t="n">
@@ -76440,19 +77007,19 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>シゲ</t>
+          <t>サトル</t>
         </is>
       </c>
       <c r="B420" t="n">
@@ -76460,19 +77027,19 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>シマ</t>
+          <t>ザッキー</t>
         </is>
       </c>
       <c r="B421" t="n">
@@ -76480,19 +77047,19 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>シュウ</t>
+          <t>シゲ</t>
         </is>
       </c>
       <c r="B422" t="n">
@@ -76500,19 +77067,19 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>シュン</t>
+          <t>シマ</t>
         </is>
       </c>
       <c r="B423" t="n">
@@ -76520,19 +77087,19 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-10-02</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>シュンヤ</t>
+          <t>シュウ</t>
         </is>
       </c>
       <c r="B424" t="n">
@@ -76540,19 +77107,19 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>シン</t>
+          <t>シュン</t>
         </is>
       </c>
       <c r="B425" t="n">
@@ -76560,19 +77127,19 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>シン変質者</t>
+          <t>シュンヤ</t>
         </is>
       </c>
       <c r="B426" t="n">
@@ -76580,19 +77147,19 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>ジャッキー</t>
+          <t>シン</t>
         </is>
       </c>
       <c r="B427" t="n">
@@ -76600,19 +77167,19 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>ジョーカー</t>
+          <t>シン変質者</t>
         </is>
       </c>
       <c r="B428" t="n">
@@ -76620,19 +77187,19 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>スズ</t>
+          <t>ジャッキー</t>
         </is>
       </c>
       <c r="B429" t="n">
@@ -76640,19 +77207,19 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>ソルト</t>
+          <t>ジョーカー</t>
         </is>
       </c>
       <c r="B430" t="n">
@@ -76660,19 +77227,19 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>タイガ</t>
+          <t>スズ</t>
         </is>
       </c>
       <c r="B431" t="n">
@@ -76692,7 +77259,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>タカス</t>
+          <t>ソルト</t>
         </is>
       </c>
       <c r="B432" t="n">
@@ -76700,19 +77267,19 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>タカ御一行</t>
+          <t>タイガ</t>
         </is>
       </c>
       <c r="B433" t="n">
@@ -76720,19 +77287,19 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>ダイキ</t>
+          <t>タカス</t>
         </is>
       </c>
       <c r="B434" t="n">
@@ -76740,19 +77307,19 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>ダイチ</t>
+          <t>タカ御一行</t>
         </is>
       </c>
       <c r="B435" t="n">
@@ -76760,19 +77327,19 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>チェスカ</t>
+          <t>ダイキ</t>
         </is>
       </c>
       <c r="B436" t="n">
@@ -76780,19 +77347,19 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>ツシマ</t>
+          <t>ダイチ</t>
         </is>
       </c>
       <c r="B437" t="n">
@@ -76800,19 +77367,19 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>ツボ</t>
+          <t>チェスカ</t>
         </is>
       </c>
       <c r="B438" t="n">
@@ -76820,19 +77387,19 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>テクノとポチ</t>
+          <t>ツシマ</t>
         </is>
       </c>
       <c r="B439" t="n">
@@ -76840,19 +77407,19 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>テクノ＆おおつか＆みこと＆もも</t>
+          <t>ツボ</t>
         </is>
       </c>
       <c r="B440" t="n">
@@ -76860,19 +77427,19 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>テクノ＆てるくん＆イブオ</t>
+          <t>テクノとポチ</t>
         </is>
       </c>
       <c r="B441" t="n">
@@ -76880,19 +77447,19 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>トニー・トニー・チョッパー</t>
+          <t>テクノ＆おおつか＆みこと＆もも</t>
         </is>
       </c>
       <c r="B442" t="n">
@@ -76900,19 +77467,19 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>トム</t>
+          <t>テクノ＆てるくん＆イブオ</t>
         </is>
       </c>
       <c r="B443" t="n">
@@ -76920,19 +77487,19 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>トルネードシャーク</t>
+          <t>トニー・トニー・チョッパー</t>
         </is>
       </c>
       <c r="B444" t="n">
@@ -76940,19 +77507,19 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>ナカヤマヤ</t>
+          <t>トム</t>
         </is>
       </c>
       <c r="B445" t="n">
@@ -76960,19 +77527,19 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>ニコチン</t>
+          <t>トルネードシャーク</t>
         </is>
       </c>
       <c r="B446" t="n">
@@ -76980,19 +77547,19 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>ニト</t>
+          <t>ナカヤマヤ</t>
         </is>
       </c>
       <c r="B447" t="n">
@@ -77000,19 +77567,19 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>ニャンまげ</t>
+          <t>ニコチン</t>
         </is>
       </c>
       <c r="B448" t="n">
@@ -77020,19 +77587,19 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>ハチ</t>
+          <t>ニト</t>
         </is>
       </c>
       <c r="B449" t="n">
@@ -77040,19 +77607,19 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>ヒロ</t>
+          <t>ニャンまげ</t>
         </is>
       </c>
       <c r="B450" t="n">
@@ -77060,19 +77627,19 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>ヒロシ</t>
+          <t>ハチ</t>
         </is>
       </c>
       <c r="B451" t="n">
@@ -77080,19 +77647,19 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>ビコー</t>
+          <t>ヒロ</t>
         </is>
       </c>
       <c r="B452" t="n">
@@ -77100,19 +77667,19 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>フジ</t>
+          <t>ヒロシ</t>
         </is>
       </c>
       <c r="B453" t="n">
@@ -77120,19 +77687,19 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>ペロとペコ</t>
+          <t>ビコー</t>
         </is>
       </c>
       <c r="B454" t="n">
@@ -77140,19 +77707,19 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>ボス</t>
+          <t>フジ</t>
         </is>
       </c>
       <c r="B455" t="n">
@@ -77160,19 +77727,19 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>ボンタ</t>
+          <t>ペロとペコ</t>
         </is>
       </c>
       <c r="B456" t="n">
@@ -77180,19 +77747,19 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>ポチ</t>
+          <t>ボス</t>
         </is>
       </c>
       <c r="B457" t="n">
@@ -77200,19 +77767,19 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>ポポ</t>
+          <t>ボンタ</t>
         </is>
       </c>
       <c r="B458" t="n">
@@ -77220,19 +77787,19 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>マッチョ</t>
+          <t>ポチ</t>
         </is>
       </c>
       <c r="B459" t="n">
@@ -77240,19 +77807,19 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>ミカミと仲間たち</t>
+          <t>ポポ</t>
         </is>
       </c>
       <c r="B460" t="n">
@@ -77260,19 +77827,19 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>ミスター工事マン</t>
+          <t>マッチョ</t>
         </is>
       </c>
       <c r="B461" t="n">
@@ -77280,19 +77847,19 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>ミッシ</t>
+          <t>ミカミと仲間たち</t>
         </is>
       </c>
       <c r="B462" t="n">
@@ -77300,19 +77867,19 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>ミッチー</t>
+          <t>ミスター工事マン</t>
         </is>
       </c>
       <c r="B463" t="n">
@@ -77320,19 +77887,19 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>ミルコ</t>
+          <t>ミッシ</t>
         </is>
       </c>
       <c r="B464" t="n">
@@ -77340,19 +77907,19 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>ミン</t>
+          <t>ミッチー</t>
         </is>
       </c>
       <c r="B465" t="n">
@@ -77360,19 +77927,19 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>メンズ5人組</t>
+          <t>ミルコ</t>
         </is>
       </c>
       <c r="B466" t="n">
@@ -77380,19 +77947,19 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>モジャ</t>
+          <t>ミン</t>
         </is>
       </c>
       <c r="B467" t="n">
@@ -77400,19 +77967,19 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>ヤノ</t>
+          <t>メンズ5人組</t>
         </is>
       </c>
       <c r="B468" t="n">
@@ -77420,19 +77987,19 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>ヤノちゃん</t>
+          <t>モジャ</t>
         </is>
       </c>
       <c r="B469" t="n">
@@ -77440,19 +78007,19 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>ヤマ</t>
+          <t>ヤノ</t>
         </is>
       </c>
       <c r="B470" t="n">
@@ -77460,19 +78027,19 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>ユウ</t>
+          <t>ヤノちゃん</t>
         </is>
       </c>
       <c r="B471" t="n">
@@ -77480,19 +78047,19 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>ユキ</t>
+          <t>ヤマ</t>
         </is>
       </c>
       <c r="B472" t="n">
@@ -77500,19 +78067,19 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>ユッキー</t>
+          <t>ユウ</t>
         </is>
       </c>
       <c r="B473" t="n">
@@ -77520,19 +78087,19 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>ヨシヤ</t>
+          <t>ユキ</t>
         </is>
       </c>
       <c r="B474" t="n">
@@ -77540,19 +78107,19 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>ラオ</t>
+          <t>ユッキー</t>
         </is>
       </c>
       <c r="B475" t="n">
@@ -77560,19 +78127,19 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>ラ王</t>
+          <t>ヨシヤ</t>
         </is>
       </c>
       <c r="B476" t="n">
@@ -77580,19 +78147,19 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>リク</t>
+          <t>ラオ</t>
         </is>
       </c>
       <c r="B477" t="n">
@@ -77600,19 +78167,19 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>リョウ</t>
+          <t>ラ王</t>
         </is>
       </c>
       <c r="B478" t="n">
@@ -77620,19 +78187,19 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>レオ</t>
+          <t>リク</t>
         </is>
       </c>
       <c r="B479" t="n">
@@ -77640,19 +78207,19 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>ロタポジ</t>
+          <t>リョウ</t>
         </is>
       </c>
       <c r="B480" t="n">
@@ -77660,19 +78227,19 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>ローズ</t>
+          <t>レオ</t>
         </is>
       </c>
       <c r="B481" t="n">
@@ -77680,19 +78247,19 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>偽マイマイ</t>
+          <t>ロタポジ</t>
         </is>
       </c>
       <c r="B482" t="n">
@@ -77700,19 +78267,19 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>僕と私</t>
+          <t>ローズ</t>
         </is>
       </c>
       <c r="B483" t="n">
@@ -77720,19 +78287,19 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>光一</t>
+          <t>偽マイマイ</t>
         </is>
       </c>
       <c r="B484" t="n">
@@ -77740,19 +78307,19 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>名無し</t>
+          <t>僕と私</t>
         </is>
       </c>
       <c r="B485" t="n">
@@ -77772,7 +78339,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>変態まっする</t>
+          <t>光一</t>
         </is>
       </c>
       <c r="B486" t="n">
@@ -77780,19 +78347,19 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>変態マッソー</t>
+          <t>名無し</t>
         </is>
       </c>
       <c r="B487" t="n">
@@ -77800,19 +78367,19 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>天我迅</t>
+          <t>変態まっする</t>
         </is>
       </c>
       <c r="B488" t="n">
@@ -77820,19 +78387,19 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>女子三人衆</t>
+          <t>変態マッソー</t>
         </is>
       </c>
       <c r="B489" t="n">
@@ -77840,19 +78407,19 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>彩 なまがき</t>
+          <t>天我迅</t>
         </is>
       </c>
       <c r="B490" t="n">
@@ -77860,19 +78427,19 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>正装しん</t>
+          <t>女子三人衆</t>
         </is>
       </c>
       <c r="B491" t="n">
@@ -77880,19 +78447,19 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>海砂利水魚</t>
+          <t>彩 なまがき</t>
         </is>
       </c>
       <c r="B492" t="n">
@@ -77900,19 +78467,19 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>田中</t>
+          <t>正装しん</t>
         </is>
       </c>
       <c r="B493" t="n">
@@ -77920,19 +78487,19 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>番</t>
+          <t>海砂利水魚</t>
         </is>
       </c>
       <c r="B494" t="n">
@@ -77940,19 +78507,19 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>碧咲</t>
+          <t>田中</t>
         </is>
       </c>
       <c r="B495" t="n">
@@ -77960,19 +78527,19 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>福ちゃん</t>
+          <t>番</t>
         </is>
       </c>
       <c r="B496" t="n">
@@ -77980,19 +78547,19 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>絶</t>
+          <t>碧咲</t>
         </is>
       </c>
       <c r="B497" t="n">
@@ -78000,19 +78567,19 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>絶ちゃん</t>
+          <t>福ちゃん</t>
         </is>
       </c>
       <c r="B498" t="n">
@@ -78020,19 +78587,19 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>美優</t>
+          <t>絶</t>
         </is>
       </c>
       <c r="B499" t="n">
@@ -78040,19 +78607,19 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>赤ちゃん</t>
+          <t>絶ちゃん</t>
         </is>
       </c>
       <c r="B500" t="n">
@@ -78060,19 +78627,19 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>赤井ヱビス</t>
+          <t>美優</t>
         </is>
       </c>
       <c r="B501" t="n">
@@ -78080,19 +78647,19 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>部長</t>
+          <t>赤ちゃん</t>
         </is>
       </c>
       <c r="B502" t="n">
@@ -78100,30 +78667,70 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
+          <t>赤井ヱビス</t>
+        </is>
+      </c>
+      <c r="B503" t="n">
+        <v>1</v>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>部長</t>
+        </is>
+      </c>
+      <c r="B504" t="n">
+        <v>1</v>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
           <t>雅-miyabi-/とも</t>
         </is>
       </c>
-      <c r="B503" t="n">
-        <v>1</v>
-      </c>
-      <c r="C503" t="inlineStr">
+      <c r="B505" t="n">
+        <v>1</v>
+      </c>
+      <c r="C505" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="D503" t="inlineStr">
+      <c r="D505" t="inlineStr">
         <is>
           <t>2026-09-23</t>
         </is>
@@ -78167,10 +78774,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C2" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3">
@@ -78445,10 +79052,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -78536,10 +79143,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C21" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="22">
@@ -78549,10 +79156,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C22" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="23">
@@ -78562,10 +79169,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C23" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="24">
@@ -78575,10 +79182,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C24" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="25">
@@ -78588,10 +79195,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C25" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -78669,13 +79276,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C4" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="D4" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/bbs_log.xlsx
+++ b/bbs_log.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H946"/>
+  <dimension ref="A1:H958"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30056,7 +30056,6 @@
           <t>キムとドM女の子</t>
         </is>
       </c>
-      <c r="E941" t="inlineStr"/>
       <c r="F941" t="inlineStr">
         <is>
           <t>初来店</t>
@@ -30067,7 +30066,6 @@
           <t>の女の子つれて</t>
         </is>
       </c>
-      <c r="H941" t="inlineStr"/>
     </row>
     <row r="942">
       <c r="A942" t="n">
@@ -30088,7 +30086,6 @@
           <t>びーだっしゅ</t>
         </is>
       </c>
-      <c r="E942" t="inlineStr"/>
       <c r="F942" t="inlineStr">
         <is>
           <t>寛ぎに</t>
@@ -30099,7 +30096,6 @@
           <t>来ました。</t>
         </is>
       </c>
-      <c r="H942" t="inlineStr"/>
     </row>
     <row r="943">
       <c r="A943" t="n">
@@ -30120,7 +30116,6 @@
           <t>よちお</t>
         </is>
       </c>
-      <c r="E943" t="inlineStr"/>
       <c r="F943" t="inlineStr">
         <is>
           <t>今日も</t>
@@ -30131,7 +30126,6 @@
           <t>代行待ちます</t>
         </is>
       </c>
-      <c r="H943" t="inlineStr"/>
     </row>
     <row r="944">
       <c r="A944" t="n">
@@ -30152,7 +30146,6 @@
           <t>ゆう</t>
         </is>
       </c>
-      <c r="E944" t="inlineStr"/>
       <c r="F944" t="inlineStr">
         <is>
           <t>遊びに</t>
@@ -30163,7 +30156,6 @@
           <t>キタ</t>
         </is>
       </c>
-      <c r="H944" t="inlineStr"/>
     </row>
     <row r="945">
       <c r="A945" t="n">
@@ -30184,7 +30176,6 @@
           <t>まいまいん</t>
         </is>
       </c>
-      <c r="E945" t="inlineStr"/>
       <c r="F945" t="inlineStr">
         <is>
           <t>しごわ</t>
@@ -30195,7 +30186,6 @@
           <t>きたよーん</t>
         </is>
       </c>
-      <c r="H945" t="inlineStr"/>
     </row>
     <row r="946">
       <c r="A946" t="n">
@@ -30249,6 +30239,411 @@
         </is>
       </c>
     </row>
+    <row r="947">
+      <c r="A947" t="n">
+        <v>28650</v>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>18:46:53</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr">
+        <is>
+          <t>ひがんたん</t>
+        </is>
+      </c>
+      <c r="E947" t="inlineStr"/>
+      <c r="F947" t="inlineStr">
+        <is>
+          <t>オープン前</t>
+        </is>
+      </c>
+      <c r="G947" t="inlineStr">
+        <is>
+          <t>遊びにきたよーん</t>
+        </is>
+      </c>
+      <c r="H947" t="inlineStr"/>
+    </row>
+    <row r="948">
+      <c r="A948" t="n">
+        <v>28652</v>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>19:16:01</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr">
+        <is>
+          <t>べー</t>
+        </is>
+      </c>
+      <c r="E948" t="inlineStr"/>
+      <c r="F948" t="inlineStr">
+        <is>
+          <t>腸内準備</t>
+        </is>
+      </c>
+      <c r="G948" t="inlineStr">
+        <is>
+          <t>2部前には行けると思います</t>
+        </is>
+      </c>
+      <c r="H948" t="inlineStr"/>
+    </row>
+    <row r="949">
+      <c r="A949" t="n">
+        <v>28654</v>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>21:41:34</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr">
+        <is>
+          <t>たっくん＆そら</t>
+        </is>
+      </c>
+      <c r="E949" t="inlineStr"/>
+      <c r="F949" t="inlineStr">
+        <is>
+          <t>ご新規さん</t>
+        </is>
+      </c>
+      <c r="G949" t="inlineStr">
+        <is>
+          <t>いらっしゃいませ〜</t>
+        </is>
+      </c>
+      <c r="H949" t="inlineStr"/>
+    </row>
+    <row r="950">
+      <c r="A950" t="n">
+        <v>28656</v>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>22:36:22</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr">
+        <is>
+          <t>ノリ</t>
+        </is>
+      </c>
+      <c r="E950" t="inlineStr"/>
+      <c r="F950" t="inlineStr">
+        <is>
+          <t>初</t>
+        </is>
+      </c>
+      <c r="G950" t="inlineStr">
+        <is>
+          <t>来ました！</t>
+        </is>
+      </c>
+      <c r="H950" t="inlineStr"/>
+    </row>
+    <row r="951">
+      <c r="A951" t="n">
+        <v>28657</v>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>22:37:07</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>みなっち</t>
+        </is>
+      </c>
+      <c r="E951" t="inlineStr"/>
+      <c r="F951" t="inlineStr">
+        <is>
+          <t>ちょっとだけよ〜</t>
+        </is>
+      </c>
+      <c r="G951" t="inlineStr">
+        <is>
+          <t>あそびにきました</t>
+        </is>
+      </c>
+      <c r="H951" t="inlineStr"/>
+    </row>
+    <row r="952">
+      <c r="A952" t="n">
+        <v>28660</v>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>22:46:29</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr">
+        <is>
+          <t>zin</t>
+        </is>
+      </c>
+      <c r="E952" t="inlineStr"/>
+      <c r="F952" t="inlineStr">
+        <is>
+          <t>久々に</t>
+        </is>
+      </c>
+      <c r="G952" t="inlineStr">
+        <is>
+          <t>きました！！</t>
+        </is>
+      </c>
+      <c r="H952" t="inlineStr"/>
+    </row>
+    <row r="953">
+      <c r="A953" t="n">
+        <v>28662</v>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>01:04:48</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr">
+        <is>
+          <t>謎の男＆マリア嬢</t>
+        </is>
+      </c>
+      <c r="E953" t="inlineStr"/>
+      <c r="F953" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G953" t="inlineStr">
+        <is>
+          <t>来ました！</t>
+        </is>
+      </c>
+      <c r="H953" t="inlineStr"/>
+    </row>
+    <row r="954">
+      <c r="A954" t="n">
+        <v>28664</v>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>01:31:35</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>てぃふ</t>
+        </is>
+      </c>
+      <c r="E954" t="inlineStr"/>
+      <c r="F954" t="inlineStr">
+        <is>
+          <t>小山から</t>
+        </is>
+      </c>
+      <c r="G954" t="inlineStr">
+        <is>
+          <t>来ちゃいました</t>
+        </is>
+      </c>
+      <c r="H954" t="inlineStr"/>
+    </row>
+    <row r="955">
+      <c r="A955" t="n">
+        <v>28666</v>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>01:35:59</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>まいまい</t>
+        </is>
+      </c>
+      <c r="E955" t="inlineStr"/>
+      <c r="F955" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G955" t="inlineStr">
+        <is>
+          <t>来ました！</t>
+        </is>
+      </c>
+      <c r="H955" t="inlineStr"/>
+    </row>
+    <row r="956">
+      <c r="A956" t="n">
+        <v>28668</v>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>03:36:57</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr">
+        <is>
+          <t>りん＆まゆちゃん</t>
+        </is>
+      </c>
+      <c r="E956" t="inlineStr"/>
+      <c r="F956" t="inlineStr">
+        <is>
+          <t>美人連れて</t>
+        </is>
+      </c>
+      <c r="G956" t="inlineStr">
+        <is>
+          <t>来ました！</t>
+        </is>
+      </c>
+      <c r="H956" t="inlineStr"/>
+    </row>
+    <row r="957">
+      <c r="A957" t="n">
+        <v>28670</v>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>03:56:55</t>
+        </is>
+      </c>
+      <c r="D957" t="inlineStr">
+        <is>
+          <t>みきちゃん</t>
+        </is>
+      </c>
+      <c r="E957" t="inlineStr"/>
+      <c r="F957" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="G957" t="inlineStr">
+        <is>
+          <t>来ちゃいました</t>
+        </is>
+      </c>
+      <c r="H957" t="inlineStr"/>
+    </row>
+    <row r="958">
+      <c r="A958" t="n">
+        <v>28672</v>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>05:03:50</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr">
+        <is>
+          <t>★BAMBITCH★</t>
+        </is>
+      </c>
+      <c r="E958" t="inlineStr">
+        <is>
+          <t>ツッコミはお任せのShizu / えちえち裏垢女子のモカチ</t>
+        </is>
+      </c>
+      <c r="F958" t="inlineStr">
+        <is>
+          <t>★☆★朝までアゲアゲの水曜日営業が始まるわよ♪★☆★</t>
+        </is>
+      </c>
+      <c r="G958" t="inlineStr">
+        <is>
+          <t>本日10月14日の営業時間は♪
+オープン19:00！ラスト5:00なのよ☆
+担当は
+ツッコミはお任せのShizu
+えちえち裏垢女子のモカチ
+なのよ♪
+どんな季節でも★BAMBITCH★は色気ムンムンで暑すぎる♪
+バンビッチでおもいっきりはじけちゃって（笑）
+精力は無くても性欲がある！？
+大人の憩いと禁断サークル盛りだくさん！
+憩いと交流の魔性の遊び場バンビッチは素敵な出会いを 提供いたします（笑)☆☆
+おつまみ等の持ち込みは自由なのでみんなで持ち寄ってお近づきのきっかけにどうぞ♪
+強制や無理強いは一切ございませんので楽しく遊びましょう♪
+宇都宮市宿郷1−12−9　カサブランカビル5F</t>
+        </is>
+      </c>
+      <c r="H958" t="inlineStr">
+        <is>
+          <t>img20261014050350.jpg</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -30260,7 +30655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1094"/>
+  <dimension ref="A1:I1105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77320,6 +77715,479 @@
       <c r="I1094" t="inlineStr">
         <is>
           <t>きたよーん</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>18:46:53</t>
+        </is>
+      </c>
+      <c r="D1095" t="n">
+        <v>28650</v>
+      </c>
+      <c r="E1095" t="inlineStr">
+        <is>
+          <t>ひがんたん</t>
+        </is>
+      </c>
+      <c r="F1095" t="n">
+        <v>7</v>
+      </c>
+      <c r="G1095" t="inlineStr">
+        <is>
+          <t>ひがんたん</t>
+        </is>
+      </c>
+      <c r="H1095" t="inlineStr">
+        <is>
+          <t>オープン前</t>
+        </is>
+      </c>
+      <c r="I1095" t="inlineStr">
+        <is>
+          <t>遊びにきたよーん</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>19:16:01</t>
+        </is>
+      </c>
+      <c r="D1096" t="n">
+        <v>28652</v>
+      </c>
+      <c r="E1096" t="inlineStr">
+        <is>
+          <t>べー</t>
+        </is>
+      </c>
+      <c r="F1096" t="n">
+        <v>6</v>
+      </c>
+      <c r="G1096" t="inlineStr">
+        <is>
+          <t>べー</t>
+        </is>
+      </c>
+      <c r="H1096" t="inlineStr">
+        <is>
+          <t>腸内準備</t>
+        </is>
+      </c>
+      <c r="I1096" t="inlineStr">
+        <is>
+          <t>2部前には行けると思います</t>
+        </is>
+      </c>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>21:41:34</t>
+        </is>
+      </c>
+      <c r="D1097" t="n">
+        <v>28654</v>
+      </c>
+      <c r="E1097" t="inlineStr">
+        <is>
+          <t>たっくん＆そら</t>
+        </is>
+      </c>
+      <c r="F1097" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1097" t="inlineStr">
+        <is>
+          <t>たっくん＆そら</t>
+        </is>
+      </c>
+      <c r="H1097" t="inlineStr">
+        <is>
+          <t>ご新規さん</t>
+        </is>
+      </c>
+      <c r="I1097" t="inlineStr">
+        <is>
+          <t>いらっしゃいませ〜</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>22:36:22</t>
+        </is>
+      </c>
+      <c r="D1098" t="n">
+        <v>28656</v>
+      </c>
+      <c r="E1098" t="inlineStr">
+        <is>
+          <t>ノリ</t>
+        </is>
+      </c>
+      <c r="F1098" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1098" t="inlineStr">
+        <is>
+          <t>ノリ</t>
+        </is>
+      </c>
+      <c r="H1098" t="inlineStr">
+        <is>
+          <t>初</t>
+        </is>
+      </c>
+      <c r="I1098" t="inlineStr">
+        <is>
+          <t>来ました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>22:37:07</t>
+        </is>
+      </c>
+      <c r="D1099" t="n">
+        <v>28657</v>
+      </c>
+      <c r="E1099" t="inlineStr">
+        <is>
+          <t>みなっち</t>
+        </is>
+      </c>
+      <c r="F1099" t="n">
+        <v>10</v>
+      </c>
+      <c r="G1099" t="inlineStr">
+        <is>
+          <t>みなっち</t>
+        </is>
+      </c>
+      <c r="H1099" t="inlineStr">
+        <is>
+          <t>ちょっとだけよ〜</t>
+        </is>
+      </c>
+      <c r="I1099" t="inlineStr">
+        <is>
+          <t>あそびにきました</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>22:46:29</t>
+        </is>
+      </c>
+      <c r="D1100" t="n">
+        <v>28660</v>
+      </c>
+      <c r="E1100" t="inlineStr">
+        <is>
+          <t>zin</t>
+        </is>
+      </c>
+      <c r="F1100" t="n">
+        <v>9</v>
+      </c>
+      <c r="G1100" t="inlineStr">
+        <is>
+          <t>zin</t>
+        </is>
+      </c>
+      <c r="H1100" t="inlineStr">
+        <is>
+          <t>久々に</t>
+        </is>
+      </c>
+      <c r="I1100" t="inlineStr">
+        <is>
+          <t>きました！！</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>01:04:48</t>
+        </is>
+      </c>
+      <c r="D1101" t="n">
+        <v>28662</v>
+      </c>
+      <c r="E1101" t="inlineStr">
+        <is>
+          <t>謎の男＆マリア嬢</t>
+        </is>
+      </c>
+      <c r="F1101" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1101" t="inlineStr">
+        <is>
+          <t>謎の男＆マリア嬢</t>
+        </is>
+      </c>
+      <c r="H1101" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="I1101" t="inlineStr">
+        <is>
+          <t>来ました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>01:31:35</t>
+        </is>
+      </c>
+      <c r="D1102" t="n">
+        <v>28664</v>
+      </c>
+      <c r="E1102" t="inlineStr">
+        <is>
+          <t>てぃふ</t>
+        </is>
+      </c>
+      <c r="F1102" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1102" t="inlineStr">
+        <is>
+          <t>てぃふ</t>
+        </is>
+      </c>
+      <c r="H1102" t="inlineStr">
+        <is>
+          <t>小山から</t>
+        </is>
+      </c>
+      <c r="I1102" t="inlineStr">
+        <is>
+          <t>来ちゃいました</t>
+        </is>
+      </c>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>01:35:59</t>
+        </is>
+      </c>
+      <c r="D1103" t="n">
+        <v>28666</v>
+      </c>
+      <c r="E1103" t="inlineStr">
+        <is>
+          <t>まいまい</t>
+        </is>
+      </c>
+      <c r="F1103" t="n">
+        <v>16</v>
+      </c>
+      <c r="G1103" t="inlineStr">
+        <is>
+          <t>まいまい</t>
+        </is>
+      </c>
+      <c r="H1103" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="I1103" t="inlineStr">
+        <is>
+          <t>来ました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>03:36:57</t>
+        </is>
+      </c>
+      <c r="D1104" t="n">
+        <v>28668</v>
+      </c>
+      <c r="E1104" t="inlineStr">
+        <is>
+          <t>りん＆まゆちゃん</t>
+        </is>
+      </c>
+      <c r="F1104" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1104" t="inlineStr">
+        <is>
+          <t>りん＆まゆちゃん</t>
+        </is>
+      </c>
+      <c r="H1104" t="inlineStr">
+        <is>
+          <t>美人連れて</t>
+        </is>
+      </c>
+      <c r="I1104" t="inlineStr">
+        <is>
+          <t>来ました！</t>
+        </is>
+      </c>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>03:56:55</t>
+        </is>
+      </c>
+      <c r="D1105" t="n">
+        <v>28670</v>
+      </c>
+      <c r="E1105" t="inlineStr">
+        <is>
+          <t>みきちゃん</t>
+        </is>
+      </c>
+      <c r="F1105" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1105" t="inlineStr">
+        <is>
+          <t>みきちゃん</t>
+        </is>
+      </c>
+      <c r="H1105" t="inlineStr">
+        <is>
+          <t>今</t>
+        </is>
+      </c>
+      <c r="I1105" t="inlineStr">
+        <is>
+          <t>来ちゃいました</t>
         </is>
       </c>
     </row>
@@ -77334,7 +78202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D557"/>
+  <dimension ref="A1:D563"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -77422,7 +78290,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>彩</t>
+          <t>まいまい</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -77430,32 +78298,32 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>まいまい</t>
+          <t>彩</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-09</t>
         </is>
       </c>
     </row>
@@ -77502,7 +78370,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ゆずきち</t>
+          <t>みなっち</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -77510,39 +78378,39 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>たいせい</t>
+          <t>ゆずきち</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>なお</t>
+          <t>zin</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -77550,19 +78418,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>みなっち</t>
+          <t>たいせい</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -77575,14 +78443,14 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ゆう</t>
+          <t>なお</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -77590,32 +78458,32 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>zin</t>
+          <t>ゆう</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
@@ -77802,7 +78670,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>るい</t>
+          <t>ひがんたん</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -77810,39 +78678,39 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>るい</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TKC</t>
+          <t>M</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -77850,19 +78718,19 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>bee</t>
+          <t>TKC</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -77875,14 +78743,14 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>あいちゃん</t>
+          <t>bee</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -77890,19 +78758,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-09</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>かな</t>
+          <t>あいちゃん</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -77910,19 +78778,19 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ちゃそたけ</t>
+          <t>かな</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -77930,19 +78798,19 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ひがんたん</t>
+          <t>ちゃそたけ</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -77955,14 +78823,14 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-09</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>キム</t>
+          <t>べー</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -77970,19 +78838,19 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>コテッチャン</t>
+          <t>キム</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -77990,19 +78858,19 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ミコト</t>
+          <t>コテッチャン</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -78010,39 +78878,39 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-10-05</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>ミコト</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>K</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -78050,7 +78918,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -78062,7 +78930,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>こてっちゃん</t>
+          <t>N</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -78070,19 +78938,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>しゅん</t>
+          <t>こてっちゃん</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -78090,19 +78958,19 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>しん</t>
+          <t>しゅん</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -78110,19 +78978,19 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ふくてゃ</t>
+          <t>しん</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -78130,19 +78998,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>べー</t>
+          <t>ふくてゃ</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -78150,12 +79018,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
@@ -82962,7 +83830,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>たっちゃん</t>
+          <t>たっくん＆そら</t>
         </is>
       </c>
       <c r="B282" t="n">
@@ -82970,19 +83838,19 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>たつお</t>
+          <t>たっちゃん</t>
         </is>
       </c>
       <c r="B283" t="n">
@@ -82990,19 +83858,19 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>たなか</t>
+          <t>たつお</t>
         </is>
       </c>
       <c r="B284" t="n">
@@ -83010,19 +83878,19 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>たま</t>
+          <t>たなか</t>
         </is>
       </c>
       <c r="B285" t="n">
@@ -83030,19 +83898,19 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>たます</t>
+          <t>たま</t>
         </is>
       </c>
       <c r="B286" t="n">
@@ -83050,19 +83918,19 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>たろう</t>
+          <t>たます</t>
         </is>
       </c>
       <c r="B287" t="n">
@@ -83070,19 +83938,19 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>たろー</t>
+          <t>たろう</t>
         </is>
       </c>
       <c r="B288" t="n">
@@ -83090,19 +83958,19 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>たー</t>
+          <t>たろー</t>
         </is>
       </c>
       <c r="B289" t="n">
@@ -83110,19 +83978,19 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>だいさく</t>
+          <t>たー</t>
         </is>
       </c>
       <c r="B290" t="n">
@@ -83130,19 +83998,19 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>だいざく</t>
+          <t>だいさく</t>
         </is>
       </c>
       <c r="B291" t="n">
@@ -83150,19 +84018,19 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>だいち</t>
+          <t>だいざく</t>
         </is>
       </c>
       <c r="B292" t="n">
@@ -83170,19 +84038,19 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>ちぇちぇ＆ガールズ</t>
+          <t>だいち</t>
         </is>
       </c>
       <c r="B293" t="n">
@@ -83190,19 +84058,19 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>ちっちてゃ</t>
+          <t>ちぇちぇ＆ガールズ</t>
         </is>
       </c>
       <c r="B294" t="n">
@@ -83210,19 +84078,19 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>ちほ</t>
+          <t>ちっちてゃ</t>
         </is>
       </c>
       <c r="B295" t="n">
@@ -83230,19 +84098,19 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>つかさ</t>
+          <t>ちほ</t>
         </is>
       </c>
       <c r="B296" t="n">
@@ -83250,19 +84118,19 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>てくのちん</t>
+          <t>つかさ</t>
         </is>
       </c>
       <c r="B297" t="n">
@@ -83270,19 +84138,19 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>てくのっち</t>
+          <t>てぃふ</t>
         </is>
       </c>
       <c r="B298" t="n">
@@ -83290,19 +84158,19 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>てっちゃん</t>
+          <t>てくのちん</t>
         </is>
       </c>
       <c r="B299" t="n">
@@ -83310,19 +84178,19 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>てつ</t>
+          <t>てくのっち</t>
         </is>
       </c>
       <c r="B300" t="n">
@@ -83330,19 +84198,19 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>でかかわ</t>
+          <t>てっちゃん</t>
         </is>
       </c>
       <c r="B301" t="n">
@@ -83350,19 +84218,19 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>ででたゃ</t>
+          <t>てつ</t>
         </is>
       </c>
       <c r="B302" t="n">
@@ -83370,19 +84238,19 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>ででちゃん</t>
+          <t>でかかわ</t>
         </is>
       </c>
       <c r="B303" t="n">
@@ -83390,19 +84258,19 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>とおちゃん</t>
+          <t>ででたゃ</t>
         </is>
       </c>
       <c r="B304" t="n">
@@ -83410,19 +84278,19 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>とっしー</t>
+          <t>ででちゃん</t>
         </is>
       </c>
       <c r="B305" t="n">
@@ -83430,19 +84298,19 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>ともち</t>
+          <t>とおちゃん</t>
         </is>
       </c>
       <c r="B306" t="n">
@@ -83450,19 +84318,19 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>ともひろ</t>
+          <t>とっしー</t>
         </is>
       </c>
       <c r="B307" t="n">
@@ -83470,19 +84338,19 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>ともゆき</t>
+          <t>ともち</t>
         </is>
       </c>
       <c r="B308" t="n">
@@ -83490,19 +84358,19 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>とーり</t>
+          <t>ともひろ</t>
         </is>
       </c>
       <c r="B309" t="n">
@@ -83510,19 +84378,19 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>どえむちゃん</t>
+          <t>ともゆき</t>
         </is>
       </c>
       <c r="B310" t="n">
@@ -83530,19 +84398,19 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>ながとも</t>
+          <t>とーり</t>
         </is>
       </c>
       <c r="B311" t="n">
@@ -83550,19 +84418,19 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>なっちゃん</t>
+          <t>どえむちゃん</t>
         </is>
       </c>
       <c r="B312" t="n">
@@ -83570,19 +84438,19 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>なべ</t>
+          <t>ながとも</t>
         </is>
       </c>
       <c r="B313" t="n">
@@ -83590,19 +84458,19 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>にゃんまげ</t>
+          <t>なっちゃん</t>
         </is>
       </c>
       <c r="B314" t="n">
@@ -83610,19 +84478,19 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>にょ</t>
+          <t>なべ</t>
         </is>
       </c>
       <c r="B315" t="n">
@@ -83630,19 +84498,19 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>ねここ</t>
+          <t>にゃんまげ</t>
         </is>
       </c>
       <c r="B316" t="n">
@@ -83650,19 +84518,19 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>ねむ</t>
+          <t>にょ</t>
         </is>
       </c>
       <c r="B317" t="n">
@@ -83670,19 +84538,19 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>のぼ</t>
+          <t>ねここ</t>
         </is>
       </c>
       <c r="B318" t="n">
@@ -83690,19 +84558,19 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>はち</t>
+          <t>ねむ</t>
         </is>
       </c>
       <c r="B319" t="n">
@@ -83710,19 +84578,19 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>はな</t>
+          <t>のぼ</t>
         </is>
       </c>
       <c r="B320" t="n">
@@ -83730,19 +84598,19 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>はなちゃん</t>
+          <t>はち</t>
         </is>
       </c>
       <c r="B321" t="n">
@@ -83750,19 +84618,19 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>はにーちゃん</t>
+          <t>はな</t>
         </is>
       </c>
       <c r="B322" t="n">
@@ -83770,19 +84638,19 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>はる</t>
+          <t>はなちゃん</t>
         </is>
       </c>
       <c r="B323" t="n">
@@ -83790,19 +84658,19 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>はんまー</t>
+          <t>はにーちゃん</t>
         </is>
       </c>
       <c r="B324" t="n">
@@ -83810,19 +84678,19 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>ひがんたそ</t>
+          <t>はる</t>
         </is>
       </c>
       <c r="B325" t="n">
@@ -83830,19 +84698,19 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>ひったん</t>
+          <t>はんまー</t>
         </is>
       </c>
       <c r="B326" t="n">
@@ -83850,19 +84718,19 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>ひで</t>
+          <t>ひがんたそ</t>
         </is>
       </c>
       <c r="B327" t="n">
@@ -83870,19 +84738,19 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-08</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>ひろし</t>
+          <t>ひったん</t>
         </is>
       </c>
       <c r="B328" t="n">
@@ -83890,19 +84758,19 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>ひろとも</t>
+          <t>ひで</t>
         </is>
       </c>
       <c r="B329" t="n">
@@ -83910,19 +84778,19 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>ひろ＆ゆう</t>
+          <t>ひろし</t>
         </is>
       </c>
       <c r="B330" t="n">
@@ -83930,19 +84798,19 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>びん</t>
+          <t>ひろとも</t>
         </is>
       </c>
       <c r="B331" t="n">
@@ -83950,19 +84818,19 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>びーだっしゅ</t>
+          <t>ひろ＆ゆう</t>
         </is>
       </c>
       <c r="B332" t="n">
@@ -83970,19 +84838,19 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>ぴよ</t>
+          <t>びん</t>
         </is>
       </c>
       <c r="B333" t="n">
@@ -83990,19 +84858,19 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>ふじくん</t>
+          <t>びーだっしゅ</t>
         </is>
       </c>
       <c r="B334" t="n">
@@ -84010,19 +84878,19 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>ふみ</t>
+          <t>ぴよ</t>
         </is>
       </c>
       <c r="B335" t="n">
@@ -84030,19 +84898,19 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>ぷらぐいん</t>
+          <t>ふじくん</t>
         </is>
       </c>
       <c r="B336" t="n">
@@ -84050,19 +84918,19 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-10-09</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>ぺぺ</t>
+          <t>ふみ</t>
         </is>
       </c>
       <c r="B337" t="n">
@@ -84070,19 +84938,19 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>ぽち</t>
+          <t>ぷらぐいん</t>
         </is>
       </c>
       <c r="B338" t="n">
@@ -84090,19 +84958,19 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>ぽて</t>
+          <t>ぺぺ</t>
         </is>
       </c>
       <c r="B339" t="n">
@@ -84110,19 +84978,19 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>まいまいさん</t>
+          <t>ぽち</t>
         </is>
       </c>
       <c r="B340" t="n">
@@ -84130,19 +84998,19 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>まいんまいん</t>
+          <t>ぽて</t>
         </is>
       </c>
       <c r="B341" t="n">
@@ -84150,19 +85018,19 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>まおし</t>
+          <t>まいまいさん</t>
         </is>
       </c>
       <c r="B342" t="n">
@@ -84170,19 +85038,19 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>ます</t>
+          <t>まいんまいん</t>
         </is>
       </c>
       <c r="B343" t="n">
@@ -84190,19 +85058,19 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>ますみ</t>
+          <t>まおし</t>
         </is>
       </c>
       <c r="B344" t="n">
@@ -84210,19 +85078,19 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>まちゃん</t>
+          <t>ます</t>
         </is>
       </c>
       <c r="B345" t="n">
@@ -84230,19 +85098,19 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>まっする</t>
+          <t>ますみ</t>
         </is>
       </c>
       <c r="B346" t="n">
@@ -84250,19 +85118,19 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>まっぴー</t>
+          <t>まちゃん</t>
         </is>
       </c>
       <c r="B347" t="n">
@@ -84270,19 +85138,19 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>まな</t>
+          <t>まっする</t>
         </is>
       </c>
       <c r="B348" t="n">
@@ -84290,19 +85158,19 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>まみ</t>
+          <t>まっぴー</t>
         </is>
       </c>
       <c r="B349" t="n">
@@ -84310,19 +85178,19 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>まや</t>
+          <t>まな</t>
         </is>
       </c>
       <c r="B350" t="n">
@@ -84330,19 +85198,19 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>まり</t>
+          <t>まみ</t>
         </is>
       </c>
       <c r="B351" t="n">
@@ -84350,19 +85218,19 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>まりーな</t>
+          <t>まや</t>
         </is>
       </c>
       <c r="B352" t="n">
@@ -84370,19 +85238,19 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>まる</t>
+          <t>まり</t>
         </is>
       </c>
       <c r="B353" t="n">
@@ -84390,19 +85258,19 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>まー</t>
+          <t>まりーな</t>
         </is>
       </c>
       <c r="B354" t="n">
@@ -84410,19 +85278,19 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>まーちゃん</t>
+          <t>まる</t>
         </is>
       </c>
       <c r="B355" t="n">
@@ -84430,19 +85298,19 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>みい</t>
+          <t>まー</t>
         </is>
       </c>
       <c r="B356" t="n">
@@ -84450,19 +85318,19 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>みお</t>
+          <t>まーちゃん</t>
         </is>
       </c>
       <c r="B357" t="n">
@@ -84470,19 +85338,19 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>みかん</t>
+          <t>みい</t>
         </is>
       </c>
       <c r="B358" t="n">
@@ -84490,19 +85358,19 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>みけけ</t>
+          <t>みお</t>
         </is>
       </c>
       <c r="B359" t="n">
@@ -84510,19 +85378,19 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>みずき</t>
+          <t>みかん</t>
         </is>
       </c>
       <c r="B360" t="n">
@@ -84542,7 +85410,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>みちゃ</t>
+          <t>みきちゃん</t>
         </is>
       </c>
       <c r="B361" t="n">
@@ -84550,19 +85418,19 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>みなつちん</t>
+          <t>みけけ</t>
         </is>
       </c>
       <c r="B362" t="n">
@@ -84570,19 +85438,19 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>みみ</t>
+          <t>みずき</t>
         </is>
       </c>
       <c r="B363" t="n">
@@ -84590,19 +85458,19 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>みやび</t>
+          <t>みちゃ</t>
         </is>
       </c>
       <c r="B364" t="n">
@@ -84610,19 +85478,19 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>みゆき</t>
+          <t>みなつちん</t>
         </is>
       </c>
       <c r="B365" t="n">
@@ -84630,19 +85498,19 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>みらい</t>
+          <t>みみ</t>
         </is>
       </c>
       <c r="B366" t="n">
@@ -84650,19 +85518,19 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>みるこ</t>
+          <t>みやび</t>
         </is>
       </c>
       <c r="B367" t="n">
@@ -84670,19 +85538,19 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>みん</t>
+          <t>みゆき</t>
         </is>
       </c>
       <c r="B368" t="n">
@@ -84690,19 +85558,19 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>みんみん</t>
+          <t>みらい</t>
         </is>
       </c>
       <c r="B369" t="n">
@@ -84710,19 +85578,19 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>みーみ</t>
+          <t>みるこ</t>
         </is>
       </c>
       <c r="B370" t="n">
@@ -84730,19 +85598,19 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-19</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>むちゅ</t>
+          <t>みん</t>
         </is>
       </c>
       <c r="B371" t="n">
@@ -84750,19 +85618,19 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>もかちんぽぽ</t>
+          <t>みんみん</t>
         </is>
       </c>
       <c r="B372" t="n">
@@ -84770,19 +85638,19 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>もっきー</t>
+          <t>みーみ</t>
         </is>
       </c>
       <c r="B373" t="n">
@@ -84790,19 +85658,19 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>もっち</t>
+          <t>むちゅ</t>
         </is>
       </c>
       <c r="B374" t="n">
@@ -84810,19 +85678,19 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>もっぴっぴ</t>
+          <t>もかちんぽぽ</t>
         </is>
       </c>
       <c r="B375" t="n">
@@ -84830,19 +85698,19 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>もっぴー</t>
+          <t>もっきー</t>
         </is>
       </c>
       <c r="B376" t="n">
@@ -84850,19 +85718,19 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-10-02</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>もと</t>
+          <t>もっち</t>
         </is>
       </c>
       <c r="B377" t="n">
@@ -84870,19 +85738,19 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>ももたろ</t>
+          <t>もっぴっぴ</t>
         </is>
       </c>
       <c r="B378" t="n">
@@ -84890,19 +85758,19 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>やえくん</t>
+          <t>もっぴー</t>
         </is>
       </c>
       <c r="B379" t="n">
@@ -84910,19 +85778,19 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>やす</t>
+          <t>もと</t>
         </is>
       </c>
       <c r="B380" t="n">
@@ -84930,19 +85798,19 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>ゆい</t>
+          <t>ももたろ</t>
         </is>
       </c>
       <c r="B381" t="n">
@@ -84950,19 +85818,19 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>ゆうじ</t>
+          <t>やえくん</t>
         </is>
       </c>
       <c r="B382" t="n">
@@ -84970,19 +85838,19 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>ゆうた</t>
+          <t>やす</t>
         </is>
       </c>
       <c r="B383" t="n">
@@ -84990,19 +85858,19 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>ゆうたん</t>
+          <t>ゆい</t>
         </is>
       </c>
       <c r="B384" t="n">
@@ -85010,19 +85878,19 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>ゆうと</t>
+          <t>ゆうじ</t>
         </is>
       </c>
       <c r="B385" t="n">
@@ -85030,19 +85898,19 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>ゆうや</t>
+          <t>ゆうた</t>
         </is>
       </c>
       <c r="B386" t="n">
@@ -85050,19 +85918,19 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>ゆかり</t>
+          <t>ゆうたん</t>
         </is>
       </c>
       <c r="B387" t="n">
@@ -85070,19 +85938,19 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>ゆきお</t>
+          <t>ゆうと</t>
         </is>
       </c>
       <c r="B388" t="n">
@@ -85090,19 +85958,19 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>ゆきんこ</t>
+          <t>ゆうや</t>
         </is>
       </c>
       <c r="B389" t="n">
@@ -85110,19 +85978,19 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>ゆず</t>
+          <t>ゆかり</t>
         </is>
       </c>
       <c r="B390" t="n">
@@ -85130,19 +85998,19 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>ゆずきちゃん</t>
+          <t>ゆきお</t>
         </is>
       </c>
       <c r="B391" t="n">
@@ -85162,7 +86030,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>ゆずきぴ</t>
+          <t>ゆきんこ</t>
         </is>
       </c>
       <c r="B392" t="n">
@@ -85170,19 +86038,19 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-08-17</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>ゆずき＆ましゅ</t>
+          <t>ゆず</t>
         </is>
       </c>
       <c r="B393" t="n">
@@ -85190,19 +86058,19 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>ゆっち</t>
+          <t>ゆずきちゃん</t>
         </is>
       </c>
       <c r="B394" t="n">
@@ -85210,19 +86078,19 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>ゆぴ</t>
+          <t>ゆずきぴ</t>
         </is>
       </c>
       <c r="B395" t="n">
@@ -85230,19 +86098,19 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>ゆり</t>
+          <t>ゆずき＆ましゅ</t>
         </is>
       </c>
       <c r="B396" t="n">
@@ -85250,19 +86118,19 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>ゆりな</t>
+          <t>ゆっち</t>
         </is>
       </c>
       <c r="B397" t="n">
@@ -85270,19 +86138,19 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>ゆん</t>
+          <t>ゆぴ</t>
         </is>
       </c>
       <c r="B398" t="n">
@@ -85290,19 +86158,19 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>ゆんちゃん</t>
+          <t>ゆり</t>
         </is>
       </c>
       <c r="B399" t="n">
@@ -85310,19 +86178,19 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>ゆんゆん</t>
+          <t>ゆりな</t>
         </is>
       </c>
       <c r="B400" t="n">
@@ -85330,19 +86198,19 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>よこい</t>
+          <t>ゆん</t>
         </is>
       </c>
       <c r="B401" t="n">
@@ -85350,19 +86218,19 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>よし</t>
+          <t>ゆんちゃん</t>
         </is>
       </c>
       <c r="B402" t="n">
@@ -85370,19 +86238,19 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>らいと</t>
+          <t>ゆんゆん</t>
         </is>
       </c>
       <c r="B403" t="n">
@@ -85390,19 +86258,19 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>らうら</t>
+          <t>よこい</t>
         </is>
       </c>
       <c r="B404" t="n">
@@ -85410,19 +86278,19 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>らん</t>
+          <t>よし</t>
         </is>
       </c>
       <c r="B405" t="n">
@@ -85430,19 +86298,19 @@
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>りえ</t>
+          <t>らいと</t>
         </is>
       </c>
       <c r="B406" t="n">
@@ -85450,19 +86318,19 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>りく</t>
+          <t>らうら</t>
         </is>
       </c>
       <c r="B407" t="n">
@@ -85470,19 +86338,19 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>りさ</t>
+          <t>らん</t>
         </is>
       </c>
       <c r="B408" t="n">
@@ -85490,19 +86358,19 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>りゅうくん</t>
+          <t>りえ</t>
         </is>
       </c>
       <c r="B409" t="n">
@@ -85510,19 +86378,19 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>りゅーちゃん</t>
+          <t>りく</t>
         </is>
       </c>
       <c r="B410" t="n">
@@ -85530,19 +86398,19 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>りょうが</t>
+          <t>りさ</t>
         </is>
       </c>
       <c r="B411" t="n">
@@ -85550,19 +86418,19 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>りょうちゃん</t>
+          <t>りゅうくん</t>
         </is>
       </c>
       <c r="B412" t="n">
@@ -85570,19 +86438,19 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>りょーが</t>
+          <t>りゅーちゃん</t>
         </is>
       </c>
       <c r="B413" t="n">
@@ -85590,19 +86458,19 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>りりこ</t>
+          <t>りょうが</t>
         </is>
       </c>
       <c r="B414" t="n">
@@ -85610,19 +86478,19 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>りん＆ゆち</t>
+          <t>りょうちゃん</t>
         </is>
       </c>
       <c r="B415" t="n">
@@ -85630,19 +86498,19 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>れい</t>
+          <t>りょーが</t>
         </is>
       </c>
       <c r="B416" t="n">
@@ -85650,19 +86518,19 @@
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>れー</t>
+          <t>りりこ</t>
         </is>
       </c>
       <c r="B417" t="n">
@@ -85670,19 +86538,19 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>わいちゃん</t>
+          <t>りん＆まゆちゃん</t>
         </is>
       </c>
       <c r="B418" t="n">
@@ -85690,19 +86558,19 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-14</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>わんころ</t>
+          <t>りん＆ゆち</t>
         </is>
       </c>
       <c r="B419" t="n">
@@ -85710,19 +86578,19 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>アイ</t>
+          <t>れい</t>
         </is>
       </c>
       <c r="B420" t="n">
@@ -85730,19 +86598,19 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>アイちゃん</t>
+          <t>れー</t>
         </is>
       </c>
       <c r="B421" t="n">
@@ -85750,19 +86618,19 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>アナルプリンス</t>
+          <t>わいちゃん</t>
         </is>
       </c>
       <c r="B422" t="n">
@@ -85770,19 +86638,19 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>イエモン</t>
+          <t>わんころ</t>
         </is>
       </c>
       <c r="B423" t="n">
@@ -85790,19 +86658,19 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>イブオ</t>
+          <t>アイ</t>
         </is>
       </c>
       <c r="B424" t="n">
@@ -85810,19 +86678,19 @@
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>イヴ男</t>
+          <t>アイちゃん</t>
         </is>
       </c>
       <c r="B425" t="n">
@@ -85830,19 +86698,19 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>エーイチ</t>
+          <t>アナルプリンス</t>
         </is>
       </c>
       <c r="B426" t="n">
@@ -85850,19 +86718,19 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>オリーブ</t>
+          <t>イエモン</t>
         </is>
       </c>
       <c r="B427" t="n">
@@ -85870,19 +86738,19 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-03</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>オ・スー</t>
+          <t>イブオ</t>
         </is>
       </c>
       <c r="B428" t="n">
@@ -85890,19 +86758,19 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>カイト</t>
+          <t>イヴ男</t>
         </is>
       </c>
       <c r="B429" t="n">
@@ -85910,19 +86778,19 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>カイトウ・キッド</t>
+          <t>エーイチ</t>
         </is>
       </c>
       <c r="B430" t="n">
@@ -85930,19 +86798,19 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>カシワ</t>
+          <t>オリーブ</t>
         </is>
       </c>
       <c r="B431" t="n">
@@ -85950,19 +86818,19 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>カナ</t>
+          <t>オ・スー</t>
         </is>
       </c>
       <c r="B432" t="n">
@@ -85970,19 +86838,19 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-08-13</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>カネキヨ</t>
+          <t>カイト</t>
         </is>
       </c>
       <c r="B433" t="n">
@@ -85990,19 +86858,19 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>カミさん</t>
+          <t>カイトウ・キッド</t>
         </is>
       </c>
       <c r="B434" t="n">
@@ -86010,19 +86878,19 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>カモリ</t>
+          <t>カシワ</t>
         </is>
       </c>
       <c r="B435" t="n">
@@ -86030,19 +86898,19 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>カルマ</t>
+          <t>カナ</t>
         </is>
       </c>
       <c r="B436" t="n">
@@ -86050,19 +86918,19 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-02</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>キムさん</t>
+          <t>カネキヨ</t>
         </is>
       </c>
       <c r="B437" t="n">
@@ -86070,19 +86938,19 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>キムとどえむちゃん</t>
+          <t>カミさん</t>
         </is>
       </c>
       <c r="B438" t="n">
@@ -86090,19 +86958,19 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>キムとドMまいまい妹</t>
+          <t>カモリ</t>
         </is>
       </c>
       <c r="B439" t="n">
@@ -86110,19 +86978,19 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>キムとドMむい</t>
+          <t>カルマ</t>
         </is>
       </c>
       <c r="B440" t="n">
@@ -86130,19 +86998,19 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>キムとドM女R</t>
+          <t>キムさん</t>
         </is>
       </c>
       <c r="B441" t="n">
@@ -86150,19 +87018,19 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>キムとドM女の子</t>
+          <t>キムとどえむちゃん</t>
         </is>
       </c>
       <c r="B442" t="n">
@@ -86170,19 +87038,19 @@
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>キムとローズ</t>
+          <t>キムとドMまいまい妹</t>
         </is>
       </c>
       <c r="B443" t="n">
@@ -86190,19 +87058,19 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>キムと奴隷</t>
+          <t>キムとドMむい</t>
         </is>
       </c>
       <c r="B444" t="n">
@@ -86210,19 +87078,19 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>キムと新しい奴隷ちゃん</t>
+          <t>キムとドM女R</t>
         </is>
       </c>
       <c r="B445" t="n">
@@ -86230,19 +87098,19 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>キムラ</t>
+          <t>キムとドM女の子</t>
         </is>
       </c>
       <c r="B446" t="n">
@@ -86250,19 +87118,19 @@
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>キム＆みい</t>
+          <t>キムとローズ</t>
         </is>
       </c>
       <c r="B447" t="n">
@@ -86270,19 +87138,19 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>キム＆みー</t>
+          <t>キムと奴隷</t>
         </is>
       </c>
       <c r="B448" t="n">
@@ -86290,19 +87158,19 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>キム＆むい</t>
+          <t>キムと新しい奴隷ちゃん</t>
         </is>
       </c>
       <c r="B449" t="n">
@@ -86310,19 +87178,19 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>クアレ</t>
+          <t>キムラ</t>
         </is>
       </c>
       <c r="B450" t="n">
@@ -86330,19 +87198,19 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-24</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>クロちゃん</t>
+          <t>キム＆みい</t>
         </is>
       </c>
       <c r="B451" t="n">
@@ -86350,19 +87218,19 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>ケケ</t>
+          <t>キム＆みー</t>
         </is>
       </c>
       <c r="B452" t="n">
@@ -86370,19 +87238,19 @@
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>ゲス</t>
+          <t>キム＆むい</t>
         </is>
       </c>
       <c r="B453" t="n">
@@ -86390,19 +87258,19 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>ゲン</t>
+          <t>クアレ</t>
         </is>
       </c>
       <c r="B454" t="n">
@@ -86410,19 +87278,19 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-21</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>コオリ</t>
+          <t>クロちゃん</t>
         </is>
       </c>
       <c r="B455" t="n">
@@ -86430,19 +87298,19 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>コマ</t>
+          <t>ケケ</t>
         </is>
       </c>
       <c r="B456" t="n">
@@ -86450,19 +87318,19 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>サカモト</t>
+          <t>ゲス</t>
         </is>
       </c>
       <c r="B457" t="n">
@@ -86470,19 +87338,19 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>サクヤ</t>
+          <t>ゲン</t>
         </is>
       </c>
       <c r="B458" t="n">
@@ -86490,19 +87358,19 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D458" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>サト</t>
+          <t>コオリ</t>
         </is>
       </c>
       <c r="B459" t="n">
@@ -86510,19 +87378,19 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>サトル</t>
+          <t>コマ</t>
         </is>
       </c>
       <c r="B460" t="n">
@@ -86530,19 +87398,19 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>ザッキー</t>
+          <t>サカモト</t>
         </is>
       </c>
       <c r="B461" t="n">
@@ -86550,19 +87418,19 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>シェフ　サトル</t>
+          <t>サクヤ</t>
         </is>
       </c>
       <c r="B462" t="n">
@@ -86570,19 +87438,19 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>シゲ</t>
+          <t>サト</t>
         </is>
       </c>
       <c r="B463" t="n">
@@ -86590,19 +87458,19 @@
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>シマ</t>
+          <t>サトル</t>
         </is>
       </c>
       <c r="B464" t="n">
@@ -86610,19 +87478,19 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>シュウ</t>
+          <t>ザッキー</t>
         </is>
       </c>
       <c r="B465" t="n">
@@ -86630,19 +87498,19 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>シュン</t>
+          <t>シェフ　サトル</t>
         </is>
       </c>
       <c r="B466" t="n">
@@ -86650,19 +87518,19 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>シュンヤ</t>
+          <t>シゲ</t>
         </is>
       </c>
       <c r="B467" t="n">
@@ -86670,19 +87538,19 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>シン</t>
+          <t>シマ</t>
         </is>
       </c>
       <c r="B468" t="n">
@@ -86690,19 +87558,19 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-02</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>シン変質者</t>
+          <t>シュウ</t>
         </is>
       </c>
       <c r="B469" t="n">
@@ -86710,19 +87578,19 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>ジャッキー</t>
+          <t>シュン</t>
         </is>
       </c>
       <c r="B470" t="n">
@@ -86730,19 +87598,19 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>ジョーカー</t>
+          <t>シュンヤ</t>
         </is>
       </c>
       <c r="B471" t="n">
@@ -86750,19 +87618,19 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>スズ</t>
+          <t>シン</t>
         </is>
       </c>
       <c r="B472" t="n">
@@ -86770,19 +87638,19 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>ソルト</t>
+          <t>シン変質者</t>
         </is>
       </c>
       <c r="B473" t="n">
@@ -86790,19 +87658,19 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>タイガ</t>
+          <t>ジャッキー</t>
         </is>
       </c>
       <c r="B474" t="n">
@@ -86810,19 +87678,19 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-08-29</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>タカス</t>
+          <t>ジョーカー</t>
         </is>
       </c>
       <c r="B475" t="n">
@@ -86830,19 +87698,19 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>タカ御一行</t>
+          <t>スズ</t>
         </is>
       </c>
       <c r="B476" t="n">
@@ -86850,19 +87718,19 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>ダイキ</t>
+          <t>ソルト</t>
         </is>
       </c>
       <c r="B477" t="n">
@@ -86870,19 +87738,19 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>ダイチ</t>
+          <t>タイガ</t>
         </is>
       </c>
       <c r="B478" t="n">
@@ -86890,19 +87758,19 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>チェスカ</t>
+          <t>タカス</t>
         </is>
       </c>
       <c r="B479" t="n">
@@ -86910,19 +87778,19 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>ツシマ</t>
+          <t>タカ御一行</t>
         </is>
       </c>
       <c r="B480" t="n">
@@ -86930,19 +87798,19 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>ツボ</t>
+          <t>ダイキ</t>
         </is>
       </c>
       <c r="B481" t="n">
@@ -86950,19 +87818,19 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>テクノとポチ</t>
+          <t>ダイチ</t>
         </is>
       </c>
       <c r="B482" t="n">
@@ -86970,19 +87838,19 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>テクノ＆おおつか＆みこと＆もも</t>
+          <t>チェスカ</t>
         </is>
       </c>
       <c r="B483" t="n">
@@ -86990,19 +87858,19 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>テクノ＆てるくん＆イブオ</t>
+          <t>ツシマ</t>
         </is>
       </c>
       <c r="B484" t="n">
@@ -87010,19 +87878,19 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-10</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>トニー・トニー・チョッパー</t>
+          <t>ツボ</t>
         </is>
       </c>
       <c r="B485" t="n">
@@ -87030,19 +87898,19 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-31</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>トム</t>
+          <t>テクノとポチ</t>
         </is>
       </c>
       <c r="B486" t="n">
@@ -87050,19 +87918,19 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>トモ</t>
+          <t>テクノ＆おおつか＆みこと＆もも</t>
         </is>
       </c>
       <c r="B487" t="n">
@@ -87070,19 +87938,19 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>トルネードシャーク</t>
+          <t>テクノ＆てるくん＆イブオ</t>
         </is>
       </c>
       <c r="B488" t="n">
@@ -87090,19 +87958,19 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>ナカ</t>
+          <t>トニー・トニー・チョッパー</t>
         </is>
       </c>
       <c r="B489" t="n">
@@ -87110,19 +87978,19 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>ナカヤマヤ</t>
+          <t>トム</t>
         </is>
       </c>
       <c r="B490" t="n">
@@ -87130,19 +87998,19 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-28</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>ニコチン</t>
+          <t>トモ</t>
         </is>
       </c>
       <c r="B491" t="n">
@@ -87150,19 +88018,19 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>ニト</t>
+          <t>トルネードシャーク</t>
         </is>
       </c>
       <c r="B492" t="n">
@@ -87170,19 +88038,19 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>ニーヤン</t>
+          <t>ナカ</t>
         </is>
       </c>
       <c r="B493" t="n">
@@ -87202,7 +88070,7 @@
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>ハチ</t>
+          <t>ナカヤマヤ</t>
         </is>
       </c>
       <c r="B494" t="n">
@@ -87210,19 +88078,19 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>ヒロシ</t>
+          <t>ニコチン</t>
         </is>
       </c>
       <c r="B495" t="n">
@@ -87230,19 +88098,19 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>ビコー</t>
+          <t>ニト</t>
         </is>
       </c>
       <c r="B496" t="n">
@@ -87250,19 +88118,19 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>フジ</t>
+          <t>ニーヤン</t>
         </is>
       </c>
       <c r="B497" t="n">
@@ -87270,19 +88138,19 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>フランク</t>
+          <t>ノリ</t>
         </is>
       </c>
       <c r="B498" t="n">
@@ -87290,19 +88158,19 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-13</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>フーミン</t>
+          <t>ハチ</t>
         </is>
       </c>
       <c r="B499" t="n">
@@ -87310,19 +88178,19 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>ペロとペコ</t>
+          <t>ヒロシ</t>
         </is>
       </c>
       <c r="B500" t="n">
@@ -87330,19 +88198,19 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-25</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>ボス</t>
+          <t>ビコー</t>
         </is>
       </c>
       <c r="B501" t="n">
@@ -87350,19 +88218,19 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>ボンタ</t>
+          <t>フジ</t>
         </is>
       </c>
       <c r="B502" t="n">
@@ -87370,19 +88238,19 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>ポチ</t>
+          <t>フランク</t>
         </is>
       </c>
       <c r="B503" t="n">
@@ -87390,19 +88258,19 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-10-09</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>ポポ</t>
+          <t>フーミン</t>
         </is>
       </c>
       <c r="B504" t="n">
@@ -87410,19 +88278,19 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-10</t>
         </is>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>マッチョ</t>
+          <t>ペロとペコ</t>
         </is>
       </c>
       <c r="B505" t="n">
@@ -87430,19 +88298,19 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-19</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>マヒロ</t>
+          <t>ボス</t>
         </is>
       </c>
       <c r="B506" t="n">
@@ -87450,19 +88318,19 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-09-22</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>ミカミと仲間たち</t>
+          <t>ボンタ</t>
         </is>
       </c>
       <c r="B507" t="n">
@@ -87470,19 +88338,19 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>ミスター工事マン</t>
+          <t>ポチ</t>
         </is>
       </c>
       <c r="B508" t="n">
@@ -87490,19 +88358,19 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>ミッシ</t>
+          <t>ポポ</t>
         </is>
       </c>
       <c r="B509" t="n">
@@ -87510,19 +88378,19 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>ミッチー</t>
+          <t>マッチョ</t>
         </is>
       </c>
       <c r="B510" t="n">
@@ -87530,19 +88398,19 @@
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>ミルコ</t>
+          <t>マヒロ</t>
         </is>
       </c>
       <c r="B511" t="n">
@@ -87550,19 +88418,19 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-10-09</t>
         </is>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>ミン</t>
+          <t>ミカミと仲間たち</t>
         </is>
       </c>
       <c r="B512" t="n">
@@ -87570,19 +88438,19 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-15</t>
         </is>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>メガネ</t>
+          <t>ミスター工事マン</t>
         </is>
       </c>
       <c r="B513" t="n">
@@ -87590,19 +88458,19 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>メンズ5人組</t>
+          <t>ミッシ</t>
         </is>
       </c>
       <c r="B514" t="n">
@@ -87610,19 +88478,19 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>モジャ</t>
+          <t>ミッチー</t>
         </is>
       </c>
       <c r="B515" t="n">
@@ -87630,19 +88498,19 @@
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>ヤス</t>
+          <t>ミルコ</t>
         </is>
       </c>
       <c r="B516" t="n">
@@ -87650,19 +88518,19 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-09-11</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>ヤノ</t>
+          <t>ミン</t>
         </is>
       </c>
       <c r="B517" t="n">
@@ -87670,19 +88538,19 @@
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>ヤノちゃん</t>
+          <t>メガネ</t>
         </is>
       </c>
       <c r="B518" t="n">
@@ -87690,19 +88558,19 @@
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>ヤマ</t>
+          <t>メンズ5人組</t>
         </is>
       </c>
       <c r="B519" t="n">
@@ -87710,19 +88578,19 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>ユウ</t>
+          <t>モジャ</t>
         </is>
       </c>
       <c r="B520" t="n">
@@ -87730,19 +88598,19 @@
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-26</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>ユキ</t>
+          <t>ヤス</t>
         </is>
       </c>
       <c r="B521" t="n">
@@ -87750,19 +88618,19 @@
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>ユッキー</t>
+          <t>ヤノ</t>
         </is>
       </c>
       <c r="B522" t="n">
@@ -87770,19 +88638,19 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-10-03</t>
         </is>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>ヨシヤ</t>
+          <t>ヤノちゃん</t>
         </is>
       </c>
       <c r="B523" t="n">
@@ -87790,19 +88658,19 @@
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-04</t>
         </is>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>ヨッシー</t>
+          <t>ヤマ</t>
         </is>
       </c>
       <c r="B524" t="n">
@@ -87810,19 +88678,19 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>ラオ</t>
+          <t>ユウ</t>
         </is>
       </c>
       <c r="B525" t="n">
@@ -87830,19 +88698,19 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>ラ王</t>
+          <t>ユキ</t>
         </is>
       </c>
       <c r="B526" t="n">
@@ -87850,19 +88718,19 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-08-28</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>リク</t>
+          <t>ユッキー</t>
         </is>
       </c>
       <c r="B527" t="n">
@@ -87870,19 +88738,19 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>リョウ</t>
+          <t>ヨシヤ</t>
         </is>
       </c>
       <c r="B528" t="n">
@@ -87902,7 +88770,7 @@
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>ロタポジ</t>
+          <t>ヨッシー</t>
         </is>
       </c>
       <c r="B529" t="n">
@@ -87910,19 +88778,19 @@
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-10-09</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>ローズ</t>
+          <t>ラオ</t>
         </is>
       </c>
       <c r="B530" t="n">
@@ -87930,19 +88798,19 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-16</t>
         </is>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>偽マイマイ</t>
+          <t>ラ王</t>
         </is>
       </c>
       <c r="B531" t="n">
@@ -87950,19 +88818,19 @@
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>僕と私</t>
+          <t>リク</t>
         </is>
       </c>
       <c r="B532" t="n">
@@ -87970,19 +88838,19 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-02</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>光一</t>
+          <t>リョウ</t>
         </is>
       </c>
       <c r="B533" t="n">
@@ -87990,19 +88858,19 @@
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-08-25</t>
         </is>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>前マン</t>
+          <t>ロタポジ</t>
         </is>
       </c>
       <c r="B534" t="n">
@@ -88010,19 +88878,19 @@
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-08-20</t>
         </is>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>名無し</t>
+          <t>ローズ</t>
         </is>
       </c>
       <c r="B535" t="n">
@@ -88030,19 +88898,19 @@
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="D535" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>変態まっする</t>
+          <t>偽マイマイ</t>
         </is>
       </c>
       <c r="B536" t="n">
@@ -88050,19 +88918,19 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="D536" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-18</t>
         </is>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>変態マッソー</t>
+          <t>僕と私</t>
         </is>
       </c>
       <c r="B537" t="n">
@@ -88070,19 +88938,19 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>天我迅</t>
+          <t>光一</t>
         </is>
       </c>
       <c r="B538" t="n">
@@ -88090,19 +88958,19 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-29</t>
         </is>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>女子ズ</t>
+          <t>前マン</t>
         </is>
       </c>
       <c r="B539" t="n">
@@ -88110,19 +88978,19 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>女子三人衆</t>
+          <t>名無し</t>
         </is>
       </c>
       <c r="B540" t="n">
@@ -88130,19 +88998,19 @@
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-23</t>
         </is>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>彩 なまがき</t>
+          <t>変態まっする</t>
         </is>
       </c>
       <c r="B541" t="n">
@@ -88150,19 +89018,19 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>正装しん</t>
+          <t>変態マッソー</t>
         </is>
       </c>
       <c r="B542" t="n">
@@ -88170,19 +89038,19 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-23</t>
         </is>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>海砂利水魚</t>
+          <t>天我迅</t>
         </is>
       </c>
       <c r="B543" t="n">
@@ -88190,19 +89058,19 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="D543" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>漢</t>
+          <t>女子ズ</t>
         </is>
       </c>
       <c r="B544" t="n">
@@ -88222,7 +89090,7 @@
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>田中</t>
+          <t>女子三人衆</t>
         </is>
       </c>
       <c r="B545" t="n">
@@ -88230,19 +89098,19 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>碧咲</t>
+          <t>彩 なまがき</t>
         </is>
       </c>
       <c r="B546" t="n">
@@ -88250,19 +89118,19 @@
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-17</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>福ちゃん</t>
+          <t>正装しん</t>
         </is>
       </c>
       <c r="B547" t="n">
@@ -88270,19 +89138,19 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D547" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>米米</t>
+          <t>海砂利水魚</t>
         </is>
       </c>
       <c r="B548" t="n">
@@ -88290,19 +89158,19 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="D548" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-08-22</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>絶</t>
+          <t>漢</t>
         </is>
       </c>
       <c r="B549" t="n">
@@ -88310,19 +89178,19 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="D549" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-10-12</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>絶ちゃん</t>
+          <t>田中</t>
         </is>
       </c>
       <c r="B550" t="n">
@@ -88330,19 +89198,19 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-05</t>
         </is>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>美優</t>
+          <t>碧咲</t>
         </is>
       </c>
       <c r="B551" t="n">
@@ -88350,19 +89218,19 @@
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-26</t>
         </is>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>赤ちゃん</t>
+          <t>福ちゃん</t>
         </is>
       </c>
       <c r="B552" t="n">
@@ -88370,19 +89238,19 @@
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>赤井ヱビス</t>
+          <t>米米</t>
         </is>
       </c>
       <c r="B553" t="n">
@@ -88390,19 +89258,19 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-10-07</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>部長</t>
+          <t>絶</t>
         </is>
       </c>
       <c r="B554" t="n">
@@ -88410,19 +89278,19 @@
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="D554" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>雅-miyabi-</t>
+          <t>絶ちゃん</t>
         </is>
       </c>
       <c r="B555" t="n">
@@ -88430,19 +89298,19 @@
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="D555" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>雅-miyabi-/とも</t>
+          <t>美優</t>
         </is>
       </c>
       <c r="B556" t="n">
@@ -88450,30 +89318,150 @@
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
+          <t>謎の男＆マリア嬢</t>
+        </is>
+      </c>
+      <c r="B557" t="n">
+        <v>1</v>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>赤ちゃん</t>
+        </is>
+      </c>
+      <c r="B558" t="n">
+        <v>1</v>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>赤井ヱビス</t>
+        </is>
+      </c>
+      <c r="B559" t="n">
+        <v>1</v>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>部長</t>
+        </is>
+      </c>
+      <c r="B560" t="n">
+        <v>1</v>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>雅-miyabi-</t>
+        </is>
+      </c>
+      <c r="B561" t="n">
+        <v>1</v>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>雅-miyabi-/とも</t>
+        </is>
+      </c>
+      <c r="B562" t="n">
+        <v>1</v>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
           <t>高山＆ふくちゃん</t>
         </is>
       </c>
-      <c r="B557" t="n">
-        <v>1</v>
-      </c>
-      <c r="C557" t="inlineStr">
+      <c r="B563" t="n">
+        <v>1</v>
+      </c>
+      <c r="C563" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="D557" t="inlineStr">
+      <c r="D563" t="inlineStr">
         <is>
           <t>2026-10-11</t>
         </is>
@@ -88530,10 +89518,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C3" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4">
@@ -88543,10 +89531,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="C4" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5">
@@ -88652,10 +89640,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C3" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4">
@@ -88678,10 +89666,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C5" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6">
@@ -88873,10 +89861,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C20" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21">
@@ -88886,10 +89874,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C21" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="22">
@@ -88912,10 +89900,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C23" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="24">
@@ -88925,10 +89913,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C24" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
     </row>
     <row r="25">
@@ -89019,13 +90007,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="C4" t="n">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="D4" t="n">
-        <v>150</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
